--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -218,10 +218,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -243,10 +243,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -268,10 +268,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -293,10 +293,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK73"/>
+  <dimension ref="A1:AK75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59" customWidth="1" min="1" max="1"/>
@@ -642,519 +642,311 @@
     <col width="7" customWidth="1" min="31" max="31"/>
     <col width="7" customWidth="1" min="32" max="32"/>
     <col width="7" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="42" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
+          <t>INFORME DE CONTROL TÉCNICO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>COORDINACIÓN ZONAL 6</t>
+          <t>No. IT-CZ06-R-2025-00XX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:MACHALA</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:MACHALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FRECUENCIA (MHz)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Frecuencia (MHz)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W10" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X10" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y10" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AA10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD8" s="3" t="n">
+      <c r="AD10" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE8" s="3" t="n">
+      <c r="AE10" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF8" s="3" t="n">
+      <c r="AF10" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG8" s="3" t="n">
+      <c r="AG10" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH10" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI8" s="3" t="inlineStr">
+      <c r="AI10" s="3" t="inlineStr">
         <is>
           <t>Ancho de Banda
 (KHz)</t>
         </is>
       </c>
-      <c r="AJ8" s="3" t="inlineStr">
+      <c r="AJ10" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="inlineStr">
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>PUBLICA FM</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>70.95999999999999</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>68.28</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>70.42</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>70.89</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>71.45999999999999</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>71.63</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>71.54000000000001</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>71.56999999999999</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>70.81999999999999</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>71.04000000000001</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>71.26000000000001</v>
-      </c>
-      <c r="U9" s="6" t="n">
-        <v>71.11</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>70.81</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>70.95999999999999</v>
-      </c>
-      <c r="X9" s="6" t="n">
-        <v>70.86</v>
-      </c>
-      <c r="Y9" s="6" t="n">
-        <v>71.14</v>
-      </c>
-      <c r="Z9" s="6" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="AA9" s="6" t="n">
-        <v>70.34</v>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>70.58</v>
-      </c>
-      <c r="AC9" s="6" t="n">
-        <v>70.89</v>
-      </c>
-      <c r="AD9" s="6" t="n">
-        <v>71.29000000000001</v>
-      </c>
-      <c r="AE9" s="6" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="AF9" s="6" t="n">
-        <v>71.51000000000001</v>
-      </c>
-      <c r="AG9" s="6" t="n">
-        <v>71.29000000000001</v>
-      </c>
-      <c r="AH9" s="6" t="n">
-        <v>70.81</v>
-      </c>
-      <c r="AI9" s="6" t="n">
-        <v>244.66</v>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>DIBLU</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>72.78</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>71.98999999999999</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>70.95999999999999</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>71.59</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>69.92</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>71.62</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>72.81</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>73.45999999999999</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>72.44</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>72.89</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>73.23</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>72.41</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>72.81999999999999</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>72.63</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>72.69</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>73.06999999999999</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>72.76000000000001</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>72.73999999999999</v>
-      </c>
-      <c r="Y10" s="6" t="n">
-        <v>73.26000000000001</v>
-      </c>
-      <c r="Z10" s="6" t="n">
-        <v>72.26000000000001</v>
-      </c>
-      <c r="AA10" s="6" t="n">
-        <v>72.54000000000001</v>
-      </c>
-      <c r="AB10" s="6" t="n">
-        <v>72.48</v>
-      </c>
-      <c r="AC10" s="6" t="n">
-        <v>73.01000000000001</v>
-      </c>
-      <c r="AD10" s="6" t="n">
-        <v>73.56</v>
-      </c>
-      <c r="AE10" s="6" t="n">
-        <v>73.04000000000001</v>
-      </c>
-      <c r="AF10" s="6" t="n">
-        <v>73.42</v>
-      </c>
-      <c r="AG10" s="6" t="n">
-        <v>72.84</v>
-      </c>
-      <c r="AH10" s="6" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="AI10" s="6" t="n">
-        <v>160.6</v>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>OVACION INTERNACIONAL FM</t>
+          <t>PUBLICA FM</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>89.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>72.09999999999999</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>72.61</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>71.40000000000001</v>
+        <v>68.28</v>
       </c>
       <c r="F11" s="6" t="n">
+        <v>70.26000000000001</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>70.54000000000001</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>70.89</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>71.45999999999999</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>71.54000000000001</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>71.11</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>70.81</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="X11" s="6" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="Z11" s="6" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="AA11" s="6" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="AB11" s="6" t="n">
+        <v>70.58</v>
+      </c>
+      <c r="AC11" s="6" t="n">
+        <v>70.89</v>
+      </c>
+      <c r="AD11" s="6" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="AE11" s="6" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AF11" s="6" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>72.34</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>72.92</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>71.98999999999999</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>71.81</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>71.54000000000001</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>71.76000000000001</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>73.19</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>72.20999999999999</v>
-      </c>
-      <c r="O11" s="6" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>73.03</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>72.39</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>71.26000000000001</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>72.38</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>71.44</v>
-      </c>
-      <c r="V11" s="6" t="n">
-        <v>71.73999999999999</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>72.17</v>
-      </c>
-      <c r="Y11" s="6" t="n">
-        <v>71.87</v>
-      </c>
-      <c r="Z11" s="6" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="AA11" s="6" t="n">
-        <v>71.51000000000001</v>
-      </c>
-      <c r="AB11" s="6" t="n">
-        <v>70.76000000000001</v>
-      </c>
-      <c r="AC11" s="6" t="n">
-        <v>71.78</v>
-      </c>
-      <c r="AD11" s="6" t="n">
-        <v>71.84</v>
-      </c>
-      <c r="AE11" s="6" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="AF11" s="6" t="n">
-        <v>71.34</v>
-      </c>
       <c r="AG11" s="6" t="n">
-        <v>70.06999999999999</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="AH11" s="6" t="n">
-        <v>71.45999999999999</v>
+        <v>70.81</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>200.59</v>
+        <v>244.66</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
       <c r="AK11" s="7" t="inlineStr"/>
@@ -1162,110 +954,110 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RADIO SAMANTHA STEREO</t>
+          <t>DIBLU</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>89.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>67.19</v>
+        <v>72.78</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>66.91</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>60.02</v>
+        <v>65.56</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>67.92</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>67.73</v>
+        <v>71.59</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>67.16</v>
+        <v>69.8</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>67.26000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>66.51000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>67.64</v>
+        <v>72.81</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>69.12</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>68.26000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>69.04000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>68.06999999999999</v>
+        <v>73.23</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>51.91</v>
+        <v>72.42</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>67.40000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>67.39</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>68.22</v>
+        <v>72.63</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>67.51000000000001</v>
+        <v>72.69</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>68.11</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>68.19</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>68.28</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>68.22</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>67.56999999999999</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>66.69</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AA12" s="6" t="n">
-        <v>67.38</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="AB12" s="6" t="n">
-        <v>67.04000000000001</v>
+        <v>72.48</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>67.63</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="AD12" s="6" t="n">
-        <v>67.89</v>
+        <v>73.56</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>67.59</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="AF12" s="6" t="n">
-        <v>67.45999999999999</v>
+        <v>73.42</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>68.75</v>
+        <v>72.84</v>
       </c>
       <c r="AH12" s="6" t="n">
-        <v>66.97</v>
+        <v>72.27</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>265.65</v>
+        <v>160.6</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
       <c r="AK12" s="7" t="inlineStr"/>
@@ -1273,110 +1065,110 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>LA OTRA FM</t>
+          <t>OVACION INTERNACIONAL FM</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>90.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>75.42</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>74.88</v>
+        <v>72.61</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>75.34999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>74.34999999999999</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>74.97</v>
+        <v>72.34</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>75.39</v>
+        <v>72.92</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>75.95999999999999</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>75.69</v>
+        <v>71.81</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>75.93000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>76.37</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>75.69</v>
+        <v>73.19</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>76.73999999999999</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>75.83</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>76.41</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>75.81999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>75.72</v>
+        <v>72.39</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>75.34</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>75.08</v>
+        <v>72.38</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>76.34999999999999</v>
+        <v>71.44</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>76.36</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>75.76000000000001</v>
+        <v>60.52</v>
       </c>
       <c r="X13" s="6" t="n">
-        <v>76.05</v>
+        <v>72.17</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>76.19</v>
+        <v>71.87</v>
       </c>
       <c r="Z13" s="6" t="n">
-        <v>74.95999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AA13" s="6" t="n">
-        <v>75.79000000000001</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="AB13" s="6" t="n">
-        <v>74.79000000000001</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="AC13" s="6" t="n">
-        <v>75.52</v>
+        <v>71.78</v>
       </c>
       <c r="AD13" s="6" t="n">
-        <v>75.75</v>
+        <v>71.84</v>
       </c>
       <c r="AE13" s="6" t="n">
-        <v>75.91</v>
+        <v>70.8</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>75.68000000000001</v>
+        <v>71.34</v>
       </c>
       <c r="AG13" s="6" t="n">
-        <v>75.70999999999999</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="AH13" s="6" t="n">
-        <v>75.67</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>229.65</v>
+        <v>200.59</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
       <c r="AK13" s="7" t="inlineStr"/>
@@ -1384,110 +1176,110 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>CANDELA 90.7 FM</t>
+          <t>RADIO SAMANTHA STEREO</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>90.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>68.95999999999999</v>
+        <v>67.19</v>
       </c>
       <c r="D14" s="6" t="n">
+        <v>66.91</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>67.26000000000001</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>67.64</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>68.06999999999999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>67.39</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <v>68.19</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="Z14" s="6" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="AA14" s="6" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="AB14" s="6" t="n">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="AC14" s="6" t="n">
+        <v>67.63</v>
+      </c>
+      <c r="AD14" s="6" t="n">
         <v>67.89</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>68.08</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>67.39</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>68.81</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>68.16</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>68.59</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>66.77</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>68.31999999999999</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>67.63</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>67.26000000000001</v>
-      </c>
-      <c r="R14" s="6" t="n">
+      <c r="AE14" s="6" t="n">
+        <v>67.59</v>
+      </c>
+      <c r="AF14" s="6" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="S14" s="6" t="n">
-        <v>67.22</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="U14" s="6" t="n">
-        <v>68.77</v>
-      </c>
-      <c r="V14" s="6" t="n">
-        <v>68.70999999999999</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>68.16</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>69.34</v>
-      </c>
-      <c r="Y14" s="6" t="n">
-        <v>68.86</v>
-      </c>
-      <c r="Z14" s="6" t="n">
-        <v>66.81</v>
-      </c>
-      <c r="AA14" s="6" t="n">
-        <v>69.08</v>
-      </c>
-      <c r="AB14" s="6" t="n">
-        <v>68.16</v>
-      </c>
-      <c r="AC14" s="6" t="n">
-        <v>67.18000000000001</v>
-      </c>
-      <c r="AD14" s="6" t="n">
-        <v>67.77</v>
-      </c>
-      <c r="AE14" s="6" t="n">
-        <v>67.11</v>
-      </c>
-      <c r="AF14" s="6" t="n">
-        <v>67.20999999999999</v>
-      </c>
       <c r="AG14" s="6" t="n">
-        <v>68.09</v>
+        <v>68.75</v>
       </c>
       <c r="AH14" s="6" t="n">
-        <v>67.72</v>
+        <v>66.97</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>428.49</v>
+        <v>265.65</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
       <c r="AK14" s="7" t="inlineStr"/>
@@ -1495,110 +1287,110 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VIVA FM</t>
+          <t>LA OTRA FM</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>91.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>70.97</v>
+        <v>75.42</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>69.94</v>
+        <v>74.88</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>65.2</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>70.09999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>70.06</v>
+        <v>74.97</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>70.98999999999999</v>
+        <v>75.39</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>71.68000000000001</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>71.15000000000001</v>
+        <v>75.69</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>70.64</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>71.81999999999999</v>
+        <v>76.37</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>70.95999999999999</v>
+        <v>75.69</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>71.64</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>70.11</v>
+        <v>75.83</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>70.51000000000001</v>
+        <v>76.41</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>70.2</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>70.83</v>
+        <v>75.72</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>70.75</v>
+        <v>75.34</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>69.44</v>
+        <v>75.08</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>70.42</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>70.51000000000001</v>
+        <v>76.36</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>70.09</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="X15" s="6" t="n">
-        <v>69.79000000000001</v>
+        <v>76.05</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>69.2</v>
+        <v>76.19</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>69.92</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AA15" s="6" t="n">
-        <v>69.08</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>69.81999999999999</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="AC15" s="6" t="n">
-        <v>70.20999999999999</v>
+        <v>75.52</v>
       </c>
       <c r="AD15" s="6" t="n">
-        <v>70.39</v>
+        <v>75.75</v>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>69.98999999999999</v>
+        <v>75.91</v>
       </c>
       <c r="AF15" s="6" t="n">
-        <v>69.2</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="AG15" s="6" t="n">
-        <v>68.95999999999999</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="AH15" s="6" t="n">
-        <v>70.15000000000001</v>
+        <v>75.67</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>388.85</v>
+        <v>229.65</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
       <c r="AK15" s="7" t="inlineStr"/>
@@ -1606,110 +1398,110 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RADIO VIGIA FM</t>
+          <t>CANDELA 90.7 FM</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>91.5</v>
+        <v>90.7</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>52.72</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>50.06</v>
+        <v>67.89</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>58.76</v>
+        <v>60.9</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>50.41</v>
+        <v>67.3</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>46.62</v>
+        <v>68.08</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>49.69</v>
+        <v>67.39</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>50.71</v>
+        <v>68.81</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>48.24</v>
+        <v>68.16</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>50.75</v>
+        <v>68.59</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>50.51</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>52.76</v>
+        <v>66.77</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>51.64</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>48.68</v>
+        <v>67.63</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>49.17</v>
+        <v>66.83</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>53.33</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>50.15</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>48.7</v>
+        <v>67.22</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>49.26</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>47.96</v>
+        <v>68.77</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>47.53</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>49.54</v>
+        <v>68.16</v>
       </c>
       <c r="X16" s="6" t="n">
-        <v>49.93</v>
+        <v>69.34</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>52.67</v>
+        <v>68.86</v>
       </c>
       <c r="Z16" s="6" t="n">
-        <v>48.81</v>
+        <v>66.81</v>
       </c>
       <c r="AA16" s="6" t="n">
-        <v>48.32</v>
+        <v>69.08</v>
       </c>
       <c r="AB16" s="6" t="n">
-        <v>49.61</v>
+        <v>68.16</v>
       </c>
       <c r="AC16" s="6" t="n">
-        <v>49.47</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="AD16" s="6" t="n">
-        <v>47.34</v>
+        <v>67.77</v>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>49.9</v>
+        <v>67.11</v>
       </c>
       <c r="AF16" s="6" t="n">
-        <v>52.66</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="AG16" s="6" t="n">
-        <v>51.71</v>
+        <v>68.09</v>
       </c>
       <c r="AH16" s="6" t="n">
-        <v>50.25</v>
+        <v>67.72</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>499.47</v>
+        <v>428.49</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
       <c r="AK16" s="7" t="inlineStr"/>
@@ -1717,110 +1509,110 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RADIO PÚBLICA JUBONES 91.9 FM</t>
+          <t>VIVA FM</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>91.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>66.62</v>
+        <v>70.97</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>66.97</v>
+        <v>69.94</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>65.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>67.31</v>
+        <v>70.06</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>66.04000000000001</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>67.39</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>67.81999999999999</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>67.41</v>
+        <v>70.64</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>67.04000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>66.87</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>67.88</v>
+        <v>71.64</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>68.03</v>
+        <v>70.11</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>67.61</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>67.38</v>
+        <v>70.2</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>67.73</v>
+        <v>70.83</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>67.64</v>
+        <v>70.75</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>67.38</v>
+        <v>69.44</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>67.33</v>
+        <v>70.42</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>68.03</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>67.86</v>
+        <v>70.09</v>
       </c>
       <c r="X17" s="6" t="n">
-        <v>67.59999999999999</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>67.22</v>
+        <v>69.2</v>
       </c>
       <c r="Z17" s="6" t="n">
-        <v>66.95</v>
+        <v>69.92</v>
       </c>
       <c r="AA17" s="6" t="n">
-        <v>67.81999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>67.92</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>67.02</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>66.37</v>
+        <v>70.39</v>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>66.31</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="AF17" s="6" t="n">
-        <v>67.34</v>
+        <v>69.2</v>
       </c>
       <c r="AG17" s="6" t="n">
-        <v>67.03</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AH17" s="6" t="n">
-        <v>67.31</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>315.82</v>
+        <v>388.85</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
       <c r="AK17" s="7" t="inlineStr"/>
@@ -1828,110 +1620,110 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ARMONICA FM STEREO</t>
+          <t>RADIO VIGIA FM</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>92.3</v>
+        <v>91.5</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>58.3</v>
+        <v>52.72</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>59.64</v>
+        <v>50.06</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>70.18000000000001</v>
+        <v>58.76</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>59.4</v>
+        <v>50.41</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>58.7</v>
+        <v>46.62</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>58.94</v>
+        <v>49.69</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>61.55</v>
+        <v>50.71</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>60.76</v>
+        <v>48.24</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>60.86</v>
+        <v>50.75</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>60.81</v>
+        <v>50.51</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>60.76</v>
+        <v>52.76</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>63.44</v>
+        <v>51.64</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>59.96</v>
+        <v>48.68</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>61.39</v>
+        <v>49.17</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>61.56</v>
+        <v>53.33</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>60.75</v>
+        <v>50.15</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>60.78</v>
+        <v>48.7</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>59.23</v>
+        <v>49.26</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>61.55</v>
+        <v>47.96</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>61.48</v>
+        <v>47.53</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>59</v>
+        <v>49.54</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>57.83</v>
+        <v>49.93</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>59.93</v>
+        <v>52.67</v>
       </c>
       <c r="Z18" s="6" t="n">
-        <v>59.41</v>
+        <v>48.81</v>
       </c>
       <c r="AA18" s="6" t="n">
-        <v>58.81</v>
+        <v>48.32</v>
       </c>
       <c r="AB18" s="6" t="n">
-        <v>59.88</v>
+        <v>49.61</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>60.09</v>
+        <v>49.47</v>
       </c>
       <c r="AD18" s="6" t="n">
-        <v>58.88</v>
+        <v>47.34</v>
       </c>
       <c r="AE18" s="6" t="n">
-        <v>61.23</v>
+        <v>49.9</v>
       </c>
       <c r="AF18" s="6" t="n">
-        <v>59.23</v>
+        <v>52.66</v>
       </c>
       <c r="AG18" s="6" t="n">
-        <v>58.85</v>
+        <v>51.71</v>
       </c>
       <c r="AH18" s="6" t="n">
-        <v>60.42</v>
+        <v>50.25</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>478.59</v>
+        <v>499.47</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
       <c r="AK18" s="7" t="inlineStr"/>
@@ -1939,110 +1731,110 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>SUPERIOR FM (NO AUTORIZADA)</t>
+          <t>RADIO PÚBLICA JUBONES 91.9 FM</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>92.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>67.28</v>
+        <v>66.62</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>68.28</v>
+        <v>66.97</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>67.95999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>68.15000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>68.69</v>
+        <v>67.31</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>66.29000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>68.18000000000001</v>
+        <v>67.39</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>66.05</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>66.42</v>
+        <v>67.41</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>66.48</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>61.24</v>
+        <v>66.87</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>63.96</v>
+        <v>67.88</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>67.36</v>
+        <v>68.03</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>65.54000000000001</v>
+        <v>67.61</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>63.69</v>
+        <v>67.38</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>63.98</v>
+        <v>67.73</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>63.7</v>
+        <v>67.64</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>62.42</v>
+        <v>67.38</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>63.45</v>
+        <v>67.33</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>63.76</v>
+        <v>68.03</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>63.32</v>
+        <v>67.86</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>64.31</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>64.64</v>
+        <v>67.22</v>
       </c>
       <c r="Z19" s="6" t="n">
-        <v>62.4</v>
+        <v>66.95</v>
       </c>
       <c r="AA19" s="6" t="n">
-        <v>62.14</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>48.92</v>
+        <v>67.92</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>42.56</v>
+        <v>67.02</v>
       </c>
       <c r="AD19" s="6" t="n">
-        <v>54.18</v>
+        <v>66.37</v>
       </c>
       <c r="AE19" s="6" t="n">
-        <v>64.91</v>
+        <v>66.31</v>
       </c>
       <c r="AF19" s="6" t="n">
-        <v>65.55</v>
+        <v>67.34</v>
       </c>
       <c r="AG19" s="6" t="n">
-        <v>66.41</v>
+        <v>67.03</v>
       </c>
       <c r="AH19" s="6" t="n">
-        <v>63.62</v>
+        <v>67.31</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>349.62</v>
+        <v>315.82</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
       <c r="AK19" s="7" t="inlineStr"/>
@@ -2050,110 +1842,110 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>LA RADIO DE LA ASAMBLEA NA</t>
+          <t>ARMONICA FM STEREO</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>93.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>59.55</v>
+        <v>58.3</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>64.26000000000001</v>
+        <v>59.64</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>67.94</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>61.62</v>
+        <v>59.4</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>62.62</v>
+        <v>58.7</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>57.23</v>
+        <v>58.94</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>56.89</v>
+        <v>61.55</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>57.64</v>
+        <v>60.76</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>61.28</v>
+        <v>60.86</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>62.13</v>
+        <v>60.81</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>59.85</v>
+        <v>60.76</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>54.39</v>
+        <v>63.44</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>61.68</v>
+        <v>59.96</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>58.36</v>
+        <v>61.39</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>62.69</v>
+        <v>61.56</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>60.4</v>
+        <v>60.75</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>58.01</v>
+        <v>60.78</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>54.16</v>
+        <v>59.23</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>54.15</v>
+        <v>61.55</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>56.63</v>
+        <v>61.48</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>53.21</v>
+        <v>59</v>
       </c>
       <c r="X20" s="6" t="n">
-        <v>57.21</v>
+        <v>57.83</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>55.49</v>
+        <v>59.93</v>
       </c>
       <c r="Z20" s="6" t="n">
-        <v>56.56</v>
+        <v>59.41</v>
       </c>
       <c r="AA20" s="6" t="n">
-        <v>57.02</v>
+        <v>58.81</v>
       </c>
       <c r="AB20" s="6" t="n">
-        <v>56.89</v>
+        <v>59.88</v>
       </c>
       <c r="AC20" s="6" t="n">
-        <v>51.04</v>
+        <v>60.09</v>
       </c>
       <c r="AD20" s="6" t="n">
-        <v>45.58</v>
+        <v>58.88</v>
       </c>
       <c r="AE20" s="6" t="n">
-        <v>45.66</v>
+        <v>61.23</v>
       </c>
       <c r="AF20" s="6" t="n">
-        <v>48.05</v>
+        <v>59.23</v>
       </c>
       <c r="AG20" s="6" t="n">
-        <v>47.09</v>
+        <v>58.85</v>
       </c>
       <c r="AH20" s="6" t="n">
-        <v>56.95</v>
+        <v>60.42</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>386.51</v>
+        <v>478.59</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
       <c r="AK20" s="7" t="inlineStr"/>
@@ -2161,110 +1953,110 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ESTELAR FM</t>
+          <t>SUPERIOR FM (NO AUTORIZADA)</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>93.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>66.69</v>
+        <v>67.28</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>67.98999999999999</v>
+        <v>68.28</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>63.84</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>66.8</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>66.92</v>
+        <v>68.69</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>66.98999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>66.62</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>66.47</v>
+        <v>66.05</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>65.03</v>
+        <v>66.42</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>64.66</v>
+        <v>66.48</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>63.94</v>
+        <v>61.24</v>
       </c>
       <c r="N21" s="6" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>63.98</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="X21" s="6" t="n">
+        <v>64.31</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="Z21" s="6" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AA21" s="6" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="AB21" s="6" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="AC21" s="6" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="AD21" s="6" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="AE21" s="6" t="n">
         <v>64.91</v>
       </c>
-      <c r="O21" s="6" t="n">
-        <v>67.92</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>67.19</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>65.98</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>66.42</v>
-      </c>
-      <c r="U21" s="6" t="n">
-        <v>66.39</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>66.95</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="X21" s="6" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="Y21" s="6" t="n">
-        <v>68.23999999999999</v>
-      </c>
-      <c r="Z21" s="6" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="AA21" s="6" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="AB21" s="6" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="AC21" s="6" t="n">
-        <v>66.69</v>
-      </c>
-      <c r="AD21" s="6" t="n">
-        <v>67.06999999999999</v>
-      </c>
-      <c r="AE21" s="6" t="n">
-        <v>68.13</v>
-      </c>
       <c r="AF21" s="6" t="n">
-        <v>67.72</v>
+        <v>65.55</v>
       </c>
       <c r="AG21" s="6" t="n">
-        <v>66.70999999999999</v>
+        <v>66.41</v>
       </c>
       <c r="AH21" s="6" t="n">
-        <v>66.53</v>
+        <v>63.62</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>219.15</v>
+        <v>349.62</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
       <c r="AK21" s="7" t="inlineStr"/>
@@ -2272,110 +2064,110 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>RADIO UNO</t>
+          <t>LA RADIO DE LA ASAMBLEA NA</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>94.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>64.47</v>
+        <v>59.55</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>65.97</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>61.84</v>
+        <v>67.94</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>65.23999999999999</v>
+        <v>61.62</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>64.51000000000001</v>
+        <v>62.62</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>64.92</v>
+        <v>57.23</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>64.04000000000001</v>
+        <v>56.89</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>63.72</v>
+        <v>57.64</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>64.91</v>
+        <v>61.28</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>64.31999999999999</v>
+        <v>62.13</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>62.96</v>
+        <v>59.85</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>65.09</v>
+        <v>54.39</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>66.59</v>
+        <v>61.68</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>65.03</v>
+        <v>58.36</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>64.33</v>
+        <v>62.69</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>64.14</v>
+        <v>60.4</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>63.59</v>
+        <v>58.01</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>64.28</v>
+        <v>54.16</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>65.02</v>
+        <v>54.15</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>65.20999999999999</v>
+        <v>56.63</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>64.38</v>
+        <v>53.21</v>
       </c>
       <c r="X22" s="6" t="n">
-        <v>64.44</v>
+        <v>57.21</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>66.12</v>
+        <v>55.49</v>
       </c>
       <c r="Z22" s="6" t="n">
-        <v>63.82</v>
+        <v>56.56</v>
       </c>
       <c r="AA22" s="6" t="n">
-        <v>65.09</v>
+        <v>57.02</v>
       </c>
       <c r="AB22" s="6" t="n">
-        <v>65.8</v>
+        <v>56.89</v>
       </c>
       <c r="AC22" s="6" t="n">
-        <v>64.81</v>
+        <v>51.04</v>
       </c>
       <c r="AD22" s="6" t="n">
-        <v>65.23</v>
+        <v>45.58</v>
       </c>
       <c r="AE22" s="6" t="n">
-        <v>66.12</v>
+        <v>45.66</v>
       </c>
       <c r="AF22" s="6" t="n">
-        <v>66.22</v>
+        <v>48.05</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>64.79000000000001</v>
+        <v>47.09</v>
       </c>
       <c r="AH22" s="6" t="n">
-        <v>64.73999999999999</v>
+        <v>56.95</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>226.77</v>
+        <v>386.51</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
       <c r="AK22" s="7" t="inlineStr"/>
@@ -2383,110 +2175,110 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>HCJB LA VOZ Y VENTANA DE L</t>
+          <t>ESTELAR FM</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>94.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>68.70999999999999</v>
+        <v>66.69</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>69.70999999999999</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>64.47</v>
+        <v>63.84</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>68.54000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>69.23999999999999</v>
+        <v>66.92</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>68.8</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>68.68000000000001</v>
+        <v>66.62</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>68.55</v>
+        <v>66.47</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>68.83</v>
+        <v>65.03</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>68.84</v>
+        <v>64.66</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>67.37</v>
+        <v>63.94</v>
       </c>
       <c r="N23" s="6" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>67.19</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>66.39</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="X23" s="6" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="Y23" s="6" t="n">
         <v>68.23999999999999</v>
       </c>
-      <c r="O23" s="6" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>68.37</v>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>67.92</v>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v>67.75</v>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>68.11</v>
-      </c>
-      <c r="T23" s="6" t="n">
-        <v>67.22</v>
-      </c>
-      <c r="U23" s="6" t="n">
-        <v>67.28</v>
-      </c>
-      <c r="V23" s="6" t="n">
-        <v>67.53</v>
-      </c>
-      <c r="W23" s="6" t="n">
-        <v>68.94</v>
-      </c>
-      <c r="X23" s="6" t="n">
-        <v>69.02</v>
-      </c>
-      <c r="Y23" s="6" t="n">
-        <v>69.25</v>
-      </c>
       <c r="Z23" s="6" t="n">
-        <v>68.22</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="AA23" s="6" t="n">
-        <v>68.59999999999999</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="AB23" s="6" t="n">
-        <v>67.76000000000001</v>
+        <v>66.97</v>
       </c>
       <c r="AC23" s="6" t="n">
-        <v>69.54000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="AD23" s="6" t="n">
-        <v>69.18000000000001</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AE23" s="6" t="n">
-        <v>68.78</v>
+        <v>68.13</v>
       </c>
       <c r="AF23" s="6" t="n">
-        <v>69.18000000000001</v>
+        <v>67.72</v>
       </c>
       <c r="AG23" s="6" t="n">
-        <v>69.81</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="AH23" s="6" t="n">
-        <v>68.48</v>
+        <v>66.53</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>123.83</v>
+        <v>219.15</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
       <c r="AK23" s="7" t="inlineStr"/>
@@ -2494,110 +2286,110 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>DORADA FM</t>
+          <t>RADIO UNO</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>95.5</v>
+        <v>94.3</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>72.45999999999999</v>
+        <v>64.47</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>72.84</v>
+        <v>65.97</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>68.31999999999999</v>
+        <v>61.84</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>72.84999999999999</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>72.31999999999999</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>74.59999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>75.09</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>73.41</v>
+        <v>63.72</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>72.36</v>
+        <v>64.91</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>71.86</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>71.45999999999999</v>
+        <v>62.96</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>72.40000000000001</v>
+        <v>65.09</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>74.67</v>
+        <v>66.59</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>74.05</v>
+        <v>65.03</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>73.43000000000001</v>
+        <v>64.33</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>72.98999999999999</v>
+        <v>64.14</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>72.76000000000001</v>
+        <v>63.59</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>72.95</v>
+        <v>64.28</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>73.26000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>73.56999999999999</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>73.54000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="X24" s="6" t="n">
-        <v>73.29000000000001</v>
+        <v>64.44</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>73.64</v>
+        <v>66.12</v>
       </c>
       <c r="Z24" s="6" t="n">
-        <v>73.19</v>
+        <v>63.82</v>
       </c>
       <c r="AA24" s="6" t="n">
-        <v>73.95999999999999</v>
+        <v>65.09</v>
       </c>
       <c r="AB24" s="6" t="n">
-        <v>72.31</v>
+        <v>65.8</v>
       </c>
       <c r="AC24" s="6" t="n">
-        <v>74.83</v>
+        <v>64.81</v>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>75.70999999999999</v>
+        <v>65.23</v>
       </c>
       <c r="AE24" s="6" t="n">
-        <v>75.36</v>
+        <v>66.12</v>
       </c>
       <c r="AF24" s="6" t="n">
-        <v>74.62</v>
+        <v>66.22</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>74.40000000000001</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="AH24" s="6" t="n">
-        <v>73.31</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>223.97</v>
+        <v>226.77</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
       <c r="AK24" s="7" t="inlineStr"/>
@@ -2605,110 +2397,110 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>RADIO MARIA</t>
+          <t>HCJB LA VOZ Y VENTANA DE L</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>95.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>59.7</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>60.51</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>52.24</v>
+        <v>64.47</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>59.5</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>58.86</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>59.35</v>
+        <v>68.8</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>60.09</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>59.86</v>
+        <v>68.55</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>59.06</v>
+        <v>68.83</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>58.9</v>
+        <v>68.84</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>58.88</v>
+        <v>67.37</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>59.69</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>61.22</v>
+        <v>70.36</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>60.84</v>
+        <v>68.37</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>60.99</v>
+        <v>67.92</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>60.34</v>
+        <v>67.75</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>60.13</v>
+        <v>68.11</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>60.43</v>
+        <v>67.22</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>60.52</v>
+        <v>67.28</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>60.23</v>
+        <v>67.53</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>60.95</v>
+        <v>68.94</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>60.09</v>
+        <v>69.02</v>
       </c>
       <c r="Y25" s="6" t="n">
-        <v>60.41</v>
+        <v>69.25</v>
       </c>
       <c r="Z25" s="6" t="n">
-        <v>59.08</v>
+        <v>68.22</v>
       </c>
       <c r="AA25" s="6" t="n">
-        <v>59.89</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AB25" s="6" t="n">
-        <v>60.36</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="AC25" s="6" t="n">
-        <v>60.82</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="AD25" s="6" t="n">
-        <v>60.08</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="AE25" s="6" t="n">
-        <v>60.62</v>
+        <v>68.78</v>
       </c>
       <c r="AF25" s="6" t="n">
-        <v>61.02</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>60.81</v>
+        <v>69.81</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>59.85</v>
+        <v>68.48</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>431.6</v>
+        <v>123.83</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
       <c r="AK25" s="7" t="inlineStr"/>
@@ -2716,110 +2508,110 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>SUPER SOL FM</t>
+          <t>DORADA FM</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>96.3</v>
+        <v>95.5</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>60.55</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>62.42</v>
+        <v>72.84</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>64.69</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>62.36</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>62.31</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>61.61</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>62.62</v>
+        <v>75.09</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>62.35</v>
+        <v>73.41</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>62.64</v>
+        <v>72.36</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>64.14</v>
+        <v>71.86</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>61.74</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>62.46</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>65.94</v>
+        <v>74.67</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>65.22</v>
+        <v>74.05</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>65.05</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>60.73</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>61.3</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>60.76</v>
+        <v>72.95</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>60.58</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>62.09</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>61.12</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="X26" s="6" t="n">
-        <v>62.12</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="Y26" s="6" t="n">
-        <v>63.75</v>
+        <v>73.64</v>
       </c>
       <c r="Z26" s="6" t="n">
-        <v>62.11</v>
+        <v>73.19</v>
       </c>
       <c r="AA26" s="6" t="n">
-        <v>61.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AB26" s="6" t="n">
-        <v>61.89</v>
+        <v>72.31</v>
       </c>
       <c r="AC26" s="6" t="n">
-        <v>61.14</v>
+        <v>74.83</v>
       </c>
       <c r="AD26" s="6" t="n">
-        <v>62.76</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="AE26" s="6" t="n">
-        <v>62.2</v>
+        <v>75.36</v>
       </c>
       <c r="AF26" s="6" t="n">
-        <v>63.74</v>
+        <v>74.62</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>63.46</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>62.51</v>
+        <v>73.31</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>478.51</v>
+        <v>223.97</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
       <c r="AK26" s="7" t="inlineStr"/>
@@ -2827,110 +2619,110 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>COSTA MAR</t>
+          <t>RADIO MARIA</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>96.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>70.28</v>
+        <v>59.7</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>70.29000000000001</v>
+        <v>60.51</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>62.02</v>
+        <v>52.24</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>70.8</v>
+        <v>59.5</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>70.56</v>
+        <v>58.86</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>70.36</v>
+        <v>59.35</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>70.59</v>
+        <v>60.09</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>69.28</v>
+        <v>59.86</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>70.34999999999999</v>
+        <v>59.06</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>70.55</v>
+        <v>58.9</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>70.64</v>
+        <v>58.88</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>70.33</v>
+        <v>59.69</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>69.48</v>
+        <v>61.22</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>69.92</v>
+        <v>60.84</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>69.95</v>
+        <v>60.99</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>70.45</v>
+        <v>60.34</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>70.41</v>
+        <v>60.13</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>70.81999999999999</v>
+        <v>60.43</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>71.41</v>
+        <v>60.52</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>70.73999999999999</v>
+        <v>60.23</v>
       </c>
       <c r="W27" s="6" t="n">
-        <v>70.98999999999999</v>
+        <v>60.95</v>
       </c>
       <c r="X27" s="6" t="n">
-        <v>70.38</v>
+        <v>60.09</v>
       </c>
       <c r="Y27" s="6" t="n">
-        <v>70.62</v>
+        <v>60.41</v>
       </c>
       <c r="Z27" s="6" t="n">
-        <v>70.51000000000001</v>
+        <v>59.08</v>
       </c>
       <c r="AA27" s="6" t="n">
-        <v>71</v>
+        <v>59.89</v>
       </c>
       <c r="AB27" s="6" t="n">
-        <v>71.16</v>
+        <v>60.36</v>
       </c>
       <c r="AC27" s="6" t="n">
-        <v>70.77</v>
+        <v>60.82</v>
       </c>
       <c r="AD27" s="6" t="n">
-        <v>71.01000000000001</v>
+        <v>60.08</v>
       </c>
       <c r="AE27" s="6" t="n">
-        <v>71.12</v>
+        <v>60.62</v>
       </c>
       <c r="AF27" s="6" t="n">
-        <v>71.72</v>
+        <v>61.02</v>
       </c>
       <c r="AG27" s="6" t="n">
-        <v>70.56</v>
+        <v>60.81</v>
       </c>
       <c r="AH27" s="6" t="n">
-        <v>70.29000000000001</v>
+        <v>59.85</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>258.64</v>
+        <v>431.6</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
       <c r="AK27" s="7" t="inlineStr"/>
@@ -2938,110 +2730,110 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>LA PROPIA</t>
+          <t>SUPER SOL FM</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>97.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>69.62</v>
+        <v>60.55</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>69.25</v>
+        <v>62.42</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>61.6</v>
+        <v>64.69</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>70.01000000000001</v>
+        <v>62.36</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>69.61</v>
+        <v>62.31</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>68.84999999999999</v>
+        <v>61.61</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>69.55</v>
+        <v>62.62</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>58.66</v>
+        <v>62.35</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>68.88</v>
+        <v>62.64</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>69.31</v>
+        <v>64.14</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>69.06999999999999</v>
+        <v>61.74</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>69.09</v>
+        <v>62.46</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>67.34</v>
+        <v>65.94</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>67.97</v>
+        <v>65.22</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>67.03</v>
+        <v>65.05</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>68.8</v>
+        <v>60.73</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>68.91</v>
+        <v>61.3</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>69.18000000000001</v>
+        <v>60.76</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>69.41</v>
+        <v>60.58</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>68.5</v>
+        <v>62.09</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>68.97</v>
+        <v>61.12</v>
       </c>
       <c r="X28" s="6" t="n">
-        <v>69.33</v>
+        <v>62.12</v>
       </c>
       <c r="Y28" s="6" t="n">
-        <v>68.73</v>
+        <v>63.75</v>
       </c>
       <c r="Z28" s="6" t="n">
-        <v>69.65000000000001</v>
+        <v>62.11</v>
       </c>
       <c r="AA28" s="6" t="n">
-        <v>68.75</v>
+        <v>61.92</v>
       </c>
       <c r="AB28" s="6" t="n">
-        <v>69.12</v>
+        <v>61.89</v>
       </c>
       <c r="AC28" s="6" t="n">
-        <v>69.88</v>
+        <v>61.14</v>
       </c>
       <c r="AD28" s="6" t="n">
-        <v>70.22</v>
+        <v>62.76</v>
       </c>
       <c r="AE28" s="6" t="n">
-        <v>70.36</v>
+        <v>62.2</v>
       </c>
       <c r="AF28" s="6" t="n">
-        <v>71.01000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="AG28" s="6" t="n">
-        <v>69.2</v>
+        <v>63.46</v>
       </c>
       <c r="AH28" s="6" t="n">
-        <v>68.58</v>
+        <v>62.51</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>254.74</v>
+        <v>478.51</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
       <c r="AK28" s="7" t="inlineStr"/>
@@ -3049,110 +2841,110 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>HITS &amp; FLOW</t>
+          <t>COSTA MAR</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>97.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>49.18</v>
+        <v>70.28</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>38.17</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>39.78</v>
+        <v>62.02</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>48.22</v>
+        <v>70.8</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>45.28</v>
+        <v>70.56</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>47.22</v>
+        <v>70.36</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>47.81</v>
+        <v>70.59</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>46.02</v>
+        <v>69.28</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>47.37</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>45.26</v>
+        <v>70.55</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>49.09</v>
+        <v>70.64</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>47</v>
+        <v>70.33</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>47.71</v>
+        <v>69.48</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>53.23</v>
+        <v>69.92</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>43.31</v>
+        <v>69.95</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>42.73</v>
+        <v>70.45</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>36.38</v>
+        <v>70.41</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>42.77</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>40.38</v>
+        <v>71.41</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>44.49</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>45.69</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="X29" s="6" t="n">
-        <v>45.4</v>
+        <v>70.38</v>
       </c>
       <c r="Y29" s="6" t="n">
-        <v>40.74</v>
+        <v>70.62</v>
       </c>
       <c r="Z29" s="6" t="n">
-        <v>41.24</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="AA29" s="6" t="n">
-        <v>41.48</v>
+        <v>71</v>
       </c>
       <c r="AB29" s="6" t="n">
-        <v>42.87</v>
+        <v>71.16</v>
       </c>
       <c r="AC29" s="6" t="n">
-        <v>49.16</v>
+        <v>70.77</v>
       </c>
       <c r="AD29" s="6" t="n">
-        <v>40.41</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="AE29" s="6" t="n">
-        <v>47.34</v>
+        <v>71.12</v>
       </c>
       <c r="AF29" s="6" t="n">
-        <v>51.7</v>
+        <v>71.72</v>
       </c>
       <c r="AG29" s="6" t="n">
-        <v>45.77</v>
+        <v>70.56</v>
       </c>
       <c r="AH29" s="6" t="n">
-        <v>44.94</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>485.2</v>
+        <v>258.64</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
       <c r="AK29" s="7" t="inlineStr"/>
@@ -3160,110 +2952,110 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>RTP 96.5</t>
+          <t>LA PROPIA</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>98.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>56.19</v>
+        <v>69.62</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>55.07</v>
+        <v>69.25</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>52.52</v>
+        <v>61.6</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>56.21</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>57</v>
+        <v>69.61</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>55.69</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>54.63</v>
+        <v>69.55</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>54.37</v>
+        <v>58.66</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>55.76</v>
+        <v>68.88</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>55.24</v>
+        <v>69.31</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>56.34</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>56.26</v>
+        <v>69.09</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>54.48</v>
+        <v>67.34</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>54.57</v>
+        <v>67.97</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>54.34</v>
+        <v>67.03</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>55.11</v>
+        <v>68.8</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>54.74</v>
+        <v>68.91</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>55.15</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>56</v>
+        <v>69.41</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>56.91</v>
+        <v>68.5</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>57.04</v>
+        <v>68.97</v>
       </c>
       <c r="X30" s="6" t="n">
-        <v>56.21</v>
+        <v>69.33</v>
       </c>
       <c r="Y30" s="6" t="n">
-        <v>55.12</v>
+        <v>68.73</v>
       </c>
       <c r="Z30" s="6" t="n">
-        <v>56.95</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AA30" s="6" t="n">
-        <v>55.64</v>
+        <v>68.75</v>
       </c>
       <c r="AB30" s="6" t="n">
-        <v>56.39</v>
+        <v>69.12</v>
       </c>
       <c r="AC30" s="6" t="n">
-        <v>57.72</v>
+        <v>69.88</v>
       </c>
       <c r="AD30" s="6" t="n">
-        <v>55.58</v>
+        <v>70.22</v>
       </c>
       <c r="AE30" s="6" t="n">
-        <v>57.07</v>
+        <v>70.36</v>
       </c>
       <c r="AF30" s="6" t="n">
-        <v>57.31</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="AG30" s="6" t="n">
-        <v>55.64</v>
+        <v>69.2</v>
       </c>
       <c r="AH30" s="6" t="n">
-        <v>55.72</v>
+        <v>68.58</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>474.57</v>
+        <v>254.74</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
       <c r="AK30" s="7" t="inlineStr"/>
@@ -3271,110 +3063,110 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>B.B.N. 99.5 FM</t>
+          <t>HITS &amp; FLOW</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>99.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>76.2</v>
+        <v>49.18</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>76.95999999999999</v>
+        <v>38.17</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>75.94</v>
+        <v>39.78</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>75.91</v>
+        <v>48.22</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>77.06</v>
+        <v>45.28</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>76.61</v>
+        <v>47.22</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>76.84999999999999</v>
+        <v>47.81</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>76.97</v>
+        <v>46.02</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>77.41</v>
+        <v>47.37</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>76.81</v>
+        <v>45.26</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>76.91</v>
+        <v>49.09</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>77.29000000000001</v>
+        <v>47</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>76.98999999999999</v>
+        <v>47.71</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>76.81999999999999</v>
+        <v>53.23</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>76.93000000000001</v>
+        <v>43.31</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>76.72</v>
+        <v>42.73</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>77.2</v>
+        <v>36.38</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>76.95999999999999</v>
+        <v>42.77</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>77.56999999999999</v>
+        <v>40.38</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>77.09</v>
+        <v>44.49</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>76.53</v>
+        <v>45.69</v>
       </c>
       <c r="X31" s="6" t="n">
-        <v>77.14</v>
+        <v>45.4</v>
       </c>
       <c r="Y31" s="6" t="n">
-        <v>77.29000000000001</v>
+        <v>40.74</v>
       </c>
       <c r="Z31" s="6" t="n">
-        <v>76.73999999999999</v>
+        <v>41.24</v>
       </c>
       <c r="AA31" s="6" t="n">
-        <v>76.45</v>
+        <v>41.48</v>
       </c>
       <c r="AB31" s="6" t="n">
-        <v>77.54000000000001</v>
+        <v>42.87</v>
       </c>
       <c r="AC31" s="6" t="n">
-        <v>77.26000000000001</v>
+        <v>49.16</v>
       </c>
       <c r="AD31" s="6" t="n">
-        <v>76.68000000000001</v>
+        <v>40.41</v>
       </c>
       <c r="AE31" s="6" t="n">
-        <v>77.01000000000001</v>
+        <v>47.34</v>
       </c>
       <c r="AF31" s="6" t="n">
-        <v>77.08</v>
+        <v>51.7</v>
       </c>
       <c r="AG31" s="6" t="n">
-        <v>76.45999999999999</v>
+        <v>45.77</v>
       </c>
       <c r="AH31" s="6" t="n">
-        <v>76.88</v>
+        <v>44.94</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>326</v>
+        <v>485.2</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
       <c r="AK31" s="7" t="inlineStr"/>
@@ -3382,110 +3174,110 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>CATOLICA NACIONAL FM</t>
+          <t>RTP 96.5</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>62.49</v>
+        <v>56.19</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>65.53</v>
+        <v>55.07</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>56.56</v>
+        <v>52.52</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>65.81999999999999</v>
+        <v>56.21</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>66.03</v>
+        <v>57</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>65.11</v>
+        <v>55.69</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>65.84999999999999</v>
+        <v>54.63</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>64.95999999999999</v>
+        <v>54.37</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>66.03</v>
+        <v>55.76</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>66.95999999999999</v>
+        <v>55.24</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>65.37</v>
+        <v>56.34</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>66.76000000000001</v>
+        <v>56.26</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>66.78</v>
+        <v>54.48</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>66.86</v>
+        <v>54.57</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>65.68000000000001</v>
+        <v>54.34</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>66.78</v>
+        <v>55.11</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>66.48999999999999</v>
+        <v>54.74</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>65.76000000000001</v>
+        <v>55.15</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>66.04000000000001</v>
+        <v>56</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>66.42</v>
+        <v>56.91</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>67.48</v>
+        <v>57.04</v>
       </c>
       <c r="X32" s="6" t="n">
-        <v>68.12</v>
+        <v>56.21</v>
       </c>
       <c r="Y32" s="6" t="n">
-        <v>68.37</v>
+        <v>55.12</v>
       </c>
       <c r="Z32" s="6" t="n">
-        <v>66</v>
+        <v>56.95</v>
       </c>
       <c r="AA32" s="6" t="n">
-        <v>66.53</v>
+        <v>55.64</v>
       </c>
       <c r="AB32" s="6" t="n">
-        <v>66.68000000000001</v>
+        <v>56.39</v>
       </c>
       <c r="AC32" s="6" t="n">
-        <v>67.56999999999999</v>
+        <v>57.72</v>
       </c>
       <c r="AD32" s="6" t="n">
-        <v>67.37</v>
+        <v>55.58</v>
       </c>
       <c r="AE32" s="6" t="n">
-        <v>66.8</v>
+        <v>57.07</v>
       </c>
       <c r="AF32" s="6" t="n">
-        <v>64.17</v>
+        <v>57.31</v>
       </c>
       <c r="AG32" s="6" t="n">
-        <v>67.31999999999999</v>
+        <v>55.64</v>
       </c>
       <c r="AH32" s="6" t="n">
-        <v>65.95999999999999</v>
+        <v>55.72</v>
       </c>
       <c r="AI32" s="6" t="n">
-        <v>478.65</v>
+        <v>474.57</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
       <c r="AK32" s="7" t="inlineStr"/>
@@ -3493,110 +3285,110 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>BRISA AZUL</t>
+          <t>B.B.N. 99.5 FM</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>100.3</v>
+        <v>99.5</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>61.94</v>
+        <v>76.2</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>61.37</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>64.2</v>
+        <v>75.94</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>61.69</v>
+        <v>75.91</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>61.82</v>
+        <v>77.06</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>62.42</v>
+        <v>76.61</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>59.68</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>60.43</v>
+        <v>76.97</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>58.74</v>
+        <v>77.41</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>60.15</v>
+        <v>76.81</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>61.25</v>
+        <v>76.91</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>59.7</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>61.84</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>61.41</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>59.86</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>59.32</v>
+        <v>76.72</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>60.75</v>
+        <v>77.2</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>58.68</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="U33" s="6" t="n">
-        <v>57.96</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="V33" s="6" t="n">
-        <v>59.95</v>
+        <v>77.09</v>
       </c>
       <c r="W33" s="6" t="n">
-        <v>58.4</v>
+        <v>76.53</v>
       </c>
       <c r="X33" s="6" t="n">
-        <v>59.2</v>
+        <v>77.14</v>
       </c>
       <c r="Y33" s="6" t="n">
-        <v>59.93</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="Z33" s="6" t="n">
-        <v>57.76</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="AA33" s="6" t="n">
-        <v>59.89</v>
+        <v>76.45</v>
       </c>
       <c r="AB33" s="6" t="n">
-        <v>61.02</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="AC33" s="6" t="n">
-        <v>60.55</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="AD33" s="6" t="n">
-        <v>61.73</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="AE33" s="6" t="n">
-        <v>60.34</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="AF33" s="6" t="n">
-        <v>59.4</v>
+        <v>77.08</v>
       </c>
       <c r="AG33" s="6" t="n">
-        <v>61.26</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="AH33" s="6" t="n">
-        <v>60.41</v>
+        <v>76.88</v>
       </c>
       <c r="AI33" s="6" t="n">
-        <v>497.28</v>
+        <v>326</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
       <c r="AK33" s="7" t="inlineStr"/>
@@ -3604,110 +3396,110 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>CANELA EL ORO</t>
+          <t>CATOLICA NACIONAL FM</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>100.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>65.72</v>
+        <v>62.49</v>
       </c>
       <c r="D34" s="6" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="E34" s="6" t="n">
-        <v>62.38</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>66.20999999999999</v>
-      </c>
-      <c r="I34" s="6" t="n">
+      <c r="K34" s="6" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>66.95999999999999</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>66.86</v>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v>65.68000000000001</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="T34" s="6" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="U34" s="6" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="W34" s="6" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="X34" s="6" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="Y34" s="6" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="Z34" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="J34" s="6" t="n">
-        <v>65.55</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>65.69</v>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>64.47</v>
-      </c>
-      <c r="O34" s="6" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="S34" s="6" t="n">
-        <v>64.95999999999999</v>
-      </c>
-      <c r="T34" s="6" t="n">
-        <v>65.39</v>
-      </c>
-      <c r="U34" s="6" t="n">
-        <v>64.59</v>
-      </c>
-      <c r="V34" s="6" t="n">
-        <v>65.04000000000001</v>
-      </c>
-      <c r="W34" s="6" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="X34" s="6" t="n">
-        <v>64.47</v>
-      </c>
-      <c r="Y34" s="6" t="n">
-        <v>65.12</v>
-      </c>
-      <c r="Z34" s="6" t="n">
-        <v>63.69</v>
-      </c>
       <c r="AA34" s="6" t="n">
-        <v>64.76000000000001</v>
+        <v>66.53</v>
       </c>
       <c r="AB34" s="6" t="n">
-        <v>64.67</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="AC34" s="6" t="n">
-        <v>64.2</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="AD34" s="6" t="n">
-        <v>64.52</v>
+        <v>67.37</v>
       </c>
       <c r="AE34" s="6" t="n">
-        <v>65.34999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="AF34" s="6" t="n">
-        <v>65.12</v>
+        <v>64.17</v>
       </c>
       <c r="AG34" s="6" t="n">
-        <v>65.62</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="AH34" s="6" t="n">
-        <v>65.18000000000001</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>431.37</v>
+        <v>478.65</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
       <c r="AK34" s="7" t="inlineStr"/>
@@ -3715,110 +3507,110 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>RADIO SONORAMA FM</t>
+          <t>BRISA AZUL</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>101.1</v>
+        <v>100.3</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>41.52</v>
+        <v>61.94</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>37.06</v>
+        <v>61.37</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>39.89</v>
+        <v>64.2</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>41.01</v>
+        <v>61.69</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>40.08</v>
+        <v>61.82</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>41.32</v>
+        <v>62.42</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>40.03</v>
+        <v>59.68</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>40.92</v>
+        <v>60.43</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>39.57</v>
+        <v>58.74</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>40.51</v>
+        <v>60.15</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>44.43</v>
+        <v>61.25</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>40.55</v>
+        <v>59.7</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>43.01</v>
+        <v>61.84</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>43.79</v>
+        <v>61.41</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>40.86</v>
+        <v>59.86</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>36.73</v>
+        <v>59.32</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>36.76</v>
+        <v>60.75</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>38.71</v>
+        <v>58.68</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>36.86</v>
+        <v>57.96</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>40.22</v>
+        <v>59.95</v>
       </c>
       <c r="W35" s="6" t="n">
-        <v>40.92</v>
+        <v>58.4</v>
       </c>
       <c r="X35" s="6" t="n">
-        <v>39.83</v>
+        <v>59.2</v>
       </c>
       <c r="Y35" s="6" t="n">
-        <v>37.26</v>
+        <v>59.93</v>
       </c>
       <c r="Z35" s="6" t="n">
-        <v>38.74</v>
+        <v>57.76</v>
       </c>
       <c r="AA35" s="6" t="n">
-        <v>37.96</v>
+        <v>59.89</v>
       </c>
       <c r="AB35" s="6" t="n">
-        <v>41.61</v>
+        <v>61.02</v>
       </c>
       <c r="AC35" s="6" t="n">
-        <v>41.84</v>
+        <v>60.55</v>
       </c>
       <c r="AD35" s="6" t="n">
-        <v>38.69</v>
+        <v>61.73</v>
       </c>
       <c r="AE35" s="6" t="n">
-        <v>41.51</v>
+        <v>60.34</v>
       </c>
       <c r="AF35" s="6" t="n">
-        <v>41.72</v>
+        <v>59.4</v>
       </c>
       <c r="AG35" s="6" t="n">
-        <v>41.58</v>
+        <v>61.26</v>
       </c>
       <c r="AH35" s="6" t="n">
-        <v>40.18</v>
+        <v>60.41</v>
       </c>
       <c r="AI35" s="6" t="n">
-        <v>499.53</v>
+        <v>497.28</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
       <c r="AK35" s="7" t="inlineStr"/>
@@ -3826,110 +3618,110 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>LIDER FM</t>
+          <t>CANELA EL ORO</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>101.5</v>
+        <v>100.7</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>78.09999999999999</v>
+        <v>65.72</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>77.16</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>72.40000000000001</v>
+        <v>62.38</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>77.88</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>77.68000000000001</v>
+        <v>66.14</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>77.70999999999999</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>77.22</v>
+        <v>66</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>77.28</v>
+        <v>65.55</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>77.56</v>
+        <v>66.36</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>77.36</v>
+        <v>65.69</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>77.15000000000001</v>
+        <v>65.42</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>77.54000000000001</v>
+        <v>64.47</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>77.86</v>
+        <v>66.12</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>77.40000000000001</v>
+        <v>66.12</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>77.11</v>
+        <v>66.02</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>77.11</v>
+        <v>65.45</v>
       </c>
       <c r="S36" s="6" t="n">
-        <v>77.18000000000001</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>77.28</v>
+        <v>65.39</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>77.53</v>
+        <v>64.59</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>77.73</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="W36" s="6" t="n">
-        <v>76.98999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="X36" s="6" t="n">
-        <v>77.02</v>
+        <v>64.47</v>
       </c>
       <c r="Y36" s="6" t="n">
-        <v>77.03</v>
+        <v>65.12</v>
       </c>
       <c r="Z36" s="6" t="n">
-        <v>77.04000000000001</v>
+        <v>63.69</v>
       </c>
       <c r="AA36" s="6" t="n">
-        <v>77.90000000000001</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="AB36" s="6" t="n">
-        <v>77.90000000000001</v>
+        <v>64.67</v>
       </c>
       <c r="AC36" s="6" t="n">
-        <v>78.04000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="AD36" s="6" t="n">
-        <v>77.84</v>
+        <v>64.52</v>
       </c>
       <c r="AE36" s="6" t="n">
-        <v>78.12</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AF36" s="6" t="n">
-        <v>78.01000000000001</v>
+        <v>65.12</v>
       </c>
       <c r="AG36" s="6" t="n">
-        <v>77.81</v>
+        <v>65.62</v>
       </c>
       <c r="AH36" s="6" t="n">
-        <v>77.34999999999999</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>159.74</v>
+        <v>431.37</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
       <c r="AK36" s="7" t="inlineStr"/>
@@ -3937,110 +3729,110 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>RADIO LA VOZ DEL PUEBLO</t>
+          <t>RADIO SONORAMA FM</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>102.3</v>
+        <v>101.1</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>70.98999999999999</v>
+        <v>41.52</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>70.63</v>
+        <v>37.06</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>66.64</v>
+        <v>39.89</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>71.08</v>
+        <v>41.01</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>71.31999999999999</v>
+        <v>40.08</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>71.18000000000001</v>
+        <v>41.32</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>71.13</v>
+        <v>40.03</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>71.28</v>
+        <v>40.92</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>71.3</v>
+        <v>39.57</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>71.34999999999999</v>
+        <v>40.51</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>70.84</v>
+        <v>44.43</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>71.38</v>
+        <v>40.55</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>71.52</v>
+        <v>43.01</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>72.11</v>
+        <v>43.79</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>71.31999999999999</v>
+        <v>40.86</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>70.79000000000001</v>
+        <v>36.73</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>71.26000000000001</v>
+        <v>36.76</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>71.37</v>
+        <v>38.71</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>71.91</v>
+        <v>36.86</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>72.36</v>
+        <v>40.22</v>
       </c>
       <c r="W37" s="6" t="n">
-        <v>71.31</v>
+        <v>40.92</v>
       </c>
       <c r="X37" s="6" t="n">
-        <v>71.27</v>
+        <v>39.83</v>
       </c>
       <c r="Y37" s="6" t="n">
-        <v>71.64</v>
+        <v>37.26</v>
       </c>
       <c r="Z37" s="6" t="n">
-        <v>71.56</v>
+        <v>38.74</v>
       </c>
       <c r="AA37" s="6" t="n">
-        <v>72.79000000000001</v>
+        <v>37.96</v>
       </c>
       <c r="AB37" s="6" t="n">
-        <v>71.95</v>
+        <v>41.61</v>
       </c>
       <c r="AC37" s="6" t="n">
-        <v>72.20999999999999</v>
+        <v>41.84</v>
       </c>
       <c r="AD37" s="6" t="n">
-        <v>72.06</v>
+        <v>38.69</v>
       </c>
       <c r="AE37" s="6" t="n">
-        <v>73.04000000000001</v>
+        <v>41.51</v>
       </c>
       <c r="AF37" s="6" t="n">
-        <v>72.36</v>
+        <v>41.72</v>
       </c>
       <c r="AG37" s="6" t="n">
-        <v>72.70999999999999</v>
+        <v>41.58</v>
       </c>
       <c r="AH37" s="6" t="n">
-        <v>71.44</v>
+        <v>40.18</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>422.29</v>
+        <v>499.53</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
       <c r="AK37" s="7" t="inlineStr"/>
@@ -4048,110 +3840,110 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>MANANTIAL FM</t>
+          <t>LIDER FM</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>102.7</v>
+        <v>101.5</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>58.14</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>57.6</v>
+        <v>77.16</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>62.89</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>57.41</v>
+        <v>77.88</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>57.04</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>56.29</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>57.62</v>
+        <v>77.22</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>57.9</v>
+        <v>77.28</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>57.87</v>
+        <v>77.56</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>58.19</v>
+        <v>77.36</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>59.66</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>57.31</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>57.81</v>
+        <v>77.86</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>58.09</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>59.71</v>
+        <v>77.11</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>58.68</v>
+        <v>77.11</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>58.13</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>58.57</v>
+        <v>77.28</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>58.45</v>
+        <v>77.53</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>58.68</v>
+        <v>77.73</v>
       </c>
       <c r="W38" s="6" t="n">
-        <v>58.76</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="X38" s="6" t="n">
-        <v>58.66</v>
+        <v>77.02</v>
       </c>
       <c r="Y38" s="6" t="n">
-        <v>58.76</v>
+        <v>77.03</v>
       </c>
       <c r="Z38" s="6" t="n">
-        <v>56.95</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="AA38" s="6" t="n">
-        <v>58.78</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AB38" s="6" t="n">
-        <v>59.01</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AC38" s="6" t="n">
-        <v>58.66</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="AD38" s="6" t="n">
-        <v>58.24</v>
+        <v>77.84</v>
       </c>
       <c r="AE38" s="6" t="n">
-        <v>58.16</v>
+        <v>78.12</v>
       </c>
       <c r="AF38" s="6" t="n">
-        <v>58.82</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="AG38" s="6" t="n">
-        <v>58.96</v>
+        <v>77.81</v>
       </c>
       <c r="AH38" s="6" t="n">
-        <v>58.38</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>471.03</v>
+        <v>159.74</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
       <c r="AK38" s="7" t="inlineStr"/>
@@ -4159,110 +3951,110 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>J.C. RADIO (NO AUT)</t>
+          <t>RADIO LA VOZ DEL PUEBLO</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>103.1</v>
+        <v>102.3</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>46.72</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>35.76</v>
+        <v>70.63</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>36.4</v>
+        <v>66.64</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>45.76</v>
+        <v>71.08</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>43.98</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>45.91</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>42.62</v>
+        <v>71.13</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>44.54</v>
+        <v>71.28</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>43.32</v>
+        <v>71.3</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>43.78</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>46.12</v>
+        <v>70.84</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>45.71</v>
+        <v>71.38</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>45.21</v>
+        <v>71.52</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>42.01</v>
+        <v>72.11</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>47.36</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>43.31</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>37.48</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>43.12</v>
+        <v>71.37</v>
       </c>
       <c r="U39" s="6" t="n">
-        <v>41.52</v>
+        <v>71.91</v>
       </c>
       <c r="V39" s="6" t="n">
-        <v>42.48</v>
+        <v>72.36</v>
       </c>
       <c r="W39" s="6" t="n">
-        <v>42.72</v>
+        <v>71.31</v>
       </c>
       <c r="X39" s="6" t="n">
-        <v>46.34</v>
+        <v>71.27</v>
       </c>
       <c r="Y39" s="6" t="n">
-        <v>42.01</v>
+        <v>71.64</v>
       </c>
       <c r="Z39" s="6" t="n">
-        <v>40.41</v>
+        <v>71.56</v>
       </c>
       <c r="AA39" s="6" t="n">
-        <v>41.55</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="AB39" s="6" t="n">
-        <v>41.22</v>
+        <v>71.95</v>
       </c>
       <c r="AC39" s="6" t="n">
-        <v>44.88</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="AD39" s="6" t="n">
-        <v>38.64</v>
+        <v>72.06</v>
       </c>
       <c r="AE39" s="6" t="n">
-        <v>41.14</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="AF39" s="6" t="n">
-        <v>47.4</v>
+        <v>72.36</v>
       </c>
       <c r="AG39" s="6" t="n">
-        <v>48.04</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="AH39" s="6" t="n">
-        <v>43.14</v>
+        <v>71.44</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>161.11</v>
+        <v>422.29</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
       <c r="AK39" s="7" t="inlineStr"/>
@@ -4270,110 +4062,110 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>LA MEGA ESTACION (SIS NO AUTORI</t>
+          <t>MANANTIAL FM</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>103.5</v>
+        <v>102.7</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>46.89</v>
+        <v>58.14</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>36.46</v>
+        <v>57.6</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>37.76</v>
+        <v>62.89</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>45.51</v>
+        <v>57.41</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>44.04</v>
+        <v>57.04</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>45.22</v>
+        <v>56.29</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>43.04</v>
+        <v>57.62</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>42.79</v>
+        <v>57.9</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>47.75</v>
+        <v>57.87</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>45.64</v>
+        <v>58.19</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>46.23</v>
+        <v>59.66</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>44.39</v>
+        <v>57.31</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>45.54</v>
+        <v>57.81</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>46.71</v>
+        <v>58.09</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>42.49</v>
+        <v>59.71</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>39.33</v>
+        <v>58.68</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>40.14</v>
+        <v>58.13</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>38.01</v>
+        <v>58.57</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>38.08</v>
+        <v>58.45</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>38.74</v>
+        <v>58.68</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>43.46</v>
+        <v>58.76</v>
       </c>
       <c r="X40" s="6" t="n">
-        <v>46.21</v>
+        <v>58.66</v>
       </c>
       <c r="Y40" s="6" t="n">
-        <v>40.55</v>
+        <v>58.76</v>
       </c>
       <c r="Z40" s="6" t="n">
-        <v>40.41</v>
+        <v>56.95</v>
       </c>
       <c r="AA40" s="6" t="n">
-        <v>36.65</v>
+        <v>58.78</v>
       </c>
       <c r="AB40" s="6" t="n">
-        <v>42.29</v>
+        <v>59.01</v>
       </c>
       <c r="AC40" s="6" t="n">
-        <v>45.95</v>
+        <v>58.66</v>
       </c>
       <c r="AD40" s="6" t="n">
-        <v>43.71</v>
+        <v>58.24</v>
       </c>
       <c r="AE40" s="6" t="n">
-        <v>45.76</v>
+        <v>58.16</v>
       </c>
       <c r="AF40" s="6" t="n">
-        <v>47.26</v>
+        <v>58.82</v>
       </c>
       <c r="AG40" s="6" t="n">
-        <v>44.16</v>
+        <v>58.96</v>
       </c>
       <c r="AH40" s="6" t="n">
-        <v>42.94</v>
+        <v>58.38</v>
       </c>
       <c r="AI40" s="6" t="n">
-        <v>141.85</v>
+        <v>471.03</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
       <c r="AK40" s="7" t="inlineStr"/>
@@ -4381,110 +4173,110 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>LA MEGA ESTACION (SIS NO AUTORI</t>
+          <t>J.C. RADIO (NO AUT)</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>103.7</v>
+        <v>103.1</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>47.79</v>
+        <v>46.72</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>36.54</v>
+        <v>35.76</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>35.36</v>
+        <v>36.4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>39.5</v>
+        <v>45.76</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>39.05</v>
+        <v>43.98</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>44.41</v>
+        <v>45.91</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>42.89</v>
+        <v>42.62</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>45.39</v>
+        <v>44.54</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>46.43</v>
+        <v>43.32</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>44.24</v>
+        <v>43.78</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>46.82</v>
+        <v>46.12</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>43.69</v>
+        <v>45.71</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>48.21</v>
+        <v>45.21</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>47.44</v>
+        <v>42.01</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>43.59</v>
+        <v>47.36</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>39.13</v>
+        <v>43.31</v>
       </c>
       <c r="S41" s="6" t="n">
-        <v>38.44</v>
+        <v>37.48</v>
       </c>
       <c r="T41" s="6" t="n">
-        <v>42</v>
+        <v>43.12</v>
       </c>
       <c r="U41" s="6" t="n">
-        <v>42.06</v>
+        <v>41.52</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>39.01</v>
+        <v>42.48</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>42.07</v>
+        <v>42.72</v>
       </c>
       <c r="X41" s="6" t="n">
-        <v>46.61</v>
+        <v>46.34</v>
       </c>
       <c r="Y41" s="6" t="n">
-        <v>36.92</v>
+        <v>42.01</v>
       </c>
       <c r="Z41" s="6" t="n">
-        <v>37.61</v>
+        <v>40.41</v>
       </c>
       <c r="AA41" s="6" t="n">
-        <v>36.41</v>
+        <v>41.55</v>
       </c>
       <c r="AB41" s="6" t="n">
-        <v>40.19</v>
+        <v>41.22</v>
       </c>
       <c r="AC41" s="6" t="n">
-        <v>39.22</v>
+        <v>44.88</v>
       </c>
       <c r="AD41" s="6" t="n">
-        <v>40.28</v>
+        <v>38.64</v>
       </c>
       <c r="AE41" s="6" t="n">
-        <v>47.26</v>
+        <v>41.14</v>
       </c>
       <c r="AF41" s="6" t="n">
-        <v>46.28</v>
+        <v>47.4</v>
       </c>
       <c r="AG41" s="6" t="n">
-        <v>45.59</v>
+        <v>48.04</v>
       </c>
       <c r="AH41" s="6" t="n">
-        <v>42.27</v>
+        <v>43.14</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>140.45</v>
+        <v>161.11</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
       <c r="AK41" s="7" t="inlineStr"/>
@@ -4492,110 +4284,110 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>ONDAS DEL PACIFICO *MAS CANDELA</t>
+          <t>LA MEGA ESTACION (SIS NO AUTORI</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>103.9</v>
+        <v>103.5</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>77.51000000000001</v>
+        <v>46.89</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>77.72</v>
+        <v>36.46</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>74.59999999999999</v>
+        <v>37.76</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>77.3</v>
+        <v>45.51</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>77.68000000000001</v>
+        <v>44.04</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>78.04000000000001</v>
+        <v>45.22</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>76.72</v>
+        <v>43.04</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>77.09999999999999</v>
+        <v>42.79</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>77.23</v>
+        <v>47.75</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>76.86</v>
+        <v>45.64</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>78.38</v>
+        <v>46.23</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>77.09999999999999</v>
+        <v>44.39</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>78.19</v>
+        <v>45.54</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>77.08</v>
+        <v>46.71</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>77.70999999999999</v>
+        <v>42.49</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>78.08</v>
+        <v>39.33</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>77.56</v>
+        <v>40.14</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>78.36</v>
+        <v>38.01</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>77.41</v>
+        <v>38.08</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>77.61</v>
+        <v>38.74</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>77.5</v>
+        <v>43.46</v>
       </c>
       <c r="X42" s="6" t="n">
-        <v>77.51000000000001</v>
+        <v>46.21</v>
       </c>
       <c r="Y42" s="6" t="n">
-        <v>77.47</v>
+        <v>40.55</v>
       </c>
       <c r="Z42" s="6" t="n">
-        <v>77.18000000000001</v>
+        <v>40.41</v>
       </c>
       <c r="AA42" s="6" t="n">
-        <v>77.81999999999999</v>
+        <v>36.65</v>
       </c>
       <c r="AB42" s="6" t="n">
-        <v>78.15000000000001</v>
+        <v>42.29</v>
       </c>
       <c r="AC42" s="6" t="n">
-        <v>78.34</v>
+        <v>45.95</v>
       </c>
       <c r="AD42" s="6" t="n">
-        <v>77.31</v>
+        <v>43.71</v>
       </c>
       <c r="AE42" s="6" t="n">
-        <v>77.93000000000001</v>
+        <v>45.76</v>
       </c>
       <c r="AF42" s="6" t="n">
-        <v>77.95999999999999</v>
+        <v>47.26</v>
       </c>
       <c r="AG42" s="6" t="n">
-        <v>78.26000000000001</v>
+        <v>44.16</v>
       </c>
       <c r="AH42" s="6" t="n">
-        <v>77.54000000000001</v>
+        <v>42.94</v>
       </c>
       <c r="AI42" s="6" t="n">
-        <v>181.85</v>
+        <v>141.85</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
       <c r="AK42" s="7" t="inlineStr"/>
@@ -4603,110 +4395,110 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>LA VECINA FM</t>
+          <t>LA MEGA ESTACION (SIS NO AUTORI</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>66.14</v>
+        <v>47.79</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>66.64</v>
+        <v>36.54</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>66.44</v>
+        <v>35.36</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>67.09999999999999</v>
+        <v>39.5</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>67.31</v>
+        <v>39.05</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>67.41</v>
+        <v>44.41</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>66.36</v>
+        <v>42.89</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>67.08</v>
+        <v>45.39</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>67.01000000000001</v>
+        <v>46.43</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>66.56999999999999</v>
+        <v>44.24</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>66.58</v>
+        <v>46.82</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>66.59</v>
+        <v>43.69</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>66.29000000000001</v>
+        <v>48.21</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>66.31</v>
+        <v>47.44</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>66.12</v>
+        <v>43.59</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>67.26000000000001</v>
+        <v>39.13</v>
       </c>
       <c r="S43" s="6" t="n">
-        <v>67.55</v>
+        <v>38.44</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>66.61</v>
+        <v>42</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>67.26000000000001</v>
+        <v>42.06</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>67.62</v>
+        <v>39.01</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>67.06</v>
+        <v>42.07</v>
       </c>
       <c r="X43" s="6" t="n">
-        <v>67.76000000000001</v>
+        <v>46.61</v>
       </c>
       <c r="Y43" s="6" t="n">
-        <v>67.22</v>
+        <v>36.92</v>
       </c>
       <c r="Z43" s="6" t="n">
-        <v>66.69</v>
+        <v>37.61</v>
       </c>
       <c r="AA43" s="6" t="n">
-        <v>67</v>
+        <v>36.41</v>
       </c>
       <c r="AB43" s="6" t="n">
-        <v>66.44</v>
+        <v>40.19</v>
       </c>
       <c r="AC43" s="6" t="n">
-        <v>66.86</v>
+        <v>39.22</v>
       </c>
       <c r="AD43" s="6" t="n">
-        <v>66.92</v>
+        <v>40.28</v>
       </c>
       <c r="AE43" s="6" t="n">
-        <v>66.56</v>
+        <v>47.26</v>
       </c>
       <c r="AF43" s="6" t="n">
-        <v>67.11</v>
+        <v>46.28</v>
       </c>
       <c r="AG43" s="6" t="n">
-        <v>66.86</v>
+        <v>45.59</v>
       </c>
       <c r="AH43" s="6" t="n">
-        <v>66.86</v>
+        <v>42.27</v>
       </c>
       <c r="AI43" s="6" t="n">
-        <v>243.9</v>
+        <v>140.45</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
       <c r="AK43" s="7" t="inlineStr"/>
@@ -4714,110 +4506,110 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>MACHALA FM</t>
+          <t>ONDAS DEL PACIFICO *MAS CANDELA</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>104.7</v>
+        <v>103.9</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>70.06</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>71.16</v>
+        <v>77.72</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>66.28</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>69.68000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>69.76000000000001</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>70.01000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>69.19</v>
+        <v>76.72</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>70.18000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>70.44</v>
+        <v>77.23</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>70.5</v>
+        <v>76.86</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>70.22</v>
+        <v>78.38</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>69.84</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>69.81999999999999</v>
+        <v>78.19</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>69.31999999999999</v>
+        <v>77.08</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>70.29000000000001</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>70.84</v>
+        <v>78.08</v>
       </c>
       <c r="S44" s="6" t="n">
-        <v>70.44</v>
+        <v>77.56</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>70.70999999999999</v>
+        <v>78.36</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>70.53</v>
+        <v>77.41</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>70.63</v>
+        <v>77.61</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>70.33</v>
+        <v>77.5</v>
       </c>
       <c r="X44" s="6" t="n">
-        <v>70.08</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="Y44" s="6" t="n">
-        <v>70.14</v>
+        <v>77.47</v>
       </c>
       <c r="Z44" s="6" t="n">
-        <v>69.06</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="AA44" s="6" t="n">
-        <v>70.09999999999999</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="AB44" s="6" t="n">
-        <v>69.51000000000001</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="AC44" s="6" t="n">
-        <v>70.54000000000001</v>
+        <v>78.34</v>
       </c>
       <c r="AD44" s="6" t="n">
-        <v>70.2</v>
+        <v>77.31</v>
       </c>
       <c r="AE44" s="6" t="n">
-        <v>70.81</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="AF44" s="6" t="n">
-        <v>71.68000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="AG44" s="6" t="n">
-        <v>71.01000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="AH44" s="6" t="n">
-        <v>70.11</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="AI44" s="6" t="n">
-        <v>252.32</v>
+        <v>181.85</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
       <c r="AK44" s="7" t="inlineStr"/>
@@ -4825,110 +4617,110 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>GAVIOTA FM STEREO</t>
+          <t>LA VECINA FM</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>105.1</v>
+        <v>104.3</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>80.31999999999999</v>
+        <v>66.14</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>79.70999999999999</v>
+        <v>66.64</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>77.03</v>
+        <v>66.44</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>79.97</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>79.47</v>
+        <v>67.31</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>79.81</v>
+        <v>67.41</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>79.3</v>
+        <v>66.36</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>79.39</v>
+        <v>67.08</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>79.23999999999999</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>79.56</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>80.08</v>
+        <v>66.58</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>79.52</v>
+        <v>66.59</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>79.02</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>79.15000000000001</v>
+        <v>66.31</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>79.28</v>
+        <v>66.12</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>79.69</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="S45" s="6" t="n">
-        <v>79.54000000000001</v>
+        <v>67.55</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>79.36</v>
+        <v>66.61</v>
       </c>
       <c r="U45" s="6" t="n">
-        <v>79.76000000000001</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>79.66</v>
+        <v>67.62</v>
       </c>
       <c r="W45" s="6" t="n">
-        <v>79.83</v>
+        <v>67.06</v>
       </c>
       <c r="X45" s="6" t="n">
-        <v>79.47</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="Y45" s="6" t="n">
-        <v>80.41</v>
+        <v>67.22</v>
       </c>
       <c r="Z45" s="6" t="n">
-        <v>79.79000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="AA45" s="6" t="n">
-        <v>80.11</v>
+        <v>67</v>
       </c>
       <c r="AB45" s="6" t="n">
-        <v>79.79000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="AC45" s="6" t="n">
-        <v>79.66</v>
+        <v>66.86</v>
       </c>
       <c r="AD45" s="6" t="n">
-        <v>79.3</v>
+        <v>66.92</v>
       </c>
       <c r="AE45" s="6" t="n">
-        <v>79.68000000000001</v>
+        <v>66.56</v>
       </c>
       <c r="AF45" s="6" t="n">
-        <v>79.64</v>
+        <v>67.11</v>
       </c>
       <c r="AG45" s="6" t="n">
-        <v>80.06</v>
+        <v>66.86</v>
       </c>
       <c r="AH45" s="6" t="n">
-        <v>79.56999999999999</v>
+        <v>66.86</v>
       </c>
       <c r="AI45" s="6" t="n">
-        <v>254.37</v>
+        <v>243.9</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
       <c r="AK45" s="7" t="inlineStr"/>
@@ -4936,110 +4728,110 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>RADIO FIESTA F.M.</t>
+          <t>MACHALA FM</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>105.5</v>
+        <v>104.7</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>57.51</v>
+        <v>70.06</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>56.33</v>
+        <v>71.16</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>52.45</v>
+        <v>66.28</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>54.84</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>56.89</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>56.58</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>56.42</v>
+        <v>69.19</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>55.91</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>55.03</v>
+        <v>70.44</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>56.9</v>
+        <v>70.5</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>56.44</v>
+        <v>70.22</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>56.82</v>
+        <v>69.84</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>55.44</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>54.61</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>54.7</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>56.19</v>
+        <v>70.84</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>55.34</v>
+        <v>70.44</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>56.69</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>55.47</v>
+        <v>70.53</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>56.24</v>
+        <v>70.63</v>
       </c>
       <c r="W46" s="6" t="n">
-        <v>56.59</v>
+        <v>70.33</v>
       </c>
       <c r="X46" s="6" t="n">
-        <v>55.64</v>
+        <v>70.08</v>
       </c>
       <c r="Y46" s="6" t="n">
-        <v>56.9</v>
+        <v>70.14</v>
       </c>
       <c r="Z46" s="6" t="n">
-        <v>55.12</v>
+        <v>69.06</v>
       </c>
       <c r="AA46" s="6" t="n">
-        <v>55.36</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AB46" s="6" t="n">
-        <v>55.66</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="AC46" s="6" t="n">
-        <v>56.56</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="AD46" s="6" t="n">
-        <v>55.57</v>
+        <v>70.2</v>
       </c>
       <c r="AE46" s="6" t="n">
-        <v>55.86</v>
+        <v>70.81</v>
       </c>
       <c r="AF46" s="6" t="n">
-        <v>56.94</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="AG46" s="6" t="n">
-        <v>55.31</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="AH46" s="6" t="n">
-        <v>55.88</v>
+        <v>70.11</v>
       </c>
       <c r="AI46" s="6" t="n">
-        <v>487.79</v>
+        <v>252.32</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
       <c r="AK46" s="7" t="inlineStr"/>
@@ -5047,110 +4839,110 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>RADIO K1</t>
+          <t>GAVIOTA FM STEREO</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>105.9</v>
+        <v>105.1</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>66.36</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>66.62</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>66.68000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>66.76000000000001</v>
+        <v>79.97</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>66.55</v>
+        <v>79.47</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>66.90000000000001</v>
+        <v>79.81</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>67.11</v>
+        <v>79.3</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>67.22</v>
+        <v>79.39</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>66.48</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>66.77</v>
+        <v>79.56</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>66.68000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>66.81</v>
+        <v>79.52</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>66.81</v>
+        <v>79.02</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>67.01000000000001</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>66.45999999999999</v>
+        <v>79.28</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>66.86</v>
+        <v>79.69</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>66.98</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>66.95999999999999</v>
+        <v>79.36</v>
       </c>
       <c r="U47" s="6" t="n">
-        <v>67.08</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>66.89</v>
+        <v>79.66</v>
       </c>
       <c r="W47" s="6" t="n">
-        <v>67.59</v>
+        <v>79.83</v>
       </c>
       <c r="X47" s="6" t="n">
-        <v>67.19</v>
+        <v>79.47</v>
       </c>
       <c r="Y47" s="6" t="n">
-        <v>66.66</v>
+        <v>80.41</v>
       </c>
       <c r="Z47" s="6" t="n">
-        <v>67.11</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="AA47" s="6" t="n">
-        <v>66.53</v>
+        <v>80.11</v>
       </c>
       <c r="AB47" s="6" t="n">
-        <v>66.53</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="AC47" s="6" t="n">
-        <v>67.18000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="AD47" s="6" t="n">
-        <v>66.62</v>
+        <v>79.3</v>
       </c>
       <c r="AE47" s="6" t="n">
-        <v>67.23999999999999</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="AF47" s="6" t="n">
-        <v>67.06</v>
+        <v>79.64</v>
       </c>
       <c r="AG47" s="6" t="n">
-        <v>66.27</v>
+        <v>80.06</v>
       </c>
       <c r="AH47" s="6" t="n">
-        <v>66.84</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="AI47" s="6" t="n">
-        <v>385.5</v>
+        <v>254.37</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
       <c r="AK47" s="7" t="inlineStr"/>
@@ -5158,110 +4950,110 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>LA COQUETA</t>
+          <t>RADIO FIESTA F.M.</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>106.3</v>
+        <v>105.5</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>73.01000000000001</v>
+        <v>57.51</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>72.91</v>
+        <v>56.33</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>71.3</v>
+        <v>52.45</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>73.45999999999999</v>
+        <v>54.84</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>73.98999999999999</v>
+        <v>56.89</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>73.91</v>
+        <v>56.58</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>74.38</v>
+        <v>56.42</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>74.19</v>
+        <v>55.91</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>73.87</v>
+        <v>55.03</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>74.20999999999999</v>
+        <v>56.9</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>74.53</v>
+        <v>56.44</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>74.2</v>
+        <v>56.82</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>73.95999999999999</v>
+        <v>55.44</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>73.73999999999999</v>
+        <v>54.61</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>74.29000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>73.86</v>
+        <v>56.19</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>73.61</v>
+        <v>55.34</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>73.37</v>
+        <v>56.69</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>74.39</v>
+        <v>55.47</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>73.94</v>
+        <v>56.24</v>
       </c>
       <c r="W48" s="6" t="n">
-        <v>74.06</v>
+        <v>56.59</v>
       </c>
       <c r="X48" s="6" t="n">
-        <v>74.12</v>
+        <v>55.64</v>
       </c>
       <c r="Y48" s="6" t="n">
-        <v>74.31999999999999</v>
+        <v>56.9</v>
       </c>
       <c r="Z48" s="6" t="n">
-        <v>74.15000000000001</v>
+        <v>55.12</v>
       </c>
       <c r="AA48" s="6" t="n">
-        <v>73.75</v>
+        <v>55.36</v>
       </c>
       <c r="AB48" s="6" t="n">
-        <v>74.08</v>
+        <v>55.66</v>
       </c>
       <c r="AC48" s="6" t="n">
-        <v>74.33</v>
+        <v>56.56</v>
       </c>
       <c r="AD48" s="6" t="n">
-        <v>73.81999999999999</v>
+        <v>55.57</v>
       </c>
       <c r="AE48" s="6" t="n">
-        <v>73.87</v>
+        <v>55.86</v>
       </c>
       <c r="AF48" s="6" t="n">
-        <v>73.78</v>
+        <v>56.94</v>
       </c>
       <c r="AG48" s="6" t="n">
-        <v>73.59</v>
+        <v>55.31</v>
       </c>
       <c r="AH48" s="6" t="n">
-        <v>73.84</v>
+        <v>55.88</v>
       </c>
       <c r="AI48" s="6" t="n">
-        <v>236.24</v>
+        <v>487.79</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
       <c r="AK48" s="7" t="inlineStr"/>
@@ -5269,722 +5061,726 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>RADIO PÚBLICA EL GUABO 106.7 FM</t>
+          <t>RADIO K1</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>106.7</v>
+        <v>105.9</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>45.59</v>
+        <v>66.36</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>44.29</v>
+        <v>66.62</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>45.42</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>45.54</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>45.36</v>
+        <v>66.55</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>44.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>45.04</v>
+        <v>67.11</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>45.04</v>
+        <v>67.22</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>45.84</v>
+        <v>66.48</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>43.74</v>
+        <v>66.77</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>44.87</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>45.91</v>
+        <v>66.81</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>45.61</v>
+        <v>66.81</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>45.42</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>45.88</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>45.66</v>
+        <v>66.86</v>
       </c>
       <c r="S49" s="6" t="n">
-        <v>45.7</v>
+        <v>66.98</v>
       </c>
       <c r="T49" s="6" t="n">
-        <v>46.39</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="U49" s="6" t="n">
-        <v>45.44</v>
+        <v>67.08</v>
       </c>
       <c r="V49" s="6" t="n">
-        <v>43.86</v>
+        <v>66.89</v>
       </c>
       <c r="W49" s="6" t="n">
-        <v>44.56</v>
+        <v>67.59</v>
       </c>
       <c r="X49" s="6" t="n">
-        <v>44.54</v>
+        <v>67.19</v>
       </c>
       <c r="Y49" s="6" t="n">
-        <v>44.78</v>
+        <v>66.66</v>
       </c>
       <c r="Z49" s="6" t="n">
-        <v>43.79</v>
+        <v>67.11</v>
       </c>
       <c r="AA49" s="6" t="n">
-        <v>45.58</v>
+        <v>66.53</v>
       </c>
       <c r="AB49" s="6" t="n">
-        <v>43.16</v>
+        <v>66.53</v>
       </c>
       <c r="AC49" s="6" t="n">
-        <v>43.36</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="AD49" s="6" t="n">
-        <v>44.17</v>
+        <v>66.62</v>
       </c>
       <c r="AE49" s="6" t="n">
-        <v>46.02</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="AF49" s="6" t="n">
-        <v>45.81</v>
+        <v>67.06</v>
       </c>
       <c r="AG49" s="6" t="n">
-        <v>44.48</v>
+        <v>66.27</v>
       </c>
       <c r="AH49" s="6" t="n">
-        <v>45</v>
+        <v>66.84</v>
       </c>
       <c r="AI49" s="6" t="n">
-        <v>468.87</v>
+        <v>385.5</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
       <c r="AK49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>LA COQUETA</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>72.91</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>73.91</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>74.20999999999999</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v>73.61</v>
+      </c>
+      <c r="T50" s="6" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="U50" s="6" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="V50" s="6" t="n">
+        <v>73.94</v>
+      </c>
+      <c r="W50" s="6" t="n">
+        <v>74.06</v>
+      </c>
+      <c r="X50" s="6" t="n">
+        <v>74.12</v>
+      </c>
+      <c r="Y50" s="6" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="Z50" s="6" t="n">
+        <v>74.15000000000001</v>
+      </c>
+      <c r="AA50" s="6" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AB50" s="6" t="n">
+        <v>74.08</v>
+      </c>
+      <c r="AC50" s="6" t="n">
+        <v>74.33</v>
+      </c>
+      <c r="AD50" s="6" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="AE50" s="6" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="AF50" s="6" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="AG50" s="6" t="n">
+        <v>73.59</v>
+      </c>
+      <c r="AH50" s="6" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="AI50" s="6" t="n">
+        <v>236.24</v>
+      </c>
+      <c r="AJ50" s="6" t="inlineStr"/>
+      <c r="AK50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>RADIO PÚBLICA EL GUABO 106.7 FM</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>45.61</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="S51" s="6" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="T51" s="6" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="U51" s="6" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="V51" s="6" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="W51" s="6" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="X51" s="6" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="Y51" s="6" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="Z51" s="6" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="AA51" s="6" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="AB51" s="6" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="AC51" s="6" t="n">
+        <v>43.36</v>
+      </c>
+      <c r="AD51" s="6" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="AE51" s="6" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="AF51" s="6" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="AG51" s="6" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="AH51" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI51" s="6" t="n">
+        <v>468.87</v>
+      </c>
+      <c r="AJ51" s="6" t="inlineStr"/>
+      <c r="AK51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>GENESIS FM STEREO</t>
         </is>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B52" s="9" t="n">
         <v>107.5</v>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C52" s="9" t="n">
         <v>45.55</v>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="D52" s="9" t="n">
         <v>45.58</v>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="E52" s="9" t="n">
         <v>46.18</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F52" s="9" t="n">
         <v>45.65</v>
       </c>
-      <c r="G50" s="9" t="n">
+      <c r="G52" s="9" t="n">
         <v>47.34</v>
       </c>
-      <c r="H50" s="9" t="n">
+      <c r="H52" s="9" t="n">
         <v>47.62</v>
       </c>
-      <c r="I50" s="9" t="n">
+      <c r="I52" s="9" t="n">
         <v>46.46</v>
       </c>
-      <c r="J50" s="9" t="n">
+      <c r="J52" s="9" t="n">
         <v>45.94</v>
       </c>
-      <c r="K50" s="9" t="n">
+      <c r="K52" s="9" t="n">
         <v>45.49</v>
       </c>
-      <c r="L50" s="9" t="n">
+      <c r="L52" s="9" t="n">
         <v>45.62</v>
       </c>
-      <c r="M50" s="9" t="n">
+      <c r="M52" s="9" t="n">
         <v>46.22</v>
       </c>
-      <c r="N50" s="9" t="n">
+      <c r="N52" s="9" t="n">
         <v>47.42</v>
       </c>
-      <c r="O50" s="9" t="n">
+      <c r="O52" s="9" t="n">
         <v>46.59</v>
       </c>
-      <c r="P50" s="9" t="n">
+      <c r="P52" s="9" t="n">
         <v>46.35</v>
       </c>
-      <c r="Q50" s="9" t="n">
+      <c r="Q52" s="9" t="n">
         <v>46.21</v>
       </c>
-      <c r="R50" s="9" t="n">
+      <c r="R52" s="9" t="n">
         <v>46.19</v>
       </c>
-      <c r="S50" s="9" t="n">
+      <c r="S52" s="9" t="n">
         <v>47.04</v>
       </c>
-      <c r="T50" s="9" t="n">
+      <c r="T52" s="9" t="n">
         <v>45.74</v>
       </c>
-      <c r="U50" s="9" t="n">
+      <c r="U52" s="9" t="n">
         <v>45.27</v>
       </c>
-      <c r="V50" s="9" t="n">
+      <c r="V52" s="9" t="n">
         <v>45.62</v>
       </c>
-      <c r="W50" s="9" t="n">
+      <c r="W52" s="9" t="n">
         <v>44.74</v>
       </c>
-      <c r="X50" s="9" t="n">
+      <c r="X52" s="9" t="n">
         <v>49.16</v>
       </c>
-      <c r="Y50" s="9" t="n">
+      <c r="Y52" s="9" t="n">
         <v>46.34</v>
       </c>
-      <c r="Z50" s="9" t="n">
+      <c r="Z52" s="9" t="n">
         <v>45.4</v>
       </c>
-      <c r="AA50" s="9" t="n">
+      <c r="AA52" s="9" t="n">
         <v>45.42</v>
       </c>
-      <c r="AB50" s="9" t="n">
+      <c r="AB52" s="9" t="n">
         <v>47.13</v>
       </c>
-      <c r="AC50" s="9" t="n">
+      <c r="AC52" s="9" t="n">
         <v>45.49</v>
       </c>
-      <c r="AD50" s="9" t="n">
+      <c r="AD52" s="9" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE50" s="9" t="n">
+      <c r="AE52" s="9" t="n">
         <v>46.79</v>
       </c>
-      <c r="AF50" s="9" t="n">
+      <c r="AF52" s="9" t="n">
         <v>47.06</v>
       </c>
-      <c r="AG50" s="9" t="n">
+      <c r="AG52" s="9" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH50" s="9" t="n">
+      <c r="AH52" s="9" t="n">
         <v>46.28</v>
       </c>
-      <c r="AI50" s="9" t="n">
+      <c r="AI52" s="9" t="n">
         <v>497.9</v>
       </c>
-      <c r="AJ50" s="9" t="inlineStr"/>
-      <c r="AK50" s="10" t="inlineStr"/>
-    </row>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>COORDINACIÓN ZONAL 6</t>
-        </is>
-      </c>
-    </row>
+      <c r="AJ52" s="9" t="inlineStr"/>
+      <c r="AK52" s="10" t="inlineStr"/>
+    </row>
+    <row r="53"/>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:MACHALA</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:MACHALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Frecuencia (MHz)</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C62" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D62" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E62" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F62" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G62" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="H62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I62" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="J62" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K62" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L60" s="3" t="n">
+      <c r="L62" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M60" s="3" t="n">
+      <c r="M62" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="N62" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O60" s="3" t="n">
+      <c r="O62" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P60" s="3" t="n">
+      <c r="P62" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q60" s="3" t="n">
+      <c r="Q62" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R60" s="3" t="n">
+      <c r="R62" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S60" s="3" t="n">
+      <c r="S62" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T60" s="3" t="n">
+      <c r="T62" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U60" s="3" t="n">
+      <c r="U62" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V60" s="3" t="n">
+      <c r="V62" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W60" s="3" t="n">
+      <c r="W62" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X60" s="3" t="n">
+      <c r="X62" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y60" s="3" t="n">
+      <c r="Y62" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z60" s="3" t="n">
+      <c r="Z62" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA60" s="3" t="n">
+      <c r="AA62" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB60" s="3" t="n">
+      <c r="AB62" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC60" s="3" t="n">
+      <c r="AC62" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD60" s="3" t="n">
+      <c r="AD62" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE60" s="3" t="n">
+      <c r="AE62" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF60" s="3" t="n">
+      <c r="AF62" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG60" s="3" t="n">
+      <c r="AG62" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH60" s="3" t="inlineStr">
+      <c r="AH62" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI60" s="3" t="inlineStr">
+      <c r="AI62" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AJ60" s="3" t="inlineStr">
+      <c r="AJ62" s="3" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>RED TELESISTEMA (R.T.S)</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>64.05</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>63.56</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>63.48</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>64.12</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>64.53</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>64.03</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>63.63</v>
-      </c>
-      <c r="L61" s="6" t="n">
-        <v>63.38</v>
-      </c>
-      <c r="M61" s="6" t="n">
-        <v>63.85</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>63.69</v>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="S61" s="6" t="n">
-        <v>62.96</v>
-      </c>
-      <c r="T61" s="6" t="n">
-        <v>62.88</v>
-      </c>
-      <c r="U61" s="6" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="V61" s="6" t="n">
-        <v>62.84</v>
-      </c>
-      <c r="W61" s="6" t="n">
-        <v>62.69</v>
-      </c>
-      <c r="X61" s="6" t="n">
-        <v>62.51</v>
-      </c>
-      <c r="Y61" s="6" t="n">
-        <v>62.42</v>
-      </c>
-      <c r="Z61" s="6" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="AA61" s="6" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="AB61" s="6" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="AC61" s="6" t="n">
-        <v>64.26000000000001</v>
-      </c>
-      <c r="AD61" s="6" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="AE61" s="6" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="AF61" s="6" t="n">
-        <v>63.14</v>
-      </c>
-      <c r="AG61" s="6" t="n">
-        <v>63.04</v>
-      </c>
-      <c r="AH61" s="6" t="n">
-        <v>63.58</v>
-      </c>
-      <c r="AI61" s="6" t="inlineStr"/>
-      <c r="AJ61" s="6" t="inlineStr"/>
-      <c r="AK61" s="7" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>TELERAMA</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="C62" s="6" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="E62" s="6" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>35.95</v>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="I62" s="6" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>36.34</v>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="L62" s="6" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="M62" s="6" t="n">
-        <v>35.95</v>
-      </c>
-      <c r="N62" s="6" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="O62" s="6" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v>37.15</v>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="S62" s="6" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="T62" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="U62" s="6" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="V62" s="6" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="W62" s="6" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="X62" s="6" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="Y62" s="6" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="Z62" s="6" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="AA62" s="6" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="AB62" s="6" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AC62" s="6" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="AD62" s="6" t="n">
-        <v>37.56</v>
-      </c>
-      <c r="AE62" s="6" t="n">
-        <v>38.91</v>
-      </c>
-      <c r="AF62" s="6" t="n">
-        <v>36.38</v>
-      </c>
-      <c r="AG62" s="6" t="n">
-        <v>37.45</v>
-      </c>
-      <c r="AH62" s="6" t="n">
-        <v>37.24</v>
-      </c>
-      <c r="AI62" s="6" t="inlineStr"/>
-      <c r="AJ62" s="6" t="inlineStr"/>
-      <c r="AK62" s="7" t="n"/>
+      <c r="AK62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>ECUADOR TV</t>
+          <t>RED TELESISTEMA (R.T.S)</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>175.25</v>
+        <v>61.25</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>39.7</v>
+        <v>64.05</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>37.34</v>
+        <v>63.56</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>38.12</v>
+        <v>64.08</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>37.12</v>
+        <v>63.48</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>38.33</v>
+        <v>64.12</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>39.69</v>
+        <v>64.53</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>42.09</v>
+        <v>64.03</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>42.04</v>
+        <v>63.8</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>38.28</v>
+        <v>63.63</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>41.34</v>
+        <v>63.38</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>41.94</v>
+        <v>63.85</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>40.49</v>
+        <v>63.69</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>38.61</v>
+        <v>63.81</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>37.79</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>37.79</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R63" s="6" t="n">
-        <v>36.92</v>
+        <v>63.94</v>
       </c>
       <c r="S63" s="6" t="n">
-        <v>38.35</v>
+        <v>62.96</v>
       </c>
       <c r="T63" s="6" t="n">
-        <v>36.67</v>
+        <v>62.88</v>
       </c>
       <c r="U63" s="6" t="n">
-        <v>36.88</v>
+        <v>62.7</v>
       </c>
       <c r="V63" s="6" t="n">
-        <v>37.59</v>
+        <v>62.84</v>
       </c>
       <c r="W63" s="6" t="n">
-        <v>37.49</v>
+        <v>62.69</v>
       </c>
       <c r="X63" s="6" t="n">
-        <v>40.59</v>
+        <v>62.51</v>
       </c>
       <c r="Y63" s="6" t="n">
-        <v>42.94</v>
+        <v>62.42</v>
       </c>
       <c r="Z63" s="6" t="n">
-        <v>38.3</v>
+        <v>63.88</v>
       </c>
       <c r="AA63" s="6" t="n">
-        <v>36.58</v>
+        <v>63.6</v>
       </c>
       <c r="AB63" s="6" t="n">
-        <v>43.08</v>
+        <v>64.08</v>
       </c>
       <c r="AC63" s="6" t="n">
-        <v>39.4</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="AD63" s="6" t="n">
-        <v>37.41</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="AE63" s="6" t="n">
-        <v>37.99</v>
+        <v>63.49</v>
       </c>
       <c r="AF63" s="6" t="n">
-        <v>41.21</v>
+        <v>63.14</v>
       </c>
       <c r="AG63" s="6" t="n">
-        <v>37.2</v>
+        <v>63.04</v>
       </c>
       <c r="AH63" s="6" t="n">
-        <v>39.01</v>
+        <v>63.58</v>
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
@@ -5993,107 +5789,107 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>CORPORACIÓN ECUATORIANA</t>
+          <t>TELERAMA</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>181.25</v>
+        <v>83.25</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>77.92</v>
+        <v>37.2</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>77.51000000000001</v>
+        <v>37.1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>77.88</v>
+        <v>36.25</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>76.68000000000001</v>
+        <v>35.95</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>77.39</v>
+        <v>38.22</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>77.95</v>
+        <v>35.83</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>77.47</v>
+        <v>38.13</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>77.65000000000001</v>
+        <v>36.34</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>77.83</v>
+        <v>37.93</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>77.78</v>
+        <v>37.71</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>77.59</v>
+        <v>35.95</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>77.76000000000001</v>
+        <v>35.99</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>77.22</v>
+        <v>38.22</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>77.45</v>
+        <v>37.3</v>
       </c>
       <c r="Q64" s="6" t="n">
-        <v>77.72</v>
+        <v>37.15</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>77.34</v>
+        <v>37.29</v>
       </c>
       <c r="S64" s="6" t="n">
-        <v>77.19</v>
+        <v>38.9</v>
       </c>
       <c r="T64" s="6" t="n">
-        <v>77.66</v>
+        <v>38</v>
       </c>
       <c r="U64" s="6" t="n">
-        <v>77.62</v>
+        <v>37.5</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>77.40000000000001</v>
+        <v>36.25</v>
       </c>
       <c r="W64" s="6" t="n">
-        <v>77.11</v>
+        <v>36.9</v>
       </c>
       <c r="X64" s="6" t="n">
-        <v>76.81</v>
+        <v>36.92</v>
       </c>
       <c r="Y64" s="6" t="n">
-        <v>77.45999999999999</v>
+        <v>35.42</v>
       </c>
       <c r="Z64" s="6" t="n">
-        <v>77.7</v>
+        <v>38.12</v>
       </c>
       <c r="AA64" s="6" t="n">
-        <v>77.28</v>
+        <v>37.35</v>
       </c>
       <c r="AB64" s="6" t="n">
-        <v>77.31</v>
+        <v>38.41</v>
       </c>
       <c r="AC64" s="6" t="n">
-        <v>77.28</v>
+        <v>37.71</v>
       </c>
       <c r="AD64" s="6" t="n">
-        <v>77.45999999999999</v>
+        <v>37.56</v>
       </c>
       <c r="AE64" s="6" t="n">
-        <v>77.23</v>
+        <v>38.91</v>
       </c>
       <c r="AF64" s="6" t="n">
-        <v>77.73999999999999</v>
+        <v>36.38</v>
       </c>
       <c r="AG64" s="6" t="n">
-        <v>77.44</v>
+        <v>37.45</v>
       </c>
       <c r="AH64" s="6" t="n">
-        <v>77.48</v>
+        <v>37.24</v>
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
@@ -6102,107 +5898,107 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TELEVISION DEL PACIFICO</t>
+          <t>ECUADOR TV</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>187.25</v>
+        <v>175.25</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>40.3</v>
+        <v>39.7</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>41.59</v>
+        <v>37.34</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>38.95</v>
+        <v>38.12</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>40.75</v>
+        <v>37.12</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>41.29</v>
+        <v>38.33</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>40.61</v>
+        <v>39.69</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>40.69</v>
+        <v>42.09</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>43.48</v>
+        <v>42.04</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>41.87</v>
+        <v>38.28</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>41.22</v>
+        <v>41.34</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>40.41</v>
+        <v>41.94</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>41.46</v>
+        <v>40.49</v>
       </c>
       <c r="O65" s="6" t="n">
-        <v>40.07</v>
+        <v>38.61</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>40.54</v>
+        <v>37.79</v>
       </c>
       <c r="Q65" s="6" t="n">
-        <v>40.48</v>
+        <v>37.79</v>
       </c>
       <c r="R65" s="6" t="n">
-        <v>41.38</v>
+        <v>36.92</v>
       </c>
       <c r="S65" s="6" t="n">
-        <v>41.15</v>
+        <v>38.35</v>
       </c>
       <c r="T65" s="6" t="n">
-        <v>39.41</v>
+        <v>36.67</v>
       </c>
       <c r="U65" s="6" t="n">
-        <v>39.12</v>
+        <v>36.88</v>
       </c>
       <c r="V65" s="6" t="n">
-        <v>40.48</v>
+        <v>37.59</v>
       </c>
       <c r="W65" s="6" t="n">
-        <v>40.44</v>
+        <v>37.49</v>
       </c>
       <c r="X65" s="6" t="n">
-        <v>40.11</v>
+        <v>40.59</v>
       </c>
       <c r="Y65" s="6" t="n">
-        <v>38.81</v>
+        <v>42.94</v>
       </c>
       <c r="Z65" s="6" t="n">
-        <v>40.83</v>
+        <v>38.3</v>
       </c>
       <c r="AA65" s="6" t="n">
-        <v>39.05</v>
+        <v>36.58</v>
       </c>
       <c r="AB65" s="6" t="n">
-        <v>39.54</v>
+        <v>43.08</v>
       </c>
       <c r="AC65" s="6" t="n">
-        <v>38.81</v>
+        <v>39.4</v>
       </c>
       <c r="AD65" s="6" t="n">
-        <v>39.5</v>
+        <v>37.41</v>
       </c>
       <c r="AE65" s="6" t="n">
-        <v>40.44</v>
+        <v>37.99</v>
       </c>
       <c r="AF65" s="6" t="n">
-        <v>40.04</v>
+        <v>41.21</v>
       </c>
       <c r="AG65" s="6" t="n">
-        <v>39.62</v>
+        <v>37.2</v>
       </c>
       <c r="AH65" s="6" t="n">
-        <v>40.4</v>
+        <v>39.01</v>
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
@@ -6211,107 +6007,107 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>TELEAMAZONAS</t>
+          <t>CORPORACIÓN ECUATORIANA</t>
         </is>
       </c>
       <c r="B66" s="6" t="n">
-        <v>199.25</v>
+        <v>181.25</v>
       </c>
       <c r="C66" s="6" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>77.39</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>77.47</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="L66" s="6" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="M66" s="6" t="n">
+        <v>77.59</v>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="O66" s="6" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="P66" s="6" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="Q66" s="6" t="n">
         <v>77.72</v>
       </c>
-      <c r="D66" s="6" t="n">
-        <v>78.01000000000001</v>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>77.81999999999999</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>78.12</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>78.11</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="I66" s="6" t="n">
-        <v>78.06</v>
-      </c>
-      <c r="J66" s="6" t="n">
-        <v>78.15000000000001</v>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="L66" s="6" t="n">
-        <v>78.45</v>
-      </c>
-      <c r="M66" s="6" t="n">
-        <v>78.76000000000001</v>
-      </c>
-      <c r="N66" s="6" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="O66" s="6" t="n">
-        <v>77.97</v>
-      </c>
-      <c r="P66" s="6" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="Q66" s="6" t="n">
-        <v>78.45999999999999</v>
-      </c>
       <c r="R66" s="6" t="n">
-        <v>78.12</v>
+        <v>77.34</v>
       </c>
       <c r="S66" s="6" t="n">
-        <v>77.81999999999999</v>
+        <v>77.19</v>
       </c>
       <c r="T66" s="6" t="n">
-        <v>78.47</v>
+        <v>77.66</v>
       </c>
       <c r="U66" s="6" t="n">
-        <v>78.36</v>
+        <v>77.62</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>78.39</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="W66" s="6" t="n">
-        <v>78.31</v>
+        <v>77.11</v>
       </c>
       <c r="X66" s="6" t="n">
-        <v>77.81999999999999</v>
+        <v>76.81</v>
       </c>
       <c r="Y66" s="6" t="n">
-        <v>78.40000000000001</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="Z66" s="6" t="n">
-        <v>78.55</v>
+        <v>77.7</v>
       </c>
       <c r="AA66" s="6" t="n">
-        <v>78.40000000000001</v>
+        <v>77.28</v>
       </c>
       <c r="AB66" s="6" t="n">
-        <v>78.45</v>
+        <v>77.31</v>
       </c>
       <c r="AC66" s="6" t="n">
-        <v>78.31</v>
+        <v>77.28</v>
       </c>
       <c r="AD66" s="6" t="n">
-        <v>78.41</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="AE66" s="6" t="n">
-        <v>77.87</v>
+        <v>77.23</v>
       </c>
       <c r="AF66" s="6" t="n">
-        <v>78.44</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="AG66" s="6" t="n">
-        <v>78.26000000000001</v>
+        <v>77.44</v>
       </c>
       <c r="AH66" s="6" t="n">
-        <v>78.28</v>
+        <v>77.48</v>
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
@@ -6320,107 +6116,107 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>CADENA ECUATORIANA DE TEL</t>
+          <t>TELEVISION DEL PACIFICO</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>211.25</v>
+        <v>187.25</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>72.53</v>
+        <v>40.3</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>72.84</v>
+        <v>41.59</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>73.08</v>
+        <v>38.95</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>72.03</v>
+        <v>40.75</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>72.42</v>
+        <v>41.29</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>72.61</v>
+        <v>40.61</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>72.16</v>
+        <v>40.69</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>72.28</v>
+        <v>43.48</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>72.98</v>
+        <v>41.87</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>72.66</v>
+        <v>41.22</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>72.59999999999999</v>
+        <v>40.41</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>72.76000000000001</v>
+        <v>41.46</v>
       </c>
       <c r="O67" s="6" t="n">
-        <v>71.54000000000001</v>
+        <v>40.07</v>
       </c>
       <c r="P67" s="6" t="n">
-        <v>72.36</v>
+        <v>40.54</v>
       </c>
       <c r="Q67" s="6" t="n">
-        <v>72.65000000000001</v>
+        <v>40.48</v>
       </c>
       <c r="R67" s="6" t="n">
-        <v>72.38</v>
+        <v>41.38</v>
       </c>
       <c r="S67" s="6" t="n">
-        <v>72.12</v>
+        <v>41.15</v>
       </c>
       <c r="T67" s="6" t="n">
-        <v>72.94</v>
+        <v>39.41</v>
       </c>
       <c r="U67" s="6" t="n">
-        <v>72.81</v>
+        <v>39.12</v>
       </c>
       <c r="V67" s="6" t="n">
-        <v>72.56</v>
+        <v>40.48</v>
       </c>
       <c r="W67" s="6" t="n">
-        <v>72.27</v>
+        <v>40.44</v>
       </c>
       <c r="X67" s="6" t="n">
-        <v>72.03</v>
+        <v>40.11</v>
       </c>
       <c r="Y67" s="6" t="n">
-        <v>72.51000000000001</v>
+        <v>38.81</v>
       </c>
       <c r="Z67" s="6" t="n">
-        <v>72.88</v>
+        <v>40.83</v>
       </c>
       <c r="AA67" s="6" t="n">
-        <v>72.31999999999999</v>
+        <v>39.05</v>
       </c>
       <c r="AB67" s="6" t="n">
-        <v>72.3</v>
+        <v>39.54</v>
       </c>
       <c r="AC67" s="6" t="n">
-        <v>72.70999999999999</v>
+        <v>38.81</v>
       </c>
       <c r="AD67" s="6" t="n">
-        <v>72.77</v>
+        <v>39.5</v>
       </c>
       <c r="AE67" s="6" t="n">
-        <v>72.26000000000001</v>
+        <v>40.44</v>
       </c>
       <c r="AF67" s="6" t="n">
-        <v>72.72</v>
+        <v>40.04</v>
       </c>
       <c r="AG67" s="6" t="n">
-        <v>72.59999999999999</v>
+        <v>39.62</v>
       </c>
       <c r="AH67" s="6" t="n">
-        <v>72.51000000000001</v>
+        <v>40.4</v>
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
@@ -6429,107 +6225,107 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>OK TV-TEVECORP</t>
+          <t>TELEAMAZONAS</t>
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>549.25</v>
+        <v>199.25</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>31.82</v>
+        <v>77.72</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>34.01</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>31.3</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>31.78</v>
+        <v>78.12</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>31.44</v>
+        <v>78.11</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>31.81</v>
+        <v>78.5</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>31.13</v>
+        <v>78.06</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>32.33</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>31.17</v>
+        <v>78.7</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>30.91</v>
+        <v>78.45</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>31.56</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>31.3</v>
+        <v>78.95</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>31.59</v>
+        <v>77.97</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>31.9</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q68" s="6" t="n">
-        <v>31.52</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="R68" s="6" t="n">
-        <v>31.22</v>
+        <v>78.12</v>
       </c>
       <c r="S68" s="6" t="n">
-        <v>31.62</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="T68" s="6" t="n">
-        <v>31.62</v>
+        <v>78.47</v>
       </c>
       <c r="U68" s="6" t="n">
-        <v>31.75</v>
+        <v>78.36</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>32.01</v>
+        <v>78.39</v>
       </c>
       <c r="W68" s="6" t="n">
-        <v>32.09</v>
+        <v>78.31</v>
       </c>
       <c r="X68" s="6" t="n">
-        <v>32.17</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="Y68" s="6" t="n">
-        <v>31.41</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z68" s="6" t="n">
-        <v>31.92</v>
+        <v>78.55</v>
       </c>
       <c r="AA68" s="6" t="n">
-        <v>34.1</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AB68" s="6" t="n">
-        <v>31.28</v>
+        <v>78.45</v>
       </c>
       <c r="AC68" s="6" t="n">
-        <v>31.6</v>
+        <v>78.31</v>
       </c>
       <c r="AD68" s="6" t="n">
-        <v>32.31</v>
+        <v>78.41</v>
       </c>
       <c r="AE68" s="6" t="n">
-        <v>32.11</v>
+        <v>77.87</v>
       </c>
       <c r="AF68" s="6" t="n">
-        <v>31.26</v>
+        <v>78.44</v>
       </c>
       <c r="AG68" s="6" t="n">
-        <v>32.11</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="AH68" s="6" t="n">
-        <v>31.81</v>
+        <v>78.28</v>
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
@@ -6538,107 +6334,107 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>CANAL UNO no</t>
+          <t>CADENA ECUATORIANA DE TEL</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>573.25</v>
+        <v>211.25</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>30.1</v>
+        <v>72.53</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>31.2</v>
+        <v>72.84</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>29.72</v>
+        <v>73.08</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>30.8</v>
+        <v>72.03</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>31.7</v>
+        <v>72.42</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>29.91</v>
+        <v>72.61</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>30.73</v>
+        <v>72.16</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>34.14</v>
+        <v>72.28</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>30.47</v>
+        <v>72.98</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>32.12</v>
+        <v>72.66</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>29.9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>30.12</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="O69" s="6" t="n">
-        <v>29.56</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>30.11</v>
+        <v>72.36</v>
       </c>
       <c r="Q69" s="6" t="n">
-        <v>31.05</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="R69" s="6" t="n">
-        <v>29.82</v>
+        <v>72.38</v>
       </c>
       <c r="S69" s="6" t="n">
-        <v>30.34</v>
+        <v>72.12</v>
       </c>
       <c r="T69" s="6" t="n">
-        <v>29.44</v>
+        <v>72.94</v>
       </c>
       <c r="U69" s="6" t="n">
-        <v>29.68</v>
+        <v>72.81</v>
       </c>
       <c r="V69" s="6" t="n">
-        <v>29.7</v>
+        <v>72.56</v>
       </c>
       <c r="W69" s="6" t="n">
-        <v>29.73</v>
+        <v>72.27</v>
       </c>
       <c r="X69" s="6" t="n">
-        <v>31.34</v>
+        <v>72.03</v>
       </c>
       <c r="Y69" s="6" t="n">
-        <v>34.96</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="Z69" s="6" t="n">
-        <v>29.62</v>
+        <v>72.88</v>
       </c>
       <c r="AA69" s="6" t="n">
-        <v>29.48</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="AB69" s="6" t="n">
-        <v>29.66</v>
+        <v>72.3</v>
       </c>
       <c r="AC69" s="6" t="n">
-        <v>29.65</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="AD69" s="6" t="n">
-        <v>29.81</v>
+        <v>72.77</v>
       </c>
       <c r="AE69" s="6" t="n">
-        <v>29.57</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AF69" s="6" t="n">
-        <v>29.62</v>
+        <v>72.72</v>
       </c>
       <c r="AG69" s="6" t="n">
-        <v>32.01</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AH69" s="6" t="n">
-        <v>30.52</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
@@ -6647,107 +6443,107 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>TELEATAHUALPA (RTU)</t>
+          <t>OK TV-TEVECORP</t>
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>585.25</v>
+        <v>549.25</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>33.38</v>
+        <v>31.82</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>32.61</v>
+        <v>34.01</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>32.72</v>
+        <v>31.3</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>32.6</v>
+        <v>31.78</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>32.51</v>
+        <v>31.44</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>32.48</v>
+        <v>31.81</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>31.93</v>
+        <v>31.13</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>35.1</v>
+        <v>32.33</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>32.72</v>
+        <v>31.17</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>34.05</v>
+        <v>30.91</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>34.14</v>
+        <v>31.56</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>32.36</v>
+        <v>31.3</v>
       </c>
       <c r="O70" s="6" t="n">
-        <v>32.78</v>
+        <v>31.59</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>34.24</v>
+        <v>31.9</v>
       </c>
       <c r="Q70" s="6" t="n">
-        <v>32.56</v>
+        <v>31.52</v>
       </c>
       <c r="R70" s="6" t="n">
-        <v>32.69</v>
+        <v>31.22</v>
       </c>
       <c r="S70" s="6" t="n">
-        <v>32.33</v>
+        <v>31.62</v>
       </c>
       <c r="T70" s="6" t="n">
-        <v>32.36</v>
+        <v>31.62</v>
       </c>
       <c r="U70" s="6" t="n">
-        <v>32.29</v>
+        <v>31.75</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>32</v>
+        <v>32.01</v>
       </c>
       <c r="W70" s="6" t="n">
-        <v>32.46</v>
+        <v>32.09</v>
       </c>
       <c r="X70" s="6" t="n">
-        <v>31.89</v>
+        <v>32.17</v>
       </c>
       <c r="Y70" s="6" t="n">
-        <v>32.44</v>
+        <v>31.41</v>
       </c>
       <c r="Z70" s="6" t="n">
-        <v>31.9</v>
+        <v>31.92</v>
       </c>
       <c r="AA70" s="6" t="n">
-        <v>32.17</v>
+        <v>34.1</v>
       </c>
       <c r="AB70" s="6" t="n">
-        <v>33.28</v>
+        <v>31.28</v>
       </c>
       <c r="AC70" s="6" t="n">
-        <v>32.95</v>
+        <v>31.6</v>
       </c>
       <c r="AD70" s="6" t="n">
-        <v>32.63</v>
+        <v>32.31</v>
       </c>
       <c r="AE70" s="6" t="n">
-        <v>32.53</v>
+        <v>32.11</v>
       </c>
       <c r="AF70" s="6" t="n">
-        <v>32.38</v>
+        <v>31.26</v>
       </c>
       <c r="AG70" s="6" t="n">
-        <v>32.41</v>
+        <v>32.11</v>
       </c>
       <c r="AH70" s="6" t="n">
-        <v>32.74</v>
+        <v>31.81</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
@@ -6756,107 +6552,107 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TELEVICENTRO TVC</t>
+          <t>CANAL UNO no</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>597.25</v>
+        <v>573.25</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>79.81999999999999</v>
+        <v>30.1</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>79.70999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>78.09999999999999</v>
+        <v>29.72</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>79.84999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>79.90000000000001</v>
+        <v>31.7</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>79.95</v>
+        <v>29.91</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>80.20999999999999</v>
+        <v>30.73</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>79.58</v>
+        <v>34.14</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>79.67</v>
+        <v>30.47</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>79.06</v>
+        <v>32.12</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>79.97</v>
+        <v>29.9</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>55.45</v>
+        <v>30.12</v>
       </c>
       <c r="O71" s="6" t="n">
-        <v>79.84999999999999</v>
+        <v>29.56</v>
       </c>
       <c r="P71" s="6" t="n">
-        <v>79.78</v>
+        <v>30.11</v>
       </c>
       <c r="Q71" s="6" t="n">
-        <v>80.29000000000001</v>
+        <v>31.05</v>
       </c>
       <c r="R71" s="6" t="n">
-        <v>79.95999999999999</v>
+        <v>29.82</v>
       </c>
       <c r="S71" s="6" t="n">
-        <v>79.34</v>
+        <v>30.34</v>
       </c>
       <c r="T71" s="6" t="n">
-        <v>78.88</v>
+        <v>29.44</v>
       </c>
       <c r="U71" s="6" t="n">
-        <v>79.08</v>
+        <v>29.68</v>
       </c>
       <c r="V71" s="6" t="n">
-        <v>79.84</v>
+        <v>29.7</v>
       </c>
       <c r="W71" s="6" t="n">
-        <v>79.31</v>
+        <v>29.73</v>
       </c>
       <c r="X71" s="6" t="n">
-        <v>80.03</v>
+        <v>31.34</v>
       </c>
       <c r="Y71" s="6" t="n">
-        <v>79.94</v>
+        <v>34.96</v>
       </c>
       <c r="Z71" s="6" t="n">
-        <v>80.08</v>
+        <v>29.62</v>
       </c>
       <c r="AA71" s="6" t="n">
-        <v>80.09999999999999</v>
+        <v>29.48</v>
       </c>
       <c r="AB71" s="6" t="n">
-        <v>79.20999999999999</v>
+        <v>29.66</v>
       </c>
       <c r="AC71" s="6" t="n">
-        <v>79.62</v>
+        <v>29.65</v>
       </c>
       <c r="AD71" s="6" t="n">
-        <v>80.29000000000001</v>
+        <v>29.81</v>
       </c>
       <c r="AE71" s="6" t="n">
-        <v>80.06</v>
+        <v>29.57</v>
       </c>
       <c r="AF71" s="6" t="n">
-        <v>79.29000000000001</v>
+        <v>29.62</v>
       </c>
       <c r="AG71" s="6" t="n">
-        <v>79.79000000000001</v>
+        <v>32.01</v>
       </c>
       <c r="AH71" s="6" t="n">
-        <v>78.90000000000001</v>
+        <v>30.52</v>
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
@@ -6865,236 +6661,456 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>UCSG TELEVISION</t>
+          <t>TELEATAHUALPA (RTU)</t>
         </is>
       </c>
       <c r="B72" s="6" t="n">
-        <v>621.25</v>
+        <v>585.25</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>30.32</v>
+        <v>33.38</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>30.3</v>
+        <v>32.61</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>30.2</v>
+        <v>32.72</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>29.75</v>
+        <v>32.6</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>29.9</v>
+        <v>32.51</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>29.98</v>
+        <v>32.48</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>29.66</v>
+        <v>31.93</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>29.84</v>
+        <v>35.1</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>30.35</v>
+        <v>32.72</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>33.02</v>
+        <v>34.05</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>30.01</v>
+        <v>34.14</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>29.79</v>
+        <v>32.36</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>32.08</v>
+        <v>32.78</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>30.26</v>
+        <v>34.24</v>
       </c>
       <c r="Q72" s="6" t="n">
-        <v>30.26</v>
+        <v>32.56</v>
       </c>
       <c r="R72" s="6" t="n">
-        <v>29.52</v>
+        <v>32.69</v>
       </c>
       <c r="S72" s="6" t="n">
-        <v>30.26</v>
+        <v>32.33</v>
       </c>
       <c r="T72" s="6" t="n">
-        <v>29.72</v>
+        <v>32.36</v>
       </c>
       <c r="U72" s="6" t="n">
-        <v>31.64</v>
+        <v>32.29</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>29.29</v>
+        <v>32</v>
       </c>
       <c r="W72" s="6" t="n">
-        <v>29.83</v>
+        <v>32.46</v>
       </c>
       <c r="X72" s="6" t="n">
-        <v>30.21</v>
+        <v>31.89</v>
       </c>
       <c r="Y72" s="6" t="n">
-        <v>31.16</v>
+        <v>32.44</v>
       </c>
       <c r="Z72" s="6" t="n">
-        <v>29.88</v>
+        <v>31.9</v>
       </c>
       <c r="AA72" s="6" t="n">
-        <v>33.85</v>
+        <v>32.17</v>
       </c>
       <c r="AB72" s="6" t="n">
-        <v>29.26</v>
+        <v>33.28</v>
       </c>
       <c r="AC72" s="6" t="n">
-        <v>31.25</v>
+        <v>32.95</v>
       </c>
       <c r="AD72" s="6" t="n">
-        <v>30.8</v>
+        <v>32.63</v>
       </c>
       <c r="AE72" s="6" t="n">
-        <v>29.49</v>
+        <v>32.53</v>
       </c>
       <c r="AF72" s="6" t="n">
-        <v>30.38</v>
+        <v>32.38</v>
       </c>
       <c r="AG72" s="6" t="n">
-        <v>30.25</v>
+        <v>32.41</v>
       </c>
       <c r="AH72" s="6" t="n">
-        <v>30.4</v>
+        <v>32.74</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
       <c r="AK72" s="7" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TELEVICENTRO TVC</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>597.25</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>79.81999999999999</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>79.70999999999999</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>80.20999999999999</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>79.58</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>79.67</v>
+      </c>
+      <c r="L73" s="6" t="n">
+        <v>79.06</v>
+      </c>
+      <c r="M73" s="6" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="O73" s="6" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="P73" s="6" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="Q73" s="6" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v>79.95999999999999</v>
+      </c>
+      <c r="S73" s="6" t="n">
+        <v>79.34</v>
+      </c>
+      <c r="T73" s="6" t="n">
+        <v>78.88</v>
+      </c>
+      <c r="U73" s="6" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="V73" s="6" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="W73" s="6" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="X73" s="6" t="n">
+        <v>80.03</v>
+      </c>
+      <c r="Y73" s="6" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="Z73" s="6" t="n">
+        <v>80.08</v>
+      </c>
+      <c r="AA73" s="6" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="AB73" s="6" t="n">
+        <v>79.20999999999999</v>
+      </c>
+      <c r="AC73" s="6" t="n">
+        <v>79.62</v>
+      </c>
+      <c r="AD73" s="6" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="AE73" s="6" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="AF73" s="6" t="n">
+        <v>79.29000000000001</v>
+      </c>
+      <c r="AG73" s="6" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="AH73" s="6" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AI73" s="6" t="inlineStr"/>
+      <c r="AJ73" s="6" t="inlineStr"/>
+      <c r="AK73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>UCSG TELEVISION</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>621.25</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="M74" s="6" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="O74" s="6" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="P74" s="6" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="Q74" s="6" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="S74" s="6" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="T74" s="6" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="U74" s="6" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="V74" s="6" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="W74" s="6" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="X74" s="6" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="Y74" s="6" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="Z74" s="6" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="AA74" s="6" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="AB74" s="6" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="AC74" s="6" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="AD74" s="6" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="AE74" s="6" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="AF74" s="6" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="AG74" s="6" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="AH74" s="6" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AI74" s="6" t="inlineStr"/>
+      <c r="AJ74" s="6" t="inlineStr"/>
+      <c r="AK74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
+      <c r="B75" s="9" t="n">
         <v>633.25</v>
       </c>
-      <c r="C73" s="9" t="n">
+      <c r="C75" s="9" t="n">
         <v>29.02</v>
       </c>
-      <c r="D73" s="9" t="n">
+      <c r="D75" s="9" t="n">
         <v>30.64</v>
       </c>
-      <c r="E73" s="9" t="n">
+      <c r="E75" s="9" t="n">
         <v>28.75</v>
       </c>
-      <c r="F73" s="9" t="n">
+      <c r="F75" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="G73" s="9" t="n">
+      <c r="G75" s="9" t="n">
         <v>29.96</v>
       </c>
-      <c r="H73" s="9" t="n">
+      <c r="H75" s="9" t="n">
         <v>29.38</v>
       </c>
-      <c r="I73" s="9" t="n">
+      <c r="I75" s="9" t="n">
         <v>28.91</v>
       </c>
-      <c r="J73" s="9" t="n">
+      <c r="J75" s="9" t="n">
         <v>29.28</v>
       </c>
-      <c r="K73" s="9" t="n">
+      <c r="K75" s="9" t="n">
         <v>30.2</v>
       </c>
-      <c r="L73" s="9" t="n">
+      <c r="L75" s="9" t="n">
         <v>30.12</v>
       </c>
-      <c r="M73" s="9" t="n">
+      <c r="M75" s="9" t="n">
         <v>31.44</v>
       </c>
-      <c r="N73" s="9" t="n">
+      <c r="N75" s="9" t="n">
         <v>29.04</v>
       </c>
-      <c r="O73" s="9" t="n">
+      <c r="O75" s="9" t="n">
         <v>29.02</v>
       </c>
-      <c r="P73" s="9" t="n">
+      <c r="P75" s="9" t="n">
         <v>29.38</v>
       </c>
-      <c r="Q73" s="9" t="n">
+      <c r="Q75" s="9" t="n">
         <v>29.29</v>
       </c>
-      <c r="R73" s="9" t="n">
+      <c r="R75" s="9" t="n">
         <v>29.71</v>
       </c>
-      <c r="S73" s="9" t="n">
+      <c r="S75" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="T73" s="9" t="n">
+      <c r="T75" s="9" t="n">
         <v>29.38</v>
       </c>
-      <c r="U73" s="9" t="n">
+      <c r="U75" s="9" t="n">
         <v>29.78</v>
       </c>
-      <c r="V73" s="9" t="n">
+      <c r="V75" s="9" t="n">
         <v>29.85</v>
       </c>
-      <c r="W73" s="9" t="n">
+      <c r="W75" s="9" t="n">
         <v>29.16</v>
       </c>
-      <c r="X73" s="9" t="n">
+      <c r="X75" s="9" t="n">
         <v>29.29</v>
       </c>
-      <c r="Y73" s="9" t="n">
+      <c r="Y75" s="9" t="n">
         <v>29.48</v>
       </c>
-      <c r="Z73" s="9" t="n">
+      <c r="Z75" s="9" t="n">
         <v>37.17</v>
       </c>
-      <c r="AA73" s="9" t="n">
+      <c r="AA75" s="9" t="n">
         <v>28.92</v>
       </c>
-      <c r="AB73" s="9" t="n">
+      <c r="AB75" s="9" t="n">
         <v>31.6</v>
       </c>
-      <c r="AC73" s="9" t="n">
+      <c r="AC75" s="9" t="n">
         <v>30.51</v>
       </c>
-      <c r="AD73" s="9" t="n">
+      <c r="AD75" s="9" t="n">
         <v>29.07</v>
       </c>
-      <c r="AE73" s="9" t="n">
+      <c r="AE75" s="9" t="n">
         <v>28.94</v>
       </c>
-      <c r="AF73" s="9" t="n">
+      <c r="AF75" s="9" t="n">
         <v>29.25</v>
       </c>
-      <c r="AG73" s="9" t="n">
+      <c r="AG75" s="9" t="n">
         <v>29.59</v>
       </c>
-      <c r="AH73" s="9" t="n">
+      <c r="AH75" s="9" t="n">
         <v>29.84</v>
       </c>
-      <c r="AI73" s="9" t="inlineStr"/>
-      <c r="AJ73" s="9" t="inlineStr"/>
-      <c r="AK73" s="10" t="n"/>
+      <c r="AI75" s="9" t="inlineStr"/>
+      <c r="AJ75" s="9" t="inlineStr"/>
+      <c r="AK75" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="A4:AK4"/>
     <mergeCell ref="A3:AK3"/>
-    <mergeCell ref="A53:AK53"/>
     <mergeCell ref="A55:AK55"/>
     <mergeCell ref="A7:AK7"/>
     <mergeCell ref="A59:AK59"/>
     <mergeCell ref="A57:AK57"/>
     <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="A54:AK54"/>
+    <mergeCell ref="A56:AK56"/>
     <mergeCell ref="A58:AK58"/>
+    <mergeCell ref="A60:AK60"/>
     <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="A9:AK9"/>
+    <mergeCell ref="A8:AK8"/>
+    <mergeCell ref="A61:AK61"/>
     <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -218,7 +218,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -268,7 +268,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -100,11 +100,60 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +185,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +696,7 @@
     <col width="7" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="23" customWidth="1" min="36" max="36"/>
+    <col width="38" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
@@ -5675,7 +5727,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK62" s="4" t="n"/>
+      <c r="AK62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5784,7 +5836,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="7" t="n"/>
+      <c r="AK63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5893,7 +5945,7 @@
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="7" t="n"/>
+      <c r="AK64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -6002,7 +6054,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="7" t="n"/>
+      <c r="AK65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6111,7 +6163,7 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="7" t="n"/>
+      <c r="AK66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6220,7 +6272,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="7" t="n"/>
+      <c r="AK67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6329,7 +6381,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="7" t="n"/>
+      <c r="AK68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6438,7 +6490,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="7" t="n"/>
+      <c r="AK69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6547,7 +6599,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="7" t="n"/>
+      <c r="AK70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6656,7 +6708,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="7" t="n"/>
+      <c r="AK71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6765,7 +6817,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="7" t="n"/>
+      <c r="AK72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6874,7 +6926,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="7" t="n"/>
+      <c r="AK73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6983,7 +7035,7 @@
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="7" t="n"/>
+      <c r="AK74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -7092,26 +7144,40 @@
       </c>
       <c r="AI75" s="9" t="inlineStr"/>
       <c r="AJ75" s="9" t="inlineStr"/>
-      <c r="AK75" s="10" t="n"/>
+      <c r="AK75" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="A4:AK4"/>
+  <mergeCells count="30">
     <mergeCell ref="A3:AK3"/>
     <mergeCell ref="A55:AK55"/>
-    <mergeCell ref="A7:AK7"/>
-    <mergeCell ref="A59:AK59"/>
     <mergeCell ref="A57:AK57"/>
     <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="AJ71:AK71"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AJ70:AK70"/>
+    <mergeCell ref="A8:AK8"/>
+    <mergeCell ref="A4:AK4"/>
+    <mergeCell ref="AJ73:AK73"/>
+    <mergeCell ref="AJ72:AK72"/>
+    <mergeCell ref="AJ67:AK67"/>
+    <mergeCell ref="AJ66:AK66"/>
+    <mergeCell ref="A9:AK9"/>
     <mergeCell ref="A58:AK58"/>
+    <mergeCell ref="AJ69:AK69"/>
+    <mergeCell ref="A59:AK59"/>
+    <mergeCell ref="AJ68:AK68"/>
+    <mergeCell ref="AJ62:AK62"/>
     <mergeCell ref="A60:AK60"/>
     <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A9:AK9"/>
-    <mergeCell ref="A8:AK8"/>
+    <mergeCell ref="AJ74:AK74"/>
+    <mergeCell ref="AJ65:AK65"/>
     <mergeCell ref="A61:AK61"/>
     <mergeCell ref="A6:AK6"/>
+    <mergeCell ref="AJ64:AK64"/>
+    <mergeCell ref="A7:AK7"/>
+    <mergeCell ref="AJ63:AK63"/>
+    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="AJ75:AK75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -30,12 +30,30 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFE9F"/>
+        <bgColor rgb="FFFFFE9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFD9BCB"/>
+        <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -153,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,7 +191,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,11 +209,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -759,7 +792,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -901,97 +934,97 @@
       <c r="B11" s="6" t="n">
         <v>88.3</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>68.28</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>70.26000000000001</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>70.42</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="7" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>70.89</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>71.63</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="7" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="7" t="n">
         <v>71.54000000000001</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="7" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <v>70.81999999999999</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="7" t="n">
         <v>70.75</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <v>71.04000000000001</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="7" t="n">
         <v>71.26000000000001</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="7" t="n">
         <v>71.11</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" s="7" t="n">
         <v>70.81</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" s="7" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="7" t="n">
         <v>70.86</v>
       </c>
-      <c r="Y11" s="6" t="n">
+      <c r="Y11" s="7" t="n">
         <v>71.14</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="Z11" s="7" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="AA11" s="6" t="n">
+      <c r="AA11" s="7" t="n">
         <v>70.34</v>
       </c>
-      <c r="AB11" s="6" t="n">
+      <c r="AB11" s="7" t="n">
         <v>70.58</v>
       </c>
-      <c r="AC11" s="6" t="n">
+      <c r="AC11" s="7" t="n">
         <v>70.89</v>
       </c>
-      <c r="AD11" s="6" t="n">
+      <c r="AD11" s="7" t="n">
         <v>71.29000000000001</v>
       </c>
-      <c r="AE11" s="6" t="n">
+      <c r="AE11" s="7" t="n">
         <v>70.7</v>
       </c>
-      <c r="AF11" s="6" t="n">
+      <c r="AF11" s="7" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="AG11" s="6" t="n">
+      <c r="AG11" s="7" t="n">
         <v>71.29000000000001</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1001,7 +1034,7 @@
         <v>244.66</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="7" t="inlineStr"/>
+      <c r="AK11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1012,97 +1045,97 @@
       <c r="B12" s="6" t="n">
         <v>88.7</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>72.78</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>65.56</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>71.59</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>69.8</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>69.92</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="7" t="n">
         <v>71.62</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>72.81</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="M12" s="7" t="n">
         <v>72.44</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="7" t="n">
         <v>72.89</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="O12" s="7" t="n">
         <v>73.23</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="7" t="n">
         <v>72.42</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="7" t="n">
         <v>72.41</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="7" t="n">
         <v>72.81999999999999</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <v>72.63</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="T12" s="7" t="n">
         <v>72.69</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="U12" s="7" t="n">
         <v>73.51000000000001</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="V12" s="7" t="n">
         <v>73.06999999999999</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="W12" s="7" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="X12" s="7" t="n">
         <v>72.73999999999999</v>
       </c>
-      <c r="Y12" s="6" t="n">
+      <c r="Y12" s="7" t="n">
         <v>73.26000000000001</v>
       </c>
-      <c r="Z12" s="6" t="n">
+      <c r="Z12" s="7" t="n">
         <v>72.26000000000001</v>
       </c>
-      <c r="AA12" s="6" t="n">
+      <c r="AA12" s="7" t="n">
         <v>72.54000000000001</v>
       </c>
-      <c r="AB12" s="6" t="n">
+      <c r="AB12" s="7" t="n">
         <v>72.48</v>
       </c>
-      <c r="AC12" s="6" t="n">
+      <c r="AC12" s="7" t="n">
         <v>73.01000000000001</v>
       </c>
-      <c r="AD12" s="6" t="n">
+      <c r="AD12" s="7" t="n">
         <v>73.56</v>
       </c>
-      <c r="AE12" s="6" t="n">
+      <c r="AE12" s="7" t="n">
         <v>73.04000000000001</v>
       </c>
-      <c r="AF12" s="6" t="n">
+      <c r="AF12" s="7" t="n">
         <v>73.42</v>
       </c>
-      <c r="AG12" s="6" t="n">
+      <c r="AG12" s="7" t="n">
         <v>72.84</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1112,7 +1145,7 @@
         <v>160.6</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="7" t="inlineStr"/>
+      <c r="AK12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1123,97 +1156,97 @@
       <c r="B13" s="6" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>72.61</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>72.34</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>72.92</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="7" t="n">
         <v>71.81</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" s="7" t="n">
         <v>71.54000000000001</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="7" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M13" s="7" t="n">
         <v>73.19</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" s="7" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="O13" s="7" t="n">
         <v>72.51000000000001</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="7" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="7" t="n">
         <v>73.03</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="7" t="n">
         <v>72.39</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <v>71.26000000000001</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="T13" s="7" t="n">
         <v>72.38</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U13" s="7" t="n">
         <v>71.44</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="V13" s="7" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="W13" s="6" t="n">
+      <c r="W13" s="7" t="n">
         <v>60.52</v>
       </c>
-      <c r="X13" s="6" t="n">
+      <c r="X13" s="7" t="n">
         <v>72.17</v>
       </c>
-      <c r="Y13" s="6" t="n">
+      <c r="Y13" s="7" t="n">
         <v>71.87</v>
       </c>
-      <c r="Z13" s="6" t="n">
+      <c r="Z13" s="7" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="AA13" s="6" t="n">
+      <c r="AA13" s="7" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="AB13" s="6" t="n">
+      <c r="AB13" s="7" t="n">
         <v>70.76000000000001</v>
       </c>
-      <c r="AC13" s="6" t="n">
+      <c r="AC13" s="7" t="n">
         <v>71.78</v>
       </c>
-      <c r="AD13" s="6" t="n">
+      <c r="AD13" s="7" t="n">
         <v>71.84</v>
       </c>
-      <c r="AE13" s="6" t="n">
+      <c r="AE13" s="7" t="n">
         <v>70.8</v>
       </c>
-      <c r="AF13" s="6" t="n">
+      <c r="AF13" s="7" t="n">
         <v>71.34</v>
       </c>
-      <c r="AG13" s="6" t="n">
+      <c r="AG13" s="7" t="n">
         <v>70.06999999999999</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1223,7 +1256,7 @@
         <v>200.59</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="7" t="inlineStr"/>
+      <c r="AK13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1234,97 +1267,97 @@
       <c r="B14" s="6" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>67.19</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>66.91</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>60.02</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>67.92</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>67.73</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>67.16</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="7" t="n">
         <v>66.51000000000001</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>67.64</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>69.12</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>68.26000000000001</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="7" t="n">
         <v>69.04000000000001</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="7" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="9" t="n">
         <v>51.91</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="7" t="n">
         <v>67.39</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>68.22</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="7" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="7" t="n">
         <v>68.11</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="V14" s="7" t="n">
         <v>68.19</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="W14" s="7" t="n">
         <v>68.28</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <v>68.22</v>
       </c>
-      <c r="Y14" s="6" t="n">
+      <c r="Y14" s="7" t="n">
         <v>67.56999999999999</v>
       </c>
-      <c r="Z14" s="6" t="n">
+      <c r="Z14" s="7" t="n">
         <v>66.69</v>
       </c>
-      <c r="AA14" s="6" t="n">
+      <c r="AA14" s="7" t="n">
         <v>67.38</v>
       </c>
-      <c r="AB14" s="6" t="n">
+      <c r="AB14" s="7" t="n">
         <v>67.04000000000001</v>
       </c>
-      <c r="AC14" s="6" t="n">
+      <c r="AC14" s="7" t="n">
         <v>67.63</v>
       </c>
-      <c r="AD14" s="6" t="n">
+      <c r="AD14" s="7" t="n">
         <v>67.89</v>
       </c>
-      <c r="AE14" s="6" t="n">
+      <c r="AE14" s="7" t="n">
         <v>67.59</v>
       </c>
-      <c r="AF14" s="6" t="n">
+      <c r="AF14" s="7" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="AG14" s="6" t="n">
+      <c r="AG14" s="7" t="n">
         <v>68.75</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1334,7 +1367,7 @@
         <v>265.65</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="7" t="inlineStr"/>
+      <c r="AK14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1345,97 +1378,97 @@
       <c r="B15" s="6" t="n">
         <v>90.3</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>75.42</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>74.88</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>75.34999999999999</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>74.34999999999999</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>74.97</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>75.39</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>75.95999999999999</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="7" t="n">
         <v>75.69</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="7" t="n">
         <v>75.93000000000001</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="7" t="n">
         <v>76.37</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="7" t="n">
         <v>75.69</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="7" t="n">
         <v>76.73999999999999</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="O15" s="7" t="n">
         <v>75.83</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="7" t="n">
         <v>76.41</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="7" t="n">
         <v>75.81999999999999</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="7" t="n">
         <v>75.72</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <v>75.34</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" s="7" t="n">
         <v>75.08</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" s="7" t="n">
         <v>76.34999999999999</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="V15" s="7" t="n">
         <v>76.36</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="W15" s="7" t="n">
         <v>75.76000000000001</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="7" t="n">
         <v>76.05</v>
       </c>
-      <c r="Y15" s="6" t="n">
+      <c r="Y15" s="7" t="n">
         <v>76.19</v>
       </c>
-      <c r="Z15" s="6" t="n">
+      <c r="Z15" s="7" t="n">
         <v>74.95999999999999</v>
       </c>
-      <c r="AA15" s="6" t="n">
+      <c r="AA15" s="7" t="n">
         <v>75.79000000000001</v>
       </c>
-      <c r="AB15" s="6" t="n">
+      <c r="AB15" s="7" t="n">
         <v>74.79000000000001</v>
       </c>
-      <c r="AC15" s="6" t="n">
+      <c r="AC15" s="7" t="n">
         <v>75.52</v>
       </c>
-      <c r="AD15" s="6" t="n">
+      <c r="AD15" s="7" t="n">
         <v>75.75</v>
       </c>
-      <c r="AE15" s="6" t="n">
+      <c r="AE15" s="7" t="n">
         <v>75.91</v>
       </c>
-      <c r="AF15" s="6" t="n">
+      <c r="AF15" s="7" t="n">
         <v>75.68000000000001</v>
       </c>
-      <c r="AG15" s="6" t="n">
+      <c r="AG15" s="7" t="n">
         <v>75.70999999999999</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1445,7 +1478,7 @@
         <v>229.65</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="7" t="inlineStr"/>
+      <c r="AK15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1456,97 +1489,97 @@
       <c r="B16" s="6" t="n">
         <v>90.7</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>67.89</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>60.9</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>67.3</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>68.08</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>67.39</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>68.81</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="7" t="n">
         <v>68.16</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>68.59</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>66.77</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="7" t="n">
         <v>68.31999999999999</v>
       </c>
-      <c r="O16" s="6" t="n">
+      <c r="O16" s="7" t="n">
         <v>67.63</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="7" t="n">
         <v>66.83</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="7" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>67.22</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="7" t="n">
         <v>67.54000000000001</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="U16" s="7" t="n">
         <v>68.77</v>
       </c>
-      <c r="V16" s="6" t="n">
+      <c r="V16" s="7" t="n">
         <v>68.70999999999999</v>
       </c>
-      <c r="W16" s="6" t="n">
+      <c r="W16" s="7" t="n">
         <v>68.16</v>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="7" t="n">
         <v>69.34</v>
       </c>
-      <c r="Y16" s="6" t="n">
+      <c r="Y16" s="7" t="n">
         <v>68.86</v>
       </c>
-      <c r="Z16" s="6" t="n">
+      <c r="Z16" s="7" t="n">
         <v>66.81</v>
       </c>
-      <c r="AA16" s="6" t="n">
+      <c r="AA16" s="7" t="n">
         <v>69.08</v>
       </c>
-      <c r="AB16" s="6" t="n">
+      <c r="AB16" s="7" t="n">
         <v>68.16</v>
       </c>
-      <c r="AC16" s="6" t="n">
+      <c r="AC16" s="7" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="AD16" s="6" t="n">
+      <c r="AD16" s="7" t="n">
         <v>67.77</v>
       </c>
-      <c r="AE16" s="6" t="n">
+      <c r="AE16" s="7" t="n">
         <v>67.11</v>
       </c>
-      <c r="AF16" s="6" t="n">
+      <c r="AF16" s="7" t="n">
         <v>67.20999999999999</v>
       </c>
-      <c r="AG16" s="6" t="n">
+      <c r="AG16" s="7" t="n">
         <v>68.09</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1556,7 +1589,7 @@
         <v>428.49</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="7" t="inlineStr"/>
+      <c r="AK16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1567,97 +1600,97 @@
       <c r="B17" s="6" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>70.97</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>69.94</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>65.2</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>70.06</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="7" t="n">
         <v>71.15000000000001</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>70.64</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>71.81999999999999</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="7" t="n">
         <v>71.64</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="O17" s="7" t="n">
         <v>70.11</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="7" t="n">
         <v>70.51000000000001</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="7" t="n">
         <v>70.2</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="7" t="n">
         <v>70.83</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>70.75</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="7" t="n">
         <v>69.44</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U17" s="7" t="n">
         <v>70.42</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="V17" s="7" t="n">
         <v>70.51000000000001</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="W17" s="7" t="n">
         <v>70.09</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="7" t="n">
         <v>69.79000000000001</v>
       </c>
-      <c r="Y17" s="6" t="n">
+      <c r="Y17" s="7" t="n">
         <v>69.2</v>
       </c>
-      <c r="Z17" s="6" t="n">
+      <c r="Z17" s="7" t="n">
         <v>69.92</v>
       </c>
-      <c r="AA17" s="6" t="n">
+      <c r="AA17" s="7" t="n">
         <v>69.08</v>
       </c>
-      <c r="AB17" s="6" t="n">
+      <c r="AB17" s="7" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="AC17" s="6" t="n">
+      <c r="AC17" s="7" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="AD17" s="6" t="n">
+      <c r="AD17" s="7" t="n">
         <v>70.39</v>
       </c>
-      <c r="AE17" s="6" t="n">
+      <c r="AE17" s="7" t="n">
         <v>69.98999999999999</v>
       </c>
-      <c r="AF17" s="6" t="n">
+      <c r="AF17" s="7" t="n">
         <v>69.2</v>
       </c>
-      <c r="AG17" s="6" t="n">
+      <c r="AG17" s="7" t="n">
         <v>68.95999999999999</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1667,7 +1700,7 @@
         <v>388.85</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="7" t="inlineStr"/>
+      <c r="AK17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1678,97 +1711,97 @@
       <c r="B18" s="6" t="n">
         <v>91.5</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="9" t="n">
         <v>52.72</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="9" t="n">
         <v>50.06</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>58.76</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>50.41</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>46.62</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>49.69</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>50.71</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="9" t="n">
         <v>48.24</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>50.75</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="9" t="n">
         <v>50.51</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>52.76</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" s="9" t="n">
         <v>51.64</v>
       </c>
-      <c r="O18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>48.68</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="9" t="n">
         <v>49.17</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>53.33</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="9" t="n">
         <v>50.15</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>48.7</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="T18" s="9" t="n">
         <v>49.26</v>
       </c>
-      <c r="U18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>47.96</v>
       </c>
-      <c r="V18" s="6" t="n">
+      <c r="V18" s="9" t="n">
         <v>47.53</v>
       </c>
-      <c r="W18" s="6" t="n">
+      <c r="W18" s="9" t="n">
         <v>49.54</v>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="9" t="n">
         <v>49.93</v>
       </c>
-      <c r="Y18" s="6" t="n">
+      <c r="Y18" s="9" t="n">
         <v>52.67</v>
       </c>
-      <c r="Z18" s="6" t="n">
+      <c r="Z18" s="9" t="n">
         <v>48.81</v>
       </c>
-      <c r="AA18" s="6" t="n">
+      <c r="AA18" s="9" t="n">
         <v>48.32</v>
       </c>
-      <c r="AB18" s="6" t="n">
+      <c r="AB18" s="9" t="n">
         <v>49.61</v>
       </c>
-      <c r="AC18" s="6" t="n">
+      <c r="AC18" s="9" t="n">
         <v>49.47</v>
       </c>
-      <c r="AD18" s="6" t="n">
+      <c r="AD18" s="9" t="n">
         <v>47.34</v>
       </c>
-      <c r="AE18" s="6" t="n">
+      <c r="AE18" s="9" t="n">
         <v>49.9</v>
       </c>
-      <c r="AF18" s="6" t="n">
+      <c r="AF18" s="9" t="n">
         <v>52.66</v>
       </c>
-      <c r="AG18" s="6" t="n">
+      <c r="AG18" s="9" t="n">
         <v>51.71</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1778,7 +1811,7 @@
         <v>499.47</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="7" t="inlineStr"/>
+      <c r="AK18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1789,97 +1822,97 @@
       <c r="B19" s="6" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>66.62</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <v>66.97</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>68.7</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>67.31</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>66.04000000000001</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="7" t="n">
         <v>67.39</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="7" t="n">
         <v>67.81999999999999</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" s="7" t="n">
         <v>67.41</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="7" t="n">
         <v>67.04000000000001</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M19" s="7" t="n">
         <v>66.87</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" s="7" t="n">
         <v>67.88</v>
       </c>
-      <c r="O19" s="6" t="n">
+      <c r="O19" s="7" t="n">
         <v>68.03</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="P19" s="7" t="n">
         <v>67.61</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="7" t="n">
         <v>67.38</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="7" t="n">
         <v>67.73</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="S19" s="7" t="n">
         <v>67.64</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="T19" s="7" t="n">
         <v>67.38</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U19" s="7" t="n">
         <v>67.33</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="V19" s="7" t="n">
         <v>68.03</v>
       </c>
-      <c r="W19" s="6" t="n">
+      <c r="W19" s="7" t="n">
         <v>67.86</v>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" s="7" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="Y19" s="6" t="n">
+      <c r="Y19" s="7" t="n">
         <v>67.22</v>
       </c>
-      <c r="Z19" s="6" t="n">
+      <c r="Z19" s="7" t="n">
         <v>66.95</v>
       </c>
-      <c r="AA19" s="6" t="n">
+      <c r="AA19" s="7" t="n">
         <v>67.81999999999999</v>
       </c>
-      <c r="AB19" s="6" t="n">
+      <c r="AB19" s="7" t="n">
         <v>67.92</v>
       </c>
-      <c r="AC19" s="6" t="n">
+      <c r="AC19" s="7" t="n">
         <v>67.02</v>
       </c>
-      <c r="AD19" s="6" t="n">
+      <c r="AD19" s="7" t="n">
         <v>66.37</v>
       </c>
-      <c r="AE19" s="6" t="n">
+      <c r="AE19" s="7" t="n">
         <v>66.31</v>
       </c>
-      <c r="AF19" s="6" t="n">
+      <c r="AF19" s="7" t="n">
         <v>67.34</v>
       </c>
-      <c r="AG19" s="6" t="n">
+      <c r="AG19" s="7" t="n">
         <v>67.03</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1889,7 +1922,7 @@
         <v>315.82</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="7" t="inlineStr"/>
+      <c r="AK19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1900,97 +1933,97 @@
       <c r="B20" s="6" t="n">
         <v>92.3</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>58.3</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>59.64</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>59.4</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>58.7</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>58.94</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>61.55</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="7" t="n">
         <v>60.76</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K20" s="7" t="n">
         <v>60.86</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" s="7" t="n">
         <v>60.81</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="M20" s="7" t="n">
         <v>60.76</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" s="7" t="n">
         <v>63.44</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="O20" s="7" t="n">
         <v>59.96</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="7" t="n">
         <v>61.39</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="7" t="n">
         <v>61.56</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R20" s="7" t="n">
         <v>60.75</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="S20" s="7" t="n">
         <v>60.78</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="T20" s="7" t="n">
         <v>59.23</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="U20" s="7" t="n">
         <v>61.55</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="V20" s="7" t="n">
         <v>61.48</v>
       </c>
-      <c r="W20" s="6" t="n">
+      <c r="W20" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="X20" s="6" t="n">
+      <c r="X20" s="7" t="n">
         <v>57.83</v>
       </c>
-      <c r="Y20" s="6" t="n">
+      <c r="Y20" s="7" t="n">
         <v>59.93</v>
       </c>
-      <c r="Z20" s="6" t="n">
+      <c r="Z20" s="7" t="n">
         <v>59.41</v>
       </c>
-      <c r="AA20" s="6" t="n">
+      <c r="AA20" s="7" t="n">
         <v>58.81</v>
       </c>
-      <c r="AB20" s="6" t="n">
+      <c r="AB20" s="7" t="n">
         <v>59.88</v>
       </c>
-      <c r="AC20" s="6" t="n">
+      <c r="AC20" s="7" t="n">
         <v>60.09</v>
       </c>
-      <c r="AD20" s="6" t="n">
+      <c r="AD20" s="7" t="n">
         <v>58.88</v>
       </c>
-      <c r="AE20" s="6" t="n">
+      <c r="AE20" s="7" t="n">
         <v>61.23</v>
       </c>
-      <c r="AF20" s="6" t="n">
+      <c r="AF20" s="7" t="n">
         <v>59.23</v>
       </c>
-      <c r="AG20" s="6" t="n">
+      <c r="AG20" s="7" t="n">
         <v>58.85</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2000,7 +2033,7 @@
         <v>478.59</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="7" t="inlineStr"/>
+      <c r="AK20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2011,97 +2044,97 @@
       <c r="B21" s="6" t="n">
         <v>92.7</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>67.28</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>68.28</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>67.95999999999999</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>68.15000000000001</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>68.69</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>66.29000000000001</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>68.18000000000001</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <v>66.05</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <v>66.42</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="7" t="n">
         <v>66.48</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M21" s="7" t="n">
         <v>61.24</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="7" t="n">
         <v>63.96</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="O21" s="7" t="n">
         <v>67.36</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="7" t="n">
         <v>65.54000000000001</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="7" t="n">
         <v>63.69</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="7" t="n">
         <v>63.98</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>63.7</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" s="7" t="n">
         <v>62.42</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" s="7" t="n">
         <v>63.45</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="V21" s="7" t="n">
         <v>63.76</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="W21" s="7" t="n">
         <v>63.32</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="7" t="n">
         <v>64.31</v>
       </c>
-      <c r="Y21" s="6" t="n">
+      <c r="Y21" s="7" t="n">
         <v>64.64</v>
       </c>
-      <c r="Z21" s="6" t="n">
+      <c r="Z21" s="7" t="n">
         <v>62.4</v>
       </c>
-      <c r="AA21" s="6" t="n">
+      <c r="AA21" s="7" t="n">
         <v>62.14</v>
       </c>
-      <c r="AB21" s="6" t="n">
+      <c r="AB21" s="9" t="n">
         <v>48.92</v>
       </c>
-      <c r="AC21" s="6" t="n">
+      <c r="AC21" s="10" t="n">
         <v>42.56</v>
       </c>
-      <c r="AD21" s="6" t="n">
+      <c r="AD21" s="7" t="n">
         <v>54.18</v>
       </c>
-      <c r="AE21" s="6" t="n">
+      <c r="AE21" s="7" t="n">
         <v>64.91</v>
       </c>
-      <c r="AF21" s="6" t="n">
+      <c r="AF21" s="7" t="n">
         <v>65.55</v>
       </c>
-      <c r="AG21" s="6" t="n">
+      <c r="AG21" s="7" t="n">
         <v>66.41</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2111,7 +2144,7 @@
         <v>349.62</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="7" t="inlineStr"/>
+      <c r="AK21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2122,97 +2155,97 @@
       <c r="B22" s="6" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>59.55</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>67.94</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>61.62</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>62.62</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>57.23</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>56.89</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <v>57.64</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <v>61.28</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="7" t="n">
         <v>62.13</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M22" s="7" t="n">
         <v>59.85</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" s="7" t="n">
         <v>54.39</v>
       </c>
-      <c r="O22" s="6" t="n">
+      <c r="O22" s="7" t="n">
         <v>61.68</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P22" s="7" t="n">
         <v>58.36</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="7" t="n">
         <v>62.69</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R22" s="7" t="n">
         <v>60.4</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <v>58.01</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="T22" s="7" t="n">
         <v>54.16</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="U22" s="7" t="n">
         <v>54.15</v>
       </c>
-      <c r="V22" s="6" t="n">
+      <c r="V22" s="7" t="n">
         <v>56.63</v>
       </c>
-      <c r="W22" s="6" t="n">
+      <c r="W22" s="9" t="n">
         <v>53.21</v>
       </c>
-      <c r="X22" s="6" t="n">
+      <c r="X22" s="7" t="n">
         <v>57.21</v>
       </c>
-      <c r="Y22" s="6" t="n">
+      <c r="Y22" s="7" t="n">
         <v>55.49</v>
       </c>
-      <c r="Z22" s="6" t="n">
+      <c r="Z22" s="7" t="n">
         <v>56.56</v>
       </c>
-      <c r="AA22" s="6" t="n">
+      <c r="AA22" s="7" t="n">
         <v>57.02</v>
       </c>
-      <c r="AB22" s="6" t="n">
+      <c r="AB22" s="7" t="n">
         <v>56.89</v>
       </c>
-      <c r="AC22" s="6" t="n">
+      <c r="AC22" s="9" t="n">
         <v>51.04</v>
       </c>
-      <c r="AD22" s="6" t="n">
+      <c r="AD22" s="9" t="n">
         <v>45.58</v>
       </c>
-      <c r="AE22" s="6" t="n">
+      <c r="AE22" s="9" t="n">
         <v>45.66</v>
       </c>
-      <c r="AF22" s="6" t="n">
+      <c r="AF22" s="9" t="n">
         <v>48.05</v>
       </c>
-      <c r="AG22" s="6" t="n">
+      <c r="AG22" s="9" t="n">
         <v>47.09</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2222,7 +2255,7 @@
         <v>386.51</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="7" t="inlineStr"/>
+      <c r="AK22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2233,97 +2266,97 @@
       <c r="B23" s="6" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="7" t="n">
         <v>66.69</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>63.84</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>66.8</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>66.92</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <v>66.98999999999999</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="7" t="n">
         <v>66.62</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="7" t="n">
         <v>66.47</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K23" s="7" t="n">
         <v>65.03</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" s="7" t="n">
         <v>64.66</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M23" s="7" t="n">
         <v>63.94</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="7" t="n">
         <v>64.91</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="O23" s="7" t="n">
         <v>67.92</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="7" t="n">
         <v>67.19</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" s="7" t="n">
         <v>66.47</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="R23" s="7" t="n">
         <v>66.12</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="S23" s="7" t="n">
         <v>65.98</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" s="7" t="n">
         <v>66.42</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" s="7" t="n">
         <v>66.39</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="V23" s="7" t="n">
         <v>66.95</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" s="7" t="n">
         <v>66.5</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="7" t="n">
         <v>66.36</v>
       </c>
-      <c r="Y23" s="6" t="n">
+      <c r="Y23" s="7" t="n">
         <v>68.23999999999999</v>
       </c>
-      <c r="Z23" s="6" t="n">
+      <c r="Z23" s="7" t="n">
         <v>67.15000000000001</v>
       </c>
-      <c r="AA23" s="6" t="n">
+      <c r="AA23" s="7" t="n">
         <v>66.51000000000001</v>
       </c>
-      <c r="AB23" s="6" t="n">
+      <c r="AB23" s="7" t="n">
         <v>66.97</v>
       </c>
-      <c r="AC23" s="6" t="n">
+      <c r="AC23" s="7" t="n">
         <v>66.69</v>
       </c>
-      <c r="AD23" s="6" t="n">
+      <c r="AD23" s="7" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="AE23" s="6" t="n">
+      <c r="AE23" s="7" t="n">
         <v>68.13</v>
       </c>
-      <c r="AF23" s="6" t="n">
+      <c r="AF23" s="7" t="n">
         <v>67.72</v>
       </c>
-      <c r="AG23" s="6" t="n">
+      <c r="AG23" s="7" t="n">
         <v>66.70999999999999</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2333,7 +2366,7 @@
         <v>219.15</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="7" t="inlineStr"/>
+      <c r="AK23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2344,97 +2377,97 @@
       <c r="B24" s="6" t="n">
         <v>94.3</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="7" t="n">
         <v>64.47</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>65.97</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>61.84</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>65.23999999999999</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>64.51000000000001</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>64.92</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="7" t="n">
         <v>63.72</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="K24" s="7" t="n">
         <v>64.91</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" s="7" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="M24" s="7" t="n">
         <v>62.96</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" s="7" t="n">
         <v>65.09</v>
       </c>
-      <c r="O24" s="6" t="n">
+      <c r="O24" s="7" t="n">
         <v>66.59</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="P24" s="7" t="n">
         <v>65.03</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="7" t="n">
         <v>64.33</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R24" s="7" t="n">
         <v>64.14</v>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="7" t="n">
         <v>63.59</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="T24" s="7" t="n">
         <v>64.28</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="U24" s="7" t="n">
         <v>65.02</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="V24" s="7" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="W24" s="6" t="n">
+      <c r="W24" s="7" t="n">
         <v>64.38</v>
       </c>
-      <c r="X24" s="6" t="n">
+      <c r="X24" s="7" t="n">
         <v>64.44</v>
       </c>
-      <c r="Y24" s="6" t="n">
+      <c r="Y24" s="7" t="n">
         <v>66.12</v>
       </c>
-      <c r="Z24" s="6" t="n">
+      <c r="Z24" s="7" t="n">
         <v>63.82</v>
       </c>
-      <c r="AA24" s="6" t="n">
+      <c r="AA24" s="7" t="n">
         <v>65.09</v>
       </c>
-      <c r="AB24" s="6" t="n">
+      <c r="AB24" s="7" t="n">
         <v>65.8</v>
       </c>
-      <c r="AC24" s="6" t="n">
+      <c r="AC24" s="7" t="n">
         <v>64.81</v>
       </c>
-      <c r="AD24" s="6" t="n">
+      <c r="AD24" s="7" t="n">
         <v>65.23</v>
       </c>
-      <c r="AE24" s="6" t="n">
+      <c r="AE24" s="7" t="n">
         <v>66.12</v>
       </c>
-      <c r="AF24" s="6" t="n">
+      <c r="AF24" s="7" t="n">
         <v>66.22</v>
       </c>
-      <c r="AG24" s="6" t="n">
+      <c r="AG24" s="7" t="n">
         <v>64.79000000000001</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2444,7 +2477,7 @@
         <v>226.77</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="7" t="inlineStr"/>
+      <c r="AK24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2455,97 +2488,97 @@
       <c r="B25" s="6" t="n">
         <v>94.7</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="7" t="n">
         <v>68.70999999999999</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <v>69.70999999999999</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>64.47</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>68.54000000000001</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <v>69.23999999999999</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <v>68.8</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <v>68.68000000000001</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="7" t="n">
         <v>68.55</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="7" t="n">
         <v>68.83</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" s="7" t="n">
         <v>68.84</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M25" s="7" t="n">
         <v>67.37</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="7" t="n">
         <v>68.23999999999999</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="O25" s="7" t="n">
         <v>70.36</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="7" t="n">
         <v>68.37</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="7" t="n">
         <v>67.92</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="R25" s="7" t="n">
         <v>67.75</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="7" t="n">
         <v>68.11</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="T25" s="7" t="n">
         <v>67.22</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" s="7" t="n">
         <v>67.28</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="V25" s="7" t="n">
         <v>67.53</v>
       </c>
-      <c r="W25" s="6" t="n">
+      <c r="W25" s="7" t="n">
         <v>68.94</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" s="7" t="n">
         <v>69.02</v>
       </c>
-      <c r="Y25" s="6" t="n">
+      <c r="Y25" s="7" t="n">
         <v>69.25</v>
       </c>
-      <c r="Z25" s="6" t="n">
+      <c r="Z25" s="7" t="n">
         <v>68.22</v>
       </c>
-      <c r="AA25" s="6" t="n">
+      <c r="AA25" s="7" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="AB25" s="6" t="n">
+      <c r="AB25" s="7" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="AC25" s="6" t="n">
+      <c r="AC25" s="7" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="AD25" s="6" t="n">
+      <c r="AD25" s="7" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="AE25" s="6" t="n">
+      <c r="AE25" s="7" t="n">
         <v>68.78</v>
       </c>
-      <c r="AF25" s="6" t="n">
+      <c r="AF25" s="7" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="AG25" s="6" t="n">
+      <c r="AG25" s="7" t="n">
         <v>69.81</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2555,7 +2588,7 @@
         <v>123.83</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="7" t="inlineStr"/>
+      <c r="AK25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2566,97 +2599,97 @@
       <c r="B26" s="6" t="n">
         <v>95.5</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="7" t="n">
         <v>72.45999999999999</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>72.84</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>68.31999999999999</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>72.84999999999999</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>72.31999999999999</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="7" t="n">
         <v>75.09</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="7" t="n">
         <v>73.41</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="K26" s="7" t="n">
         <v>72.36</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" s="7" t="n">
         <v>71.86</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="M26" s="7" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="7" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="O26" s="6" t="n">
+      <c r="O26" s="7" t="n">
         <v>74.67</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="P26" s="7" t="n">
         <v>74.05</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="7" t="n">
         <v>73.43000000000001</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="R26" s="7" t="n">
         <v>72.98999999999999</v>
       </c>
-      <c r="S26" s="6" t="n">
+      <c r="S26" s="7" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="T26" s="7" t="n">
         <v>72.95</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="U26" s="7" t="n">
         <v>73.26000000000001</v>
       </c>
-      <c r="V26" s="6" t="n">
+      <c r="V26" s="7" t="n">
         <v>73.56999999999999</v>
       </c>
-      <c r="W26" s="6" t="n">
+      <c r="W26" s="7" t="n">
         <v>73.54000000000001</v>
       </c>
-      <c r="X26" s="6" t="n">
+      <c r="X26" s="7" t="n">
         <v>73.29000000000001</v>
       </c>
-      <c r="Y26" s="6" t="n">
+      <c r="Y26" s="7" t="n">
         <v>73.64</v>
       </c>
-      <c r="Z26" s="6" t="n">
+      <c r="Z26" s="7" t="n">
         <v>73.19</v>
       </c>
-      <c r="AA26" s="6" t="n">
+      <c r="AA26" s="7" t="n">
         <v>73.95999999999999</v>
       </c>
-      <c r="AB26" s="6" t="n">
+      <c r="AB26" s="7" t="n">
         <v>72.31</v>
       </c>
-      <c r="AC26" s="6" t="n">
+      <c r="AC26" s="7" t="n">
         <v>74.83</v>
       </c>
-      <c r="AD26" s="6" t="n">
+      <c r="AD26" s="7" t="n">
         <v>75.70999999999999</v>
       </c>
-      <c r="AE26" s="6" t="n">
+      <c r="AE26" s="7" t="n">
         <v>75.36</v>
       </c>
-      <c r="AF26" s="6" t="n">
+      <c r="AF26" s="7" t="n">
         <v>74.62</v>
       </c>
-      <c r="AG26" s="6" t="n">
+      <c r="AG26" s="7" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2666,7 +2699,7 @@
         <v>223.97</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="7" t="inlineStr"/>
+      <c r="AK26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2677,97 +2710,97 @@
       <c r="B27" s="6" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="7" t="n">
         <v>59.7</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <v>60.51</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="9" t="n">
         <v>52.24</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>59.5</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>58.86</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="7" t="n">
         <v>59.35</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="7" t="n">
         <v>60.09</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="7" t="n">
         <v>59.86</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="K27" s="7" t="n">
         <v>59.06</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="L27" s="7" t="n">
         <v>58.9</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="M27" s="7" t="n">
         <v>58.88</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="7" t="n">
         <v>59.69</v>
       </c>
-      <c r="O27" s="6" t="n">
+      <c r="O27" s="7" t="n">
         <v>61.22</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="P27" s="7" t="n">
         <v>60.84</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="7" t="n">
         <v>60.99</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="R27" s="7" t="n">
         <v>60.34</v>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="S27" s="7" t="n">
         <v>60.13</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="T27" s="7" t="n">
         <v>60.43</v>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U27" s="7" t="n">
         <v>60.52</v>
       </c>
-      <c r="V27" s="6" t="n">
+      <c r="V27" s="7" t="n">
         <v>60.23</v>
       </c>
-      <c r="W27" s="6" t="n">
+      <c r="W27" s="7" t="n">
         <v>60.95</v>
       </c>
-      <c r="X27" s="6" t="n">
+      <c r="X27" s="7" t="n">
         <v>60.09</v>
       </c>
-      <c r="Y27" s="6" t="n">
+      <c r="Y27" s="7" t="n">
         <v>60.41</v>
       </c>
-      <c r="Z27" s="6" t="n">
+      <c r="Z27" s="7" t="n">
         <v>59.08</v>
       </c>
-      <c r="AA27" s="6" t="n">
+      <c r="AA27" s="7" t="n">
         <v>59.89</v>
       </c>
-      <c r="AB27" s="6" t="n">
+      <c r="AB27" s="7" t="n">
         <v>60.36</v>
       </c>
-      <c r="AC27" s="6" t="n">
+      <c r="AC27" s="7" t="n">
         <v>60.82</v>
       </c>
-      <c r="AD27" s="6" t="n">
+      <c r="AD27" s="7" t="n">
         <v>60.08</v>
       </c>
-      <c r="AE27" s="6" t="n">
+      <c r="AE27" s="7" t="n">
         <v>60.62</v>
       </c>
-      <c r="AF27" s="6" t="n">
+      <c r="AF27" s="7" t="n">
         <v>61.02</v>
       </c>
-      <c r="AG27" s="6" t="n">
+      <c r="AG27" s="7" t="n">
         <v>60.81</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2777,7 +2810,7 @@
         <v>431.6</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="7" t="inlineStr"/>
+      <c r="AK27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2788,97 +2821,97 @@
       <c r="B28" s="6" t="n">
         <v>96.3</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="7" t="n">
         <v>60.55</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <v>62.42</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>64.69</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>62.36</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <v>62.31</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="7" t="n">
         <v>61.61</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="7" t="n">
         <v>62.62</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="7" t="n">
         <v>62.35</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="K28" s="7" t="n">
         <v>62.64</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L28" s="7" t="n">
         <v>64.14</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="M28" s="7" t="n">
         <v>61.74</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" s="7" t="n">
         <v>62.46</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="O28" s="7" t="n">
         <v>65.94</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P28" s="7" t="n">
         <v>65.22</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="7" t="n">
         <v>65.05</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R28" s="7" t="n">
         <v>60.73</v>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S28" s="7" t="n">
         <v>61.3</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="T28" s="7" t="n">
         <v>60.76</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="U28" s="7" t="n">
         <v>60.58</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="V28" s="7" t="n">
         <v>62.09</v>
       </c>
-      <c r="W28" s="6" t="n">
+      <c r="W28" s="7" t="n">
         <v>61.12</v>
       </c>
-      <c r="X28" s="6" t="n">
+      <c r="X28" s="7" t="n">
         <v>62.12</v>
       </c>
-      <c r="Y28" s="6" t="n">
+      <c r="Y28" s="7" t="n">
         <v>63.75</v>
       </c>
-      <c r="Z28" s="6" t="n">
+      <c r="Z28" s="7" t="n">
         <v>62.11</v>
       </c>
-      <c r="AA28" s="6" t="n">
+      <c r="AA28" s="7" t="n">
         <v>61.92</v>
       </c>
-      <c r="AB28" s="6" t="n">
+      <c r="AB28" s="7" t="n">
         <v>61.89</v>
       </c>
-      <c r="AC28" s="6" t="n">
+      <c r="AC28" s="7" t="n">
         <v>61.14</v>
       </c>
-      <c r="AD28" s="6" t="n">
+      <c r="AD28" s="7" t="n">
         <v>62.76</v>
       </c>
-      <c r="AE28" s="6" t="n">
+      <c r="AE28" s="7" t="n">
         <v>62.2</v>
       </c>
-      <c r="AF28" s="6" t="n">
+      <c r="AF28" s="7" t="n">
         <v>63.74</v>
       </c>
-      <c r="AG28" s="6" t="n">
+      <c r="AG28" s="7" t="n">
         <v>63.46</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -2888,7 +2921,7 @@
         <v>478.51</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="7" t="inlineStr"/>
+      <c r="AK28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2899,97 +2932,97 @@
       <c r="B29" s="6" t="n">
         <v>96.7</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="7" t="n">
         <v>70.28</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>62.02</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>70.8</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <v>70.56</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="7" t="n">
         <v>70.36</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="7" t="n">
         <v>70.59</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="7" t="n">
         <v>69.28</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="K29" s="7" t="n">
         <v>70.34999999999999</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="L29" s="7" t="n">
         <v>70.55</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="M29" s="7" t="n">
         <v>70.64</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N29" s="7" t="n">
         <v>70.33</v>
       </c>
-      <c r="O29" s="6" t="n">
+      <c r="O29" s="7" t="n">
         <v>69.48</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="P29" s="7" t="n">
         <v>69.92</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="Q29" s="7" t="n">
         <v>69.95</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="R29" s="7" t="n">
         <v>70.45</v>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="S29" s="7" t="n">
         <v>70.41</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="T29" s="7" t="n">
         <v>70.81999999999999</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="U29" s="7" t="n">
         <v>71.41</v>
       </c>
-      <c r="V29" s="6" t="n">
+      <c r="V29" s="7" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="W29" s="6" t="n">
+      <c r="W29" s="7" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="X29" s="7" t="n">
         <v>70.38</v>
       </c>
-      <c r="Y29" s="6" t="n">
+      <c r="Y29" s="7" t="n">
         <v>70.62</v>
       </c>
-      <c r="Z29" s="6" t="n">
+      <c r="Z29" s="7" t="n">
         <v>70.51000000000001</v>
       </c>
-      <c r="AA29" s="6" t="n">
+      <c r="AA29" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="AB29" s="6" t="n">
+      <c r="AB29" s="7" t="n">
         <v>71.16</v>
       </c>
-      <c r="AC29" s="6" t="n">
+      <c r="AC29" s="7" t="n">
         <v>70.77</v>
       </c>
-      <c r="AD29" s="6" t="n">
+      <c r="AD29" s="7" t="n">
         <v>71.01000000000001</v>
       </c>
-      <c r="AE29" s="6" t="n">
+      <c r="AE29" s="7" t="n">
         <v>71.12</v>
       </c>
-      <c r="AF29" s="6" t="n">
+      <c r="AF29" s="7" t="n">
         <v>71.72</v>
       </c>
-      <c r="AG29" s="6" t="n">
+      <c r="AG29" s="7" t="n">
         <v>70.56</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -2999,7 +3032,7 @@
         <v>258.64</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="7" t="inlineStr"/>
+      <c r="AK29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3010,97 +3043,97 @@
       <c r="B30" s="6" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="7" t="n">
         <v>69.62</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>69.25</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>61.6</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>70.01000000000001</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>69.61</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="7" t="n">
         <v>68.84999999999999</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="7" t="n">
         <v>69.55</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="7" t="n">
         <v>58.66</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="K30" s="7" t="n">
         <v>68.88</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="L30" s="7" t="n">
         <v>69.31</v>
       </c>
-      <c r="M30" s="6" t="n">
+      <c r="M30" s="7" t="n">
         <v>69.06999999999999</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="7" t="n">
         <v>69.09</v>
       </c>
-      <c r="O30" s="6" t="n">
+      <c r="O30" s="7" t="n">
         <v>67.34</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="P30" s="7" t="n">
         <v>67.97</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="Q30" s="7" t="n">
         <v>67.03</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="R30" s="7" t="n">
         <v>68.8</v>
       </c>
-      <c r="S30" s="6" t="n">
+      <c r="S30" s="7" t="n">
         <v>68.91</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="T30" s="7" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="U30" s="6" t="n">
+      <c r="U30" s="7" t="n">
         <v>69.41</v>
       </c>
-      <c r="V30" s="6" t="n">
+      <c r="V30" s="7" t="n">
         <v>68.5</v>
       </c>
-      <c r="W30" s="6" t="n">
+      <c r="W30" s="7" t="n">
         <v>68.97</v>
       </c>
-      <c r="X30" s="6" t="n">
+      <c r="X30" s="7" t="n">
         <v>69.33</v>
       </c>
-      <c r="Y30" s="6" t="n">
+      <c r="Y30" s="7" t="n">
         <v>68.73</v>
       </c>
-      <c r="Z30" s="6" t="n">
+      <c r="Z30" s="7" t="n">
         <v>69.65000000000001</v>
       </c>
-      <c r="AA30" s="6" t="n">
+      <c r="AA30" s="7" t="n">
         <v>68.75</v>
       </c>
-      <c r="AB30" s="6" t="n">
+      <c r="AB30" s="7" t="n">
         <v>69.12</v>
       </c>
-      <c r="AC30" s="6" t="n">
+      <c r="AC30" s="7" t="n">
         <v>69.88</v>
       </c>
-      <c r="AD30" s="6" t="n">
+      <c r="AD30" s="7" t="n">
         <v>70.22</v>
       </c>
-      <c r="AE30" s="6" t="n">
+      <c r="AE30" s="7" t="n">
         <v>70.36</v>
       </c>
-      <c r="AF30" s="6" t="n">
+      <c r="AF30" s="7" t="n">
         <v>71.01000000000001</v>
       </c>
-      <c r="AG30" s="6" t="n">
+      <c r="AG30" s="7" t="n">
         <v>69.2</v>
       </c>
       <c r="AH30" s="6" t="n">
@@ -3110,7 +3143,7 @@
         <v>254.74</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="7" t="inlineStr"/>
+      <c r="AK30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3121,97 +3154,97 @@
       <c r="B31" s="6" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="9" t="n">
         <v>49.18</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="10" t="n">
         <v>38.17</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="10" t="n">
         <v>39.78</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>48.22</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>45.28</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>47.81</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="9" t="n">
         <v>46.02</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>47.37</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="L31" s="9" t="n">
         <v>45.26</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>49.09</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="O31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>47.71</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P31" s="9" t="n">
         <v>53.23</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>43.31</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="R31" s="10" t="n">
         <v>42.73</v>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="S31" s="10" t="n">
         <v>36.38</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="T31" s="10" t="n">
         <v>42.77</v>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="U31" s="10" t="n">
         <v>40.38</v>
       </c>
-      <c r="V31" s="6" t="n">
+      <c r="V31" s="9" t="n">
         <v>44.49</v>
       </c>
-      <c r="W31" s="6" t="n">
+      <c r="W31" s="9" t="n">
         <v>45.69</v>
       </c>
-      <c r="X31" s="6" t="n">
+      <c r="X31" s="9" t="n">
         <v>45.4</v>
       </c>
-      <c r="Y31" s="6" t="n">
+      <c r="Y31" s="10" t="n">
         <v>40.74</v>
       </c>
-      <c r="Z31" s="6" t="n">
+      <c r="Z31" s="10" t="n">
         <v>41.24</v>
       </c>
-      <c r="AA31" s="6" t="n">
+      <c r="AA31" s="10" t="n">
         <v>41.48</v>
       </c>
-      <c r="AB31" s="6" t="n">
+      <c r="AB31" s="10" t="n">
         <v>42.87</v>
       </c>
-      <c r="AC31" s="6" t="n">
+      <c r="AC31" s="9" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="6" t="n">
+      <c r="AD31" s="10" t="n">
         <v>40.41</v>
       </c>
-      <c r="AE31" s="6" t="n">
+      <c r="AE31" s="9" t="n">
         <v>47.34</v>
       </c>
-      <c r="AF31" s="6" t="n">
+      <c r="AF31" s="9" t="n">
         <v>51.7</v>
       </c>
-      <c r="AG31" s="6" t="n">
+      <c r="AG31" s="9" t="n">
         <v>45.77</v>
       </c>
       <c r="AH31" s="6" t="n">
@@ -3221,7 +3254,7 @@
         <v>485.2</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="7" t="inlineStr"/>
+      <c r="AK31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3232,97 +3265,97 @@
       <c r="B32" s="6" t="n">
         <v>98.7</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="7" t="n">
         <v>56.19</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <v>55.07</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="9" t="n">
         <v>52.52</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>56.21</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <v>55.69</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="7" t="n">
         <v>54.63</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="7" t="n">
         <v>54.37</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="K32" s="7" t="n">
         <v>55.76</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="L32" s="7" t="n">
         <v>55.24</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="M32" s="7" t="n">
         <v>56.34</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N32" s="7" t="n">
         <v>56.26</v>
       </c>
-      <c r="O32" s="6" t="n">
+      <c r="O32" s="7" t="n">
         <v>54.48</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="P32" s="7" t="n">
         <v>54.57</v>
       </c>
-      <c r="Q32" s="6" t="n">
+      <c r="Q32" s="7" t="n">
         <v>54.34</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="R32" s="7" t="n">
         <v>55.11</v>
       </c>
-      <c r="S32" s="6" t="n">
+      <c r="S32" s="7" t="n">
         <v>54.74</v>
       </c>
-      <c r="T32" s="6" t="n">
+      <c r="T32" s="7" t="n">
         <v>55.15</v>
       </c>
-      <c r="U32" s="6" t="n">
+      <c r="U32" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="V32" s="6" t="n">
+      <c r="V32" s="7" t="n">
         <v>56.91</v>
       </c>
-      <c r="W32" s="6" t="n">
+      <c r="W32" s="7" t="n">
         <v>57.04</v>
       </c>
-      <c r="X32" s="6" t="n">
+      <c r="X32" s="7" t="n">
         <v>56.21</v>
       </c>
-      <c r="Y32" s="6" t="n">
+      <c r="Y32" s="7" t="n">
         <v>55.12</v>
       </c>
-      <c r="Z32" s="6" t="n">
+      <c r="Z32" s="7" t="n">
         <v>56.95</v>
       </c>
-      <c r="AA32" s="6" t="n">
+      <c r="AA32" s="7" t="n">
         <v>55.64</v>
       </c>
-      <c r="AB32" s="6" t="n">
+      <c r="AB32" s="7" t="n">
         <v>56.39</v>
       </c>
-      <c r="AC32" s="6" t="n">
+      <c r="AC32" s="7" t="n">
         <v>57.72</v>
       </c>
-      <c r="AD32" s="6" t="n">
+      <c r="AD32" s="7" t="n">
         <v>55.58</v>
       </c>
-      <c r="AE32" s="6" t="n">
+      <c r="AE32" s="7" t="n">
         <v>57.07</v>
       </c>
-      <c r="AF32" s="6" t="n">
+      <c r="AF32" s="7" t="n">
         <v>57.31</v>
       </c>
-      <c r="AG32" s="6" t="n">
+      <c r="AG32" s="7" t="n">
         <v>55.64</v>
       </c>
       <c r="AH32" s="6" t="n">
@@ -3332,7 +3365,7 @@
         <v>474.57</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="7" t="inlineStr"/>
+      <c r="AK32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3343,97 +3376,97 @@
       <c r="B33" s="6" t="n">
         <v>99.5</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C33" s="7" t="n">
         <v>76.2</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="7" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>75.94</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>75.91</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="7" t="n">
         <v>77.06</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="7" t="n">
         <v>76.61</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="7" t="n">
         <v>76.84999999999999</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="7" t="n">
         <v>76.97</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K33" s="7" t="n">
         <v>77.41</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="L33" s="7" t="n">
         <v>76.81</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="M33" s="7" t="n">
         <v>76.91</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="7" t="n">
         <v>77.29000000000001</v>
       </c>
-      <c r="O33" s="6" t="n">
+      <c r="O33" s="7" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="P33" s="7" t="n">
         <v>76.81999999999999</v>
       </c>
-      <c r="Q33" s="6" t="n">
+      <c r="Q33" s="7" t="n">
         <v>76.93000000000001</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="R33" s="7" t="n">
         <v>76.72</v>
       </c>
-      <c r="S33" s="6" t="n">
+      <c r="S33" s="7" t="n">
         <v>77.2</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="T33" s="7" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="U33" s="7" t="n">
         <v>77.56999999999999</v>
       </c>
-      <c r="V33" s="6" t="n">
+      <c r="V33" s="7" t="n">
         <v>77.09</v>
       </c>
-      <c r="W33" s="6" t="n">
+      <c r="W33" s="7" t="n">
         <v>76.53</v>
       </c>
-      <c r="X33" s="6" t="n">
+      <c r="X33" s="7" t="n">
         <v>77.14</v>
       </c>
-      <c r="Y33" s="6" t="n">
+      <c r="Y33" s="7" t="n">
         <v>77.29000000000001</v>
       </c>
-      <c r="Z33" s="6" t="n">
+      <c r="Z33" s="7" t="n">
         <v>76.73999999999999</v>
       </c>
-      <c r="AA33" s="6" t="n">
+      <c r="AA33" s="7" t="n">
         <v>76.45</v>
       </c>
-      <c r="AB33" s="6" t="n">
+      <c r="AB33" s="7" t="n">
         <v>77.54000000000001</v>
       </c>
-      <c r="AC33" s="6" t="n">
+      <c r="AC33" s="7" t="n">
         <v>77.26000000000001</v>
       </c>
-      <c r="AD33" s="6" t="n">
+      <c r="AD33" s="7" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="AE33" s="6" t="n">
+      <c r="AE33" s="7" t="n">
         <v>77.01000000000001</v>
       </c>
-      <c r="AF33" s="6" t="n">
+      <c r="AF33" s="7" t="n">
         <v>77.08</v>
       </c>
-      <c r="AG33" s="6" t="n">
+      <c r="AG33" s="7" t="n">
         <v>76.45999999999999</v>
       </c>
       <c r="AH33" s="6" t="n">
@@ -3443,7 +3476,7 @@
         <v>326</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="7" t="inlineStr"/>
+      <c r="AK33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3454,97 +3487,97 @@
       <c r="B34" s="6" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C34" s="7" t="n">
         <v>62.49</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="7" t="n">
         <v>65.53</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>56.56</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <v>66.03</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="7" t="n">
         <v>65.11</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="7" t="n">
         <v>65.84999999999999</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="7" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="K34" s="7" t="n">
         <v>66.03</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="L34" s="7" t="n">
         <v>66.95999999999999</v>
       </c>
-      <c r="M34" s="6" t="n">
+      <c r="M34" s="7" t="n">
         <v>65.37</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="N34" s="7" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="O34" s="6" t="n">
+      <c r="O34" s="7" t="n">
         <v>66.78</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="P34" s="7" t="n">
         <v>66.86</v>
       </c>
-      <c r="Q34" s="6" t="n">
+      <c r="Q34" s="7" t="n">
         <v>65.68000000000001</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="R34" s="7" t="n">
         <v>66.78</v>
       </c>
-      <c r="S34" s="6" t="n">
+      <c r="S34" s="7" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="T34" s="7" t="n">
         <v>65.76000000000001</v>
       </c>
-      <c r="U34" s="6" t="n">
+      <c r="U34" s="7" t="n">
         <v>66.04000000000001</v>
       </c>
-      <c r="V34" s="6" t="n">
+      <c r="V34" s="7" t="n">
         <v>66.42</v>
       </c>
-      <c r="W34" s="6" t="n">
+      <c r="W34" s="7" t="n">
         <v>67.48</v>
       </c>
-      <c r="X34" s="6" t="n">
+      <c r="X34" s="7" t="n">
         <v>68.12</v>
       </c>
-      <c r="Y34" s="6" t="n">
+      <c r="Y34" s="7" t="n">
         <v>68.37</v>
       </c>
-      <c r="Z34" s="6" t="n">
+      <c r="Z34" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="AA34" s="6" t="n">
+      <c r="AA34" s="7" t="n">
         <v>66.53</v>
       </c>
-      <c r="AB34" s="6" t="n">
+      <c r="AB34" s="7" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="AC34" s="6" t="n">
+      <c r="AC34" s="7" t="n">
         <v>67.56999999999999</v>
       </c>
-      <c r="AD34" s="6" t="n">
+      <c r="AD34" s="7" t="n">
         <v>67.37</v>
       </c>
-      <c r="AE34" s="6" t="n">
+      <c r="AE34" s="7" t="n">
         <v>66.8</v>
       </c>
-      <c r="AF34" s="6" t="n">
+      <c r="AF34" s="7" t="n">
         <v>64.17</v>
       </c>
-      <c r="AG34" s="6" t="n">
+      <c r="AG34" s="7" t="n">
         <v>67.31999999999999</v>
       </c>
       <c r="AH34" s="6" t="n">
@@ -3554,7 +3587,7 @@
         <v>478.65</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="7" t="inlineStr"/>
+      <c r="AK34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3565,97 +3598,97 @@
       <c r="B35" s="6" t="n">
         <v>100.3</v>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C35" s="7" t="n">
         <v>61.94</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="7" t="n">
         <v>61.37</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>64.2</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>61.69</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <v>61.82</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <v>62.42</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="7" t="n">
         <v>59.68</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="7" t="n">
         <v>60.43</v>
       </c>
-      <c r="K35" s="6" t="n">
+      <c r="K35" s="7" t="n">
         <v>58.74</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="L35" s="7" t="n">
         <v>60.15</v>
       </c>
-      <c r="M35" s="6" t="n">
+      <c r="M35" s="7" t="n">
         <v>61.25</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="7" t="n">
         <v>59.7</v>
       </c>
-      <c r="O35" s="6" t="n">
+      <c r="O35" s="7" t="n">
         <v>61.84</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="P35" s="7" t="n">
         <v>61.41</v>
       </c>
-      <c r="Q35" s="6" t="n">
+      <c r="Q35" s="7" t="n">
         <v>59.86</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="R35" s="7" t="n">
         <v>59.32</v>
       </c>
-      <c r="S35" s="6" t="n">
+      <c r="S35" s="7" t="n">
         <v>60.75</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="T35" s="7" t="n">
         <v>58.68</v>
       </c>
-      <c r="U35" s="6" t="n">
+      <c r="U35" s="7" t="n">
         <v>57.96</v>
       </c>
-      <c r="V35" s="6" t="n">
+      <c r="V35" s="7" t="n">
         <v>59.95</v>
       </c>
-      <c r="W35" s="6" t="n">
+      <c r="W35" s="7" t="n">
         <v>58.4</v>
       </c>
-      <c r="X35" s="6" t="n">
+      <c r="X35" s="7" t="n">
         <v>59.2</v>
       </c>
-      <c r="Y35" s="6" t="n">
+      <c r="Y35" s="7" t="n">
         <v>59.93</v>
       </c>
-      <c r="Z35" s="6" t="n">
+      <c r="Z35" s="7" t="n">
         <v>57.76</v>
       </c>
-      <c r="AA35" s="6" t="n">
+      <c r="AA35" s="7" t="n">
         <v>59.89</v>
       </c>
-      <c r="AB35" s="6" t="n">
+      <c r="AB35" s="7" t="n">
         <v>61.02</v>
       </c>
-      <c r="AC35" s="6" t="n">
+      <c r="AC35" s="7" t="n">
         <v>60.55</v>
       </c>
-      <c r="AD35" s="6" t="n">
+      <c r="AD35" s="7" t="n">
         <v>61.73</v>
       </c>
-      <c r="AE35" s="6" t="n">
+      <c r="AE35" s="7" t="n">
         <v>60.34</v>
       </c>
-      <c r="AF35" s="6" t="n">
+      <c r="AF35" s="7" t="n">
         <v>59.4</v>
       </c>
-      <c r="AG35" s="6" t="n">
+      <c r="AG35" s="7" t="n">
         <v>61.26</v>
       </c>
       <c r="AH35" s="6" t="n">
@@ -3665,7 +3698,7 @@
         <v>497.28</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="7" t="inlineStr"/>
+      <c r="AK35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3676,97 +3709,97 @@
       <c r="B36" s="6" t="n">
         <v>100.7</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="7" t="n">
         <v>65.72</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="7" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>62.38</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>66.23999999999999</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="7" t="n">
         <v>66.14</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="7" t="n">
         <v>66.20999999999999</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="7" t="n">
         <v>65.55</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="K36" s="7" t="n">
         <v>66.36</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L36" s="7" t="n">
         <v>65.69</v>
       </c>
-      <c r="M36" s="6" t="n">
+      <c r="M36" s="7" t="n">
         <v>65.42</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="7" t="n">
         <v>64.47</v>
       </c>
-      <c r="O36" s="6" t="n">
+      <c r="O36" s="7" t="n">
         <v>66.12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="P36" s="7" t="n">
         <v>66.12</v>
       </c>
-      <c r="Q36" s="6" t="n">
+      <c r="Q36" s="7" t="n">
         <v>66.02</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="R36" s="7" t="n">
         <v>65.45</v>
       </c>
-      <c r="S36" s="6" t="n">
+      <c r="S36" s="7" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="T36" s="6" t="n">
+      <c r="T36" s="7" t="n">
         <v>65.39</v>
       </c>
-      <c r="U36" s="6" t="n">
+      <c r="U36" s="7" t="n">
         <v>64.59</v>
       </c>
-      <c r="V36" s="6" t="n">
+      <c r="V36" s="7" t="n">
         <v>65.04000000000001</v>
       </c>
-      <c r="W36" s="6" t="n">
+      <c r="W36" s="7" t="n">
         <v>64.38</v>
       </c>
-      <c r="X36" s="6" t="n">
+      <c r="X36" s="7" t="n">
         <v>64.47</v>
       </c>
-      <c r="Y36" s="6" t="n">
+      <c r="Y36" s="7" t="n">
         <v>65.12</v>
       </c>
-      <c r="Z36" s="6" t="n">
+      <c r="Z36" s="7" t="n">
         <v>63.69</v>
       </c>
-      <c r="AA36" s="6" t="n">
+      <c r="AA36" s="7" t="n">
         <v>64.76000000000001</v>
       </c>
-      <c r="AB36" s="6" t="n">
+      <c r="AB36" s="7" t="n">
         <v>64.67</v>
       </c>
-      <c r="AC36" s="6" t="n">
+      <c r="AC36" s="7" t="n">
         <v>64.2</v>
       </c>
-      <c r="AD36" s="6" t="n">
+      <c r="AD36" s="7" t="n">
         <v>64.52</v>
       </c>
-      <c r="AE36" s="6" t="n">
+      <c r="AE36" s="7" t="n">
         <v>65.34999999999999</v>
       </c>
-      <c r="AF36" s="6" t="n">
+      <c r="AF36" s="7" t="n">
         <v>65.12</v>
       </c>
-      <c r="AG36" s="6" t="n">
+      <c r="AG36" s="7" t="n">
         <v>65.62</v>
       </c>
       <c r="AH36" s="6" t="n">
@@ -3776,7 +3809,7 @@
         <v>431.37</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="7" t="inlineStr"/>
+      <c r="AK36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3787,97 +3820,97 @@
       <c r="B37" s="6" t="n">
         <v>101.1</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C37" s="10" t="n">
         <v>41.52</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="10" t="n">
         <v>37.06</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="10" t="n">
         <v>39.89</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="10" t="n">
         <v>41.01</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="10" t="n">
         <v>40.08</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="10" t="n">
         <v>41.32</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="10" t="n">
         <v>40.03</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="10" t="n">
         <v>40.92</v>
       </c>
-      <c r="K37" s="6" t="n">
+      <c r="K37" s="10" t="n">
         <v>39.57</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="L37" s="10" t="n">
         <v>40.51</v>
       </c>
-      <c r="M37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>44.43</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="10" t="n">
         <v>40.55</v>
       </c>
-      <c r="O37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>43.01</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="P37" s="9" t="n">
         <v>43.79</v>
       </c>
-      <c r="Q37" s="6" t="n">
+      <c r="Q37" s="10" t="n">
         <v>40.86</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="R37" s="10" t="n">
         <v>36.73</v>
       </c>
-      <c r="S37" s="6" t="n">
+      <c r="S37" s="10" t="n">
         <v>36.76</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="T37" s="10" t="n">
         <v>38.71</v>
       </c>
-      <c r="U37" s="6" t="n">
+      <c r="U37" s="10" t="n">
         <v>36.86</v>
       </c>
-      <c r="V37" s="6" t="n">
+      <c r="V37" s="10" t="n">
         <v>40.22</v>
       </c>
-      <c r="W37" s="6" t="n">
+      <c r="W37" s="10" t="n">
         <v>40.92</v>
       </c>
-      <c r="X37" s="6" t="n">
+      <c r="X37" s="10" t="n">
         <v>39.83</v>
       </c>
-      <c r="Y37" s="6" t="n">
+      <c r="Y37" s="10" t="n">
         <v>37.26</v>
       </c>
-      <c r="Z37" s="6" t="n">
+      <c r="Z37" s="10" t="n">
         <v>38.74</v>
       </c>
-      <c r="AA37" s="6" t="n">
+      <c r="AA37" s="10" t="n">
         <v>37.96</v>
       </c>
-      <c r="AB37" s="6" t="n">
+      <c r="AB37" s="10" t="n">
         <v>41.61</v>
       </c>
-      <c r="AC37" s="6" t="n">
+      <c r="AC37" s="10" t="n">
         <v>41.84</v>
       </c>
-      <c r="AD37" s="6" t="n">
+      <c r="AD37" s="10" t="n">
         <v>38.69</v>
       </c>
-      <c r="AE37" s="6" t="n">
+      <c r="AE37" s="10" t="n">
         <v>41.51</v>
       </c>
-      <c r="AF37" s="6" t="n">
+      <c r="AF37" s="10" t="n">
         <v>41.72</v>
       </c>
-      <c r="AG37" s="6" t="n">
+      <c r="AG37" s="10" t="n">
         <v>41.58</v>
       </c>
       <c r="AH37" s="6" t="n">
@@ -3887,7 +3920,7 @@
         <v>499.53</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="7" t="inlineStr"/>
+      <c r="AK37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3898,97 +3931,97 @@
       <c r="B38" s="6" t="n">
         <v>101.5</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C38" s="7" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="7" t="n">
         <v>77.16</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>77.88</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="7" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="7" t="n">
         <v>77.70999999999999</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="7" t="n">
         <v>77.22</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="7" t="n">
         <v>77.28</v>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="K38" s="7" t="n">
         <v>77.56</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="L38" s="7" t="n">
         <v>77.36</v>
       </c>
-      <c r="M38" s="6" t="n">
+      <c r="M38" s="7" t="n">
         <v>77.15000000000001</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N38" s="7" t="n">
         <v>77.54000000000001</v>
       </c>
-      <c r="O38" s="6" t="n">
+      <c r="O38" s="7" t="n">
         <v>77.86</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="P38" s="7" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="Q38" s="7" t="n">
         <v>77.11</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="R38" s="7" t="n">
         <v>77.11</v>
       </c>
-      <c r="S38" s="6" t="n">
+      <c r="S38" s="7" t="n">
         <v>77.18000000000001</v>
       </c>
-      <c r="T38" s="6" t="n">
+      <c r="T38" s="7" t="n">
         <v>77.28</v>
       </c>
-      <c r="U38" s="6" t="n">
+      <c r="U38" s="7" t="n">
         <v>77.53</v>
       </c>
-      <c r="V38" s="6" t="n">
+      <c r="V38" s="7" t="n">
         <v>77.73</v>
       </c>
-      <c r="W38" s="6" t="n">
+      <c r="W38" s="7" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="X38" s="6" t="n">
+      <c r="X38" s="7" t="n">
         <v>77.02</v>
       </c>
-      <c r="Y38" s="6" t="n">
+      <c r="Y38" s="7" t="n">
         <v>77.03</v>
       </c>
-      <c r="Z38" s="6" t="n">
+      <c r="Z38" s="7" t="n">
         <v>77.04000000000001</v>
       </c>
-      <c r="AA38" s="6" t="n">
+      <c r="AA38" s="7" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="AB38" s="6" t="n">
+      <c r="AB38" s="7" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="AC38" s="6" t="n">
+      <c r="AC38" s="7" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="AD38" s="6" t="n">
+      <c r="AD38" s="7" t="n">
         <v>77.84</v>
       </c>
-      <c r="AE38" s="6" t="n">
+      <c r="AE38" s="7" t="n">
         <v>78.12</v>
       </c>
-      <c r="AF38" s="6" t="n">
+      <c r="AF38" s="7" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="AG38" s="6" t="n">
+      <c r="AG38" s="7" t="n">
         <v>77.81</v>
       </c>
       <c r="AH38" s="6" t="n">
@@ -3998,7 +4031,7 @@
         <v>159.74</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="7" t="inlineStr"/>
+      <c r="AK38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4009,97 +4042,97 @@
       <c r="B39" s="6" t="n">
         <v>102.3</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C39" s="7" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="7" t="n">
         <v>70.63</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <v>66.64</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>71.08</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <v>71.31999999999999</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <v>71.18000000000001</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" s="7" t="n">
         <v>71.13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="7" t="n">
         <v>71.28</v>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="7" t="n">
         <v>71.3</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="L39" s="7" t="n">
         <v>71.34999999999999</v>
       </c>
-      <c r="M39" s="6" t="n">
+      <c r="M39" s="7" t="n">
         <v>70.84</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="7" t="n">
         <v>71.38</v>
       </c>
-      <c r="O39" s="6" t="n">
+      <c r="O39" s="7" t="n">
         <v>71.52</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="P39" s="7" t="n">
         <v>72.11</v>
       </c>
-      <c r="Q39" s="6" t="n">
+      <c r="Q39" s="7" t="n">
         <v>71.31999999999999</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="R39" s="7" t="n">
         <v>70.79000000000001</v>
       </c>
-      <c r="S39" s="6" t="n">
+      <c r="S39" s="7" t="n">
         <v>71.26000000000001</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="T39" s="7" t="n">
         <v>71.37</v>
       </c>
-      <c r="U39" s="6" t="n">
+      <c r="U39" s="7" t="n">
         <v>71.91</v>
       </c>
-      <c r="V39" s="6" t="n">
+      <c r="V39" s="7" t="n">
         <v>72.36</v>
       </c>
-      <c r="W39" s="6" t="n">
+      <c r="W39" s="7" t="n">
         <v>71.31</v>
       </c>
-      <c r="X39" s="6" t="n">
+      <c r="X39" s="7" t="n">
         <v>71.27</v>
       </c>
-      <c r="Y39" s="6" t="n">
+      <c r="Y39" s="7" t="n">
         <v>71.64</v>
       </c>
-      <c r="Z39" s="6" t="n">
+      <c r="Z39" s="7" t="n">
         <v>71.56</v>
       </c>
-      <c r="AA39" s="6" t="n">
+      <c r="AA39" s="7" t="n">
         <v>72.79000000000001</v>
       </c>
-      <c r="AB39" s="6" t="n">
+      <c r="AB39" s="7" t="n">
         <v>71.95</v>
       </c>
-      <c r="AC39" s="6" t="n">
+      <c r="AC39" s="7" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="AD39" s="6" t="n">
+      <c r="AD39" s="7" t="n">
         <v>72.06</v>
       </c>
-      <c r="AE39" s="6" t="n">
+      <c r="AE39" s="7" t="n">
         <v>73.04000000000001</v>
       </c>
-      <c r="AF39" s="6" t="n">
+      <c r="AF39" s="7" t="n">
         <v>72.36</v>
       </c>
-      <c r="AG39" s="6" t="n">
+      <c r="AG39" s="7" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="AH39" s="6" t="n">
@@ -4109,7 +4142,7 @@
         <v>422.29</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="7" t="inlineStr"/>
+      <c r="AK39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4120,97 +4153,97 @@
       <c r="B40" s="6" t="n">
         <v>102.7</v>
       </c>
-      <c r="C40" s="6" t="n">
+      <c r="C40" s="7" t="n">
         <v>58.14</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="7" t="n">
         <v>57.6</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>62.89</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="7" t="n">
         <v>57.41</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="7" t="n">
         <v>57.04</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="7" t="n">
         <v>56.29</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I40" s="7" t="n">
         <v>57.62</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="7" t="n">
         <v>57.9</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="K40" s="7" t="n">
         <v>57.87</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="L40" s="7" t="n">
         <v>58.19</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="M40" s="7" t="n">
         <v>59.66</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="7" t="n">
         <v>57.31</v>
       </c>
-      <c r="O40" s="6" t="n">
+      <c r="O40" s="7" t="n">
         <v>57.81</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="P40" s="7" t="n">
         <v>58.09</v>
       </c>
-      <c r="Q40" s="6" t="n">
+      <c r="Q40" s="7" t="n">
         <v>59.71</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="R40" s="7" t="n">
         <v>58.68</v>
       </c>
-      <c r="S40" s="6" t="n">
+      <c r="S40" s="7" t="n">
         <v>58.13</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="T40" s="7" t="n">
         <v>58.57</v>
       </c>
-      <c r="U40" s="6" t="n">
+      <c r="U40" s="7" t="n">
         <v>58.45</v>
       </c>
-      <c r="V40" s="6" t="n">
+      <c r="V40" s="7" t="n">
         <v>58.68</v>
       </c>
-      <c r="W40" s="6" t="n">
+      <c r="W40" s="7" t="n">
         <v>58.76</v>
       </c>
-      <c r="X40" s="6" t="n">
+      <c r="X40" s="7" t="n">
         <v>58.66</v>
       </c>
-      <c r="Y40" s="6" t="n">
+      <c r="Y40" s="7" t="n">
         <v>58.76</v>
       </c>
-      <c r="Z40" s="6" t="n">
+      <c r="Z40" s="7" t="n">
         <v>56.95</v>
       </c>
-      <c r="AA40" s="6" t="n">
+      <c r="AA40" s="7" t="n">
         <v>58.78</v>
       </c>
-      <c r="AB40" s="6" t="n">
+      <c r="AB40" s="7" t="n">
         <v>59.01</v>
       </c>
-      <c r="AC40" s="6" t="n">
+      <c r="AC40" s="7" t="n">
         <v>58.66</v>
       </c>
-      <c r="AD40" s="6" t="n">
+      <c r="AD40" s="7" t="n">
         <v>58.24</v>
       </c>
-      <c r="AE40" s="6" t="n">
+      <c r="AE40" s="7" t="n">
         <v>58.16</v>
       </c>
-      <c r="AF40" s="6" t="n">
+      <c r="AF40" s="7" t="n">
         <v>58.82</v>
       </c>
-      <c r="AG40" s="6" t="n">
+      <c r="AG40" s="7" t="n">
         <v>58.96</v>
       </c>
       <c r="AH40" s="6" t="n">
@@ -4220,7 +4253,7 @@
         <v>471.03</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="7" t="inlineStr"/>
+      <c r="AK40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4231,97 +4264,97 @@
       <c r="B41" s="6" t="n">
         <v>103.1</v>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C41" s="9" t="n">
         <v>46.72</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="10" t="n">
         <v>35.76</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="10" t="n">
         <v>36.4</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>45.76</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>43.98</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>45.91</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" s="10" t="n">
         <v>42.62</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="9" t="n">
         <v>44.54</v>
       </c>
-      <c r="K41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>43.32</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="L41" s="9" t="n">
         <v>43.78</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>46.12</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="9" t="n">
         <v>45.71</v>
       </c>
-      <c r="O41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>45.21</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="P41" s="10" t="n">
         <v>42.01</v>
       </c>
-      <c r="Q41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>47.36</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="R41" s="9" t="n">
         <v>43.31</v>
       </c>
-      <c r="S41" s="6" t="n">
+      <c r="S41" s="10" t="n">
         <v>37.48</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="T41" s="9" t="n">
         <v>43.12</v>
       </c>
-      <c r="U41" s="6" t="n">
+      <c r="U41" s="10" t="n">
         <v>41.52</v>
       </c>
-      <c r="V41" s="6" t="n">
+      <c r="V41" s="10" t="n">
         <v>42.48</v>
       </c>
-      <c r="W41" s="6" t="n">
+      <c r="W41" s="10" t="n">
         <v>42.72</v>
       </c>
-      <c r="X41" s="6" t="n">
+      <c r="X41" s="9" t="n">
         <v>46.34</v>
       </c>
-      <c r="Y41" s="6" t="n">
+      <c r="Y41" s="10" t="n">
         <v>42.01</v>
       </c>
-      <c r="Z41" s="6" t="n">
+      <c r="Z41" s="10" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA41" s="6" t="n">
+      <c r="AA41" s="10" t="n">
         <v>41.55</v>
       </c>
-      <c r="AB41" s="6" t="n">
+      <c r="AB41" s="10" t="n">
         <v>41.22</v>
       </c>
-      <c r="AC41" s="6" t="n">
+      <c r="AC41" s="9" t="n">
         <v>44.88</v>
       </c>
-      <c r="AD41" s="6" t="n">
+      <c r="AD41" s="10" t="n">
         <v>38.64</v>
       </c>
-      <c r="AE41" s="6" t="n">
+      <c r="AE41" s="10" t="n">
         <v>41.14</v>
       </c>
-      <c r="AF41" s="6" t="n">
+      <c r="AF41" s="9" t="n">
         <v>47.4</v>
       </c>
-      <c r="AG41" s="6" t="n">
+      <c r="AG41" s="9" t="n">
         <v>48.04</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -4331,7 +4364,7 @@
         <v>161.11</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="7" t="inlineStr"/>
+      <c r="AK41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4342,97 +4375,97 @@
       <c r="B42" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" s="9" t="n">
         <v>46.89</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="10" t="n">
         <v>36.46</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="10" t="n">
         <v>37.76</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>45.51</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>44.04</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>45.22</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>43.04</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="10" t="n">
         <v>42.79</v>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>47.75</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="L42" s="9" t="n">
         <v>45.64</v>
       </c>
-      <c r="M42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>46.23</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="N42" s="9" t="n">
         <v>44.39</v>
       </c>
-      <c r="O42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>45.54</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="P42" s="9" t="n">
         <v>46.71</v>
       </c>
-      <c r="Q42" s="6" t="n">
+      <c r="Q42" s="10" t="n">
         <v>42.49</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="R42" s="10" t="n">
         <v>39.33</v>
       </c>
-      <c r="S42" s="6" t="n">
+      <c r="S42" s="10" t="n">
         <v>40.14</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="T42" s="10" t="n">
         <v>38.01</v>
       </c>
-      <c r="U42" s="6" t="n">
+      <c r="U42" s="10" t="n">
         <v>38.08</v>
       </c>
-      <c r="V42" s="6" t="n">
+      <c r="V42" s="10" t="n">
         <v>38.74</v>
       </c>
-      <c r="W42" s="6" t="n">
+      <c r="W42" s="9" t="n">
         <v>43.46</v>
       </c>
-      <c r="X42" s="6" t="n">
+      <c r="X42" s="9" t="n">
         <v>46.21</v>
       </c>
-      <c r="Y42" s="6" t="n">
+      <c r="Y42" s="10" t="n">
         <v>40.55</v>
       </c>
-      <c r="Z42" s="6" t="n">
+      <c r="Z42" s="10" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA42" s="6" t="n">
+      <c r="AA42" s="10" t="n">
         <v>36.65</v>
       </c>
-      <c r="AB42" s="6" t="n">
+      <c r="AB42" s="10" t="n">
         <v>42.29</v>
       </c>
-      <c r="AC42" s="6" t="n">
+      <c r="AC42" s="9" t="n">
         <v>45.95</v>
       </c>
-      <c r="AD42" s="6" t="n">
+      <c r="AD42" s="9" t="n">
         <v>43.71</v>
       </c>
-      <c r="AE42" s="6" t="n">
+      <c r="AE42" s="9" t="n">
         <v>45.76</v>
       </c>
-      <c r="AF42" s="6" t="n">
+      <c r="AF42" s="9" t="n">
         <v>47.26</v>
       </c>
-      <c r="AG42" s="6" t="n">
+      <c r="AG42" s="9" t="n">
         <v>44.16</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -4442,7 +4475,7 @@
         <v>141.85</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="7" t="inlineStr"/>
+      <c r="AK42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4453,97 +4486,97 @@
       <c r="B43" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C43" s="9" t="n">
         <v>47.79</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="10" t="n">
         <v>36.54</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="10" t="n">
         <v>35.36</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="10" t="n">
         <v>39.5</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="10" t="n">
         <v>39.05</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>44.41</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" s="10" t="n">
         <v>42.89</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="9" t="n">
         <v>45.39</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>46.43</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="L43" s="9" t="n">
         <v>44.24</v>
       </c>
-      <c r="M43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>46.82</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="N43" s="9" t="n">
         <v>43.69</v>
       </c>
-      <c r="O43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>48.21</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="P43" s="9" t="n">
         <v>47.44</v>
       </c>
-      <c r="Q43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>43.59</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="R43" s="10" t="n">
         <v>39.13</v>
       </c>
-      <c r="S43" s="6" t="n">
+      <c r="S43" s="10" t="n">
         <v>38.44</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="T43" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="U43" s="6" t="n">
+      <c r="U43" s="10" t="n">
         <v>42.06</v>
       </c>
-      <c r="V43" s="6" t="n">
+      <c r="V43" s="10" t="n">
         <v>39.01</v>
       </c>
-      <c r="W43" s="6" t="n">
+      <c r="W43" s="10" t="n">
         <v>42.07</v>
       </c>
-      <c r="X43" s="6" t="n">
+      <c r="X43" s="9" t="n">
         <v>46.61</v>
       </c>
-      <c r="Y43" s="6" t="n">
+      <c r="Y43" s="10" t="n">
         <v>36.92</v>
       </c>
-      <c r="Z43" s="6" t="n">
+      <c r="Z43" s="10" t="n">
         <v>37.61</v>
       </c>
-      <c r="AA43" s="6" t="n">
+      <c r="AA43" s="10" t="n">
         <v>36.41</v>
       </c>
-      <c r="AB43" s="6" t="n">
+      <c r="AB43" s="10" t="n">
         <v>40.19</v>
       </c>
-      <c r="AC43" s="6" t="n">
+      <c r="AC43" s="10" t="n">
         <v>39.22</v>
       </c>
-      <c r="AD43" s="6" t="n">
+      <c r="AD43" s="10" t="n">
         <v>40.28</v>
       </c>
-      <c r="AE43" s="6" t="n">
+      <c r="AE43" s="9" t="n">
         <v>47.26</v>
       </c>
-      <c r="AF43" s="6" t="n">
+      <c r="AF43" s="9" t="n">
         <v>46.28</v>
       </c>
-      <c r="AG43" s="6" t="n">
+      <c r="AG43" s="9" t="n">
         <v>45.59</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -4553,7 +4586,7 @@
         <v>140.45</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="7" t="inlineStr"/>
+      <c r="AK43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4564,97 +4597,97 @@
       <c r="B44" s="6" t="n">
         <v>103.9</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="7" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="7" t="n">
         <v>77.72</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>77.3</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="7" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="7" t="n">
         <v>76.72</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="7" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="K44" s="7" t="n">
         <v>77.23</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="L44" s="7" t="n">
         <v>76.86</v>
       </c>
-      <c r="M44" s="6" t="n">
+      <c r="M44" s="7" t="n">
         <v>78.38</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="N44" s="7" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="O44" s="6" t="n">
+      <c r="O44" s="7" t="n">
         <v>78.19</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="P44" s="7" t="n">
         <v>77.08</v>
       </c>
-      <c r="Q44" s="6" t="n">
+      <c r="Q44" s="7" t="n">
         <v>77.70999999999999</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="R44" s="7" t="n">
         <v>78.08</v>
       </c>
-      <c r="S44" s="6" t="n">
+      <c r="S44" s="7" t="n">
         <v>77.56</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="T44" s="7" t="n">
         <v>78.36</v>
       </c>
-      <c r="U44" s="6" t="n">
+      <c r="U44" s="7" t="n">
         <v>77.41</v>
       </c>
-      <c r="V44" s="6" t="n">
+      <c r="V44" s="7" t="n">
         <v>77.61</v>
       </c>
-      <c r="W44" s="6" t="n">
+      <c r="W44" s="7" t="n">
         <v>77.5</v>
       </c>
-      <c r="X44" s="6" t="n">
+      <c r="X44" s="7" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="Y44" s="6" t="n">
+      <c r="Y44" s="7" t="n">
         <v>77.47</v>
       </c>
-      <c r="Z44" s="6" t="n">
+      <c r="Z44" s="7" t="n">
         <v>77.18000000000001</v>
       </c>
-      <c r="AA44" s="6" t="n">
+      <c r="AA44" s="7" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="AB44" s="6" t="n">
+      <c r="AB44" s="7" t="n">
         <v>78.15000000000001</v>
       </c>
-      <c r="AC44" s="6" t="n">
+      <c r="AC44" s="7" t="n">
         <v>78.34</v>
       </c>
-      <c r="AD44" s="6" t="n">
+      <c r="AD44" s="7" t="n">
         <v>77.31</v>
       </c>
-      <c r="AE44" s="6" t="n">
+      <c r="AE44" s="7" t="n">
         <v>77.93000000000001</v>
       </c>
-      <c r="AF44" s="6" t="n">
+      <c r="AF44" s="7" t="n">
         <v>77.95999999999999</v>
       </c>
-      <c r="AG44" s="6" t="n">
+      <c r="AG44" s="7" t="n">
         <v>78.26000000000001</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -4664,7 +4697,7 @@
         <v>181.85</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="7" t="inlineStr"/>
+      <c r="AK44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4675,97 +4708,97 @@
       <c r="B45" s="6" t="n">
         <v>104.3</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C45" s="7" t="n">
         <v>66.14</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="7" t="n">
         <v>66.64</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>66.44</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <v>67.31</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" s="7" t="n">
         <v>67.41</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="7" t="n">
         <v>66.36</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="7" t="n">
         <v>67.08</v>
       </c>
-      <c r="K45" s="6" t="n">
+      <c r="K45" s="7" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="L45" s="7" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="M45" s="6" t="n">
+      <c r="M45" s="7" t="n">
         <v>66.58</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="N45" s="7" t="n">
         <v>66.59</v>
       </c>
-      <c r="O45" s="6" t="n">
+      <c r="O45" s="7" t="n">
         <v>66.29000000000001</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="P45" s="7" t="n">
         <v>66.31</v>
       </c>
-      <c r="Q45" s="6" t="n">
+      <c r="Q45" s="7" t="n">
         <v>66.12</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="R45" s="7" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="S45" s="6" t="n">
+      <c r="S45" s="7" t="n">
         <v>67.55</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="T45" s="7" t="n">
         <v>66.61</v>
       </c>
-      <c r="U45" s="6" t="n">
+      <c r="U45" s="7" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="V45" s="6" t="n">
+      <c r="V45" s="7" t="n">
         <v>67.62</v>
       </c>
-      <c r="W45" s="6" t="n">
+      <c r="W45" s="7" t="n">
         <v>67.06</v>
       </c>
-      <c r="X45" s="6" t="n">
+      <c r="X45" s="7" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="Y45" s="6" t="n">
+      <c r="Y45" s="7" t="n">
         <v>67.22</v>
       </c>
-      <c r="Z45" s="6" t="n">
+      <c r="Z45" s="7" t="n">
         <v>66.69</v>
       </c>
-      <c r="AA45" s="6" t="n">
+      <c r="AA45" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="AB45" s="6" t="n">
+      <c r="AB45" s="7" t="n">
         <v>66.44</v>
       </c>
-      <c r="AC45" s="6" t="n">
+      <c r="AC45" s="7" t="n">
         <v>66.86</v>
       </c>
-      <c r="AD45" s="6" t="n">
+      <c r="AD45" s="7" t="n">
         <v>66.92</v>
       </c>
-      <c r="AE45" s="6" t="n">
+      <c r="AE45" s="7" t="n">
         <v>66.56</v>
       </c>
-      <c r="AF45" s="6" t="n">
+      <c r="AF45" s="7" t="n">
         <v>67.11</v>
       </c>
-      <c r="AG45" s="6" t="n">
+      <c r="AG45" s="7" t="n">
         <v>66.86</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -4775,7 +4808,7 @@
         <v>243.9</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="7" t="inlineStr"/>
+      <c r="AK45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4786,97 +4819,97 @@
       <c r="B46" s="6" t="n">
         <v>104.7</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="7" t="n">
         <v>70.06</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="7" t="n">
         <v>71.16</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>66.28</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="7" t="n">
         <v>69.68000000000001</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="7" t="n">
         <v>69.76000000000001</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="7" t="n">
         <v>70.01000000000001</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" s="7" t="n">
         <v>69.19</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="J46" s="7" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="K46" s="6" t="n">
+      <c r="K46" s="7" t="n">
         <v>70.44</v>
       </c>
-      <c r="L46" s="6" t="n">
+      <c r="L46" s="7" t="n">
         <v>70.5</v>
       </c>
-      <c r="M46" s="6" t="n">
+      <c r="M46" s="7" t="n">
         <v>70.22</v>
       </c>
-      <c r="N46" s="6" t="n">
+      <c r="N46" s="7" t="n">
         <v>69.84</v>
       </c>
-      <c r="O46" s="6" t="n">
+      <c r="O46" s="7" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="P46" s="6" t="n">
+      <c r="P46" s="7" t="n">
         <v>69.31999999999999</v>
       </c>
-      <c r="Q46" s="6" t="n">
+      <c r="Q46" s="7" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="R46" s="6" t="n">
+      <c r="R46" s="7" t="n">
         <v>70.84</v>
       </c>
-      <c r="S46" s="6" t="n">
+      <c r="S46" s="7" t="n">
         <v>70.44</v>
       </c>
-      <c r="T46" s="6" t="n">
+      <c r="T46" s="7" t="n">
         <v>70.70999999999999</v>
       </c>
-      <c r="U46" s="6" t="n">
+      <c r="U46" s="7" t="n">
         <v>70.53</v>
       </c>
-      <c r="V46" s="6" t="n">
+      <c r="V46" s="7" t="n">
         <v>70.63</v>
       </c>
-      <c r="W46" s="6" t="n">
+      <c r="W46" s="7" t="n">
         <v>70.33</v>
       </c>
-      <c r="X46" s="6" t="n">
+      <c r="X46" s="7" t="n">
         <v>70.08</v>
       </c>
-      <c r="Y46" s="6" t="n">
+      <c r="Y46" s="7" t="n">
         <v>70.14</v>
       </c>
-      <c r="Z46" s="6" t="n">
+      <c r="Z46" s="7" t="n">
         <v>69.06</v>
       </c>
-      <c r="AA46" s="6" t="n">
+      <c r="AA46" s="7" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="AB46" s="6" t="n">
+      <c r="AB46" s="7" t="n">
         <v>69.51000000000001</v>
       </c>
-      <c r="AC46" s="6" t="n">
+      <c r="AC46" s="7" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="AD46" s="6" t="n">
+      <c r="AD46" s="7" t="n">
         <v>70.2</v>
       </c>
-      <c r="AE46" s="6" t="n">
+      <c r="AE46" s="7" t="n">
         <v>70.81</v>
       </c>
-      <c r="AF46" s="6" t="n">
+      <c r="AF46" s="7" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="AG46" s="6" t="n">
+      <c r="AG46" s="7" t="n">
         <v>71.01000000000001</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4886,7 +4919,7 @@
         <v>252.32</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="7" t="inlineStr"/>
+      <c r="AK46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4897,97 +4930,97 @@
       <c r="B47" s="6" t="n">
         <v>105.1</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C47" s="7" t="n">
         <v>80.31999999999999</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="7" t="n">
         <v>79.70999999999999</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>77.03</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="7" t="n">
         <v>79.97</v>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="7" t="n">
         <v>79.47</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="7" t="n">
         <v>79.81</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="7" t="n">
         <v>79.3</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="7" t="n">
         <v>79.39</v>
       </c>
-      <c r="K47" s="6" t="n">
+      <c r="K47" s="7" t="n">
         <v>79.23999999999999</v>
       </c>
-      <c r="L47" s="6" t="n">
+      <c r="L47" s="7" t="n">
         <v>79.56</v>
       </c>
-      <c r="M47" s="6" t="n">
+      <c r="M47" s="7" t="n">
         <v>80.08</v>
       </c>
-      <c r="N47" s="6" t="n">
+      <c r="N47" s="7" t="n">
         <v>79.52</v>
       </c>
-      <c r="O47" s="6" t="n">
+      <c r="O47" s="7" t="n">
         <v>79.02</v>
       </c>
-      <c r="P47" s="6" t="n">
+      <c r="P47" s="7" t="n">
         <v>79.15000000000001</v>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="Q47" s="7" t="n">
         <v>79.28</v>
       </c>
-      <c r="R47" s="6" t="n">
+      <c r="R47" s="7" t="n">
         <v>79.69</v>
       </c>
-      <c r="S47" s="6" t="n">
+      <c r="S47" s="7" t="n">
         <v>79.54000000000001</v>
       </c>
-      <c r="T47" s="6" t="n">
+      <c r="T47" s="7" t="n">
         <v>79.36</v>
       </c>
-      <c r="U47" s="6" t="n">
+      <c r="U47" s="7" t="n">
         <v>79.76000000000001</v>
       </c>
-      <c r="V47" s="6" t="n">
+      <c r="V47" s="7" t="n">
         <v>79.66</v>
       </c>
-      <c r="W47" s="6" t="n">
+      <c r="W47" s="7" t="n">
         <v>79.83</v>
       </c>
-      <c r="X47" s="6" t="n">
+      <c r="X47" s="7" t="n">
         <v>79.47</v>
       </c>
-      <c r="Y47" s="6" t="n">
+      <c r="Y47" s="7" t="n">
         <v>80.41</v>
       </c>
-      <c r="Z47" s="6" t="n">
+      <c r="Z47" s="7" t="n">
         <v>79.79000000000001</v>
       </c>
-      <c r="AA47" s="6" t="n">
+      <c r="AA47" s="7" t="n">
         <v>80.11</v>
       </c>
-      <c r="AB47" s="6" t="n">
+      <c r="AB47" s="7" t="n">
         <v>79.79000000000001</v>
       </c>
-      <c r="AC47" s="6" t="n">
+      <c r="AC47" s="7" t="n">
         <v>79.66</v>
       </c>
-      <c r="AD47" s="6" t="n">
+      <c r="AD47" s="7" t="n">
         <v>79.3</v>
       </c>
-      <c r="AE47" s="6" t="n">
+      <c r="AE47" s="7" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="AF47" s="6" t="n">
+      <c r="AF47" s="7" t="n">
         <v>79.64</v>
       </c>
-      <c r="AG47" s="6" t="n">
+      <c r="AG47" s="7" t="n">
         <v>80.06</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4997,7 +5030,7 @@
         <v>254.37</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="7" t="inlineStr"/>
+      <c r="AK47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5008,97 +5041,97 @@
       <c r="B48" s="6" t="n">
         <v>105.5</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="7" t="n">
         <v>57.51</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="7" t="n">
         <v>56.33</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="9" t="n">
         <v>52.45</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="7" t="n">
         <v>54.84</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" s="7" t="n">
         <v>56.89</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" s="7" t="n">
         <v>56.58</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" s="7" t="n">
         <v>56.42</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="7" t="n">
         <v>55.91</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="K48" s="7" t="n">
         <v>55.03</v>
       </c>
-      <c r="L48" s="6" t="n">
+      <c r="L48" s="7" t="n">
         <v>56.9</v>
       </c>
-      <c r="M48" s="6" t="n">
+      <c r="M48" s="7" t="n">
         <v>56.44</v>
       </c>
-      <c r="N48" s="6" t="n">
+      <c r="N48" s="7" t="n">
         <v>56.82</v>
       </c>
-      <c r="O48" s="6" t="n">
+      <c r="O48" s="7" t="n">
         <v>55.44</v>
       </c>
-      <c r="P48" s="6" t="n">
+      <c r="P48" s="7" t="n">
         <v>54.61</v>
       </c>
-      <c r="Q48" s="6" t="n">
+      <c r="Q48" s="7" t="n">
         <v>54.7</v>
       </c>
-      <c r="R48" s="6" t="n">
+      <c r="R48" s="7" t="n">
         <v>56.19</v>
       </c>
-      <c r="S48" s="6" t="n">
+      <c r="S48" s="7" t="n">
         <v>55.34</v>
       </c>
-      <c r="T48" s="6" t="n">
+      <c r="T48" s="7" t="n">
         <v>56.69</v>
       </c>
-      <c r="U48" s="6" t="n">
+      <c r="U48" s="7" t="n">
         <v>55.47</v>
       </c>
-      <c r="V48" s="6" t="n">
+      <c r="V48" s="7" t="n">
         <v>56.24</v>
       </c>
-      <c r="W48" s="6" t="n">
+      <c r="W48" s="7" t="n">
         <v>56.59</v>
       </c>
-      <c r="X48" s="6" t="n">
+      <c r="X48" s="7" t="n">
         <v>55.64</v>
       </c>
-      <c r="Y48" s="6" t="n">
+      <c r="Y48" s="7" t="n">
         <v>56.9</v>
       </c>
-      <c r="Z48" s="6" t="n">
+      <c r="Z48" s="7" t="n">
         <v>55.12</v>
       </c>
-      <c r="AA48" s="6" t="n">
+      <c r="AA48" s="7" t="n">
         <v>55.36</v>
       </c>
-      <c r="AB48" s="6" t="n">
+      <c r="AB48" s="7" t="n">
         <v>55.66</v>
       </c>
-      <c r="AC48" s="6" t="n">
+      <c r="AC48" s="7" t="n">
         <v>56.56</v>
       </c>
-      <c r="AD48" s="6" t="n">
+      <c r="AD48" s="7" t="n">
         <v>55.57</v>
       </c>
-      <c r="AE48" s="6" t="n">
+      <c r="AE48" s="7" t="n">
         <v>55.86</v>
       </c>
-      <c r="AF48" s="6" t="n">
+      <c r="AF48" s="7" t="n">
         <v>56.94</v>
       </c>
-      <c r="AG48" s="6" t="n">
+      <c r="AG48" s="7" t="n">
         <v>55.31</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -5108,7 +5141,7 @@
         <v>487.79</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="7" t="inlineStr"/>
+      <c r="AK48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5119,97 +5152,97 @@
       <c r="B49" s="6" t="n">
         <v>105.9</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C49" s="7" t="n">
         <v>66.36</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="7" t="n">
         <v>66.62</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="7" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G49" s="7" t="n">
         <v>66.55</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H49" s="7" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="7" t="n">
         <v>67.11</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="7" t="n">
         <v>67.22</v>
       </c>
-      <c r="K49" s="6" t="n">
+      <c r="K49" s="7" t="n">
         <v>66.48</v>
       </c>
-      <c r="L49" s="6" t="n">
+      <c r="L49" s="7" t="n">
         <v>66.77</v>
       </c>
-      <c r="M49" s="6" t="n">
+      <c r="M49" s="7" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="N49" s="6" t="n">
+      <c r="N49" s="7" t="n">
         <v>66.81</v>
       </c>
-      <c r="O49" s="6" t="n">
+      <c r="O49" s="7" t="n">
         <v>66.81</v>
       </c>
-      <c r="P49" s="6" t="n">
+      <c r="P49" s="7" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="Q49" s="6" t="n">
+      <c r="Q49" s="7" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="R49" s="6" t="n">
+      <c r="R49" s="7" t="n">
         <v>66.86</v>
       </c>
-      <c r="S49" s="6" t="n">
+      <c r="S49" s="7" t="n">
         <v>66.98</v>
       </c>
-      <c r="T49" s="6" t="n">
+      <c r="T49" s="7" t="n">
         <v>66.95999999999999</v>
       </c>
-      <c r="U49" s="6" t="n">
+      <c r="U49" s="7" t="n">
         <v>67.08</v>
       </c>
-      <c r="V49" s="6" t="n">
+      <c r="V49" s="7" t="n">
         <v>66.89</v>
       </c>
-      <c r="W49" s="6" t="n">
+      <c r="W49" s="7" t="n">
         <v>67.59</v>
       </c>
-      <c r="X49" s="6" t="n">
+      <c r="X49" s="7" t="n">
         <v>67.19</v>
       </c>
-      <c r="Y49" s="6" t="n">
+      <c r="Y49" s="7" t="n">
         <v>66.66</v>
       </c>
-      <c r="Z49" s="6" t="n">
+      <c r="Z49" s="7" t="n">
         <v>67.11</v>
       </c>
-      <c r="AA49" s="6" t="n">
+      <c r="AA49" s="7" t="n">
         <v>66.53</v>
       </c>
-      <c r="AB49" s="6" t="n">
+      <c r="AB49" s="7" t="n">
         <v>66.53</v>
       </c>
-      <c r="AC49" s="6" t="n">
+      <c r="AC49" s="7" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="AD49" s="6" t="n">
+      <c r="AD49" s="7" t="n">
         <v>66.62</v>
       </c>
-      <c r="AE49" s="6" t="n">
+      <c r="AE49" s="7" t="n">
         <v>67.23999999999999</v>
       </c>
-      <c r="AF49" s="6" t="n">
+      <c r="AF49" s="7" t="n">
         <v>67.06</v>
       </c>
-      <c r="AG49" s="6" t="n">
+      <c r="AG49" s="7" t="n">
         <v>66.27</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -5219,7 +5252,7 @@
         <v>385.5</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="7" t="inlineStr"/>
+      <c r="AK49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5230,97 +5263,97 @@
       <c r="B50" s="6" t="n">
         <v>106.3</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" s="7" t="n">
         <v>73.01000000000001</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="7" t="n">
         <v>72.91</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>71.3</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="7" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" s="7" t="n">
         <v>73.98999999999999</v>
       </c>
-      <c r="H50" s="6" t="n">
+      <c r="H50" s="7" t="n">
         <v>73.91</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" s="7" t="n">
         <v>74.38</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="7" t="n">
         <v>74.19</v>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="K50" s="7" t="n">
         <v>73.87</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="L50" s="7" t="n">
         <v>74.20999999999999</v>
       </c>
-      <c r="M50" s="6" t="n">
+      <c r="M50" s="7" t="n">
         <v>74.53</v>
       </c>
-      <c r="N50" s="6" t="n">
+      <c r="N50" s="7" t="n">
         <v>74.2</v>
       </c>
-      <c r="O50" s="6" t="n">
+      <c r="O50" s="7" t="n">
         <v>73.95999999999999</v>
       </c>
-      <c r="P50" s="6" t="n">
+      <c r="P50" s="7" t="n">
         <v>73.73999999999999</v>
       </c>
-      <c r="Q50" s="6" t="n">
+      <c r="Q50" s="7" t="n">
         <v>74.29000000000001</v>
       </c>
-      <c r="R50" s="6" t="n">
+      <c r="R50" s="7" t="n">
         <v>73.86</v>
       </c>
-      <c r="S50" s="6" t="n">
+      <c r="S50" s="7" t="n">
         <v>73.61</v>
       </c>
-      <c r="T50" s="6" t="n">
+      <c r="T50" s="7" t="n">
         <v>73.37</v>
       </c>
-      <c r="U50" s="6" t="n">
+      <c r="U50" s="7" t="n">
         <v>74.39</v>
       </c>
-      <c r="V50" s="6" t="n">
+      <c r="V50" s="7" t="n">
         <v>73.94</v>
       </c>
-      <c r="W50" s="6" t="n">
+      <c r="W50" s="7" t="n">
         <v>74.06</v>
       </c>
-      <c r="X50" s="6" t="n">
+      <c r="X50" s="7" t="n">
         <v>74.12</v>
       </c>
-      <c r="Y50" s="6" t="n">
+      <c r="Y50" s="7" t="n">
         <v>74.31999999999999</v>
       </c>
-      <c r="Z50" s="6" t="n">
+      <c r="Z50" s="7" t="n">
         <v>74.15000000000001</v>
       </c>
-      <c r="AA50" s="6" t="n">
+      <c r="AA50" s="7" t="n">
         <v>73.75</v>
       </c>
-      <c r="AB50" s="6" t="n">
+      <c r="AB50" s="7" t="n">
         <v>74.08</v>
       </c>
-      <c r="AC50" s="6" t="n">
+      <c r="AC50" s="7" t="n">
         <v>74.33</v>
       </c>
-      <c r="AD50" s="6" t="n">
+      <c r="AD50" s="7" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="AE50" s="6" t="n">
+      <c r="AE50" s="7" t="n">
         <v>73.87</v>
       </c>
-      <c r="AF50" s="6" t="n">
+      <c r="AF50" s="7" t="n">
         <v>73.78</v>
       </c>
-      <c r="AG50" s="6" t="n">
+      <c r="AG50" s="7" t="n">
         <v>73.59</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -5330,7 +5363,7 @@
         <v>236.24</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="7" t="inlineStr"/>
+      <c r="AK50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -5341,97 +5374,97 @@
       <c r="B51" s="6" t="n">
         <v>106.7</v>
       </c>
-      <c r="C51" s="6" t="n">
+      <c r="C51" s="9" t="n">
         <v>45.59</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="9" t="n">
         <v>44.29</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="9" t="n">
         <v>45.42</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="9" t="n">
         <v>45.54</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G51" s="9" t="n">
         <v>45.36</v>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="H51" s="9" t="n">
         <v>44.1</v>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I51" s="9" t="n">
         <v>45.04</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="J51" s="9" t="n">
         <v>45.04</v>
       </c>
-      <c r="K51" s="6" t="n">
+      <c r="K51" s="9" t="n">
         <v>45.84</v>
       </c>
-      <c r="L51" s="6" t="n">
+      <c r="L51" s="9" t="n">
         <v>43.74</v>
       </c>
-      <c r="M51" s="6" t="n">
+      <c r="M51" s="9" t="n">
         <v>44.87</v>
       </c>
-      <c r="N51" s="6" t="n">
+      <c r="N51" s="9" t="n">
         <v>45.91</v>
       </c>
-      <c r="O51" s="6" t="n">
+      <c r="O51" s="9" t="n">
         <v>45.61</v>
       </c>
-      <c r="P51" s="6" t="n">
+      <c r="P51" s="9" t="n">
         <v>45.42</v>
       </c>
-      <c r="Q51" s="6" t="n">
+      <c r="Q51" s="9" t="n">
         <v>45.88</v>
       </c>
-      <c r="R51" s="6" t="n">
+      <c r="R51" s="9" t="n">
         <v>45.66</v>
       </c>
-      <c r="S51" s="6" t="n">
+      <c r="S51" s="9" t="n">
         <v>45.7</v>
       </c>
-      <c r="T51" s="6" t="n">
+      <c r="T51" s="9" t="n">
         <v>46.39</v>
       </c>
-      <c r="U51" s="6" t="n">
+      <c r="U51" s="9" t="n">
         <v>45.44</v>
       </c>
-      <c r="V51" s="6" t="n">
+      <c r="V51" s="9" t="n">
         <v>43.86</v>
       </c>
-      <c r="W51" s="6" t="n">
+      <c r="W51" s="9" t="n">
         <v>44.56</v>
       </c>
-      <c r="X51" s="6" t="n">
+      <c r="X51" s="9" t="n">
         <v>44.54</v>
       </c>
-      <c r="Y51" s="6" t="n">
+      <c r="Y51" s="9" t="n">
         <v>44.78</v>
       </c>
-      <c r="Z51" s="6" t="n">
+      <c r="Z51" s="9" t="n">
         <v>43.79</v>
       </c>
-      <c r="AA51" s="6" t="n">
+      <c r="AA51" s="9" t="n">
         <v>45.58</v>
       </c>
-      <c r="AB51" s="6" t="n">
+      <c r="AB51" s="9" t="n">
         <v>43.16</v>
       </c>
-      <c r="AC51" s="6" t="n">
+      <c r="AC51" s="9" t="n">
         <v>43.36</v>
       </c>
-      <c r="AD51" s="6" t="n">
+      <c r="AD51" s="9" t="n">
         <v>44.17</v>
       </c>
-      <c r="AE51" s="6" t="n">
+      <c r="AE51" s="9" t="n">
         <v>46.02</v>
       </c>
-      <c r="AF51" s="6" t="n">
+      <c r="AF51" s="9" t="n">
         <v>45.81</v>
       </c>
-      <c r="AG51" s="6" t="n">
+      <c r="AG51" s="9" t="n">
         <v>44.48</v>
       </c>
       <c r="AH51" s="6" t="n">
@@ -5441,118 +5474,118 @@
         <v>468.87</v>
       </c>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="7" t="inlineStr"/>
+      <c r="AK51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>GENESIS FM STEREO</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" s="12" t="n">
         <v>107.5</v>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="C52" s="13" t="n">
         <v>45.55</v>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="D52" s="13" t="n">
         <v>45.58</v>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="E52" s="13" t="n">
         <v>46.18</v>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="13" t="n">
         <v>45.65</v>
       </c>
-      <c r="G52" s="9" t="n">
+      <c r="G52" s="13" t="n">
         <v>47.34</v>
       </c>
-      <c r="H52" s="9" t="n">
+      <c r="H52" s="13" t="n">
         <v>47.62</v>
       </c>
-      <c r="I52" s="9" t="n">
+      <c r="I52" s="13" t="n">
         <v>46.46</v>
       </c>
-      <c r="J52" s="9" t="n">
+      <c r="J52" s="13" t="n">
         <v>45.94</v>
       </c>
-      <c r="K52" s="9" t="n">
+      <c r="K52" s="13" t="n">
         <v>45.49</v>
       </c>
-      <c r="L52" s="9" t="n">
+      <c r="L52" s="13" t="n">
         <v>45.62</v>
       </c>
-      <c r="M52" s="9" t="n">
+      <c r="M52" s="13" t="n">
         <v>46.22</v>
       </c>
-      <c r="N52" s="9" t="n">
+      <c r="N52" s="13" t="n">
         <v>47.42</v>
       </c>
-      <c r="O52" s="9" t="n">
+      <c r="O52" s="13" t="n">
         <v>46.59</v>
       </c>
-      <c r="P52" s="9" t="n">
+      <c r="P52" s="13" t="n">
         <v>46.35</v>
       </c>
-      <c r="Q52" s="9" t="n">
+      <c r="Q52" s="13" t="n">
         <v>46.21</v>
       </c>
-      <c r="R52" s="9" t="n">
+      <c r="R52" s="13" t="n">
         <v>46.19</v>
       </c>
-      <c r="S52" s="9" t="n">
+      <c r="S52" s="13" t="n">
         <v>47.04</v>
       </c>
-      <c r="T52" s="9" t="n">
+      <c r="T52" s="13" t="n">
         <v>45.74</v>
       </c>
-      <c r="U52" s="9" t="n">
+      <c r="U52" s="13" t="n">
         <v>45.27</v>
       </c>
-      <c r="V52" s="9" t="n">
+      <c r="V52" s="13" t="n">
         <v>45.62</v>
       </c>
-      <c r="W52" s="9" t="n">
+      <c r="W52" s="13" t="n">
         <v>44.74</v>
       </c>
-      <c r="X52" s="9" t="n">
+      <c r="X52" s="13" t="n">
         <v>49.16</v>
       </c>
-      <c r="Y52" s="9" t="n">
+      <c r="Y52" s="13" t="n">
         <v>46.34</v>
       </c>
-      <c r="Z52" s="9" t="n">
+      <c r="Z52" s="13" t="n">
         <v>45.4</v>
       </c>
-      <c r="AA52" s="9" t="n">
+      <c r="AA52" s="13" t="n">
         <v>45.42</v>
       </c>
-      <c r="AB52" s="9" t="n">
+      <c r="AB52" s="13" t="n">
         <v>47.13</v>
       </c>
-      <c r="AC52" s="9" t="n">
+      <c r="AC52" s="13" t="n">
         <v>45.49</v>
       </c>
-      <c r="AD52" s="9" t="n">
+      <c r="AD52" s="13" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE52" s="9" t="n">
+      <c r="AE52" s="13" t="n">
         <v>46.79</v>
       </c>
-      <c r="AF52" s="9" t="n">
+      <c r="AF52" s="13" t="n">
         <v>47.06</v>
       </c>
-      <c r="AG52" s="9" t="n">
+      <c r="AG52" s="13" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH52" s="9" t="n">
+      <c r="AH52" s="12" t="n">
         <v>46.28</v>
       </c>
-      <c r="AI52" s="9" t="n">
+      <c r="AI52" s="12" t="n">
         <v>497.9</v>
       </c>
-      <c r="AJ52" s="9" t="inlineStr"/>
-      <c r="AK52" s="10" t="inlineStr"/>
+      <c r="AJ52" s="12" t="inlineStr"/>
+      <c r="AK52" s="14" t="inlineStr"/>
     </row>
     <row r="53"/>
     <row r="54"/>
@@ -5601,7 +5634,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5760,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK62" s="11" t="n"/>
+      <c r="AK62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5738,97 +5771,97 @@
       <c r="B63" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C63" s="6" t="n">
+      <c r="C63" s="7" t="n">
         <v>64.05</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="7" t="n">
         <v>63.56</v>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="7" t="n">
         <v>64.08</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="7" t="n">
         <v>63.48</v>
       </c>
-      <c r="G63" s="6" t="n">
+      <c r="G63" s="7" t="n">
         <v>64.12</v>
       </c>
-      <c r="H63" s="6" t="n">
+      <c r="H63" s="7" t="n">
         <v>64.53</v>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I63" s="7" t="n">
         <v>64.03</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="J63" s="7" t="n">
         <v>63.8</v>
       </c>
-      <c r="K63" s="6" t="n">
+      <c r="K63" s="7" t="n">
         <v>63.63</v>
       </c>
-      <c r="L63" s="6" t="n">
+      <c r="L63" s="7" t="n">
         <v>63.38</v>
       </c>
-      <c r="M63" s="6" t="n">
+      <c r="M63" s="7" t="n">
         <v>63.85</v>
       </c>
-      <c r="N63" s="6" t="n">
+      <c r="N63" s="7" t="n">
         <v>63.69</v>
       </c>
-      <c r="O63" s="6" t="n">
+      <c r="O63" s="7" t="n">
         <v>63.81</v>
       </c>
-      <c r="P63" s="6" t="n">
+      <c r="P63" s="7" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="Q63" s="6" t="n">
+      <c r="Q63" s="7" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="R63" s="6" t="n">
+      <c r="R63" s="7" t="n">
         <v>63.94</v>
       </c>
-      <c r="S63" s="6" t="n">
+      <c r="S63" s="7" t="n">
         <v>62.96</v>
       </c>
-      <c r="T63" s="6" t="n">
+      <c r="T63" s="7" t="n">
         <v>62.88</v>
       </c>
-      <c r="U63" s="6" t="n">
+      <c r="U63" s="7" t="n">
         <v>62.7</v>
       </c>
-      <c r="V63" s="6" t="n">
+      <c r="V63" s="7" t="n">
         <v>62.84</v>
       </c>
-      <c r="W63" s="6" t="n">
+      <c r="W63" s="7" t="n">
         <v>62.69</v>
       </c>
-      <c r="X63" s="6" t="n">
+      <c r="X63" s="7" t="n">
         <v>62.51</v>
       </c>
-      <c r="Y63" s="6" t="n">
+      <c r="Y63" s="7" t="n">
         <v>62.42</v>
       </c>
-      <c r="Z63" s="6" t="n">
+      <c r="Z63" s="7" t="n">
         <v>63.88</v>
       </c>
-      <c r="AA63" s="6" t="n">
+      <c r="AA63" s="7" t="n">
         <v>63.6</v>
       </c>
-      <c r="AB63" s="6" t="n">
+      <c r="AB63" s="7" t="n">
         <v>64.08</v>
       </c>
-      <c r="AC63" s="6" t="n">
+      <c r="AC63" s="7" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="AD63" s="6" t="n">
+      <c r="AD63" s="7" t="n">
         <v>64.01000000000001</v>
       </c>
-      <c r="AE63" s="6" t="n">
+      <c r="AE63" s="7" t="n">
         <v>63.49</v>
       </c>
-      <c r="AF63" s="6" t="n">
+      <c r="AF63" s="7" t="n">
         <v>63.14</v>
       </c>
-      <c r="AG63" s="6" t="n">
+      <c r="AG63" s="7" t="n">
         <v>63.04</v>
       </c>
       <c r="AH63" s="6" t="n">
@@ -5836,7 +5869,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="12" t="n"/>
+      <c r="AK63" s="16" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5847,97 +5880,97 @@
       <c r="B64" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C64" s="10" t="n">
         <v>37.2</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="10" t="n">
         <v>37.1</v>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="10" t="n">
         <v>36.25</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="10" t="n">
         <v>35.95</v>
       </c>
-      <c r="G64" s="6" t="n">
+      <c r="G64" s="10" t="n">
         <v>38.22</v>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H64" s="10" t="n">
         <v>35.83</v>
       </c>
-      <c r="I64" s="6" t="n">
+      <c r="I64" s="10" t="n">
         <v>38.13</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="J64" s="10" t="n">
         <v>36.34</v>
       </c>
-      <c r="K64" s="6" t="n">
+      <c r="K64" s="10" t="n">
         <v>37.93</v>
       </c>
-      <c r="L64" s="6" t="n">
+      <c r="L64" s="10" t="n">
         <v>37.71</v>
       </c>
-      <c r="M64" s="6" t="n">
+      <c r="M64" s="10" t="n">
         <v>35.95</v>
       </c>
-      <c r="N64" s="6" t="n">
+      <c r="N64" s="10" t="n">
         <v>35.99</v>
       </c>
-      <c r="O64" s="6" t="n">
+      <c r="O64" s="10" t="n">
         <v>38.22</v>
       </c>
-      <c r="P64" s="6" t="n">
+      <c r="P64" s="10" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q64" s="6" t="n">
+      <c r="Q64" s="10" t="n">
         <v>37.15</v>
       </c>
-      <c r="R64" s="6" t="n">
+      <c r="R64" s="10" t="n">
         <v>37.29</v>
       </c>
-      <c r="S64" s="6" t="n">
+      <c r="S64" s="10" t="n">
         <v>38.9</v>
       </c>
-      <c r="T64" s="6" t="n">
+      <c r="T64" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="U64" s="6" t="n">
+      <c r="U64" s="10" t="n">
         <v>37.5</v>
       </c>
-      <c r="V64" s="6" t="n">
+      <c r="V64" s="10" t="n">
         <v>36.25</v>
       </c>
-      <c r="W64" s="6" t="n">
+      <c r="W64" s="10" t="n">
         <v>36.9</v>
       </c>
-      <c r="X64" s="6" t="n">
+      <c r="X64" s="10" t="n">
         <v>36.92</v>
       </c>
-      <c r="Y64" s="6" t="n">
+      <c r="Y64" s="10" t="n">
         <v>35.42</v>
       </c>
-      <c r="Z64" s="6" t="n">
+      <c r="Z64" s="10" t="n">
         <v>38.12</v>
       </c>
-      <c r="AA64" s="6" t="n">
+      <c r="AA64" s="10" t="n">
         <v>37.35</v>
       </c>
-      <c r="AB64" s="6" t="n">
+      <c r="AB64" s="10" t="n">
         <v>38.41</v>
       </c>
-      <c r="AC64" s="6" t="n">
+      <c r="AC64" s="10" t="n">
         <v>37.71</v>
       </c>
-      <c r="AD64" s="6" t="n">
+      <c r="AD64" s="10" t="n">
         <v>37.56</v>
       </c>
-      <c r="AE64" s="6" t="n">
+      <c r="AE64" s="10" t="n">
         <v>38.91</v>
       </c>
-      <c r="AF64" s="6" t="n">
+      <c r="AF64" s="10" t="n">
         <v>36.38</v>
       </c>
-      <c r="AG64" s="6" t="n">
+      <c r="AG64" s="10" t="n">
         <v>37.45</v>
       </c>
       <c r="AH64" s="6" t="n">
@@ -5945,7 +5978,7 @@
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="12" t="n"/>
+      <c r="AK64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5956,97 +5989,97 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C65" s="10" t="n">
         <v>39.7</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="10" t="n">
         <v>37.34</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="10" t="n">
         <v>38.12</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="10" t="n">
         <v>37.12</v>
       </c>
-      <c r="G65" s="6" t="n">
+      <c r="G65" s="10" t="n">
         <v>38.33</v>
       </c>
-      <c r="H65" s="6" t="n">
+      <c r="H65" s="10" t="n">
         <v>39.69</v>
       </c>
-      <c r="I65" s="6" t="n">
+      <c r="I65" s="10" t="n">
         <v>42.09</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="J65" s="10" t="n">
         <v>42.04</v>
       </c>
-      <c r="K65" s="6" t="n">
+      <c r="K65" s="10" t="n">
         <v>38.28</v>
       </c>
-      <c r="L65" s="6" t="n">
+      <c r="L65" s="10" t="n">
         <v>41.34</v>
       </c>
-      <c r="M65" s="6" t="n">
+      <c r="M65" s="10" t="n">
         <v>41.94</v>
       </c>
-      <c r="N65" s="6" t="n">
+      <c r="N65" s="10" t="n">
         <v>40.49</v>
       </c>
-      <c r="O65" s="6" t="n">
+      <c r="O65" s="10" t="n">
         <v>38.61</v>
       </c>
-      <c r="P65" s="6" t="n">
+      <c r="P65" s="10" t="n">
         <v>37.79</v>
       </c>
-      <c r="Q65" s="6" t="n">
+      <c r="Q65" s="10" t="n">
         <v>37.79</v>
       </c>
-      <c r="R65" s="6" t="n">
+      <c r="R65" s="10" t="n">
         <v>36.92</v>
       </c>
-      <c r="S65" s="6" t="n">
+      <c r="S65" s="10" t="n">
         <v>38.35</v>
       </c>
-      <c r="T65" s="6" t="n">
+      <c r="T65" s="10" t="n">
         <v>36.67</v>
       </c>
-      <c r="U65" s="6" t="n">
+      <c r="U65" s="10" t="n">
         <v>36.88</v>
       </c>
-      <c r="V65" s="6" t="n">
+      <c r="V65" s="10" t="n">
         <v>37.59</v>
       </c>
-      <c r="W65" s="6" t="n">
+      <c r="W65" s="10" t="n">
         <v>37.49</v>
       </c>
-      <c r="X65" s="6" t="n">
+      <c r="X65" s="10" t="n">
         <v>40.59</v>
       </c>
-      <c r="Y65" s="6" t="n">
+      <c r="Y65" s="10" t="n">
         <v>42.94</v>
       </c>
-      <c r="Z65" s="6" t="n">
+      <c r="Z65" s="10" t="n">
         <v>38.3</v>
       </c>
-      <c r="AA65" s="6" t="n">
+      <c r="AA65" s="10" t="n">
         <v>36.58</v>
       </c>
-      <c r="AB65" s="6" t="n">
+      <c r="AB65" s="9" t="n">
         <v>43.08</v>
       </c>
-      <c r="AC65" s="6" t="n">
+      <c r="AC65" s="10" t="n">
         <v>39.4</v>
       </c>
-      <c r="AD65" s="6" t="n">
+      <c r="AD65" s="10" t="n">
         <v>37.41</v>
       </c>
-      <c r="AE65" s="6" t="n">
+      <c r="AE65" s="10" t="n">
         <v>37.99</v>
       </c>
-      <c r="AF65" s="6" t="n">
+      <c r="AF65" s="10" t="n">
         <v>41.21</v>
       </c>
-      <c r="AG65" s="6" t="n">
+      <c r="AG65" s="10" t="n">
         <v>37.2</v>
       </c>
       <c r="AH65" s="6" t="n">
@@ -6054,7 +6087,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="12" t="n"/>
+      <c r="AK65" s="16" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6065,97 +6098,97 @@
       <c r="B66" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="7" t="n">
         <v>77.92</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="7" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>77.88</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="7" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="G66" s="6" t="n">
+      <c r="G66" s="7" t="n">
         <v>77.39</v>
       </c>
-      <c r="H66" s="6" t="n">
+      <c r="H66" s="7" t="n">
         <v>77.95</v>
       </c>
-      <c r="I66" s="6" t="n">
+      <c r="I66" s="7" t="n">
         <v>77.47</v>
       </c>
-      <c r="J66" s="6" t="n">
+      <c r="J66" s="7" t="n">
         <v>77.65000000000001</v>
       </c>
-      <c r="K66" s="6" t="n">
+      <c r="K66" s="7" t="n">
         <v>77.83</v>
       </c>
-      <c r="L66" s="6" t="n">
+      <c r="L66" s="7" t="n">
         <v>77.78</v>
       </c>
-      <c r="M66" s="6" t="n">
+      <c r="M66" s="7" t="n">
         <v>77.59</v>
       </c>
-      <c r="N66" s="6" t="n">
+      <c r="N66" s="7" t="n">
         <v>77.76000000000001</v>
       </c>
-      <c r="O66" s="6" t="n">
+      <c r="O66" s="7" t="n">
         <v>77.22</v>
       </c>
-      <c r="P66" s="6" t="n">
+      <c r="P66" s="7" t="n">
         <v>77.45</v>
       </c>
-      <c r="Q66" s="6" t="n">
+      <c r="Q66" s="7" t="n">
         <v>77.72</v>
       </c>
-      <c r="R66" s="6" t="n">
+      <c r="R66" s="7" t="n">
         <v>77.34</v>
       </c>
-      <c r="S66" s="6" t="n">
+      <c r="S66" s="7" t="n">
         <v>77.19</v>
       </c>
-      <c r="T66" s="6" t="n">
+      <c r="T66" s="7" t="n">
         <v>77.66</v>
       </c>
-      <c r="U66" s="6" t="n">
+      <c r="U66" s="7" t="n">
         <v>77.62</v>
       </c>
-      <c r="V66" s="6" t="n">
+      <c r="V66" s="7" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="W66" s="6" t="n">
+      <c r="W66" s="7" t="n">
         <v>77.11</v>
       </c>
-      <c r="X66" s="6" t="n">
+      <c r="X66" s="7" t="n">
         <v>76.81</v>
       </c>
-      <c r="Y66" s="6" t="n">
+      <c r="Y66" s="7" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="Z66" s="6" t="n">
+      <c r="Z66" s="7" t="n">
         <v>77.7</v>
       </c>
-      <c r="AA66" s="6" t="n">
+      <c r="AA66" s="7" t="n">
         <v>77.28</v>
       </c>
-      <c r="AB66" s="6" t="n">
+      <c r="AB66" s="7" t="n">
         <v>77.31</v>
       </c>
-      <c r="AC66" s="6" t="n">
+      <c r="AC66" s="7" t="n">
         <v>77.28</v>
       </c>
-      <c r="AD66" s="6" t="n">
+      <c r="AD66" s="7" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="AE66" s="6" t="n">
+      <c r="AE66" s="7" t="n">
         <v>77.23</v>
       </c>
-      <c r="AF66" s="6" t="n">
+      <c r="AF66" s="7" t="n">
         <v>77.73999999999999</v>
       </c>
-      <c r="AG66" s="6" t="n">
+      <c r="AG66" s="7" t="n">
         <v>77.44</v>
       </c>
       <c r="AH66" s="6" t="n">
@@ -6163,7 +6196,7 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="12" t="n"/>
+      <c r="AK66" s="16" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6174,97 +6207,97 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="10" t="n">
         <v>40.3</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="10" t="n">
         <v>41.59</v>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="10" t="n">
         <v>38.95</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="10" t="n">
         <v>40.75</v>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="G67" s="10" t="n">
         <v>41.29</v>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H67" s="10" t="n">
         <v>40.61</v>
       </c>
-      <c r="I67" s="6" t="n">
+      <c r="I67" s="10" t="n">
         <v>40.69</v>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="J67" s="9" t="n">
         <v>43.48</v>
       </c>
-      <c r="K67" s="6" t="n">
+      <c r="K67" s="10" t="n">
         <v>41.87</v>
       </c>
-      <c r="L67" s="6" t="n">
+      <c r="L67" s="10" t="n">
         <v>41.22</v>
       </c>
-      <c r="M67" s="6" t="n">
+      <c r="M67" s="10" t="n">
         <v>40.41</v>
       </c>
-      <c r="N67" s="6" t="n">
+      <c r="N67" s="10" t="n">
         <v>41.46</v>
       </c>
-      <c r="O67" s="6" t="n">
+      <c r="O67" s="10" t="n">
         <v>40.07</v>
       </c>
-      <c r="P67" s="6" t="n">
+      <c r="P67" s="10" t="n">
         <v>40.54</v>
       </c>
-      <c r="Q67" s="6" t="n">
+      <c r="Q67" s="10" t="n">
         <v>40.48</v>
       </c>
-      <c r="R67" s="6" t="n">
+      <c r="R67" s="10" t="n">
         <v>41.38</v>
       </c>
-      <c r="S67" s="6" t="n">
+      <c r="S67" s="10" t="n">
         <v>41.15</v>
       </c>
-      <c r="T67" s="6" t="n">
+      <c r="T67" s="10" t="n">
         <v>39.41</v>
       </c>
-      <c r="U67" s="6" t="n">
+      <c r="U67" s="10" t="n">
         <v>39.12</v>
       </c>
-      <c r="V67" s="6" t="n">
+      <c r="V67" s="10" t="n">
         <v>40.48</v>
       </c>
-      <c r="W67" s="6" t="n">
+      <c r="W67" s="10" t="n">
         <v>40.44</v>
       </c>
-      <c r="X67" s="6" t="n">
+      <c r="X67" s="10" t="n">
         <v>40.11</v>
       </c>
-      <c r="Y67" s="6" t="n">
+      <c r="Y67" s="10" t="n">
         <v>38.81</v>
       </c>
-      <c r="Z67" s="6" t="n">
+      <c r="Z67" s="10" t="n">
         <v>40.83</v>
       </c>
-      <c r="AA67" s="6" t="n">
+      <c r="AA67" s="10" t="n">
         <v>39.05</v>
       </c>
-      <c r="AB67" s="6" t="n">
+      <c r="AB67" s="10" t="n">
         <v>39.54</v>
       </c>
-      <c r="AC67" s="6" t="n">
+      <c r="AC67" s="10" t="n">
         <v>38.81</v>
       </c>
-      <c r="AD67" s="6" t="n">
+      <c r="AD67" s="10" t="n">
         <v>39.5</v>
       </c>
-      <c r="AE67" s="6" t="n">
+      <c r="AE67" s="10" t="n">
         <v>40.44</v>
       </c>
-      <c r="AF67" s="6" t="n">
+      <c r="AF67" s="10" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG67" s="6" t="n">
+      <c r="AG67" s="10" t="n">
         <v>39.62</v>
       </c>
       <c r="AH67" s="6" t="n">
@@ -6272,7 +6305,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="12" t="n"/>
+      <c r="AK67" s="16" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6283,97 +6316,97 @@
       <c r="B68" s="6" t="n">
         <v>199.25</v>
       </c>
-      <c r="C68" s="6" t="n">
+      <c r="C68" s="7" t="n">
         <v>77.72</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="7" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="7" t="n">
         <v>78.12</v>
       </c>
-      <c r="G68" s="6" t="n">
+      <c r="G68" s="7" t="n">
         <v>78.11</v>
       </c>
-      <c r="H68" s="6" t="n">
+      <c r="H68" s="7" t="n">
         <v>78.5</v>
       </c>
-      <c r="I68" s="6" t="n">
+      <c r="I68" s="7" t="n">
         <v>78.06</v>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="J68" s="7" t="n">
         <v>78.15000000000001</v>
       </c>
-      <c r="K68" s="6" t="n">
+      <c r="K68" s="7" t="n">
         <v>78.7</v>
       </c>
-      <c r="L68" s="6" t="n">
+      <c r="L68" s="7" t="n">
         <v>78.45</v>
       </c>
-      <c r="M68" s="6" t="n">
+      <c r="M68" s="7" t="n">
         <v>78.76000000000001</v>
       </c>
-      <c r="N68" s="6" t="n">
+      <c r="N68" s="7" t="n">
         <v>78.95</v>
       </c>
-      <c r="O68" s="6" t="n">
+      <c r="O68" s="7" t="n">
         <v>77.97</v>
       </c>
-      <c r="P68" s="6" t="n">
+      <c r="P68" s="7" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="Q68" s="6" t="n">
+      <c r="Q68" s="7" t="n">
         <v>78.45999999999999</v>
       </c>
-      <c r="R68" s="6" t="n">
+      <c r="R68" s="7" t="n">
         <v>78.12</v>
       </c>
-      <c r="S68" s="6" t="n">
+      <c r="S68" s="7" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="T68" s="6" t="n">
+      <c r="T68" s="7" t="n">
         <v>78.47</v>
       </c>
-      <c r="U68" s="6" t="n">
+      <c r="U68" s="7" t="n">
         <v>78.36</v>
       </c>
-      <c r="V68" s="6" t="n">
+      <c r="V68" s="7" t="n">
         <v>78.39</v>
       </c>
-      <c r="W68" s="6" t="n">
+      <c r="W68" s="7" t="n">
         <v>78.31</v>
       </c>
-      <c r="X68" s="6" t="n">
+      <c r="X68" s="7" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="Y68" s="6" t="n">
+      <c r="Y68" s="7" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="Z68" s="6" t="n">
+      <c r="Z68" s="7" t="n">
         <v>78.55</v>
       </c>
-      <c r="AA68" s="6" t="n">
+      <c r="AA68" s="7" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="AB68" s="6" t="n">
+      <c r="AB68" s="7" t="n">
         <v>78.45</v>
       </c>
-      <c r="AC68" s="6" t="n">
+      <c r="AC68" s="7" t="n">
         <v>78.31</v>
       </c>
-      <c r="AD68" s="6" t="n">
+      <c r="AD68" s="7" t="n">
         <v>78.41</v>
       </c>
-      <c r="AE68" s="6" t="n">
+      <c r="AE68" s="7" t="n">
         <v>77.87</v>
       </c>
-      <c r="AF68" s="6" t="n">
+      <c r="AF68" s="7" t="n">
         <v>78.44</v>
       </c>
-      <c r="AG68" s="6" t="n">
+      <c r="AG68" s="7" t="n">
         <v>78.26000000000001</v>
       </c>
       <c r="AH68" s="6" t="n">
@@ -6381,7 +6414,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="12" t="n"/>
+      <c r="AK68" s="16" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6392,97 +6425,97 @@
       <c r="B69" s="6" t="n">
         <v>211.25</v>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="7" t="n">
         <v>72.53</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="7" t="n">
         <v>72.84</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="7" t="n">
         <v>73.08</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="7" t="n">
         <v>72.03</v>
       </c>
-      <c r="G69" s="6" t="n">
+      <c r="G69" s="7" t="n">
         <v>72.42</v>
       </c>
-      <c r="H69" s="6" t="n">
+      <c r="H69" s="7" t="n">
         <v>72.61</v>
       </c>
-      <c r="I69" s="6" t="n">
+      <c r="I69" s="7" t="n">
         <v>72.16</v>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="J69" s="7" t="n">
         <v>72.28</v>
       </c>
-      <c r="K69" s="6" t="n">
+      <c r="K69" s="7" t="n">
         <v>72.98</v>
       </c>
-      <c r="L69" s="6" t="n">
+      <c r="L69" s="7" t="n">
         <v>72.66</v>
       </c>
-      <c r="M69" s="6" t="n">
+      <c r="M69" s="7" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="N69" s="6" t="n">
+      <c r="N69" s="7" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="O69" s="6" t="n">
+      <c r="O69" s="7" t="n">
         <v>71.54000000000001</v>
       </c>
-      <c r="P69" s="6" t="n">
+      <c r="P69" s="7" t="n">
         <v>72.36</v>
       </c>
-      <c r="Q69" s="6" t="n">
+      <c r="Q69" s="7" t="n">
         <v>72.65000000000001</v>
       </c>
-      <c r="R69" s="6" t="n">
+      <c r="R69" s="7" t="n">
         <v>72.38</v>
       </c>
-      <c r="S69" s="6" t="n">
+      <c r="S69" s="7" t="n">
         <v>72.12</v>
       </c>
-      <c r="T69" s="6" t="n">
+      <c r="T69" s="7" t="n">
         <v>72.94</v>
       </c>
-      <c r="U69" s="6" t="n">
+      <c r="U69" s="7" t="n">
         <v>72.81</v>
       </c>
-      <c r="V69" s="6" t="n">
+      <c r="V69" s="7" t="n">
         <v>72.56</v>
       </c>
-      <c r="W69" s="6" t="n">
+      <c r="W69" s="7" t="n">
         <v>72.27</v>
       </c>
-      <c r="X69" s="6" t="n">
+      <c r="X69" s="7" t="n">
         <v>72.03</v>
       </c>
-      <c r="Y69" s="6" t="n">
+      <c r="Y69" s="7" t="n">
         <v>72.51000000000001</v>
       </c>
-      <c r="Z69" s="6" t="n">
+      <c r="Z69" s="7" t="n">
         <v>72.88</v>
       </c>
-      <c r="AA69" s="6" t="n">
+      <c r="AA69" s="7" t="n">
         <v>72.31999999999999</v>
       </c>
-      <c r="AB69" s="6" t="n">
+      <c r="AB69" s="7" t="n">
         <v>72.3</v>
       </c>
-      <c r="AC69" s="6" t="n">
+      <c r="AC69" s="7" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="AD69" s="6" t="n">
+      <c r="AD69" s="7" t="n">
         <v>72.77</v>
       </c>
-      <c r="AE69" s="6" t="n">
+      <c r="AE69" s="7" t="n">
         <v>72.26000000000001</v>
       </c>
-      <c r="AF69" s="6" t="n">
+      <c r="AF69" s="7" t="n">
         <v>72.72</v>
       </c>
-      <c r="AG69" s="6" t="n">
+      <c r="AG69" s="7" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="AH69" s="6" t="n">
@@ -6490,7 +6523,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="12" t="n"/>
+      <c r="AK69" s="16" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6501,97 +6534,97 @@
       <c r="B70" s="6" t="n">
         <v>549.25</v>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C70" s="10" t="n">
         <v>31.82</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="10" t="n">
         <v>34.01</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="10" t="n">
         <v>31.3</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="10" t="n">
         <v>31.78</v>
       </c>
-      <c r="G70" s="6" t="n">
+      <c r="G70" s="10" t="n">
         <v>31.44</v>
       </c>
-      <c r="H70" s="6" t="n">
+      <c r="H70" s="10" t="n">
         <v>31.81</v>
       </c>
-      <c r="I70" s="6" t="n">
+      <c r="I70" s="10" t="n">
         <v>31.13</v>
       </c>
-      <c r="J70" s="6" t="n">
+      <c r="J70" s="10" t="n">
         <v>32.33</v>
       </c>
-      <c r="K70" s="6" t="n">
+      <c r="K70" s="10" t="n">
         <v>31.17</v>
       </c>
-      <c r="L70" s="6" t="n">
+      <c r="L70" s="10" t="n">
         <v>30.91</v>
       </c>
-      <c r="M70" s="6" t="n">
+      <c r="M70" s="10" t="n">
         <v>31.56</v>
       </c>
-      <c r="N70" s="6" t="n">
+      <c r="N70" s="10" t="n">
         <v>31.3</v>
       </c>
-      <c r="O70" s="6" t="n">
+      <c r="O70" s="10" t="n">
         <v>31.59</v>
       </c>
-      <c r="P70" s="6" t="n">
+      <c r="P70" s="10" t="n">
         <v>31.9</v>
       </c>
-      <c r="Q70" s="6" t="n">
+      <c r="Q70" s="10" t="n">
         <v>31.52</v>
       </c>
-      <c r="R70" s="6" t="n">
+      <c r="R70" s="10" t="n">
         <v>31.22</v>
       </c>
-      <c r="S70" s="6" t="n">
+      <c r="S70" s="10" t="n">
         <v>31.62</v>
       </c>
-      <c r="T70" s="6" t="n">
+      <c r="T70" s="10" t="n">
         <v>31.62</v>
       </c>
-      <c r="U70" s="6" t="n">
+      <c r="U70" s="10" t="n">
         <v>31.75</v>
       </c>
-      <c r="V70" s="6" t="n">
+      <c r="V70" s="10" t="n">
         <v>32.01</v>
       </c>
-      <c r="W70" s="6" t="n">
+      <c r="W70" s="10" t="n">
         <v>32.09</v>
       </c>
-      <c r="X70" s="6" t="n">
+      <c r="X70" s="10" t="n">
         <v>32.17</v>
       </c>
-      <c r="Y70" s="6" t="n">
+      <c r="Y70" s="10" t="n">
         <v>31.41</v>
       </c>
-      <c r="Z70" s="6" t="n">
+      <c r="Z70" s="10" t="n">
         <v>31.92</v>
       </c>
-      <c r="AA70" s="6" t="n">
+      <c r="AA70" s="10" t="n">
         <v>34.1</v>
       </c>
-      <c r="AB70" s="6" t="n">
+      <c r="AB70" s="10" t="n">
         <v>31.28</v>
       </c>
-      <c r="AC70" s="6" t="n">
+      <c r="AC70" s="10" t="n">
         <v>31.6</v>
       </c>
-      <c r="AD70" s="6" t="n">
+      <c r="AD70" s="10" t="n">
         <v>32.31</v>
       </c>
-      <c r="AE70" s="6" t="n">
+      <c r="AE70" s="10" t="n">
         <v>32.11</v>
       </c>
-      <c r="AF70" s="6" t="n">
+      <c r="AF70" s="10" t="n">
         <v>31.26</v>
       </c>
-      <c r="AG70" s="6" t="n">
+      <c r="AG70" s="10" t="n">
         <v>32.11</v>
       </c>
       <c r="AH70" s="6" t="n">
@@ -6599,7 +6632,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="12" t="n"/>
+      <c r="AK70" s="16" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6610,97 +6643,97 @@
       <c r="B71" s="6" t="n">
         <v>573.25</v>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C71" s="10" t="n">
         <v>30.1</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="10" t="n">
         <v>29.72</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="G71" s="6" t="n">
+      <c r="G71" s="10" t="n">
         <v>31.7</v>
       </c>
-      <c r="H71" s="6" t="n">
+      <c r="H71" s="10" t="n">
         <v>29.91</v>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="I71" s="10" t="n">
         <v>30.73</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="J71" s="10" t="n">
         <v>34.14</v>
       </c>
-      <c r="K71" s="6" t="n">
+      <c r="K71" s="10" t="n">
         <v>30.47</v>
       </c>
-      <c r="L71" s="6" t="n">
+      <c r="L71" s="10" t="n">
         <v>32.12</v>
       </c>
-      <c r="M71" s="6" t="n">
+      <c r="M71" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="N71" s="6" t="n">
+      <c r="N71" s="10" t="n">
         <v>30.12</v>
       </c>
-      <c r="O71" s="6" t="n">
+      <c r="O71" s="10" t="n">
         <v>29.56</v>
       </c>
-      <c r="P71" s="6" t="n">
+      <c r="P71" s="10" t="n">
         <v>30.11</v>
       </c>
-      <c r="Q71" s="6" t="n">
+      <c r="Q71" s="10" t="n">
         <v>31.05</v>
       </c>
-      <c r="R71" s="6" t="n">
+      <c r="R71" s="10" t="n">
         <v>29.82</v>
       </c>
-      <c r="S71" s="6" t="n">
+      <c r="S71" s="10" t="n">
         <v>30.34</v>
       </c>
-      <c r="T71" s="6" t="n">
+      <c r="T71" s="10" t="n">
         <v>29.44</v>
       </c>
-      <c r="U71" s="6" t="n">
+      <c r="U71" s="10" t="n">
         <v>29.68</v>
       </c>
-      <c r="V71" s="6" t="n">
+      <c r="V71" s="10" t="n">
         <v>29.7</v>
       </c>
-      <c r="W71" s="6" t="n">
+      <c r="W71" s="10" t="n">
         <v>29.73</v>
       </c>
-      <c r="X71" s="6" t="n">
+      <c r="X71" s="10" t="n">
         <v>31.34</v>
       </c>
-      <c r="Y71" s="6" t="n">
+      <c r="Y71" s="10" t="n">
         <v>34.96</v>
       </c>
-      <c r="Z71" s="6" t="n">
+      <c r="Z71" s="10" t="n">
         <v>29.62</v>
       </c>
-      <c r="AA71" s="6" t="n">
+      <c r="AA71" s="10" t="n">
         <v>29.48</v>
       </c>
-      <c r="AB71" s="6" t="n">
+      <c r="AB71" s="10" t="n">
         <v>29.66</v>
       </c>
-      <c r="AC71" s="6" t="n">
+      <c r="AC71" s="10" t="n">
         <v>29.65</v>
       </c>
-      <c r="AD71" s="6" t="n">
+      <c r="AD71" s="10" t="n">
         <v>29.81</v>
       </c>
-      <c r="AE71" s="6" t="n">
+      <c r="AE71" s="10" t="n">
         <v>29.57</v>
       </c>
-      <c r="AF71" s="6" t="n">
+      <c r="AF71" s="10" t="n">
         <v>29.62</v>
       </c>
-      <c r="AG71" s="6" t="n">
+      <c r="AG71" s="10" t="n">
         <v>32.01</v>
       </c>
       <c r="AH71" s="6" t="n">
@@ -6708,7 +6741,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="12" t="n"/>
+      <c r="AK71" s="16" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6719,97 +6752,97 @@
       <c r="B72" s="6" t="n">
         <v>585.25</v>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="10" t="n">
         <v>33.38</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="10" t="n">
         <v>32.61</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="10" t="n">
         <v>32.72</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="G72" s="6" t="n">
+      <c r="G72" s="10" t="n">
         <v>32.51</v>
       </c>
-      <c r="H72" s="6" t="n">
+      <c r="H72" s="10" t="n">
         <v>32.48</v>
       </c>
-      <c r="I72" s="6" t="n">
+      <c r="I72" s="10" t="n">
         <v>31.93</v>
       </c>
-      <c r="J72" s="6" t="n">
+      <c r="J72" s="10" t="n">
         <v>35.1</v>
       </c>
-      <c r="K72" s="6" t="n">
+      <c r="K72" s="10" t="n">
         <v>32.72</v>
       </c>
-      <c r="L72" s="6" t="n">
+      <c r="L72" s="10" t="n">
         <v>34.05</v>
       </c>
-      <c r="M72" s="6" t="n">
+      <c r="M72" s="10" t="n">
         <v>34.14</v>
       </c>
-      <c r="N72" s="6" t="n">
+      <c r="N72" s="10" t="n">
         <v>32.36</v>
       </c>
-      <c r="O72" s="6" t="n">
+      <c r="O72" s="10" t="n">
         <v>32.78</v>
       </c>
-      <c r="P72" s="6" t="n">
+      <c r="P72" s="10" t="n">
         <v>34.24</v>
       </c>
-      <c r="Q72" s="6" t="n">
+      <c r="Q72" s="10" t="n">
         <v>32.56</v>
       </c>
-      <c r="R72" s="6" t="n">
+      <c r="R72" s="10" t="n">
         <v>32.69</v>
       </c>
-      <c r="S72" s="6" t="n">
+      <c r="S72" s="10" t="n">
         <v>32.33</v>
       </c>
-      <c r="T72" s="6" t="n">
+      <c r="T72" s="10" t="n">
         <v>32.36</v>
       </c>
-      <c r="U72" s="6" t="n">
+      <c r="U72" s="10" t="n">
         <v>32.29</v>
       </c>
-      <c r="V72" s="6" t="n">
+      <c r="V72" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="W72" s="6" t="n">
+      <c r="W72" s="10" t="n">
         <v>32.46</v>
       </c>
-      <c r="X72" s="6" t="n">
+      <c r="X72" s="10" t="n">
         <v>31.89</v>
       </c>
-      <c r="Y72" s="6" t="n">
+      <c r="Y72" s="10" t="n">
         <v>32.44</v>
       </c>
-      <c r="Z72" s="6" t="n">
+      <c r="Z72" s="10" t="n">
         <v>31.9</v>
       </c>
-      <c r="AA72" s="6" t="n">
+      <c r="AA72" s="10" t="n">
         <v>32.17</v>
       </c>
-      <c r="AB72" s="6" t="n">
+      <c r="AB72" s="10" t="n">
         <v>33.28</v>
       </c>
-      <c r="AC72" s="6" t="n">
+      <c r="AC72" s="10" t="n">
         <v>32.95</v>
       </c>
-      <c r="AD72" s="6" t="n">
+      <c r="AD72" s="10" t="n">
         <v>32.63</v>
       </c>
-      <c r="AE72" s="6" t="n">
+      <c r="AE72" s="10" t="n">
         <v>32.53</v>
       </c>
-      <c r="AF72" s="6" t="n">
+      <c r="AF72" s="10" t="n">
         <v>32.38</v>
       </c>
-      <c r="AG72" s="6" t="n">
+      <c r="AG72" s="10" t="n">
         <v>32.41</v>
       </c>
       <c r="AH72" s="6" t="n">
@@ -6817,7 +6850,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="12" t="n"/>
+      <c r="AK72" s="16" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6828,97 +6861,97 @@
       <c r="B73" s="6" t="n">
         <v>597.25</v>
       </c>
-      <c r="C73" s="6" t="n">
+      <c r="C73" s="7" t="n">
         <v>79.81999999999999</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="7" t="n">
         <v>79.70999999999999</v>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="7" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="7" t="n">
         <v>79.84999999999999</v>
       </c>
-      <c r="G73" s="6" t="n">
+      <c r="G73" s="7" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="H73" s="6" t="n">
+      <c r="H73" s="7" t="n">
         <v>79.95</v>
       </c>
-      <c r="I73" s="6" t="n">
+      <c r="I73" s="7" t="n">
         <v>80.20999999999999</v>
       </c>
-      <c r="J73" s="6" t="n">
+      <c r="J73" s="7" t="n">
         <v>79.58</v>
       </c>
-      <c r="K73" s="6" t="n">
+      <c r="K73" s="7" t="n">
         <v>79.67</v>
       </c>
-      <c r="L73" s="6" t="n">
+      <c r="L73" s="7" t="n">
         <v>79.06</v>
       </c>
-      <c r="M73" s="6" t="n">
+      <c r="M73" s="7" t="n">
         <v>79.97</v>
       </c>
-      <c r="N73" s="6" t="n">
+      <c r="N73" s="7" t="n">
         <v>55.45</v>
       </c>
-      <c r="O73" s="6" t="n">
+      <c r="O73" s="7" t="n">
         <v>79.84999999999999</v>
       </c>
-      <c r="P73" s="6" t="n">
+      <c r="P73" s="7" t="n">
         <v>79.78</v>
       </c>
-      <c r="Q73" s="6" t="n">
+      <c r="Q73" s="7" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="R73" s="6" t="n">
+      <c r="R73" s="7" t="n">
         <v>79.95999999999999</v>
       </c>
-      <c r="S73" s="6" t="n">
+      <c r="S73" s="7" t="n">
         <v>79.34</v>
       </c>
-      <c r="T73" s="6" t="n">
+      <c r="T73" s="7" t="n">
         <v>78.88</v>
       </c>
-      <c r="U73" s="6" t="n">
+      <c r="U73" s="7" t="n">
         <v>79.08</v>
       </c>
-      <c r="V73" s="6" t="n">
+      <c r="V73" s="7" t="n">
         <v>79.84</v>
       </c>
-      <c r="W73" s="6" t="n">
+      <c r="W73" s="7" t="n">
         <v>79.31</v>
       </c>
-      <c r="X73" s="6" t="n">
+      <c r="X73" s="7" t="n">
         <v>80.03</v>
       </c>
-      <c r="Y73" s="6" t="n">
+      <c r="Y73" s="7" t="n">
         <v>79.94</v>
       </c>
-      <c r="Z73" s="6" t="n">
+      <c r="Z73" s="7" t="n">
         <v>80.08</v>
       </c>
-      <c r="AA73" s="6" t="n">
+      <c r="AA73" s="7" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="AB73" s="6" t="n">
+      <c r="AB73" s="7" t="n">
         <v>79.20999999999999</v>
       </c>
-      <c r="AC73" s="6" t="n">
+      <c r="AC73" s="7" t="n">
         <v>79.62</v>
       </c>
-      <c r="AD73" s="6" t="n">
+      <c r="AD73" s="7" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="AE73" s="6" t="n">
+      <c r="AE73" s="7" t="n">
         <v>80.06</v>
       </c>
-      <c r="AF73" s="6" t="n">
+      <c r="AF73" s="7" t="n">
         <v>79.29000000000001</v>
       </c>
-      <c r="AG73" s="6" t="n">
+      <c r="AG73" s="7" t="n">
         <v>79.79000000000001</v>
       </c>
       <c r="AH73" s="6" t="n">
@@ -6926,7 +6959,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="12" t="n"/>
+      <c r="AK73" s="16" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6937,97 +6970,97 @@
       <c r="B74" s="6" t="n">
         <v>621.25</v>
       </c>
-      <c r="C74" s="6" t="n">
+      <c r="C74" s="10" t="n">
         <v>30.32</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="10" t="n">
         <v>30.3</v>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="10" t="n">
         <v>29.75</v>
       </c>
-      <c r="G74" s="6" t="n">
+      <c r="G74" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="H74" s="6" t="n">
+      <c r="H74" s="10" t="n">
         <v>29.98</v>
       </c>
-      <c r="I74" s="6" t="n">
+      <c r="I74" s="10" t="n">
         <v>29.66</v>
       </c>
-      <c r="J74" s="6" t="n">
+      <c r="J74" s="10" t="n">
         <v>29.84</v>
       </c>
-      <c r="K74" s="6" t="n">
+      <c r="K74" s="10" t="n">
         <v>30.35</v>
       </c>
-      <c r="L74" s="6" t="n">
+      <c r="L74" s="10" t="n">
         <v>33.02</v>
       </c>
-      <c r="M74" s="6" t="n">
+      <c r="M74" s="10" t="n">
         <v>30.01</v>
       </c>
-      <c r="N74" s="6" t="n">
+      <c r="N74" s="10" t="n">
         <v>29.79</v>
       </c>
-      <c r="O74" s="6" t="n">
+      <c r="O74" s="10" t="n">
         <v>32.08</v>
       </c>
-      <c r="P74" s="6" t="n">
+      <c r="P74" s="10" t="n">
         <v>30.26</v>
       </c>
-      <c r="Q74" s="6" t="n">
+      <c r="Q74" s="10" t="n">
         <v>30.26</v>
       </c>
-      <c r="R74" s="6" t="n">
+      <c r="R74" s="10" t="n">
         <v>29.52</v>
       </c>
-      <c r="S74" s="6" t="n">
+      <c r="S74" s="10" t="n">
         <v>30.26</v>
       </c>
-      <c r="T74" s="6" t="n">
+      <c r="T74" s="10" t="n">
         <v>29.72</v>
       </c>
-      <c r="U74" s="6" t="n">
+      <c r="U74" s="10" t="n">
         <v>31.64</v>
       </c>
-      <c r="V74" s="6" t="n">
+      <c r="V74" s="10" t="n">
         <v>29.29</v>
       </c>
-      <c r="W74" s="6" t="n">
+      <c r="W74" s="10" t="n">
         <v>29.83</v>
       </c>
-      <c r="X74" s="6" t="n">
+      <c r="X74" s="10" t="n">
         <v>30.21</v>
       </c>
-      <c r="Y74" s="6" t="n">
+      <c r="Y74" s="10" t="n">
         <v>31.16</v>
       </c>
-      <c r="Z74" s="6" t="n">
+      <c r="Z74" s="10" t="n">
         <v>29.88</v>
       </c>
-      <c r="AA74" s="6" t="n">
+      <c r="AA74" s="10" t="n">
         <v>33.85</v>
       </c>
-      <c r="AB74" s="6" t="n">
+      <c r="AB74" s="10" t="n">
         <v>29.26</v>
       </c>
-      <c r="AC74" s="6" t="n">
+      <c r="AC74" s="10" t="n">
         <v>31.25</v>
       </c>
-      <c r="AD74" s="6" t="n">
+      <c r="AD74" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="AE74" s="6" t="n">
+      <c r="AE74" s="10" t="n">
         <v>29.49</v>
       </c>
-      <c r="AF74" s="6" t="n">
+      <c r="AF74" s="10" t="n">
         <v>30.38</v>
       </c>
-      <c r="AG74" s="6" t="n">
+      <c r="AG74" s="10" t="n">
         <v>30.25</v>
       </c>
       <c r="AH74" s="6" t="n">
@@ -7035,116 +7068,116 @@
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="12" t="n"/>
+      <c r="AK74" s="16" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
+      <c r="B75" s="12" t="n">
         <v>633.25</v>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="C75" s="17" t="n">
         <v>29.02</v>
       </c>
-      <c r="D75" s="9" t="n">
+      <c r="D75" s="17" t="n">
         <v>30.64</v>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="E75" s="17" t="n">
         <v>28.75</v>
       </c>
-      <c r="F75" s="9" t="n">
+      <c r="F75" s="17" t="n">
         <v>29.3</v>
       </c>
-      <c r="G75" s="9" t="n">
+      <c r="G75" s="17" t="n">
         <v>29.96</v>
       </c>
-      <c r="H75" s="9" t="n">
+      <c r="H75" s="17" t="n">
         <v>29.38</v>
       </c>
-      <c r="I75" s="9" t="n">
+      <c r="I75" s="17" t="n">
         <v>28.91</v>
       </c>
-      <c r="J75" s="9" t="n">
+      <c r="J75" s="17" t="n">
         <v>29.28</v>
       </c>
-      <c r="K75" s="9" t="n">
+      <c r="K75" s="17" t="n">
         <v>30.2</v>
       </c>
-      <c r="L75" s="9" t="n">
+      <c r="L75" s="17" t="n">
         <v>30.12</v>
       </c>
-      <c r="M75" s="9" t="n">
+      <c r="M75" s="17" t="n">
         <v>31.44</v>
       </c>
-      <c r="N75" s="9" t="n">
+      <c r="N75" s="17" t="n">
         <v>29.04</v>
       </c>
-      <c r="O75" s="9" t="n">
+      <c r="O75" s="17" t="n">
         <v>29.02</v>
       </c>
-      <c r="P75" s="9" t="n">
+      <c r="P75" s="17" t="n">
         <v>29.38</v>
       </c>
-      <c r="Q75" s="9" t="n">
+      <c r="Q75" s="17" t="n">
         <v>29.29</v>
       </c>
-      <c r="R75" s="9" t="n">
+      <c r="R75" s="17" t="n">
         <v>29.71</v>
       </c>
-      <c r="S75" s="9" t="n">
+      <c r="S75" s="17" t="n">
         <v>29.5</v>
       </c>
-      <c r="T75" s="9" t="n">
+      <c r="T75" s="17" t="n">
         <v>29.38</v>
       </c>
-      <c r="U75" s="9" t="n">
+      <c r="U75" s="17" t="n">
         <v>29.78</v>
       </c>
-      <c r="V75" s="9" t="n">
+      <c r="V75" s="17" t="n">
         <v>29.85</v>
       </c>
-      <c r="W75" s="9" t="n">
+      <c r="W75" s="17" t="n">
         <v>29.16</v>
       </c>
-      <c r="X75" s="9" t="n">
+      <c r="X75" s="17" t="n">
         <v>29.29</v>
       </c>
-      <c r="Y75" s="9" t="n">
+      <c r="Y75" s="17" t="n">
         <v>29.48</v>
       </c>
-      <c r="Z75" s="9" t="n">
+      <c r="Z75" s="17" t="n">
         <v>37.17</v>
       </c>
-      <c r="AA75" s="9" t="n">
+      <c r="AA75" s="17" t="n">
         <v>28.92</v>
       </c>
-      <c r="AB75" s="9" t="n">
+      <c r="AB75" s="17" t="n">
         <v>31.6</v>
       </c>
-      <c r="AC75" s="9" t="n">
+      <c r="AC75" s="17" t="n">
         <v>30.51</v>
       </c>
-      <c r="AD75" s="9" t="n">
+      <c r="AD75" s="17" t="n">
         <v>29.07</v>
       </c>
-      <c r="AE75" s="9" t="n">
+      <c r="AE75" s="17" t="n">
         <v>28.94</v>
       </c>
-      <c r="AF75" s="9" t="n">
+      <c r="AF75" s="17" t="n">
         <v>29.25</v>
       </c>
-      <c r="AG75" s="9" t="n">
+      <c r="AG75" s="17" t="n">
         <v>29.59</v>
       </c>
-      <c r="AH75" s="9" t="n">
+      <c r="AH75" s="12" t="n">
         <v>29.84</v>
       </c>
-      <c r="AI75" s="9" t="inlineStr"/>
-      <c r="AJ75" s="9" t="inlineStr"/>
-      <c r="AK75" s="13" t="n"/>
+      <c r="AI75" s="12" t="inlineStr"/>
+      <c r="AJ75" s="12" t="inlineStr"/>
+      <c r="AK75" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -30,30 +30,12 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE9F"/>
-        <bgColor rgb="FFFFFE9F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFD9BCB"/>
-        <bgColor rgb="FFFD9BCB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -171,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,16 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,17 +182,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -792,7 +759,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -934,97 +901,97 @@
       <c r="B11" s="6" t="n">
         <v>88.3</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="6" t="n">
         <v>68.28</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>70.26000000000001</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="6" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="6" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="6" t="n">
         <v>70.42</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="6" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="6" t="n">
         <v>70.89</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="6" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="6" t="n">
         <v>71.63</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="N11" s="6" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="6" t="n">
         <v>71.54000000000001</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="6" t="n">
         <v>71.56999999999999</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="6" t="n">
         <v>70.81999999999999</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="R11" s="6" t="n">
         <v>70.75</v>
       </c>
-      <c r="S11" s="7" t="n">
+      <c r="S11" s="6" t="n">
         <v>71.04000000000001</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="T11" s="6" t="n">
         <v>71.26000000000001</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="6" t="n">
         <v>71.11</v>
       </c>
-      <c r="V11" s="7" t="n">
+      <c r="V11" s="6" t="n">
         <v>70.81</v>
       </c>
-      <c r="W11" s="7" t="n">
+      <c r="W11" s="6" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="X11" s="7" t="n">
+      <c r="X11" s="6" t="n">
         <v>70.86</v>
       </c>
-      <c r="Y11" s="7" t="n">
+      <c r="Y11" s="6" t="n">
         <v>71.14</v>
       </c>
-      <c r="Z11" s="7" t="n">
+      <c r="Z11" s="6" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="AA11" s="7" t="n">
+      <c r="AA11" s="6" t="n">
         <v>70.34</v>
       </c>
-      <c r="AB11" s="7" t="n">
+      <c r="AB11" s="6" t="n">
         <v>70.58</v>
       </c>
-      <c r="AC11" s="7" t="n">
+      <c r="AC11" s="6" t="n">
         <v>70.89</v>
       </c>
-      <c r="AD11" s="7" t="n">
+      <c r="AD11" s="6" t="n">
         <v>71.29000000000001</v>
       </c>
-      <c r="AE11" s="7" t="n">
+      <c r="AE11" s="6" t="n">
         <v>70.7</v>
       </c>
-      <c r="AF11" s="7" t="n">
+      <c r="AF11" s="6" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="AG11" s="7" t="n">
+      <c r="AG11" s="6" t="n">
         <v>71.29000000000001</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1034,7 +1001,7 @@
         <v>244.66</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1045,97 +1012,97 @@
       <c r="B12" s="6" t="n">
         <v>88.7</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>72.78</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="6" t="n">
         <v>65.56</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>71.59</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="6" t="n">
         <v>69.8</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="6" t="n">
         <v>69.92</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="6" t="n">
         <v>71.62</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="6" t="n">
         <v>72.81</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="6" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="6" t="n">
         <v>72.44</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="N12" s="6" t="n">
         <v>72.89</v>
       </c>
-      <c r="O12" s="7" t="n">
+      <c r="O12" s="6" t="n">
         <v>73.23</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="6" t="n">
         <v>72.42</v>
       </c>
-      <c r="Q12" s="7" t="n">
+      <c r="Q12" s="6" t="n">
         <v>72.41</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="R12" s="6" t="n">
         <v>72.81999999999999</v>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="S12" s="6" t="n">
         <v>72.63</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="T12" s="6" t="n">
         <v>72.69</v>
       </c>
-      <c r="U12" s="7" t="n">
+      <c r="U12" s="6" t="n">
         <v>73.51000000000001</v>
       </c>
-      <c r="V12" s="7" t="n">
+      <c r="V12" s="6" t="n">
         <v>73.06999999999999</v>
       </c>
-      <c r="W12" s="7" t="n">
+      <c r="W12" s="6" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="X12" s="7" t="n">
+      <c r="X12" s="6" t="n">
         <v>72.73999999999999</v>
       </c>
-      <c r="Y12" s="7" t="n">
+      <c r="Y12" s="6" t="n">
         <v>73.26000000000001</v>
       </c>
-      <c r="Z12" s="7" t="n">
+      <c r="Z12" s="6" t="n">
         <v>72.26000000000001</v>
       </c>
-      <c r="AA12" s="7" t="n">
+      <c r="AA12" s="6" t="n">
         <v>72.54000000000001</v>
       </c>
-      <c r="AB12" s="7" t="n">
+      <c r="AB12" s="6" t="n">
         <v>72.48</v>
       </c>
-      <c r="AC12" s="7" t="n">
+      <c r="AC12" s="6" t="n">
         <v>73.01000000000001</v>
       </c>
-      <c r="AD12" s="7" t="n">
+      <c r="AD12" s="6" t="n">
         <v>73.56</v>
       </c>
-      <c r="AE12" s="7" t="n">
+      <c r="AE12" s="6" t="n">
         <v>73.04000000000001</v>
       </c>
-      <c r="AF12" s="7" t="n">
+      <c r="AF12" s="6" t="n">
         <v>73.42</v>
       </c>
-      <c r="AG12" s="7" t="n">
+      <c r="AG12" s="6" t="n">
         <v>72.84</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1145,7 +1112,7 @@
         <v>160.6</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1156,97 +1123,97 @@
       <c r="B13" s="6" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>72.61</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="6" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>72.34</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="6" t="n">
         <v>72.92</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="6" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="6" t="n">
         <v>71.81</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="6" t="n">
         <v>71.54000000000001</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="6" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="6" t="n">
         <v>73.19</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="N13" s="6" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="O13" s="7" t="n">
+      <c r="O13" s="6" t="n">
         <v>72.51000000000001</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="P13" s="6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="Q13" s="7" t="n">
+      <c r="Q13" s="6" t="n">
         <v>73.03</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="R13" s="6" t="n">
         <v>72.39</v>
       </c>
-      <c r="S13" s="7" t="n">
+      <c r="S13" s="6" t="n">
         <v>71.26000000000001</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="T13" s="6" t="n">
         <v>72.38</v>
       </c>
-      <c r="U13" s="7" t="n">
+      <c r="U13" s="6" t="n">
         <v>71.44</v>
       </c>
-      <c r="V13" s="7" t="n">
+      <c r="V13" s="6" t="n">
         <v>71.73999999999999</v>
       </c>
-      <c r="W13" s="7" t="n">
+      <c r="W13" s="6" t="n">
         <v>60.52</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="X13" s="6" t="n">
         <v>72.17</v>
       </c>
-      <c r="Y13" s="7" t="n">
+      <c r="Y13" s="6" t="n">
         <v>71.87</v>
       </c>
-      <c r="Z13" s="7" t="n">
+      <c r="Z13" s="6" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="AA13" s="7" t="n">
+      <c r="AA13" s="6" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="AB13" s="7" t="n">
+      <c r="AB13" s="6" t="n">
         <v>70.76000000000001</v>
       </c>
-      <c r="AC13" s="7" t="n">
+      <c r="AC13" s="6" t="n">
         <v>71.78</v>
       </c>
-      <c r="AD13" s="7" t="n">
+      <c r="AD13" s="6" t="n">
         <v>71.84</v>
       </c>
-      <c r="AE13" s="7" t="n">
+      <c r="AE13" s="6" t="n">
         <v>70.8</v>
       </c>
-      <c r="AF13" s="7" t="n">
+      <c r="AF13" s="6" t="n">
         <v>71.34</v>
       </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AG13" s="6" t="n">
         <v>70.06999999999999</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1256,7 +1223,7 @@
         <v>200.59</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1267,97 +1234,97 @@
       <c r="B14" s="6" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>67.19</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>66.91</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>60.02</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>67.92</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>67.73</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="6" t="n">
         <v>67.16</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="6" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="6" t="n">
         <v>66.51000000000001</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="6" t="n">
         <v>67.64</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="6" t="n">
         <v>69.12</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="6" t="n">
         <v>68.26000000000001</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="N14" s="6" t="n">
         <v>69.04000000000001</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="6" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="6" t="n">
         <v>51.91</v>
       </c>
-      <c r="Q14" s="7" t="n">
+      <c r="Q14" s="6" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="R14" s="6" t="n">
         <v>67.39</v>
       </c>
-      <c r="S14" s="7" t="n">
+      <c r="S14" s="6" t="n">
         <v>68.22</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="T14" s="6" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="U14" s="7" t="n">
+      <c r="U14" s="6" t="n">
         <v>68.11</v>
       </c>
-      <c r="V14" s="7" t="n">
+      <c r="V14" s="6" t="n">
         <v>68.19</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="W14" s="6" t="n">
         <v>68.28</v>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="X14" s="6" t="n">
         <v>68.22</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Y14" s="6" t="n">
         <v>67.56999999999999</v>
       </c>
-      <c r="Z14" s="7" t="n">
+      <c r="Z14" s="6" t="n">
         <v>66.69</v>
       </c>
-      <c r="AA14" s="7" t="n">
+      <c r="AA14" s="6" t="n">
         <v>67.38</v>
       </c>
-      <c r="AB14" s="7" t="n">
+      <c r="AB14" s="6" t="n">
         <v>67.04000000000001</v>
       </c>
-      <c r="AC14" s="7" t="n">
+      <c r="AC14" s="6" t="n">
         <v>67.63</v>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AD14" s="6" t="n">
         <v>67.89</v>
       </c>
-      <c r="AE14" s="7" t="n">
+      <c r="AE14" s="6" t="n">
         <v>67.59</v>
       </c>
-      <c r="AF14" s="7" t="n">
+      <c r="AF14" s="6" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AG14" s="6" t="n">
         <v>68.75</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1367,7 +1334,7 @@
         <v>265.65</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1378,97 +1345,97 @@
       <c r="B15" s="6" t="n">
         <v>90.3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>75.42</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>74.88</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="6" t="n">
         <v>75.34999999999999</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>74.34999999999999</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="6" t="n">
         <v>74.97</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="6" t="n">
         <v>75.39</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="6" t="n">
         <v>75.95999999999999</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="6" t="n">
         <v>75.69</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" s="6" t="n">
         <v>75.93000000000001</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" s="6" t="n">
         <v>76.37</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="6" t="n">
         <v>75.69</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="N15" s="6" t="n">
         <v>76.73999999999999</v>
       </c>
-      <c r="O15" s="7" t="n">
+      <c r="O15" s="6" t="n">
         <v>75.83</v>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="P15" s="6" t="n">
         <v>76.41</v>
       </c>
-      <c r="Q15" s="7" t="n">
+      <c r="Q15" s="6" t="n">
         <v>75.81999999999999</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="R15" s="6" t="n">
         <v>75.72</v>
       </c>
-      <c r="S15" s="7" t="n">
+      <c r="S15" s="6" t="n">
         <v>75.34</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="T15" s="6" t="n">
         <v>75.08</v>
       </c>
-      <c r="U15" s="7" t="n">
+      <c r="U15" s="6" t="n">
         <v>76.34999999999999</v>
       </c>
-      <c r="V15" s="7" t="n">
+      <c r="V15" s="6" t="n">
         <v>76.36</v>
       </c>
-      <c r="W15" s="7" t="n">
+      <c r="W15" s="6" t="n">
         <v>75.76000000000001</v>
       </c>
-      <c r="X15" s="7" t="n">
+      <c r="X15" s="6" t="n">
         <v>76.05</v>
       </c>
-      <c r="Y15" s="7" t="n">
+      <c r="Y15" s="6" t="n">
         <v>76.19</v>
       </c>
-      <c r="Z15" s="7" t="n">
+      <c r="Z15" s="6" t="n">
         <v>74.95999999999999</v>
       </c>
-      <c r="AA15" s="7" t="n">
+      <c r="AA15" s="6" t="n">
         <v>75.79000000000001</v>
       </c>
-      <c r="AB15" s="7" t="n">
+      <c r="AB15" s="6" t="n">
         <v>74.79000000000001</v>
       </c>
-      <c r="AC15" s="7" t="n">
+      <c r="AC15" s="6" t="n">
         <v>75.52</v>
       </c>
-      <c r="AD15" s="7" t="n">
+      <c r="AD15" s="6" t="n">
         <v>75.75</v>
       </c>
-      <c r="AE15" s="7" t="n">
+      <c r="AE15" s="6" t="n">
         <v>75.91</v>
       </c>
-      <c r="AF15" s="7" t="n">
+      <c r="AF15" s="6" t="n">
         <v>75.68000000000001</v>
       </c>
-      <c r="AG15" s="7" t="n">
+      <c r="AG15" s="6" t="n">
         <v>75.70999999999999</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1478,7 +1445,7 @@
         <v>229.65</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1489,97 +1456,97 @@
       <c r="B16" s="6" t="n">
         <v>90.7</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>67.89</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="6" t="n">
         <v>60.9</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>67.3</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>68.08</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="6" t="n">
         <v>67.39</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="6" t="n">
         <v>68.81</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="6" t="n">
         <v>68.16</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="6" t="n">
         <v>68.59</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="6" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="6" t="n">
         <v>66.77</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="N16" s="6" t="n">
         <v>68.31999999999999</v>
       </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="6" t="n">
         <v>67.63</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="P16" s="6" t="n">
         <v>66.83</v>
       </c>
-      <c r="Q16" s="7" t="n">
+      <c r="Q16" s="6" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="R16" s="6" t="n">
         <v>67.45999999999999</v>
       </c>
-      <c r="S16" s="7" t="n">
+      <c r="S16" s="6" t="n">
         <v>67.22</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="T16" s="6" t="n">
         <v>67.54000000000001</v>
       </c>
-      <c r="U16" s="7" t="n">
+      <c r="U16" s="6" t="n">
         <v>68.77</v>
       </c>
-      <c r="V16" s="7" t="n">
+      <c r="V16" s="6" t="n">
         <v>68.70999999999999</v>
       </c>
-      <c r="W16" s="7" t="n">
+      <c r="W16" s="6" t="n">
         <v>68.16</v>
       </c>
-      <c r="X16" s="7" t="n">
+      <c r="X16" s="6" t="n">
         <v>69.34</v>
       </c>
-      <c r="Y16" s="7" t="n">
+      <c r="Y16" s="6" t="n">
         <v>68.86</v>
       </c>
-      <c r="Z16" s="7" t="n">
+      <c r="Z16" s="6" t="n">
         <v>66.81</v>
       </c>
-      <c r="AA16" s="7" t="n">
+      <c r="AA16" s="6" t="n">
         <v>69.08</v>
       </c>
-      <c r="AB16" s="7" t="n">
+      <c r="AB16" s="6" t="n">
         <v>68.16</v>
       </c>
-      <c r="AC16" s="7" t="n">
+      <c r="AC16" s="6" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="AD16" s="7" t="n">
+      <c r="AD16" s="6" t="n">
         <v>67.77</v>
       </c>
-      <c r="AE16" s="7" t="n">
+      <c r="AE16" s="6" t="n">
         <v>67.11</v>
       </c>
-      <c r="AF16" s="7" t="n">
+      <c r="AF16" s="6" t="n">
         <v>67.20999999999999</v>
       </c>
-      <c r="AG16" s="7" t="n">
+      <c r="AG16" s="6" t="n">
         <v>68.09</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1589,7 +1556,7 @@
         <v>428.49</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1600,97 +1567,97 @@
       <c r="B17" s="6" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>70.97</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>69.94</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="6" t="n">
         <v>65.2</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>70.06</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="6" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="6" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="6" t="n">
         <v>71.15000000000001</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="6" t="n">
         <v>70.64</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="6" t="n">
         <v>71.81999999999999</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="6" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="N17" s="6" t="n">
         <v>71.64</v>
       </c>
-      <c r="O17" s="7" t="n">
+      <c r="O17" s="6" t="n">
         <v>70.11</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="P17" s="6" t="n">
         <v>70.51000000000001</v>
       </c>
-      <c r="Q17" s="7" t="n">
+      <c r="Q17" s="6" t="n">
         <v>70.2</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="R17" s="6" t="n">
         <v>70.83</v>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="S17" s="6" t="n">
         <v>70.75</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="6" t="n">
         <v>69.44</v>
       </c>
-      <c r="U17" s="7" t="n">
+      <c r="U17" s="6" t="n">
         <v>70.42</v>
       </c>
-      <c r="V17" s="7" t="n">
+      <c r="V17" s="6" t="n">
         <v>70.51000000000001</v>
       </c>
-      <c r="W17" s="7" t="n">
+      <c r="W17" s="6" t="n">
         <v>70.09</v>
       </c>
-      <c r="X17" s="7" t="n">
+      <c r="X17" s="6" t="n">
         <v>69.79000000000001</v>
       </c>
-      <c r="Y17" s="7" t="n">
+      <c r="Y17" s="6" t="n">
         <v>69.2</v>
       </c>
-      <c r="Z17" s="7" t="n">
+      <c r="Z17" s="6" t="n">
         <v>69.92</v>
       </c>
-      <c r="AA17" s="7" t="n">
+      <c r="AA17" s="6" t="n">
         <v>69.08</v>
       </c>
-      <c r="AB17" s="7" t="n">
+      <c r="AB17" s="6" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="AC17" s="7" t="n">
+      <c r="AC17" s="6" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="AD17" s="7" t="n">
+      <c r="AD17" s="6" t="n">
         <v>70.39</v>
       </c>
-      <c r="AE17" s="7" t="n">
+      <c r="AE17" s="6" t="n">
         <v>69.98999999999999</v>
       </c>
-      <c r="AF17" s="7" t="n">
+      <c r="AF17" s="6" t="n">
         <v>69.2</v>
       </c>
-      <c r="AG17" s="7" t="n">
+      <c r="AG17" s="6" t="n">
         <v>68.95999999999999</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1700,7 +1667,7 @@
         <v>388.85</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1711,97 +1678,97 @@
       <c r="B18" s="6" t="n">
         <v>91.5</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="6" t="n">
         <v>52.72</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="6" t="n">
         <v>50.06</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="6" t="n">
         <v>58.76</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="6" t="n">
         <v>50.41</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="6" t="n">
         <v>46.62</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="6" t="n">
         <v>49.69</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="6" t="n">
         <v>50.71</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="6" t="n">
         <v>48.24</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="6" t="n">
         <v>50.75</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="6" t="n">
         <v>50.51</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="6" t="n">
         <v>52.76</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="6" t="n">
         <v>51.64</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="6" t="n">
         <v>48.68</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" s="6" t="n">
         <v>49.17</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="6" t="n">
         <v>53.33</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="6" t="n">
         <v>50.15</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="6" t="n">
         <v>48.7</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="6" t="n">
         <v>49.26</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="6" t="n">
         <v>47.96</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="6" t="n">
         <v>47.53</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="6" t="n">
         <v>49.54</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" s="6" t="n">
         <v>49.93</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="6" t="n">
         <v>52.67</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="Z18" s="6" t="n">
         <v>48.81</v>
       </c>
-      <c r="AA18" s="9" t="n">
+      <c r="AA18" s="6" t="n">
         <v>48.32</v>
       </c>
-      <c r="AB18" s="9" t="n">
+      <c r="AB18" s="6" t="n">
         <v>49.61</v>
       </c>
-      <c r="AC18" s="9" t="n">
+      <c r="AC18" s="6" t="n">
         <v>49.47</v>
       </c>
-      <c r="AD18" s="9" t="n">
+      <c r="AD18" s="6" t="n">
         <v>47.34</v>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AE18" s="6" t="n">
         <v>49.9</v>
       </c>
-      <c r="AF18" s="9" t="n">
+      <c r="AF18" s="6" t="n">
         <v>52.66</v>
       </c>
-      <c r="AG18" s="9" t="n">
+      <c r="AG18" s="6" t="n">
         <v>51.71</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1811,7 +1778,7 @@
         <v>499.47</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1822,97 +1789,97 @@
       <c r="B19" s="6" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="6" t="n">
         <v>66.62</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>66.97</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="6" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="6" t="n">
         <v>68.7</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>67.31</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="6" t="n">
         <v>66.04000000000001</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="6" t="n">
         <v>67.39</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="6" t="n">
         <v>67.81999999999999</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="6" t="n">
         <v>67.41</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="6" t="n">
         <v>67.04000000000001</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="6" t="n">
         <v>66.87</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="N19" s="6" t="n">
         <v>67.88</v>
       </c>
-      <c r="O19" s="7" t="n">
+      <c r="O19" s="6" t="n">
         <v>68.03</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="P19" s="6" t="n">
         <v>67.61</v>
       </c>
-      <c r="Q19" s="7" t="n">
+      <c r="Q19" s="6" t="n">
         <v>67.38</v>
       </c>
-      <c r="R19" s="7" t="n">
+      <c r="R19" s="6" t="n">
         <v>67.73</v>
       </c>
-      <c r="S19" s="7" t="n">
+      <c r="S19" s="6" t="n">
         <v>67.64</v>
       </c>
-      <c r="T19" s="7" t="n">
+      <c r="T19" s="6" t="n">
         <v>67.38</v>
       </c>
-      <c r="U19" s="7" t="n">
+      <c r="U19" s="6" t="n">
         <v>67.33</v>
       </c>
-      <c r="V19" s="7" t="n">
+      <c r="V19" s="6" t="n">
         <v>68.03</v>
       </c>
-      <c r="W19" s="7" t="n">
+      <c r="W19" s="6" t="n">
         <v>67.86</v>
       </c>
-      <c r="X19" s="7" t="n">
+      <c r="X19" s="6" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="Y19" s="7" t="n">
+      <c r="Y19" s="6" t="n">
         <v>67.22</v>
       </c>
-      <c r="Z19" s="7" t="n">
+      <c r="Z19" s="6" t="n">
         <v>66.95</v>
       </c>
-      <c r="AA19" s="7" t="n">
+      <c r="AA19" s="6" t="n">
         <v>67.81999999999999</v>
       </c>
-      <c r="AB19" s="7" t="n">
+      <c r="AB19" s="6" t="n">
         <v>67.92</v>
       </c>
-      <c r="AC19" s="7" t="n">
+      <c r="AC19" s="6" t="n">
         <v>67.02</v>
       </c>
-      <c r="AD19" s="7" t="n">
+      <c r="AD19" s="6" t="n">
         <v>66.37</v>
       </c>
-      <c r="AE19" s="7" t="n">
+      <c r="AE19" s="6" t="n">
         <v>66.31</v>
       </c>
-      <c r="AF19" s="7" t="n">
+      <c r="AF19" s="6" t="n">
         <v>67.34</v>
       </c>
-      <c r="AG19" s="7" t="n">
+      <c r="AG19" s="6" t="n">
         <v>67.03</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1922,7 +1889,7 @@
         <v>315.82</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1933,97 +1900,97 @@
       <c r="B20" s="6" t="n">
         <v>92.3</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>58.3</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>59.64</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="6" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>59.4</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>58.7</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="6" t="n">
         <v>58.94</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="6" t="n">
         <v>61.55</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>60.76</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="6" t="n">
         <v>60.86</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="6" t="n">
         <v>60.81</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="6" t="n">
         <v>60.76</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="N20" s="6" t="n">
         <v>63.44</v>
       </c>
-      <c r="O20" s="7" t="n">
+      <c r="O20" s="6" t="n">
         <v>59.96</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="P20" s="6" t="n">
         <v>61.39</v>
       </c>
-      <c r="Q20" s="7" t="n">
+      <c r="Q20" s="6" t="n">
         <v>61.56</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="R20" s="6" t="n">
         <v>60.75</v>
       </c>
-      <c r="S20" s="7" t="n">
+      <c r="S20" s="6" t="n">
         <v>60.78</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="T20" s="6" t="n">
         <v>59.23</v>
       </c>
-      <c r="U20" s="7" t="n">
+      <c r="U20" s="6" t="n">
         <v>61.55</v>
       </c>
-      <c r="V20" s="7" t="n">
+      <c r="V20" s="6" t="n">
         <v>61.48</v>
       </c>
-      <c r="W20" s="7" t="n">
+      <c r="W20" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="X20" s="7" t="n">
+      <c r="X20" s="6" t="n">
         <v>57.83</v>
       </c>
-      <c r="Y20" s="7" t="n">
+      <c r="Y20" s="6" t="n">
         <v>59.93</v>
       </c>
-      <c r="Z20" s="7" t="n">
+      <c r="Z20" s="6" t="n">
         <v>59.41</v>
       </c>
-      <c r="AA20" s="7" t="n">
+      <c r="AA20" s="6" t="n">
         <v>58.81</v>
       </c>
-      <c r="AB20" s="7" t="n">
+      <c r="AB20" s="6" t="n">
         <v>59.88</v>
       </c>
-      <c r="AC20" s="7" t="n">
+      <c r="AC20" s="6" t="n">
         <v>60.09</v>
       </c>
-      <c r="AD20" s="7" t="n">
+      <c r="AD20" s="6" t="n">
         <v>58.88</v>
       </c>
-      <c r="AE20" s="7" t="n">
+      <c r="AE20" s="6" t="n">
         <v>61.23</v>
       </c>
-      <c r="AF20" s="7" t="n">
+      <c r="AF20" s="6" t="n">
         <v>59.23</v>
       </c>
-      <c r="AG20" s="7" t="n">
+      <c r="AG20" s="6" t="n">
         <v>58.85</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2033,7 +2000,7 @@
         <v>478.59</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2044,97 +2011,97 @@
       <c r="B21" s="6" t="n">
         <v>92.7</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="6" t="n">
         <v>67.28</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>68.28</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="6" t="n">
         <v>67.95999999999999</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>68.15000000000001</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>68.69</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="6" t="n">
         <v>66.29000000000001</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="6" t="n">
         <v>68.18000000000001</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>66.05</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="6" t="n">
         <v>66.42</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="6" t="n">
         <v>66.48</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="6" t="n">
         <v>61.24</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="N21" s="6" t="n">
         <v>63.96</v>
       </c>
-      <c r="O21" s="7" t="n">
+      <c r="O21" s="6" t="n">
         <v>67.36</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="P21" s="6" t="n">
         <v>65.54000000000001</v>
       </c>
-      <c r="Q21" s="7" t="n">
+      <c r="Q21" s="6" t="n">
         <v>63.69</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="R21" s="6" t="n">
         <v>63.98</v>
       </c>
-      <c r="S21" s="7" t="n">
+      <c r="S21" s="6" t="n">
         <v>63.7</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="T21" s="6" t="n">
         <v>62.42</v>
       </c>
-      <c r="U21" s="7" t="n">
+      <c r="U21" s="6" t="n">
         <v>63.45</v>
       </c>
-      <c r="V21" s="7" t="n">
+      <c r="V21" s="6" t="n">
         <v>63.76</v>
       </c>
-      <c r="W21" s="7" t="n">
+      <c r="W21" s="6" t="n">
         <v>63.32</v>
       </c>
-      <c r="X21" s="7" t="n">
+      <c r="X21" s="6" t="n">
         <v>64.31</v>
       </c>
-      <c r="Y21" s="7" t="n">
+      <c r="Y21" s="6" t="n">
         <v>64.64</v>
       </c>
-      <c r="Z21" s="7" t="n">
+      <c r="Z21" s="6" t="n">
         <v>62.4</v>
       </c>
-      <c r="AA21" s="7" t="n">
+      <c r="AA21" s="6" t="n">
         <v>62.14</v>
       </c>
-      <c r="AB21" s="9" t="n">
+      <c r="AB21" s="6" t="n">
         <v>48.92</v>
       </c>
-      <c r="AC21" s="10" t="n">
+      <c r="AC21" s="6" t="n">
         <v>42.56</v>
       </c>
-      <c r="AD21" s="7" t="n">
+      <c r="AD21" s="6" t="n">
         <v>54.18</v>
       </c>
-      <c r="AE21" s="7" t="n">
+      <c r="AE21" s="6" t="n">
         <v>64.91</v>
       </c>
-      <c r="AF21" s="7" t="n">
+      <c r="AF21" s="6" t="n">
         <v>65.55</v>
       </c>
-      <c r="AG21" s="7" t="n">
+      <c r="AG21" s="6" t="n">
         <v>66.41</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2144,7 +2111,7 @@
         <v>349.62</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2155,97 +2122,97 @@
       <c r="B22" s="6" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="6" t="n">
         <v>59.55</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="6" t="n">
         <v>67.94</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>61.62</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>62.62</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="6" t="n">
         <v>57.23</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="6" t="n">
         <v>56.89</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>57.64</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="6" t="n">
         <v>61.28</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="6" t="n">
         <v>62.13</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="6" t="n">
         <v>59.85</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="N22" s="6" t="n">
         <v>54.39</v>
       </c>
-      <c r="O22" s="7" t="n">
+      <c r="O22" s="6" t="n">
         <v>61.68</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="P22" s="6" t="n">
         <v>58.36</v>
       </c>
-      <c r="Q22" s="7" t="n">
+      <c r="Q22" s="6" t="n">
         <v>62.69</v>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="R22" s="6" t="n">
         <v>60.4</v>
       </c>
-      <c r="S22" s="7" t="n">
+      <c r="S22" s="6" t="n">
         <v>58.01</v>
       </c>
-      <c r="T22" s="7" t="n">
+      <c r="T22" s="6" t="n">
         <v>54.16</v>
       </c>
-      <c r="U22" s="7" t="n">
+      <c r="U22" s="6" t="n">
         <v>54.15</v>
       </c>
-      <c r="V22" s="7" t="n">
+      <c r="V22" s="6" t="n">
         <v>56.63</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="6" t="n">
         <v>53.21</v>
       </c>
-      <c r="X22" s="7" t="n">
+      <c r="X22" s="6" t="n">
         <v>57.21</v>
       </c>
-      <c r="Y22" s="7" t="n">
+      <c r="Y22" s="6" t="n">
         <v>55.49</v>
       </c>
-      <c r="Z22" s="7" t="n">
+      <c r="Z22" s="6" t="n">
         <v>56.56</v>
       </c>
-      <c r="AA22" s="7" t="n">
+      <c r="AA22" s="6" t="n">
         <v>57.02</v>
       </c>
-      <c r="AB22" s="7" t="n">
+      <c r="AB22" s="6" t="n">
         <v>56.89</v>
       </c>
-      <c r="AC22" s="9" t="n">
+      <c r="AC22" s="6" t="n">
         <v>51.04</v>
       </c>
-      <c r="AD22" s="9" t="n">
+      <c r="AD22" s="6" t="n">
         <v>45.58</v>
       </c>
-      <c r="AE22" s="9" t="n">
+      <c r="AE22" s="6" t="n">
         <v>45.66</v>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AF22" s="6" t="n">
         <v>48.05</v>
       </c>
-      <c r="AG22" s="9" t="n">
+      <c r="AG22" s="6" t="n">
         <v>47.09</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2255,7 +2222,7 @@
         <v>386.51</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2266,97 +2233,97 @@
       <c r="B23" s="6" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="6" t="n">
         <v>66.69</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="6" t="n">
         <v>63.84</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>66.8</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>66.92</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="6" t="n">
         <v>66.98999999999999</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="6" t="n">
         <v>66.62</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="6" t="n">
         <v>66.47</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="6" t="n">
         <v>65.03</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="6" t="n">
         <v>64.66</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="6" t="n">
         <v>63.94</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="6" t="n">
         <v>64.91</v>
       </c>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="6" t="n">
         <v>67.92</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="P23" s="6" t="n">
         <v>67.19</v>
       </c>
-      <c r="Q23" s="7" t="n">
+      <c r="Q23" s="6" t="n">
         <v>66.47</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="R23" s="6" t="n">
         <v>66.12</v>
       </c>
-      <c r="S23" s="7" t="n">
+      <c r="S23" s="6" t="n">
         <v>65.98</v>
       </c>
-      <c r="T23" s="7" t="n">
+      <c r="T23" s="6" t="n">
         <v>66.42</v>
       </c>
-      <c r="U23" s="7" t="n">
+      <c r="U23" s="6" t="n">
         <v>66.39</v>
       </c>
-      <c r="V23" s="7" t="n">
+      <c r="V23" s="6" t="n">
         <v>66.95</v>
       </c>
-      <c r="W23" s="7" t="n">
+      <c r="W23" s="6" t="n">
         <v>66.5</v>
       </c>
-      <c r="X23" s="7" t="n">
+      <c r="X23" s="6" t="n">
         <v>66.36</v>
       </c>
-      <c r="Y23" s="7" t="n">
+      <c r="Y23" s="6" t="n">
         <v>68.23999999999999</v>
       </c>
-      <c r="Z23" s="7" t="n">
+      <c r="Z23" s="6" t="n">
         <v>67.15000000000001</v>
       </c>
-      <c r="AA23" s="7" t="n">
+      <c r="AA23" s="6" t="n">
         <v>66.51000000000001</v>
       </c>
-      <c r="AB23" s="7" t="n">
+      <c r="AB23" s="6" t="n">
         <v>66.97</v>
       </c>
-      <c r="AC23" s="7" t="n">
+      <c r="AC23" s="6" t="n">
         <v>66.69</v>
       </c>
-      <c r="AD23" s="7" t="n">
+      <c r="AD23" s="6" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="AE23" s="7" t="n">
+      <c r="AE23" s="6" t="n">
         <v>68.13</v>
       </c>
-      <c r="AF23" s="7" t="n">
+      <c r="AF23" s="6" t="n">
         <v>67.72</v>
       </c>
-      <c r="AG23" s="7" t="n">
+      <c r="AG23" s="6" t="n">
         <v>66.70999999999999</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2366,7 +2333,7 @@
         <v>219.15</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2377,97 +2344,97 @@
       <c r="B24" s="6" t="n">
         <v>94.3</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>64.47</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>65.97</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="6" t="n">
         <v>61.84</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="6" t="n">
         <v>65.23999999999999</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="6" t="n">
         <v>64.51000000000001</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="6" t="n">
         <v>64.92</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="6" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>63.72</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="6" t="n">
         <v>64.91</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="6" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="6" t="n">
         <v>62.96</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N24" s="6" t="n">
         <v>65.09</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O24" s="6" t="n">
         <v>66.59</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="P24" s="6" t="n">
         <v>65.03</v>
       </c>
-      <c r="Q24" s="7" t="n">
+      <c r="Q24" s="6" t="n">
         <v>64.33</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="R24" s="6" t="n">
         <v>64.14</v>
       </c>
-      <c r="S24" s="7" t="n">
+      <c r="S24" s="6" t="n">
         <v>63.59</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="T24" s="6" t="n">
         <v>64.28</v>
       </c>
-      <c r="U24" s="7" t="n">
+      <c r="U24" s="6" t="n">
         <v>65.02</v>
       </c>
-      <c r="V24" s="7" t="n">
+      <c r="V24" s="6" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="W24" s="7" t="n">
+      <c r="W24" s="6" t="n">
         <v>64.38</v>
       </c>
-      <c r="X24" s="7" t="n">
+      <c r="X24" s="6" t="n">
         <v>64.44</v>
       </c>
-      <c r="Y24" s="7" t="n">
+      <c r="Y24" s="6" t="n">
         <v>66.12</v>
       </c>
-      <c r="Z24" s="7" t="n">
+      <c r="Z24" s="6" t="n">
         <v>63.82</v>
       </c>
-      <c r="AA24" s="7" t="n">
+      <c r="AA24" s="6" t="n">
         <v>65.09</v>
       </c>
-      <c r="AB24" s="7" t="n">
+      <c r="AB24" s="6" t="n">
         <v>65.8</v>
       </c>
-      <c r="AC24" s="7" t="n">
+      <c r="AC24" s="6" t="n">
         <v>64.81</v>
       </c>
-      <c r="AD24" s="7" t="n">
+      <c r="AD24" s="6" t="n">
         <v>65.23</v>
       </c>
-      <c r="AE24" s="7" t="n">
+      <c r="AE24" s="6" t="n">
         <v>66.12</v>
       </c>
-      <c r="AF24" s="7" t="n">
+      <c r="AF24" s="6" t="n">
         <v>66.22</v>
       </c>
-      <c r="AG24" s="7" t="n">
+      <c r="AG24" s="6" t="n">
         <v>64.79000000000001</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2477,7 +2444,7 @@
         <v>226.77</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2488,97 +2455,97 @@
       <c r="B25" s="6" t="n">
         <v>94.7</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="6" t="n">
         <v>68.70999999999999</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="6" t="n">
         <v>69.70999999999999</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="6" t="n">
         <v>64.47</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="6" t="n">
         <v>68.54000000000001</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="6" t="n">
         <v>69.23999999999999</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="H25" s="6" t="n">
         <v>68.8</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="6" t="n">
         <v>68.68000000000001</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="6" t="n">
         <v>68.55</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="K25" s="6" t="n">
         <v>68.83</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="6" t="n">
         <v>68.84</v>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="6" t="n">
         <v>67.37</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="N25" s="6" t="n">
         <v>68.23999999999999</v>
       </c>
-      <c r="O25" s="7" t="n">
+      <c r="O25" s="6" t="n">
         <v>70.36</v>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="P25" s="6" t="n">
         <v>68.37</v>
       </c>
-      <c r="Q25" s="7" t="n">
+      <c r="Q25" s="6" t="n">
         <v>67.92</v>
       </c>
-      <c r="R25" s="7" t="n">
+      <c r="R25" s="6" t="n">
         <v>67.75</v>
       </c>
-      <c r="S25" s="7" t="n">
+      <c r="S25" s="6" t="n">
         <v>68.11</v>
       </c>
-      <c r="T25" s="7" t="n">
+      <c r="T25" s="6" t="n">
         <v>67.22</v>
       </c>
-      <c r="U25" s="7" t="n">
+      <c r="U25" s="6" t="n">
         <v>67.28</v>
       </c>
-      <c r="V25" s="7" t="n">
+      <c r="V25" s="6" t="n">
         <v>67.53</v>
       </c>
-      <c r="W25" s="7" t="n">
+      <c r="W25" s="6" t="n">
         <v>68.94</v>
       </c>
-      <c r="X25" s="7" t="n">
+      <c r="X25" s="6" t="n">
         <v>69.02</v>
       </c>
-      <c r="Y25" s="7" t="n">
+      <c r="Y25" s="6" t="n">
         <v>69.25</v>
       </c>
-      <c r="Z25" s="7" t="n">
+      <c r="Z25" s="6" t="n">
         <v>68.22</v>
       </c>
-      <c r="AA25" s="7" t="n">
+      <c r="AA25" s="6" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="AB25" s="7" t="n">
+      <c r="AB25" s="6" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="AC25" s="7" t="n">
+      <c r="AC25" s="6" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="AD25" s="7" t="n">
+      <c r="AD25" s="6" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="AE25" s="7" t="n">
+      <c r="AE25" s="6" t="n">
         <v>68.78</v>
       </c>
-      <c r="AF25" s="7" t="n">
+      <c r="AF25" s="6" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="AG25" s="7" t="n">
+      <c r="AG25" s="6" t="n">
         <v>69.81</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2588,7 +2555,7 @@
         <v>123.83</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2599,97 +2566,97 @@
       <c r="B26" s="6" t="n">
         <v>95.5</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="6" t="n">
         <v>72.45999999999999</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>72.84</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="6" t="n">
         <v>68.31999999999999</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>72.84999999999999</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>72.31999999999999</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="6" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="6" t="n">
         <v>75.09</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="6" t="n">
         <v>73.41</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="6" t="n">
         <v>72.36</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="L26" s="6" t="n">
         <v>71.86</v>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="6" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="N26" s="6" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="O26" s="7" t="n">
+      <c r="O26" s="6" t="n">
         <v>74.67</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="P26" s="6" t="n">
         <v>74.05</v>
       </c>
-      <c r="Q26" s="7" t="n">
+      <c r="Q26" s="6" t="n">
         <v>73.43000000000001</v>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="R26" s="6" t="n">
         <v>72.98999999999999</v>
       </c>
-      <c r="S26" s="7" t="n">
+      <c r="S26" s="6" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="T26" s="7" t="n">
+      <c r="T26" s="6" t="n">
         <v>72.95</v>
       </c>
-      <c r="U26" s="7" t="n">
+      <c r="U26" s="6" t="n">
         <v>73.26000000000001</v>
       </c>
-      <c r="V26" s="7" t="n">
+      <c r="V26" s="6" t="n">
         <v>73.56999999999999</v>
       </c>
-      <c r="W26" s="7" t="n">
+      <c r="W26" s="6" t="n">
         <v>73.54000000000001</v>
       </c>
-      <c r="X26" s="7" t="n">
+      <c r="X26" s="6" t="n">
         <v>73.29000000000001</v>
       </c>
-      <c r="Y26" s="7" t="n">
+      <c r="Y26" s="6" t="n">
         <v>73.64</v>
       </c>
-      <c r="Z26" s="7" t="n">
+      <c r="Z26" s="6" t="n">
         <v>73.19</v>
       </c>
-      <c r="AA26" s="7" t="n">
+      <c r="AA26" s="6" t="n">
         <v>73.95999999999999</v>
       </c>
-      <c r="AB26" s="7" t="n">
+      <c r="AB26" s="6" t="n">
         <v>72.31</v>
       </c>
-      <c r="AC26" s="7" t="n">
+      <c r="AC26" s="6" t="n">
         <v>74.83</v>
       </c>
-      <c r="AD26" s="7" t="n">
+      <c r="AD26" s="6" t="n">
         <v>75.70999999999999</v>
       </c>
-      <c r="AE26" s="7" t="n">
+      <c r="AE26" s="6" t="n">
         <v>75.36</v>
       </c>
-      <c r="AF26" s="7" t="n">
+      <c r="AF26" s="6" t="n">
         <v>74.62</v>
       </c>
-      <c r="AG26" s="7" t="n">
+      <c r="AG26" s="6" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2699,7 +2666,7 @@
         <v>223.97</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2710,97 +2677,97 @@
       <c r="B27" s="6" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="6" t="n">
         <v>59.7</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>60.51</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="6" t="n">
         <v>52.24</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>59.5</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="6" t="n">
         <v>58.86</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="6" t="n">
         <v>59.35</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="6" t="n">
         <v>60.09</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="J27" s="6" t="n">
         <v>59.86</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="6" t="n">
         <v>59.06</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="6" t="n">
         <v>58.9</v>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="6" t="n">
         <v>58.88</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="N27" s="6" t="n">
         <v>59.69</v>
       </c>
-      <c r="O27" s="7" t="n">
+      <c r="O27" s="6" t="n">
         <v>61.22</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="P27" s="6" t="n">
         <v>60.84</v>
       </c>
-      <c r="Q27" s="7" t="n">
+      <c r="Q27" s="6" t="n">
         <v>60.99</v>
       </c>
-      <c r="R27" s="7" t="n">
+      <c r="R27" s="6" t="n">
         <v>60.34</v>
       </c>
-      <c r="S27" s="7" t="n">
+      <c r="S27" s="6" t="n">
         <v>60.13</v>
       </c>
-      <c r="T27" s="7" t="n">
+      <c r="T27" s="6" t="n">
         <v>60.43</v>
       </c>
-      <c r="U27" s="7" t="n">
+      <c r="U27" s="6" t="n">
         <v>60.52</v>
       </c>
-      <c r="V27" s="7" t="n">
+      <c r="V27" s="6" t="n">
         <v>60.23</v>
       </c>
-      <c r="W27" s="7" t="n">
+      <c r="W27" s="6" t="n">
         <v>60.95</v>
       </c>
-      <c r="X27" s="7" t="n">
+      <c r="X27" s="6" t="n">
         <v>60.09</v>
       </c>
-      <c r="Y27" s="7" t="n">
+      <c r="Y27" s="6" t="n">
         <v>60.41</v>
       </c>
-      <c r="Z27" s="7" t="n">
+      <c r="Z27" s="6" t="n">
         <v>59.08</v>
       </c>
-      <c r="AA27" s="7" t="n">
+      <c r="AA27" s="6" t="n">
         <v>59.89</v>
       </c>
-      <c r="AB27" s="7" t="n">
+      <c r="AB27" s="6" t="n">
         <v>60.36</v>
       </c>
-      <c r="AC27" s="7" t="n">
+      <c r="AC27" s="6" t="n">
         <v>60.82</v>
       </c>
-      <c r="AD27" s="7" t="n">
+      <c r="AD27" s="6" t="n">
         <v>60.08</v>
       </c>
-      <c r="AE27" s="7" t="n">
+      <c r="AE27" s="6" t="n">
         <v>60.62</v>
       </c>
-      <c r="AF27" s="7" t="n">
+      <c r="AF27" s="6" t="n">
         <v>61.02</v>
       </c>
-      <c r="AG27" s="7" t="n">
+      <c r="AG27" s="6" t="n">
         <v>60.81</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2810,7 +2777,7 @@
         <v>431.6</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2821,97 +2788,97 @@
       <c r="B28" s="6" t="n">
         <v>96.3</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="6" t="n">
         <v>60.55</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="6" t="n">
         <v>62.42</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="6" t="n">
         <v>64.69</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="6" t="n">
         <v>62.36</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>62.31</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="6" t="n">
         <v>61.61</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="6" t="n">
         <v>62.62</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="J28" s="6" t="n">
         <v>62.35</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="K28" s="6" t="n">
         <v>62.64</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="L28" s="6" t="n">
         <v>64.14</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="6" t="n">
         <v>61.74</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="N28" s="6" t="n">
         <v>62.46</v>
       </c>
-      <c r="O28" s="7" t="n">
+      <c r="O28" s="6" t="n">
         <v>65.94</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="P28" s="6" t="n">
         <v>65.22</v>
       </c>
-      <c r="Q28" s="7" t="n">
+      <c r="Q28" s="6" t="n">
         <v>65.05</v>
       </c>
-      <c r="R28" s="7" t="n">
+      <c r="R28" s="6" t="n">
         <v>60.73</v>
       </c>
-      <c r="S28" s="7" t="n">
+      <c r="S28" s="6" t="n">
         <v>61.3</v>
       </c>
-      <c r="T28" s="7" t="n">
+      <c r="T28" s="6" t="n">
         <v>60.76</v>
       </c>
-      <c r="U28" s="7" t="n">
+      <c r="U28" s="6" t="n">
         <v>60.58</v>
       </c>
-      <c r="V28" s="7" t="n">
+      <c r="V28" s="6" t="n">
         <v>62.09</v>
       </c>
-      <c r="W28" s="7" t="n">
+      <c r="W28" s="6" t="n">
         <v>61.12</v>
       </c>
-      <c r="X28" s="7" t="n">
+      <c r="X28" s="6" t="n">
         <v>62.12</v>
       </c>
-      <c r="Y28" s="7" t="n">
+      <c r="Y28" s="6" t="n">
         <v>63.75</v>
       </c>
-      <c r="Z28" s="7" t="n">
+      <c r="Z28" s="6" t="n">
         <v>62.11</v>
       </c>
-      <c r="AA28" s="7" t="n">
+      <c r="AA28" s="6" t="n">
         <v>61.92</v>
       </c>
-      <c r="AB28" s="7" t="n">
+      <c r="AB28" s="6" t="n">
         <v>61.89</v>
       </c>
-      <c r="AC28" s="7" t="n">
+      <c r="AC28" s="6" t="n">
         <v>61.14</v>
       </c>
-      <c r="AD28" s="7" t="n">
+      <c r="AD28" s="6" t="n">
         <v>62.76</v>
       </c>
-      <c r="AE28" s="7" t="n">
+      <c r="AE28" s="6" t="n">
         <v>62.2</v>
       </c>
-      <c r="AF28" s="7" t="n">
+      <c r="AF28" s="6" t="n">
         <v>63.74</v>
       </c>
-      <c r="AG28" s="7" t="n">
+      <c r="AG28" s="6" t="n">
         <v>63.46</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -2921,7 +2888,7 @@
         <v>478.51</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2932,97 +2899,97 @@
       <c r="B29" s="6" t="n">
         <v>96.7</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="6" t="n">
         <v>70.28</v>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="6" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="6" t="n">
         <v>62.02</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>70.8</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="6" t="n">
         <v>70.56</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="6" t="n">
         <v>70.36</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="6" t="n">
         <v>70.59</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="J29" s="6" t="n">
         <v>69.28</v>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="K29" s="6" t="n">
         <v>70.34999999999999</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" s="6" t="n">
         <v>70.55</v>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="6" t="n">
         <v>70.64</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="N29" s="6" t="n">
         <v>70.33</v>
       </c>
-      <c r="O29" s="7" t="n">
+      <c r="O29" s="6" t="n">
         <v>69.48</v>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="P29" s="6" t="n">
         <v>69.92</v>
       </c>
-      <c r="Q29" s="7" t="n">
+      <c r="Q29" s="6" t="n">
         <v>69.95</v>
       </c>
-      <c r="R29" s="7" t="n">
+      <c r="R29" s="6" t="n">
         <v>70.45</v>
       </c>
-      <c r="S29" s="7" t="n">
+      <c r="S29" s="6" t="n">
         <v>70.41</v>
       </c>
-      <c r="T29" s="7" t="n">
+      <c r="T29" s="6" t="n">
         <v>70.81999999999999</v>
       </c>
-      <c r="U29" s="7" t="n">
+      <c r="U29" s="6" t="n">
         <v>71.41</v>
       </c>
-      <c r="V29" s="7" t="n">
+      <c r="V29" s="6" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="W29" s="7" t="n">
+      <c r="W29" s="6" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="X29" s="7" t="n">
+      <c r="X29" s="6" t="n">
         <v>70.38</v>
       </c>
-      <c r="Y29" s="7" t="n">
+      <c r="Y29" s="6" t="n">
         <v>70.62</v>
       </c>
-      <c r="Z29" s="7" t="n">
+      <c r="Z29" s="6" t="n">
         <v>70.51000000000001</v>
       </c>
-      <c r="AA29" s="7" t="n">
+      <c r="AA29" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="AB29" s="7" t="n">
+      <c r="AB29" s="6" t="n">
         <v>71.16</v>
       </c>
-      <c r="AC29" s="7" t="n">
+      <c r="AC29" s="6" t="n">
         <v>70.77</v>
       </c>
-      <c r="AD29" s="7" t="n">
+      <c r="AD29" s="6" t="n">
         <v>71.01000000000001</v>
       </c>
-      <c r="AE29" s="7" t="n">
+      <c r="AE29" s="6" t="n">
         <v>71.12</v>
       </c>
-      <c r="AF29" s="7" t="n">
+      <c r="AF29" s="6" t="n">
         <v>71.72</v>
       </c>
-      <c r="AG29" s="7" t="n">
+      <c r="AG29" s="6" t="n">
         <v>70.56</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -3032,7 +2999,7 @@
         <v>258.64</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3043,97 +3010,97 @@
       <c r="B30" s="6" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="6" t="n">
         <v>69.62</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>69.25</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="6" t="n">
         <v>61.6</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>70.01000000000001</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="6" t="n">
         <v>69.61</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="6" t="n">
         <v>68.84999999999999</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="6" t="n">
         <v>69.55</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J30" s="6" t="n">
         <v>58.66</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="K30" s="6" t="n">
         <v>68.88</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L30" s="6" t="n">
         <v>69.31</v>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="6" t="n">
         <v>69.06999999999999</v>
       </c>
-      <c r="N30" s="7" t="n">
+      <c r="N30" s="6" t="n">
         <v>69.09</v>
       </c>
-      <c r="O30" s="7" t="n">
+      <c r="O30" s="6" t="n">
         <v>67.34</v>
       </c>
-      <c r="P30" s="7" t="n">
+      <c r="P30" s="6" t="n">
         <v>67.97</v>
       </c>
-      <c r="Q30" s="7" t="n">
+      <c r="Q30" s="6" t="n">
         <v>67.03</v>
       </c>
-      <c r="R30" s="7" t="n">
+      <c r="R30" s="6" t="n">
         <v>68.8</v>
       </c>
-      <c r="S30" s="7" t="n">
+      <c r="S30" s="6" t="n">
         <v>68.91</v>
       </c>
-      <c r="T30" s="7" t="n">
+      <c r="T30" s="6" t="n">
         <v>69.18000000000001</v>
       </c>
-      <c r="U30" s="7" t="n">
+      <c r="U30" s="6" t="n">
         <v>69.41</v>
       </c>
-      <c r="V30" s="7" t="n">
+      <c r="V30" s="6" t="n">
         <v>68.5</v>
       </c>
-      <c r="W30" s="7" t="n">
+      <c r="W30" s="6" t="n">
         <v>68.97</v>
       </c>
-      <c r="X30" s="7" t="n">
+      <c r="X30" s="6" t="n">
         <v>69.33</v>
       </c>
-      <c r="Y30" s="7" t="n">
+      <c r="Y30" s="6" t="n">
         <v>68.73</v>
       </c>
-      <c r="Z30" s="7" t="n">
+      <c r="Z30" s="6" t="n">
         <v>69.65000000000001</v>
       </c>
-      <c r="AA30" s="7" t="n">
+      <c r="AA30" s="6" t="n">
         <v>68.75</v>
       </c>
-      <c r="AB30" s="7" t="n">
+      <c r="AB30" s="6" t="n">
         <v>69.12</v>
       </c>
-      <c r="AC30" s="7" t="n">
+      <c r="AC30" s="6" t="n">
         <v>69.88</v>
       </c>
-      <c r="AD30" s="7" t="n">
+      <c r="AD30" s="6" t="n">
         <v>70.22</v>
       </c>
-      <c r="AE30" s="7" t="n">
+      <c r="AE30" s="6" t="n">
         <v>70.36</v>
       </c>
-      <c r="AF30" s="7" t="n">
+      <c r="AF30" s="6" t="n">
         <v>71.01000000000001</v>
       </c>
-      <c r="AG30" s="7" t="n">
+      <c r="AG30" s="6" t="n">
         <v>69.2</v>
       </c>
       <c r="AH30" s="6" t="n">
@@ -3143,7 +3110,7 @@
         <v>254.74</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3154,97 +3121,97 @@
       <c r="B31" s="6" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="6" t="n">
         <v>49.18</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="6" t="n">
         <v>38.17</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="6" t="n">
         <v>39.78</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="6" t="n">
         <v>48.22</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="6" t="n">
         <v>45.28</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="6" t="n">
         <v>47.22</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="6" t="n">
         <v>47.81</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="6" t="n">
         <v>46.02</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="6" t="n">
         <v>47.37</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="6" t="n">
         <v>45.26</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="6" t="n">
         <v>49.09</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="6" t="n">
         <v>47.71</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="P31" s="6" t="n">
         <v>53.23</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="6" t="n">
         <v>43.31</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="6" t="n">
         <v>42.73</v>
       </c>
-      <c r="S31" s="10" t="n">
+      <c r="S31" s="6" t="n">
         <v>36.38</v>
       </c>
-      <c r="T31" s="10" t="n">
+      <c r="T31" s="6" t="n">
         <v>42.77</v>
       </c>
-      <c r="U31" s="10" t="n">
+      <c r="U31" s="6" t="n">
         <v>40.38</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="6" t="n">
         <v>44.49</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="6" t="n">
         <v>45.69</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X31" s="6" t="n">
         <v>45.4</v>
       </c>
-      <c r="Y31" s="10" t="n">
+      <c r="Y31" s="6" t="n">
         <v>40.74</v>
       </c>
-      <c r="Z31" s="10" t="n">
+      <c r="Z31" s="6" t="n">
         <v>41.24</v>
       </c>
-      <c r="AA31" s="10" t="n">
+      <c r="AA31" s="6" t="n">
         <v>41.48</v>
       </c>
-      <c r="AB31" s="10" t="n">
+      <c r="AB31" s="6" t="n">
         <v>42.87</v>
       </c>
-      <c r="AC31" s="9" t="n">
+      <c r="AC31" s="6" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="10" t="n">
+      <c r="AD31" s="6" t="n">
         <v>40.41</v>
       </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AE31" s="6" t="n">
         <v>47.34</v>
       </c>
-      <c r="AF31" s="9" t="n">
+      <c r="AF31" s="6" t="n">
         <v>51.7</v>
       </c>
-      <c r="AG31" s="9" t="n">
+      <c r="AG31" s="6" t="n">
         <v>45.77</v>
       </c>
       <c r="AH31" s="6" t="n">
@@ -3254,7 +3221,7 @@
         <v>485.2</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3265,97 +3232,97 @@
       <c r="B32" s="6" t="n">
         <v>98.7</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="6" t="n">
         <v>56.19</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>55.07</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="6" t="n">
         <v>52.52</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="6" t="n">
         <v>56.21</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="6" t="n">
         <v>55.69</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="6" t="n">
         <v>54.63</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="J32" s="6" t="n">
         <v>54.37</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K32" s="6" t="n">
         <v>55.76</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="L32" s="6" t="n">
         <v>55.24</v>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="6" t="n">
         <v>56.34</v>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="N32" s="6" t="n">
         <v>56.26</v>
       </c>
-      <c r="O32" s="7" t="n">
+      <c r="O32" s="6" t="n">
         <v>54.48</v>
       </c>
-      <c r="P32" s="7" t="n">
+      <c r="P32" s="6" t="n">
         <v>54.57</v>
       </c>
-      <c r="Q32" s="7" t="n">
+      <c r="Q32" s="6" t="n">
         <v>54.34</v>
       </c>
-      <c r="R32" s="7" t="n">
+      <c r="R32" s="6" t="n">
         <v>55.11</v>
       </c>
-      <c r="S32" s="7" t="n">
+      <c r="S32" s="6" t="n">
         <v>54.74</v>
       </c>
-      <c r="T32" s="7" t="n">
+      <c r="T32" s="6" t="n">
         <v>55.15</v>
       </c>
-      <c r="U32" s="7" t="n">
+      <c r="U32" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="V32" s="7" t="n">
+      <c r="V32" s="6" t="n">
         <v>56.91</v>
       </c>
-      <c r="W32" s="7" t="n">
+      <c r="W32" s="6" t="n">
         <v>57.04</v>
       </c>
-      <c r="X32" s="7" t="n">
+      <c r="X32" s="6" t="n">
         <v>56.21</v>
       </c>
-      <c r="Y32" s="7" t="n">
+      <c r="Y32" s="6" t="n">
         <v>55.12</v>
       </c>
-      <c r="Z32" s="7" t="n">
+      <c r="Z32" s="6" t="n">
         <v>56.95</v>
       </c>
-      <c r="AA32" s="7" t="n">
+      <c r="AA32" s="6" t="n">
         <v>55.64</v>
       </c>
-      <c r="AB32" s="7" t="n">
+      <c r="AB32" s="6" t="n">
         <v>56.39</v>
       </c>
-      <c r="AC32" s="7" t="n">
+      <c r="AC32" s="6" t="n">
         <v>57.72</v>
       </c>
-      <c r="AD32" s="7" t="n">
+      <c r="AD32" s="6" t="n">
         <v>55.58</v>
       </c>
-      <c r="AE32" s="7" t="n">
+      <c r="AE32" s="6" t="n">
         <v>57.07</v>
       </c>
-      <c r="AF32" s="7" t="n">
+      <c r="AF32" s="6" t="n">
         <v>57.31</v>
       </c>
-      <c r="AG32" s="7" t="n">
+      <c r="AG32" s="6" t="n">
         <v>55.64</v>
       </c>
       <c r="AH32" s="6" t="n">
@@ -3365,7 +3332,7 @@
         <v>474.57</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3376,97 +3343,97 @@
       <c r="B33" s="6" t="n">
         <v>99.5</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="6" t="n">
         <v>76.2</v>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="6" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="6" t="n">
         <v>75.94</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="6" t="n">
         <v>75.91</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="6" t="n">
         <v>77.06</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="6" t="n">
         <v>76.61</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="6" t="n">
         <v>76.84999999999999</v>
       </c>
-      <c r="J33" s="7" t="n">
+      <c r="J33" s="6" t="n">
         <v>76.97</v>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" s="6" t="n">
         <v>77.41</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L33" s="6" t="n">
         <v>76.81</v>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="6" t="n">
         <v>76.91</v>
       </c>
-      <c r="N33" s="7" t="n">
+      <c r="N33" s="6" t="n">
         <v>77.29000000000001</v>
       </c>
-      <c r="O33" s="7" t="n">
+      <c r="O33" s="6" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="P33" s="6" t="n">
         <v>76.81999999999999</v>
       </c>
-      <c r="Q33" s="7" t="n">
+      <c r="Q33" s="6" t="n">
         <v>76.93000000000001</v>
       </c>
-      <c r="R33" s="7" t="n">
+      <c r="R33" s="6" t="n">
         <v>76.72</v>
       </c>
-      <c r="S33" s="7" t="n">
+      <c r="S33" s="6" t="n">
         <v>77.2</v>
       </c>
-      <c r="T33" s="7" t="n">
+      <c r="T33" s="6" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="U33" s="7" t="n">
+      <c r="U33" s="6" t="n">
         <v>77.56999999999999</v>
       </c>
-      <c r="V33" s="7" t="n">
+      <c r="V33" s="6" t="n">
         <v>77.09</v>
       </c>
-      <c r="W33" s="7" t="n">
+      <c r="W33" s="6" t="n">
         <v>76.53</v>
       </c>
-      <c r="X33" s="7" t="n">
+      <c r="X33" s="6" t="n">
         <v>77.14</v>
       </c>
-      <c r="Y33" s="7" t="n">
+      <c r="Y33" s="6" t="n">
         <v>77.29000000000001</v>
       </c>
-      <c r="Z33" s="7" t="n">
+      <c r="Z33" s="6" t="n">
         <v>76.73999999999999</v>
       </c>
-      <c r="AA33" s="7" t="n">
+      <c r="AA33" s="6" t="n">
         <v>76.45</v>
       </c>
-      <c r="AB33" s="7" t="n">
+      <c r="AB33" s="6" t="n">
         <v>77.54000000000001</v>
       </c>
-      <c r="AC33" s="7" t="n">
+      <c r="AC33" s="6" t="n">
         <v>77.26000000000001</v>
       </c>
-      <c r="AD33" s="7" t="n">
+      <c r="AD33" s="6" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="AE33" s="7" t="n">
+      <c r="AE33" s="6" t="n">
         <v>77.01000000000001</v>
       </c>
-      <c r="AF33" s="7" t="n">
+      <c r="AF33" s="6" t="n">
         <v>77.08</v>
       </c>
-      <c r="AG33" s="7" t="n">
+      <c r="AG33" s="6" t="n">
         <v>76.45999999999999</v>
       </c>
       <c r="AH33" s="6" t="n">
@@ -3476,7 +3443,7 @@
         <v>326</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="8" t="inlineStr"/>
+      <c r="AK33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3487,97 +3454,97 @@
       <c r="B34" s="6" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="6" t="n">
         <v>62.49</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="6" t="n">
         <v>65.53</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="6" t="n">
         <v>56.56</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="6" t="n">
         <v>65.81999999999999</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="6" t="n">
         <v>66.03</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="6" t="n">
         <v>65.11</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="6" t="n">
         <v>65.84999999999999</v>
       </c>
-      <c r="J34" s="7" t="n">
+      <c r="J34" s="6" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="K34" s="7" t="n">
+      <c r="K34" s="6" t="n">
         <v>66.03</v>
       </c>
-      <c r="L34" s="7" t="n">
+      <c r="L34" s="6" t="n">
         <v>66.95999999999999</v>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="6" t="n">
         <v>65.37</v>
       </c>
-      <c r="N34" s="7" t="n">
+      <c r="N34" s="6" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="O34" s="7" t="n">
+      <c r="O34" s="6" t="n">
         <v>66.78</v>
       </c>
-      <c r="P34" s="7" t="n">
+      <c r="P34" s="6" t="n">
         <v>66.86</v>
       </c>
-      <c r="Q34" s="7" t="n">
+      <c r="Q34" s="6" t="n">
         <v>65.68000000000001</v>
       </c>
-      <c r="R34" s="7" t="n">
+      <c r="R34" s="6" t="n">
         <v>66.78</v>
       </c>
-      <c r="S34" s="7" t="n">
+      <c r="S34" s="6" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="T34" s="7" t="n">
+      <c r="T34" s="6" t="n">
         <v>65.76000000000001</v>
       </c>
-      <c r="U34" s="7" t="n">
+      <c r="U34" s="6" t="n">
         <v>66.04000000000001</v>
       </c>
-      <c r="V34" s="7" t="n">
+      <c r="V34" s="6" t="n">
         <v>66.42</v>
       </c>
-      <c r="W34" s="7" t="n">
+      <c r="W34" s="6" t="n">
         <v>67.48</v>
       </c>
-      <c r="X34" s="7" t="n">
+      <c r="X34" s="6" t="n">
         <v>68.12</v>
       </c>
-      <c r="Y34" s="7" t="n">
+      <c r="Y34" s="6" t="n">
         <v>68.37</v>
       </c>
-      <c r="Z34" s="7" t="n">
+      <c r="Z34" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="AA34" s="7" t="n">
+      <c r="AA34" s="6" t="n">
         <v>66.53</v>
       </c>
-      <c r="AB34" s="7" t="n">
+      <c r="AB34" s="6" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="AC34" s="7" t="n">
+      <c r="AC34" s="6" t="n">
         <v>67.56999999999999</v>
       </c>
-      <c r="AD34" s="7" t="n">
+      <c r="AD34" s="6" t="n">
         <v>67.37</v>
       </c>
-      <c r="AE34" s="7" t="n">
+      <c r="AE34" s="6" t="n">
         <v>66.8</v>
       </c>
-      <c r="AF34" s="7" t="n">
+      <c r="AF34" s="6" t="n">
         <v>64.17</v>
       </c>
-      <c r="AG34" s="7" t="n">
+      <c r="AG34" s="6" t="n">
         <v>67.31999999999999</v>
       </c>
       <c r="AH34" s="6" t="n">
@@ -3587,7 +3554,7 @@
         <v>478.65</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="8" t="inlineStr"/>
+      <c r="AK34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3598,97 +3565,97 @@
       <c r="B35" s="6" t="n">
         <v>100.3</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="6" t="n">
         <v>61.94</v>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="D35" s="6" t="n">
         <v>61.37</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="6" t="n">
         <v>64.2</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="6" t="n">
         <v>61.69</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="6" t="n">
         <v>61.82</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="6" t="n">
         <v>62.42</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="6" t="n">
         <v>59.68</v>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J35" s="6" t="n">
         <v>60.43</v>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="K35" s="6" t="n">
         <v>58.74</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="L35" s="6" t="n">
         <v>60.15</v>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="N35" s="7" t="n">
+      <c r="N35" s="6" t="n">
         <v>59.7</v>
       </c>
-      <c r="O35" s="7" t="n">
+      <c r="O35" s="6" t="n">
         <v>61.84</v>
       </c>
-      <c r="P35" s="7" t="n">
+      <c r="P35" s="6" t="n">
         <v>61.41</v>
       </c>
-      <c r="Q35" s="7" t="n">
+      <c r="Q35" s="6" t="n">
         <v>59.86</v>
       </c>
-      <c r="R35" s="7" t="n">
+      <c r="R35" s="6" t="n">
         <v>59.32</v>
       </c>
-      <c r="S35" s="7" t="n">
+      <c r="S35" s="6" t="n">
         <v>60.75</v>
       </c>
-      <c r="T35" s="7" t="n">
+      <c r="T35" s="6" t="n">
         <v>58.68</v>
       </c>
-      <c r="U35" s="7" t="n">
+      <c r="U35" s="6" t="n">
         <v>57.96</v>
       </c>
-      <c r="V35" s="7" t="n">
+      <c r="V35" s="6" t="n">
         <v>59.95</v>
       </c>
-      <c r="W35" s="7" t="n">
+      <c r="W35" s="6" t="n">
         <v>58.4</v>
       </c>
-      <c r="X35" s="7" t="n">
+      <c r="X35" s="6" t="n">
         <v>59.2</v>
       </c>
-      <c r="Y35" s="7" t="n">
+      <c r="Y35" s="6" t="n">
         <v>59.93</v>
       </c>
-      <c r="Z35" s="7" t="n">
+      <c r="Z35" s="6" t="n">
         <v>57.76</v>
       </c>
-      <c r="AA35" s="7" t="n">
+      <c r="AA35" s="6" t="n">
         <v>59.89</v>
       </c>
-      <c r="AB35" s="7" t="n">
+      <c r="AB35" s="6" t="n">
         <v>61.02</v>
       </c>
-      <c r="AC35" s="7" t="n">
+      <c r="AC35" s="6" t="n">
         <v>60.55</v>
       </c>
-      <c r="AD35" s="7" t="n">
+      <c r="AD35" s="6" t="n">
         <v>61.73</v>
       </c>
-      <c r="AE35" s="7" t="n">
+      <c r="AE35" s="6" t="n">
         <v>60.34</v>
       </c>
-      <c r="AF35" s="7" t="n">
+      <c r="AF35" s="6" t="n">
         <v>59.4</v>
       </c>
-      <c r="AG35" s="7" t="n">
+      <c r="AG35" s="6" t="n">
         <v>61.26</v>
       </c>
       <c r="AH35" s="6" t="n">
@@ -3698,7 +3665,7 @@
         <v>497.28</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="8" t="inlineStr"/>
+      <c r="AK35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3709,97 +3676,97 @@
       <c r="B36" s="6" t="n">
         <v>100.7</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="6" t="n">
         <v>65.72</v>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="6" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="6" t="n">
         <v>62.38</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="6" t="n">
         <v>66.23999999999999</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="6" t="n">
         <v>66.14</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="6" t="n">
         <v>66.20999999999999</v>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="I36" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="J36" s="7" t="n">
+      <c r="J36" s="6" t="n">
         <v>65.55</v>
       </c>
-      <c r="K36" s="7" t="n">
+      <c r="K36" s="6" t="n">
         <v>66.36</v>
       </c>
-      <c r="L36" s="7" t="n">
+      <c r="L36" s="6" t="n">
         <v>65.69</v>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="6" t="n">
         <v>65.42</v>
       </c>
-      <c r="N36" s="7" t="n">
+      <c r="N36" s="6" t="n">
         <v>64.47</v>
       </c>
-      <c r="O36" s="7" t="n">
+      <c r="O36" s="6" t="n">
         <v>66.12</v>
       </c>
-      <c r="P36" s="7" t="n">
+      <c r="P36" s="6" t="n">
         <v>66.12</v>
       </c>
-      <c r="Q36" s="7" t="n">
+      <c r="Q36" s="6" t="n">
         <v>66.02</v>
       </c>
-      <c r="R36" s="7" t="n">
+      <c r="R36" s="6" t="n">
         <v>65.45</v>
       </c>
-      <c r="S36" s="7" t="n">
+      <c r="S36" s="6" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="T36" s="7" t="n">
+      <c r="T36" s="6" t="n">
         <v>65.39</v>
       </c>
-      <c r="U36" s="7" t="n">
+      <c r="U36" s="6" t="n">
         <v>64.59</v>
       </c>
-      <c r="V36" s="7" t="n">
+      <c r="V36" s="6" t="n">
         <v>65.04000000000001</v>
       </c>
-      <c r="W36" s="7" t="n">
+      <c r="W36" s="6" t="n">
         <v>64.38</v>
       </c>
-      <c r="X36" s="7" t="n">
+      <c r="X36" s="6" t="n">
         <v>64.47</v>
       </c>
-      <c r="Y36" s="7" t="n">
+      <c r="Y36" s="6" t="n">
         <v>65.12</v>
       </c>
-      <c r="Z36" s="7" t="n">
+      <c r="Z36" s="6" t="n">
         <v>63.69</v>
       </c>
-      <c r="AA36" s="7" t="n">
+      <c r="AA36" s="6" t="n">
         <v>64.76000000000001</v>
       </c>
-      <c r="AB36" s="7" t="n">
+      <c r="AB36" s="6" t="n">
         <v>64.67</v>
       </c>
-      <c r="AC36" s="7" t="n">
+      <c r="AC36" s="6" t="n">
         <v>64.2</v>
       </c>
-      <c r="AD36" s="7" t="n">
+      <c r="AD36" s="6" t="n">
         <v>64.52</v>
       </c>
-      <c r="AE36" s="7" t="n">
+      <c r="AE36" s="6" t="n">
         <v>65.34999999999999</v>
       </c>
-      <c r="AF36" s="7" t="n">
+      <c r="AF36" s="6" t="n">
         <v>65.12</v>
       </c>
-      <c r="AG36" s="7" t="n">
+      <c r="AG36" s="6" t="n">
         <v>65.62</v>
       </c>
       <c r="AH36" s="6" t="n">
@@ -3809,7 +3776,7 @@
         <v>431.37</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="8" t="inlineStr"/>
+      <c r="AK36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3820,97 +3787,97 @@
       <c r="B37" s="6" t="n">
         <v>101.1</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="6" t="n">
         <v>41.52</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="6" t="n">
         <v>37.06</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="6" t="n">
         <v>39.89</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="6" t="n">
         <v>41.01</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="6" t="n">
         <v>40.08</v>
       </c>
-      <c r="H37" s="10" t="n">
+      <c r="H37" s="6" t="n">
         <v>41.32</v>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="I37" s="6" t="n">
         <v>40.03</v>
       </c>
-      <c r="J37" s="10" t="n">
+      <c r="J37" s="6" t="n">
         <v>40.92</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="K37" s="6" t="n">
         <v>39.57</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="6" t="n">
         <v>40.51</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="6" t="n">
         <v>44.43</v>
       </c>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="6" t="n">
         <v>40.55</v>
       </c>
-      <c r="O37" s="9" t="n">
+      <c r="O37" s="6" t="n">
         <v>43.01</v>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P37" s="6" t="n">
         <v>43.79</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="6" t="n">
         <v>40.86</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="6" t="n">
         <v>36.73</v>
       </c>
-      <c r="S37" s="10" t="n">
+      <c r="S37" s="6" t="n">
         <v>36.76</v>
       </c>
-      <c r="T37" s="10" t="n">
+      <c r="T37" s="6" t="n">
         <v>38.71</v>
       </c>
-      <c r="U37" s="10" t="n">
+      <c r="U37" s="6" t="n">
         <v>36.86</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="6" t="n">
         <v>40.22</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="6" t="n">
         <v>40.92</v>
       </c>
-      <c r="X37" s="10" t="n">
+      <c r="X37" s="6" t="n">
         <v>39.83</v>
       </c>
-      <c r="Y37" s="10" t="n">
+      <c r="Y37" s="6" t="n">
         <v>37.26</v>
       </c>
-      <c r="Z37" s="10" t="n">
+      <c r="Z37" s="6" t="n">
         <v>38.74</v>
       </c>
-      <c r="AA37" s="10" t="n">
+      <c r="AA37" s="6" t="n">
         <v>37.96</v>
       </c>
-      <c r="AB37" s="10" t="n">
+      <c r="AB37" s="6" t="n">
         <v>41.61</v>
       </c>
-      <c r="AC37" s="10" t="n">
+      <c r="AC37" s="6" t="n">
         <v>41.84</v>
       </c>
-      <c r="AD37" s="10" t="n">
+      <c r="AD37" s="6" t="n">
         <v>38.69</v>
       </c>
-      <c r="AE37" s="10" t="n">
+      <c r="AE37" s="6" t="n">
         <v>41.51</v>
       </c>
-      <c r="AF37" s="10" t="n">
+      <c r="AF37" s="6" t="n">
         <v>41.72</v>
       </c>
-      <c r="AG37" s="10" t="n">
+      <c r="AG37" s="6" t="n">
         <v>41.58</v>
       </c>
       <c r="AH37" s="6" t="n">
@@ -3920,7 +3887,7 @@
         <v>499.53</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="8" t="inlineStr"/>
+      <c r="AK37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3931,97 +3898,97 @@
       <c r="B38" s="6" t="n">
         <v>101.5</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="6" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="6" t="n">
         <v>77.16</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="6" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="6" t="n">
         <v>77.88</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="6" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H38" s="6" t="n">
         <v>77.70999999999999</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I38" s="6" t="n">
         <v>77.22</v>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="J38" s="6" t="n">
         <v>77.28</v>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="K38" s="6" t="n">
         <v>77.56</v>
       </c>
-      <c r="L38" s="7" t="n">
+      <c r="L38" s="6" t="n">
         <v>77.36</v>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="6" t="n">
         <v>77.15000000000001</v>
       </c>
-      <c r="N38" s="7" t="n">
+      <c r="N38" s="6" t="n">
         <v>77.54000000000001</v>
       </c>
-      <c r="O38" s="7" t="n">
+      <c r="O38" s="6" t="n">
         <v>77.86</v>
       </c>
-      <c r="P38" s="7" t="n">
+      <c r="P38" s="6" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="Q38" s="7" t="n">
+      <c r="Q38" s="6" t="n">
         <v>77.11</v>
       </c>
-      <c r="R38" s="7" t="n">
+      <c r="R38" s="6" t="n">
         <v>77.11</v>
       </c>
-      <c r="S38" s="7" t="n">
+      <c r="S38" s="6" t="n">
         <v>77.18000000000001</v>
       </c>
-      <c r="T38" s="7" t="n">
+      <c r="T38" s="6" t="n">
         <v>77.28</v>
       </c>
-      <c r="U38" s="7" t="n">
+      <c r="U38" s="6" t="n">
         <v>77.53</v>
       </c>
-      <c r="V38" s="7" t="n">
+      <c r="V38" s="6" t="n">
         <v>77.73</v>
       </c>
-      <c r="W38" s="7" t="n">
+      <c r="W38" s="6" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="X38" s="7" t="n">
+      <c r="X38" s="6" t="n">
         <v>77.02</v>
       </c>
-      <c r="Y38" s="7" t="n">
+      <c r="Y38" s="6" t="n">
         <v>77.03</v>
       </c>
-      <c r="Z38" s="7" t="n">
+      <c r="Z38" s="6" t="n">
         <v>77.04000000000001</v>
       </c>
-      <c r="AA38" s="7" t="n">
+      <c r="AA38" s="6" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="AB38" s="7" t="n">
+      <c r="AB38" s="6" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="AC38" s="7" t="n">
+      <c r="AC38" s="6" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="AD38" s="7" t="n">
+      <c r="AD38" s="6" t="n">
         <v>77.84</v>
       </c>
-      <c r="AE38" s="7" t="n">
+      <c r="AE38" s="6" t="n">
         <v>78.12</v>
       </c>
-      <c r="AF38" s="7" t="n">
+      <c r="AF38" s="6" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="AG38" s="7" t="n">
+      <c r="AG38" s="6" t="n">
         <v>77.81</v>
       </c>
       <c r="AH38" s="6" t="n">
@@ -4031,7 +3998,7 @@
         <v>159.74</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="8" t="inlineStr"/>
+      <c r="AK38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4042,97 +4009,97 @@
       <c r="B39" s="6" t="n">
         <v>102.3</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="6" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="6" t="n">
         <v>70.63</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="6" t="n">
         <v>66.64</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="6" t="n">
         <v>71.08</v>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="6" t="n">
         <v>71.31999999999999</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="6" t="n">
         <v>71.18000000000001</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="I39" s="6" t="n">
         <v>71.13</v>
       </c>
-      <c r="J39" s="7" t="n">
+      <c r="J39" s="6" t="n">
         <v>71.28</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="K39" s="6" t="n">
         <v>71.3</v>
       </c>
-      <c r="L39" s="7" t="n">
+      <c r="L39" s="6" t="n">
         <v>71.34999999999999</v>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="6" t="n">
         <v>70.84</v>
       </c>
-      <c r="N39" s="7" t="n">
+      <c r="N39" s="6" t="n">
         <v>71.38</v>
       </c>
-      <c r="O39" s="7" t="n">
+      <c r="O39" s="6" t="n">
         <v>71.52</v>
       </c>
-      <c r="P39" s="7" t="n">
+      <c r="P39" s="6" t="n">
         <v>72.11</v>
       </c>
-      <c r="Q39" s="7" t="n">
+      <c r="Q39" s="6" t="n">
         <v>71.31999999999999</v>
       </c>
-      <c r="R39" s="7" t="n">
+      <c r="R39" s="6" t="n">
         <v>70.79000000000001</v>
       </c>
-      <c r="S39" s="7" t="n">
+      <c r="S39" s="6" t="n">
         <v>71.26000000000001</v>
       </c>
-      <c r="T39" s="7" t="n">
+      <c r="T39" s="6" t="n">
         <v>71.37</v>
       </c>
-      <c r="U39" s="7" t="n">
+      <c r="U39" s="6" t="n">
         <v>71.91</v>
       </c>
-      <c r="V39" s="7" t="n">
+      <c r="V39" s="6" t="n">
         <v>72.36</v>
       </c>
-      <c r="W39" s="7" t="n">
+      <c r="W39" s="6" t="n">
         <v>71.31</v>
       </c>
-      <c r="X39" s="7" t="n">
+      <c r="X39" s="6" t="n">
         <v>71.27</v>
       </c>
-      <c r="Y39" s="7" t="n">
+      <c r="Y39" s="6" t="n">
         <v>71.64</v>
       </c>
-      <c r="Z39" s="7" t="n">
+      <c r="Z39" s="6" t="n">
         <v>71.56</v>
       </c>
-      <c r="AA39" s="7" t="n">
+      <c r="AA39" s="6" t="n">
         <v>72.79000000000001</v>
       </c>
-      <c r="AB39" s="7" t="n">
+      <c r="AB39" s="6" t="n">
         <v>71.95</v>
       </c>
-      <c r="AC39" s="7" t="n">
+      <c r="AC39" s="6" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="AD39" s="7" t="n">
+      <c r="AD39" s="6" t="n">
         <v>72.06</v>
       </c>
-      <c r="AE39" s="7" t="n">
+      <c r="AE39" s="6" t="n">
         <v>73.04000000000001</v>
       </c>
-      <c r="AF39" s="7" t="n">
+      <c r="AF39" s="6" t="n">
         <v>72.36</v>
       </c>
-      <c r="AG39" s="7" t="n">
+      <c r="AG39" s="6" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="AH39" s="6" t="n">
@@ -4142,7 +4109,7 @@
         <v>422.29</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="8" t="inlineStr"/>
+      <c r="AK39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4153,97 +4120,97 @@
       <c r="B40" s="6" t="n">
         <v>102.7</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="6" t="n">
         <v>58.14</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="6" t="n">
         <v>57.6</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="6" t="n">
         <v>62.89</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>57.41</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="6" t="n">
         <v>57.04</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H40" s="6" t="n">
         <v>56.29</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I40" s="6" t="n">
         <v>57.62</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J40" s="6" t="n">
         <v>57.9</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K40" s="6" t="n">
         <v>57.87</v>
       </c>
-      <c r="L40" s="7" t="n">
+      <c r="L40" s="6" t="n">
         <v>58.19</v>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="6" t="n">
         <v>59.66</v>
       </c>
-      <c r="N40" s="7" t="n">
+      <c r="N40" s="6" t="n">
         <v>57.31</v>
       </c>
-      <c r="O40" s="7" t="n">
+      <c r="O40" s="6" t="n">
         <v>57.81</v>
       </c>
-      <c r="P40" s="7" t="n">
+      <c r="P40" s="6" t="n">
         <v>58.09</v>
       </c>
-      <c r="Q40" s="7" t="n">
+      <c r="Q40" s="6" t="n">
         <v>59.71</v>
       </c>
-      <c r="R40" s="7" t="n">
+      <c r="R40" s="6" t="n">
         <v>58.68</v>
       </c>
-      <c r="S40" s="7" t="n">
+      <c r="S40" s="6" t="n">
         <v>58.13</v>
       </c>
-      <c r="T40" s="7" t="n">
+      <c r="T40" s="6" t="n">
         <v>58.57</v>
       </c>
-      <c r="U40" s="7" t="n">
+      <c r="U40" s="6" t="n">
         <v>58.45</v>
       </c>
-      <c r="V40" s="7" t="n">
+      <c r="V40" s="6" t="n">
         <v>58.68</v>
       </c>
-      <c r="W40" s="7" t="n">
+      <c r="W40" s="6" t="n">
         <v>58.76</v>
       </c>
-      <c r="X40" s="7" t="n">
+      <c r="X40" s="6" t="n">
         <v>58.66</v>
       </c>
-      <c r="Y40" s="7" t="n">
+      <c r="Y40" s="6" t="n">
         <v>58.76</v>
       </c>
-      <c r="Z40" s="7" t="n">
+      <c r="Z40" s="6" t="n">
         <v>56.95</v>
       </c>
-      <c r="AA40" s="7" t="n">
+      <c r="AA40" s="6" t="n">
         <v>58.78</v>
       </c>
-      <c r="AB40" s="7" t="n">
+      <c r="AB40" s="6" t="n">
         <v>59.01</v>
       </c>
-      <c r="AC40" s="7" t="n">
+      <c r="AC40" s="6" t="n">
         <v>58.66</v>
       </c>
-      <c r="AD40" s="7" t="n">
+      <c r="AD40" s="6" t="n">
         <v>58.24</v>
       </c>
-      <c r="AE40" s="7" t="n">
+      <c r="AE40" s="6" t="n">
         <v>58.16</v>
       </c>
-      <c r="AF40" s="7" t="n">
+      <c r="AF40" s="6" t="n">
         <v>58.82</v>
       </c>
-      <c r="AG40" s="7" t="n">
+      <c r="AG40" s="6" t="n">
         <v>58.96</v>
       </c>
       <c r="AH40" s="6" t="n">
@@ -4253,7 +4220,7 @@
         <v>471.03</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="8" t="inlineStr"/>
+      <c r="AK40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4264,97 +4231,97 @@
       <c r="B41" s="6" t="n">
         <v>103.1</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="6" t="n">
         <v>46.72</v>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="6" t="n">
         <v>35.76</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="6" t="n">
         <v>36.4</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="6" t="n">
         <v>45.76</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="6" t="n">
         <v>43.98</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="6" t="n">
         <v>45.91</v>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I41" s="6" t="n">
         <v>42.62</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" s="6" t="n">
         <v>44.54</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="6" t="n">
         <v>43.32</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="6" t="n">
         <v>43.78</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="6" t="n">
         <v>46.12</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="6" t="n">
         <v>45.71</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="6" t="n">
         <v>45.21</v>
       </c>
-      <c r="P41" s="10" t="n">
+      <c r="P41" s="6" t="n">
         <v>42.01</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="6" t="n">
         <v>47.36</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="6" t="n">
         <v>43.31</v>
       </c>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="6" t="n">
         <v>37.48</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="6" t="n">
         <v>43.12</v>
       </c>
-      <c r="U41" s="10" t="n">
+      <c r="U41" s="6" t="n">
         <v>41.52</v>
       </c>
-      <c r="V41" s="10" t="n">
+      <c r="V41" s="6" t="n">
         <v>42.48</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="6" t="n">
         <v>42.72</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="6" t="n">
         <v>46.34</v>
       </c>
-      <c r="Y41" s="10" t="n">
+      <c r="Y41" s="6" t="n">
         <v>42.01</v>
       </c>
-      <c r="Z41" s="10" t="n">
+      <c r="Z41" s="6" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA41" s="10" t="n">
+      <c r="AA41" s="6" t="n">
         <v>41.55</v>
       </c>
-      <c r="AB41" s="10" t="n">
+      <c r="AB41" s="6" t="n">
         <v>41.22</v>
       </c>
-      <c r="AC41" s="9" t="n">
+      <c r="AC41" s="6" t="n">
         <v>44.88</v>
       </c>
-      <c r="AD41" s="10" t="n">
+      <c r="AD41" s="6" t="n">
         <v>38.64</v>
       </c>
-      <c r="AE41" s="10" t="n">
+      <c r="AE41" s="6" t="n">
         <v>41.14</v>
       </c>
-      <c r="AF41" s="9" t="n">
+      <c r="AF41" s="6" t="n">
         <v>47.4</v>
       </c>
-      <c r="AG41" s="9" t="n">
+      <c r="AG41" s="6" t="n">
         <v>48.04</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -4364,7 +4331,7 @@
         <v>161.11</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="8" t="inlineStr"/>
+      <c r="AK41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4375,97 +4342,97 @@
       <c r="B42" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="6" t="n">
         <v>46.89</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="6" t="n">
         <v>36.46</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="6" t="n">
         <v>37.76</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="6" t="n">
         <v>45.51</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="6" t="n">
         <v>44.04</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="6" t="n">
         <v>45.22</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="6" t="n">
         <v>43.04</v>
       </c>
-      <c r="J42" s="10" t="n">
+      <c r="J42" s="6" t="n">
         <v>42.79</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="6" t="n">
         <v>47.75</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="6" t="n">
         <v>45.64</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="6" t="n">
         <v>46.23</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="6" t="n">
         <v>44.39</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="6" t="n">
         <v>45.54</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="6" t="n">
         <v>46.71</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="6" t="n">
         <v>42.49</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="6" t="n">
         <v>39.33</v>
       </c>
-      <c r="S42" s="10" t="n">
+      <c r="S42" s="6" t="n">
         <v>40.14</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="T42" s="6" t="n">
         <v>38.01</v>
       </c>
-      <c r="U42" s="10" t="n">
+      <c r="U42" s="6" t="n">
         <v>38.08</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="V42" s="6" t="n">
         <v>38.74</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="6" t="n">
         <v>43.46</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="6" t="n">
         <v>46.21</v>
       </c>
-      <c r="Y42" s="10" t="n">
+      <c r="Y42" s="6" t="n">
         <v>40.55</v>
       </c>
-      <c r="Z42" s="10" t="n">
+      <c r="Z42" s="6" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA42" s="10" t="n">
+      <c r="AA42" s="6" t="n">
         <v>36.65</v>
       </c>
-      <c r="AB42" s="10" t="n">
+      <c r="AB42" s="6" t="n">
         <v>42.29</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="6" t="n">
         <v>45.95</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AD42" s="6" t="n">
         <v>43.71</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="6" t="n">
         <v>45.76</v>
       </c>
-      <c r="AF42" s="9" t="n">
+      <c r="AF42" s="6" t="n">
         <v>47.26</v>
       </c>
-      <c r="AG42" s="9" t="n">
+      <c r="AG42" s="6" t="n">
         <v>44.16</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -4475,7 +4442,7 @@
         <v>141.85</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="8" t="inlineStr"/>
+      <c r="AK42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4486,97 +4453,97 @@
       <c r="B43" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="6" t="n">
         <v>47.79</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="6" t="n">
         <v>36.54</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="6" t="n">
         <v>35.36</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="6" t="n">
         <v>39.5</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="6" t="n">
         <v>39.05</v>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="H43" s="6" t="n">
         <v>44.41</v>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="6" t="n">
         <v>42.89</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="6" t="n">
         <v>45.39</v>
       </c>
-      <c r="K43" s="9" t="n">
+      <c r="K43" s="6" t="n">
         <v>46.43</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="6" t="n">
         <v>44.24</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="6" t="n">
         <v>46.82</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" s="6" t="n">
         <v>43.69</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="6" t="n">
         <v>48.21</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="P43" s="6" t="n">
         <v>47.44</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="6" t="n">
         <v>43.59</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="6" t="n">
         <v>39.13</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="S43" s="6" t="n">
         <v>38.44</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="T43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="U43" s="10" t="n">
+      <c r="U43" s="6" t="n">
         <v>42.06</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="6" t="n">
         <v>39.01</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="6" t="n">
         <v>42.07</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" s="6" t="n">
         <v>46.61</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="6" t="n">
         <v>36.92</v>
       </c>
-      <c r="Z43" s="10" t="n">
+      <c r="Z43" s="6" t="n">
         <v>37.61</v>
       </c>
-      <c r="AA43" s="10" t="n">
+      <c r="AA43" s="6" t="n">
         <v>36.41</v>
       </c>
-      <c r="AB43" s="10" t="n">
+      <c r="AB43" s="6" t="n">
         <v>40.19</v>
       </c>
-      <c r="AC43" s="10" t="n">
+      <c r="AC43" s="6" t="n">
         <v>39.22</v>
       </c>
-      <c r="AD43" s="10" t="n">
+      <c r="AD43" s="6" t="n">
         <v>40.28</v>
       </c>
-      <c r="AE43" s="9" t="n">
+      <c r="AE43" s="6" t="n">
         <v>47.26</v>
       </c>
-      <c r="AF43" s="9" t="n">
+      <c r="AF43" s="6" t="n">
         <v>46.28</v>
       </c>
-      <c r="AG43" s="9" t="n">
+      <c r="AG43" s="6" t="n">
         <v>45.59</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -4586,7 +4553,7 @@
         <v>140.45</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="8" t="inlineStr"/>
+      <c r="AK43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4597,97 +4564,97 @@
       <c r="B44" s="6" t="n">
         <v>103.9</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="6" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="6" t="n">
         <v>77.72</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="6" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="6" t="n">
         <v>77.3</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="6" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="6" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="6" t="n">
         <v>76.72</v>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J44" s="6" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="K44" s="6" t="n">
         <v>77.23</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="L44" s="6" t="n">
         <v>76.86</v>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="6" t="n">
         <v>78.38</v>
       </c>
-      <c r="N44" s="7" t="n">
+      <c r="N44" s="6" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="O44" s="7" t="n">
+      <c r="O44" s="6" t="n">
         <v>78.19</v>
       </c>
-      <c r="P44" s="7" t="n">
+      <c r="P44" s="6" t="n">
         <v>77.08</v>
       </c>
-      <c r="Q44" s="7" t="n">
+      <c r="Q44" s="6" t="n">
         <v>77.70999999999999</v>
       </c>
-      <c r="R44" s="7" t="n">
+      <c r="R44" s="6" t="n">
         <v>78.08</v>
       </c>
-      <c r="S44" s="7" t="n">
+      <c r="S44" s="6" t="n">
         <v>77.56</v>
       </c>
-      <c r="T44" s="7" t="n">
+      <c r="T44" s="6" t="n">
         <v>78.36</v>
       </c>
-      <c r="U44" s="7" t="n">
+      <c r="U44" s="6" t="n">
         <v>77.41</v>
       </c>
-      <c r="V44" s="7" t="n">
+      <c r="V44" s="6" t="n">
         <v>77.61</v>
       </c>
-      <c r="W44" s="7" t="n">
+      <c r="W44" s="6" t="n">
         <v>77.5</v>
       </c>
-      <c r="X44" s="7" t="n">
+      <c r="X44" s="6" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="Y44" s="7" t="n">
+      <c r="Y44" s="6" t="n">
         <v>77.47</v>
       </c>
-      <c r="Z44" s="7" t="n">
+      <c r="Z44" s="6" t="n">
         <v>77.18000000000001</v>
       </c>
-      <c r="AA44" s="7" t="n">
+      <c r="AA44" s="6" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="AB44" s="7" t="n">
+      <c r="AB44" s="6" t="n">
         <v>78.15000000000001</v>
       </c>
-      <c r="AC44" s="7" t="n">
+      <c r="AC44" s="6" t="n">
         <v>78.34</v>
       </c>
-      <c r="AD44" s="7" t="n">
+      <c r="AD44" s="6" t="n">
         <v>77.31</v>
       </c>
-      <c r="AE44" s="7" t="n">
+      <c r="AE44" s="6" t="n">
         <v>77.93000000000001</v>
       </c>
-      <c r="AF44" s="7" t="n">
+      <c r="AF44" s="6" t="n">
         <v>77.95999999999999</v>
       </c>
-      <c r="AG44" s="7" t="n">
+      <c r="AG44" s="6" t="n">
         <v>78.26000000000001</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -4697,7 +4664,7 @@
         <v>181.85</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="8" t="inlineStr"/>
+      <c r="AK44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4708,97 +4675,97 @@
       <c r="B45" s="6" t="n">
         <v>104.3</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="6" t="n">
         <v>66.14</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="6" t="n">
         <v>66.64</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="6" t="n">
         <v>66.44</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="6" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="6" t="n">
         <v>67.31</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="6" t="n">
         <v>67.41</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="6" t="n">
         <v>66.36</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="J45" s="6" t="n">
         <v>67.08</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K45" s="6" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="L45" s="6" t="n">
         <v>66.56999999999999</v>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="6" t="n">
         <v>66.58</v>
       </c>
-      <c r="N45" s="7" t="n">
+      <c r="N45" s="6" t="n">
         <v>66.59</v>
       </c>
-      <c r="O45" s="7" t="n">
+      <c r="O45" s="6" t="n">
         <v>66.29000000000001</v>
       </c>
-      <c r="P45" s="7" t="n">
+      <c r="P45" s="6" t="n">
         <v>66.31</v>
       </c>
-      <c r="Q45" s="7" t="n">
+      <c r="Q45" s="6" t="n">
         <v>66.12</v>
       </c>
-      <c r="R45" s="7" t="n">
+      <c r="R45" s="6" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="S45" s="7" t="n">
+      <c r="S45" s="6" t="n">
         <v>67.55</v>
       </c>
-      <c r="T45" s="7" t="n">
+      <c r="T45" s="6" t="n">
         <v>66.61</v>
       </c>
-      <c r="U45" s="7" t="n">
+      <c r="U45" s="6" t="n">
         <v>67.26000000000001</v>
       </c>
-      <c r="V45" s="7" t="n">
+      <c r="V45" s="6" t="n">
         <v>67.62</v>
       </c>
-      <c r="W45" s="7" t="n">
+      <c r="W45" s="6" t="n">
         <v>67.06</v>
       </c>
-      <c r="X45" s="7" t="n">
+      <c r="X45" s="6" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="Y45" s="7" t="n">
+      <c r="Y45" s="6" t="n">
         <v>67.22</v>
       </c>
-      <c r="Z45" s="7" t="n">
+      <c r="Z45" s="6" t="n">
         <v>66.69</v>
       </c>
-      <c r="AA45" s="7" t="n">
+      <c r="AA45" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="AB45" s="7" t="n">
+      <c r="AB45" s="6" t="n">
         <v>66.44</v>
       </c>
-      <c r="AC45" s="7" t="n">
+      <c r="AC45" s="6" t="n">
         <v>66.86</v>
       </c>
-      <c r="AD45" s="7" t="n">
+      <c r="AD45" s="6" t="n">
         <v>66.92</v>
       </c>
-      <c r="AE45" s="7" t="n">
+      <c r="AE45" s="6" t="n">
         <v>66.56</v>
       </c>
-      <c r="AF45" s="7" t="n">
+      <c r="AF45" s="6" t="n">
         <v>67.11</v>
       </c>
-      <c r="AG45" s="7" t="n">
+      <c r="AG45" s="6" t="n">
         <v>66.86</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -4808,7 +4775,7 @@
         <v>243.9</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="8" t="inlineStr"/>
+      <c r="AK45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4819,97 +4786,97 @@
       <c r="B46" s="6" t="n">
         <v>104.7</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="6" t="n">
         <v>70.06</v>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D46" s="6" t="n">
         <v>71.16</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" s="6" t="n">
         <v>66.28</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="6" t="n">
         <v>69.68000000000001</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="6" t="n">
         <v>69.76000000000001</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H46" s="6" t="n">
         <v>70.01000000000001</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="I46" s="6" t="n">
         <v>69.19</v>
       </c>
-      <c r="J46" s="7" t="n">
+      <c r="J46" s="6" t="n">
         <v>70.18000000000001</v>
       </c>
-      <c r="K46" s="7" t="n">
+      <c r="K46" s="6" t="n">
         <v>70.44</v>
       </c>
-      <c r="L46" s="7" t="n">
+      <c r="L46" s="6" t="n">
         <v>70.5</v>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="6" t="n">
         <v>70.22</v>
       </c>
-      <c r="N46" s="7" t="n">
+      <c r="N46" s="6" t="n">
         <v>69.84</v>
       </c>
-      <c r="O46" s="7" t="n">
+      <c r="O46" s="6" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="P46" s="7" t="n">
+      <c r="P46" s="6" t="n">
         <v>69.31999999999999</v>
       </c>
-      <c r="Q46" s="7" t="n">
+      <c r="Q46" s="6" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="R46" s="7" t="n">
+      <c r="R46" s="6" t="n">
         <v>70.84</v>
       </c>
-      <c r="S46" s="7" t="n">
+      <c r="S46" s="6" t="n">
         <v>70.44</v>
       </c>
-      <c r="T46" s="7" t="n">
+      <c r="T46" s="6" t="n">
         <v>70.70999999999999</v>
       </c>
-      <c r="U46" s="7" t="n">
+      <c r="U46" s="6" t="n">
         <v>70.53</v>
       </c>
-      <c r="V46" s="7" t="n">
+      <c r="V46" s="6" t="n">
         <v>70.63</v>
       </c>
-      <c r="W46" s="7" t="n">
+      <c r="W46" s="6" t="n">
         <v>70.33</v>
       </c>
-      <c r="X46" s="7" t="n">
+      <c r="X46" s="6" t="n">
         <v>70.08</v>
       </c>
-      <c r="Y46" s="7" t="n">
+      <c r="Y46" s="6" t="n">
         <v>70.14</v>
       </c>
-      <c r="Z46" s="7" t="n">
+      <c r="Z46" s="6" t="n">
         <v>69.06</v>
       </c>
-      <c r="AA46" s="7" t="n">
+      <c r="AA46" s="6" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="AB46" s="7" t="n">
+      <c r="AB46" s="6" t="n">
         <v>69.51000000000001</v>
       </c>
-      <c r="AC46" s="7" t="n">
+      <c r="AC46" s="6" t="n">
         <v>70.54000000000001</v>
       </c>
-      <c r="AD46" s="7" t="n">
+      <c r="AD46" s="6" t="n">
         <v>70.2</v>
       </c>
-      <c r="AE46" s="7" t="n">
+      <c r="AE46" s="6" t="n">
         <v>70.81</v>
       </c>
-      <c r="AF46" s="7" t="n">
+      <c r="AF46" s="6" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="AG46" s="7" t="n">
+      <c r="AG46" s="6" t="n">
         <v>71.01000000000001</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4919,7 +4886,7 @@
         <v>252.32</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="8" t="inlineStr"/>
+      <c r="AK46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4930,97 +4897,97 @@
       <c r="B47" s="6" t="n">
         <v>105.1</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="6" t="n">
         <v>80.31999999999999</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D47" s="6" t="n">
         <v>79.70999999999999</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="6" t="n">
         <v>77.03</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="6" t="n">
         <v>79.97</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="6" t="n">
         <v>79.47</v>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="H47" s="6" t="n">
         <v>79.81</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="I47" s="6" t="n">
         <v>79.3</v>
       </c>
-      <c r="J47" s="7" t="n">
+      <c r="J47" s="6" t="n">
         <v>79.39</v>
       </c>
-      <c r="K47" s="7" t="n">
+      <c r="K47" s="6" t="n">
         <v>79.23999999999999</v>
       </c>
-      <c r="L47" s="7" t="n">
+      <c r="L47" s="6" t="n">
         <v>79.56</v>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="6" t="n">
         <v>80.08</v>
       </c>
-      <c r="N47" s="7" t="n">
+      <c r="N47" s="6" t="n">
         <v>79.52</v>
       </c>
-      <c r="O47" s="7" t="n">
+      <c r="O47" s="6" t="n">
         <v>79.02</v>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="P47" s="6" t="n">
         <v>79.15000000000001</v>
       </c>
-      <c r="Q47" s="7" t="n">
+      <c r="Q47" s="6" t="n">
         <v>79.28</v>
       </c>
-      <c r="R47" s="7" t="n">
+      <c r="R47" s="6" t="n">
         <v>79.69</v>
       </c>
-      <c r="S47" s="7" t="n">
+      <c r="S47" s="6" t="n">
         <v>79.54000000000001</v>
       </c>
-      <c r="T47" s="7" t="n">
+      <c r="T47" s="6" t="n">
         <v>79.36</v>
       </c>
-      <c r="U47" s="7" t="n">
+      <c r="U47" s="6" t="n">
         <v>79.76000000000001</v>
       </c>
-      <c r="V47" s="7" t="n">
+      <c r="V47" s="6" t="n">
         <v>79.66</v>
       </c>
-      <c r="W47" s="7" t="n">
+      <c r="W47" s="6" t="n">
         <v>79.83</v>
       </c>
-      <c r="X47" s="7" t="n">
+      <c r="X47" s="6" t="n">
         <v>79.47</v>
       </c>
-      <c r="Y47" s="7" t="n">
+      <c r="Y47" s="6" t="n">
         <v>80.41</v>
       </c>
-      <c r="Z47" s="7" t="n">
+      <c r="Z47" s="6" t="n">
         <v>79.79000000000001</v>
       </c>
-      <c r="AA47" s="7" t="n">
+      <c r="AA47" s="6" t="n">
         <v>80.11</v>
       </c>
-      <c r="AB47" s="7" t="n">
+      <c r="AB47" s="6" t="n">
         <v>79.79000000000001</v>
       </c>
-      <c r="AC47" s="7" t="n">
+      <c r="AC47" s="6" t="n">
         <v>79.66</v>
       </c>
-      <c r="AD47" s="7" t="n">
+      <c r="AD47" s="6" t="n">
         <v>79.3</v>
       </c>
-      <c r="AE47" s="7" t="n">
+      <c r="AE47" s="6" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="AF47" s="7" t="n">
+      <c r="AF47" s="6" t="n">
         <v>79.64</v>
       </c>
-      <c r="AG47" s="7" t="n">
+      <c r="AG47" s="6" t="n">
         <v>80.06</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -5030,7 +4997,7 @@
         <v>254.37</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="8" t="inlineStr"/>
+      <c r="AK47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5041,97 +5008,97 @@
       <c r="B48" s="6" t="n">
         <v>105.5</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="6" t="n">
         <v>57.51</v>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D48" s="6" t="n">
         <v>56.33</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="6" t="n">
         <v>52.45</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="6" t="n">
         <v>54.84</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="6" t="n">
         <v>56.89</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H48" s="6" t="n">
         <v>56.58</v>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="I48" s="6" t="n">
         <v>56.42</v>
       </c>
-      <c r="J48" s="7" t="n">
+      <c r="J48" s="6" t="n">
         <v>55.91</v>
       </c>
-      <c r="K48" s="7" t="n">
+      <c r="K48" s="6" t="n">
         <v>55.03</v>
       </c>
-      <c r="L48" s="7" t="n">
+      <c r="L48" s="6" t="n">
         <v>56.9</v>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="6" t="n">
         <v>56.44</v>
       </c>
-      <c r="N48" s="7" t="n">
+      <c r="N48" s="6" t="n">
         <v>56.82</v>
       </c>
-      <c r="O48" s="7" t="n">
+      <c r="O48" s="6" t="n">
         <v>55.44</v>
       </c>
-      <c r="P48" s="7" t="n">
+      <c r="P48" s="6" t="n">
         <v>54.61</v>
       </c>
-      <c r="Q48" s="7" t="n">
+      <c r="Q48" s="6" t="n">
         <v>54.7</v>
       </c>
-      <c r="R48" s="7" t="n">
+      <c r="R48" s="6" t="n">
         <v>56.19</v>
       </c>
-      <c r="S48" s="7" t="n">
+      <c r="S48" s="6" t="n">
         <v>55.34</v>
       </c>
-      <c r="T48" s="7" t="n">
+      <c r="T48" s="6" t="n">
         <v>56.69</v>
       </c>
-      <c r="U48" s="7" t="n">
+      <c r="U48" s="6" t="n">
         <v>55.47</v>
       </c>
-      <c r="V48" s="7" t="n">
+      <c r="V48" s="6" t="n">
         <v>56.24</v>
       </c>
-      <c r="W48" s="7" t="n">
+      <c r="W48" s="6" t="n">
         <v>56.59</v>
       </c>
-      <c r="X48" s="7" t="n">
+      <c r="X48" s="6" t="n">
         <v>55.64</v>
       </c>
-      <c r="Y48" s="7" t="n">
+      <c r="Y48" s="6" t="n">
         <v>56.9</v>
       </c>
-      <c r="Z48" s="7" t="n">
+      <c r="Z48" s="6" t="n">
         <v>55.12</v>
       </c>
-      <c r="AA48" s="7" t="n">
+      <c r="AA48" s="6" t="n">
         <v>55.36</v>
       </c>
-      <c r="AB48" s="7" t="n">
+      <c r="AB48" s="6" t="n">
         <v>55.66</v>
       </c>
-      <c r="AC48" s="7" t="n">
+      <c r="AC48" s="6" t="n">
         <v>56.56</v>
       </c>
-      <c r="AD48" s="7" t="n">
+      <c r="AD48" s="6" t="n">
         <v>55.57</v>
       </c>
-      <c r="AE48" s="7" t="n">
+      <c r="AE48" s="6" t="n">
         <v>55.86</v>
       </c>
-      <c r="AF48" s="7" t="n">
+      <c r="AF48" s="6" t="n">
         <v>56.94</v>
       </c>
-      <c r="AG48" s="7" t="n">
+      <c r="AG48" s="6" t="n">
         <v>55.31</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -5141,7 +5108,7 @@
         <v>487.79</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="8" t="inlineStr"/>
+      <c r="AK48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5152,97 +5119,97 @@
       <c r="B49" s="6" t="n">
         <v>105.9</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="6" t="n">
         <v>66.36</v>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D49" s="6" t="n">
         <v>66.62</v>
       </c>
-      <c r="E49" s="7" t="n">
+      <c r="E49" s="6" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="6" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="6" t="n">
         <v>66.55</v>
       </c>
-      <c r="H49" s="7" t="n">
+      <c r="H49" s="6" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="I49" s="7" t="n">
+      <c r="I49" s="6" t="n">
         <v>67.11</v>
       </c>
-      <c r="J49" s="7" t="n">
+      <c r="J49" s="6" t="n">
         <v>67.22</v>
       </c>
-      <c r="K49" s="7" t="n">
+      <c r="K49" s="6" t="n">
         <v>66.48</v>
       </c>
-      <c r="L49" s="7" t="n">
+      <c r="L49" s="6" t="n">
         <v>66.77</v>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="6" t="n">
         <v>66.68000000000001</v>
       </c>
-      <c r="N49" s="7" t="n">
+      <c r="N49" s="6" t="n">
         <v>66.81</v>
       </c>
-      <c r="O49" s="7" t="n">
+      <c r="O49" s="6" t="n">
         <v>66.81</v>
       </c>
-      <c r="P49" s="7" t="n">
+      <c r="P49" s="6" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="Q49" s="7" t="n">
+      <c r="Q49" s="6" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="R49" s="7" t="n">
+      <c r="R49" s="6" t="n">
         <v>66.86</v>
       </c>
-      <c r="S49" s="7" t="n">
+      <c r="S49" s="6" t="n">
         <v>66.98</v>
       </c>
-      <c r="T49" s="7" t="n">
+      <c r="T49" s="6" t="n">
         <v>66.95999999999999</v>
       </c>
-      <c r="U49" s="7" t="n">
+      <c r="U49" s="6" t="n">
         <v>67.08</v>
       </c>
-      <c r="V49" s="7" t="n">
+      <c r="V49" s="6" t="n">
         <v>66.89</v>
       </c>
-      <c r="W49" s="7" t="n">
+      <c r="W49" s="6" t="n">
         <v>67.59</v>
       </c>
-      <c r="X49" s="7" t="n">
+      <c r="X49" s="6" t="n">
         <v>67.19</v>
       </c>
-      <c r="Y49" s="7" t="n">
+      <c r="Y49" s="6" t="n">
         <v>66.66</v>
       </c>
-      <c r="Z49" s="7" t="n">
+      <c r="Z49" s="6" t="n">
         <v>67.11</v>
       </c>
-      <c r="AA49" s="7" t="n">
+      <c r="AA49" s="6" t="n">
         <v>66.53</v>
       </c>
-      <c r="AB49" s="7" t="n">
+      <c r="AB49" s="6" t="n">
         <v>66.53</v>
       </c>
-      <c r="AC49" s="7" t="n">
+      <c r="AC49" s="6" t="n">
         <v>67.18000000000001</v>
       </c>
-      <c r="AD49" s="7" t="n">
+      <c r="AD49" s="6" t="n">
         <v>66.62</v>
       </c>
-      <c r="AE49" s="7" t="n">
+      <c r="AE49" s="6" t="n">
         <v>67.23999999999999</v>
       </c>
-      <c r="AF49" s="7" t="n">
+      <c r="AF49" s="6" t="n">
         <v>67.06</v>
       </c>
-      <c r="AG49" s="7" t="n">
+      <c r="AG49" s="6" t="n">
         <v>66.27</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -5252,7 +5219,7 @@
         <v>385.5</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="8" t="inlineStr"/>
+      <c r="AK49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5263,97 +5230,97 @@
       <c r="B50" s="6" t="n">
         <v>106.3</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="6" t="n">
         <v>73.01000000000001</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="6" t="n">
         <v>72.91</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="6" t="n">
         <v>71.3</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="6" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="6" t="n">
         <v>73.98999999999999</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H50" s="6" t="n">
         <v>73.91</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="I50" s="6" t="n">
         <v>74.38</v>
       </c>
-      <c r="J50" s="7" t="n">
+      <c r="J50" s="6" t="n">
         <v>74.19</v>
       </c>
-      <c r="K50" s="7" t="n">
+      <c r="K50" s="6" t="n">
         <v>73.87</v>
       </c>
-      <c r="L50" s="7" t="n">
+      <c r="L50" s="6" t="n">
         <v>74.20999999999999</v>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="6" t="n">
         <v>74.53</v>
       </c>
-      <c r="N50" s="7" t="n">
+      <c r="N50" s="6" t="n">
         <v>74.2</v>
       </c>
-      <c r="O50" s="7" t="n">
+      <c r="O50" s="6" t="n">
         <v>73.95999999999999</v>
       </c>
-      <c r="P50" s="7" t="n">
+      <c r="P50" s="6" t="n">
         <v>73.73999999999999</v>
       </c>
-      <c r="Q50" s="7" t="n">
+      <c r="Q50" s="6" t="n">
         <v>74.29000000000001</v>
       </c>
-      <c r="R50" s="7" t="n">
+      <c r="R50" s="6" t="n">
         <v>73.86</v>
       </c>
-      <c r="S50" s="7" t="n">
+      <c r="S50" s="6" t="n">
         <v>73.61</v>
       </c>
-      <c r="T50" s="7" t="n">
+      <c r="T50" s="6" t="n">
         <v>73.37</v>
       </c>
-      <c r="U50" s="7" t="n">
+      <c r="U50" s="6" t="n">
         <v>74.39</v>
       </c>
-      <c r="V50" s="7" t="n">
+      <c r="V50" s="6" t="n">
         <v>73.94</v>
       </c>
-      <c r="W50" s="7" t="n">
+      <c r="W50" s="6" t="n">
         <v>74.06</v>
       </c>
-      <c r="X50" s="7" t="n">
+      <c r="X50" s="6" t="n">
         <v>74.12</v>
       </c>
-      <c r="Y50" s="7" t="n">
+      <c r="Y50" s="6" t="n">
         <v>74.31999999999999</v>
       </c>
-      <c r="Z50" s="7" t="n">
+      <c r="Z50" s="6" t="n">
         <v>74.15000000000001</v>
       </c>
-      <c r="AA50" s="7" t="n">
+      <c r="AA50" s="6" t="n">
         <v>73.75</v>
       </c>
-      <c r="AB50" s="7" t="n">
+      <c r="AB50" s="6" t="n">
         <v>74.08</v>
       </c>
-      <c r="AC50" s="7" t="n">
+      <c r="AC50" s="6" t="n">
         <v>74.33</v>
       </c>
-      <c r="AD50" s="7" t="n">
+      <c r="AD50" s="6" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="AE50" s="7" t="n">
+      <c r="AE50" s="6" t="n">
         <v>73.87</v>
       </c>
-      <c r="AF50" s="7" t="n">
+      <c r="AF50" s="6" t="n">
         <v>73.78</v>
       </c>
-      <c r="AG50" s="7" t="n">
+      <c r="AG50" s="6" t="n">
         <v>73.59</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -5363,7 +5330,7 @@
         <v>236.24</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="8" t="inlineStr"/>
+      <c r="AK50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -5374,97 +5341,97 @@
       <c r="B51" s="6" t="n">
         <v>106.7</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="6" t="n">
         <v>45.59</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D51" s="6" t="n">
         <v>44.29</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="6" t="n">
         <v>45.42</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="6" t="n">
         <v>45.54</v>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G51" s="6" t="n">
         <v>45.36</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H51" s="6" t="n">
         <v>44.1</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="I51" s="6" t="n">
         <v>45.04</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J51" s="6" t="n">
         <v>45.04</v>
       </c>
-      <c r="K51" s="9" t="n">
+      <c r="K51" s="6" t="n">
         <v>45.84</v>
       </c>
-      <c r="L51" s="9" t="n">
+      <c r="L51" s="6" t="n">
         <v>43.74</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" s="6" t="n">
         <v>44.87</v>
       </c>
-      <c r="N51" s="9" t="n">
+      <c r="N51" s="6" t="n">
         <v>45.91</v>
       </c>
-      <c r="O51" s="9" t="n">
+      <c r="O51" s="6" t="n">
         <v>45.61</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P51" s="6" t="n">
         <v>45.42</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="Q51" s="6" t="n">
         <v>45.88</v>
       </c>
-      <c r="R51" s="9" t="n">
+      <c r="R51" s="6" t="n">
         <v>45.66</v>
       </c>
-      <c r="S51" s="9" t="n">
+      <c r="S51" s="6" t="n">
         <v>45.7</v>
       </c>
-      <c r="T51" s="9" t="n">
+      <c r="T51" s="6" t="n">
         <v>46.39</v>
       </c>
-      <c r="U51" s="9" t="n">
+      <c r="U51" s="6" t="n">
         <v>45.44</v>
       </c>
-      <c r="V51" s="9" t="n">
+      <c r="V51" s="6" t="n">
         <v>43.86</v>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W51" s="6" t="n">
         <v>44.56</v>
       </c>
-      <c r="X51" s="9" t="n">
+      <c r="X51" s="6" t="n">
         <v>44.54</v>
       </c>
-      <c r="Y51" s="9" t="n">
+      <c r="Y51" s="6" t="n">
         <v>44.78</v>
       </c>
-      <c r="Z51" s="9" t="n">
+      <c r="Z51" s="6" t="n">
         <v>43.79</v>
       </c>
-      <c r="AA51" s="9" t="n">
+      <c r="AA51" s="6" t="n">
         <v>45.58</v>
       </c>
-      <c r="AB51" s="9" t="n">
+      <c r="AB51" s="6" t="n">
         <v>43.16</v>
       </c>
-      <c r="AC51" s="9" t="n">
+      <c r="AC51" s="6" t="n">
         <v>43.36</v>
       </c>
-      <c r="AD51" s="9" t="n">
+      <c r="AD51" s="6" t="n">
         <v>44.17</v>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AE51" s="6" t="n">
         <v>46.02</v>
       </c>
-      <c r="AF51" s="9" t="n">
+      <c r="AF51" s="6" t="n">
         <v>45.81</v>
       </c>
-      <c r="AG51" s="9" t="n">
+      <c r="AG51" s="6" t="n">
         <v>44.48</v>
       </c>
       <c r="AH51" s="6" t="n">
@@ -5474,118 +5441,118 @@
         <v>468.87</v>
       </c>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="8" t="inlineStr"/>
+      <c r="AK51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>GENESIS FM STEREO</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="9" t="n">
         <v>107.5</v>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C52" s="9" t="n">
         <v>45.55</v>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="9" t="n">
         <v>45.58</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="9" t="n">
         <v>46.18</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F52" s="9" t="n">
         <v>45.65</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="9" t="n">
         <v>47.34</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="9" t="n">
         <v>47.62</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="I52" s="9" t="n">
         <v>46.46</v>
       </c>
-      <c r="J52" s="13" t="n">
+      <c r="J52" s="9" t="n">
         <v>45.94</v>
       </c>
-      <c r="K52" s="13" t="n">
+      <c r="K52" s="9" t="n">
         <v>45.49</v>
       </c>
-      <c r="L52" s="13" t="n">
+      <c r="L52" s="9" t="n">
         <v>45.62</v>
       </c>
-      <c r="M52" s="13" t="n">
+      <c r="M52" s="9" t="n">
         <v>46.22</v>
       </c>
-      <c r="N52" s="13" t="n">
+      <c r="N52" s="9" t="n">
         <v>47.42</v>
       </c>
-      <c r="O52" s="13" t="n">
+      <c r="O52" s="9" t="n">
         <v>46.59</v>
       </c>
-      <c r="P52" s="13" t="n">
+      <c r="P52" s="9" t="n">
         <v>46.35</v>
       </c>
-      <c r="Q52" s="13" t="n">
+      <c r="Q52" s="9" t="n">
         <v>46.21</v>
       </c>
-      <c r="R52" s="13" t="n">
+      <c r="R52" s="9" t="n">
         <v>46.19</v>
       </c>
-      <c r="S52" s="13" t="n">
+      <c r="S52" s="9" t="n">
         <v>47.04</v>
       </c>
-      <c r="T52" s="13" t="n">
+      <c r="T52" s="9" t="n">
         <v>45.74</v>
       </c>
-      <c r="U52" s="13" t="n">
+      <c r="U52" s="9" t="n">
         <v>45.27</v>
       </c>
-      <c r="V52" s="13" t="n">
+      <c r="V52" s="9" t="n">
         <v>45.62</v>
       </c>
-      <c r="W52" s="13" t="n">
+      <c r="W52" s="9" t="n">
         <v>44.74</v>
       </c>
-      <c r="X52" s="13" t="n">
+      <c r="X52" s="9" t="n">
         <v>49.16</v>
       </c>
-      <c r="Y52" s="13" t="n">
+      <c r="Y52" s="9" t="n">
         <v>46.34</v>
       </c>
-      <c r="Z52" s="13" t="n">
+      <c r="Z52" s="9" t="n">
         <v>45.4</v>
       </c>
-      <c r="AA52" s="13" t="n">
+      <c r="AA52" s="9" t="n">
         <v>45.42</v>
       </c>
-      <c r="AB52" s="13" t="n">
+      <c r="AB52" s="9" t="n">
         <v>47.13</v>
       </c>
-      <c r="AC52" s="13" t="n">
+      <c r="AC52" s="9" t="n">
         <v>45.49</v>
       </c>
-      <c r="AD52" s="13" t="n">
+      <c r="AD52" s="9" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE52" s="13" t="n">
+      <c r="AE52" s="9" t="n">
         <v>46.79</v>
       </c>
-      <c r="AF52" s="13" t="n">
+      <c r="AF52" s="9" t="n">
         <v>47.06</v>
       </c>
-      <c r="AG52" s="13" t="n">
+      <c r="AG52" s="9" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH52" s="12" t="n">
+      <c r="AH52" s="9" t="n">
         <v>46.28</v>
       </c>
-      <c r="AI52" s="12" t="n">
+      <c r="AI52" s="9" t="n">
         <v>497.9</v>
       </c>
-      <c r="AJ52" s="12" t="inlineStr"/>
-      <c r="AK52" s="14" t="inlineStr"/>
+      <c r="AJ52" s="9" t="inlineStr"/>
+      <c r="AK52" s="10" t="inlineStr"/>
     </row>
     <row r="53"/>
     <row r="54"/>
@@ -5634,7 +5601,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5727,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK62" s="15" t="n"/>
+      <c r="AK62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5771,97 +5738,97 @@
       <c r="B63" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="6" t="n">
         <v>64.05</v>
       </c>
-      <c r="D63" s="7" t="n">
+      <c r="D63" s="6" t="n">
         <v>63.56</v>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" s="6" t="n">
         <v>64.08</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="6" t="n">
         <v>63.48</v>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="6" t="n">
         <v>64.12</v>
       </c>
-      <c r="H63" s="7" t="n">
+      <c r="H63" s="6" t="n">
         <v>64.53</v>
       </c>
-      <c r="I63" s="7" t="n">
+      <c r="I63" s="6" t="n">
         <v>64.03</v>
       </c>
-      <c r="J63" s="7" t="n">
+      <c r="J63" s="6" t="n">
         <v>63.8</v>
       </c>
-      <c r="K63" s="7" t="n">
+      <c r="K63" s="6" t="n">
         <v>63.63</v>
       </c>
-      <c r="L63" s="7" t="n">
+      <c r="L63" s="6" t="n">
         <v>63.38</v>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="6" t="n">
         <v>63.85</v>
       </c>
-      <c r="N63" s="7" t="n">
+      <c r="N63" s="6" t="n">
         <v>63.69</v>
       </c>
-      <c r="O63" s="7" t="n">
+      <c r="O63" s="6" t="n">
         <v>63.81</v>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P63" s="6" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="Q63" s="7" t="n">
+      <c r="Q63" s="6" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="R63" s="7" t="n">
+      <c r="R63" s="6" t="n">
         <v>63.94</v>
       </c>
-      <c r="S63" s="7" t="n">
+      <c r="S63" s="6" t="n">
         <v>62.96</v>
       </c>
-      <c r="T63" s="7" t="n">
+      <c r="T63" s="6" t="n">
         <v>62.88</v>
       </c>
-      <c r="U63" s="7" t="n">
+      <c r="U63" s="6" t="n">
         <v>62.7</v>
       </c>
-      <c r="V63" s="7" t="n">
+      <c r="V63" s="6" t="n">
         <v>62.84</v>
       </c>
-      <c r="W63" s="7" t="n">
+      <c r="W63" s="6" t="n">
         <v>62.69</v>
       </c>
-      <c r="X63" s="7" t="n">
+      <c r="X63" s="6" t="n">
         <v>62.51</v>
       </c>
-      <c r="Y63" s="7" t="n">
+      <c r="Y63" s="6" t="n">
         <v>62.42</v>
       </c>
-      <c r="Z63" s="7" t="n">
+      <c r="Z63" s="6" t="n">
         <v>63.88</v>
       </c>
-      <c r="AA63" s="7" t="n">
+      <c r="AA63" s="6" t="n">
         <v>63.6</v>
       </c>
-      <c r="AB63" s="7" t="n">
+      <c r="AB63" s="6" t="n">
         <v>64.08</v>
       </c>
-      <c r="AC63" s="7" t="n">
+      <c r="AC63" s="6" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="AD63" s="7" t="n">
+      <c r="AD63" s="6" t="n">
         <v>64.01000000000001</v>
       </c>
-      <c r="AE63" s="7" t="n">
+      <c r="AE63" s="6" t="n">
         <v>63.49</v>
       </c>
-      <c r="AF63" s="7" t="n">
+      <c r="AF63" s="6" t="n">
         <v>63.14</v>
       </c>
-      <c r="AG63" s="7" t="n">
+      <c r="AG63" s="6" t="n">
         <v>63.04</v>
       </c>
       <c r="AH63" s="6" t="n">
@@ -5869,7 +5836,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="16" t="n"/>
+      <c r="AK63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5880,97 +5847,97 @@
       <c r="B64" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C64" s="10" t="n">
+      <c r="C64" s="6" t="n">
         <v>37.2</v>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D64" s="6" t="n">
         <v>37.1</v>
       </c>
-      <c r="E64" s="10" t="n">
+      <c r="E64" s="6" t="n">
         <v>36.25</v>
       </c>
-      <c r="F64" s="10" t="n">
+      <c r="F64" s="6" t="n">
         <v>35.95</v>
       </c>
-      <c r="G64" s="10" t="n">
+      <c r="G64" s="6" t="n">
         <v>38.22</v>
       </c>
-      <c r="H64" s="10" t="n">
+      <c r="H64" s="6" t="n">
         <v>35.83</v>
       </c>
-      <c r="I64" s="10" t="n">
+      <c r="I64" s="6" t="n">
         <v>38.13</v>
       </c>
-      <c r="J64" s="10" t="n">
+      <c r="J64" s="6" t="n">
         <v>36.34</v>
       </c>
-      <c r="K64" s="10" t="n">
+      <c r="K64" s="6" t="n">
         <v>37.93</v>
       </c>
-      <c r="L64" s="10" t="n">
+      <c r="L64" s="6" t="n">
         <v>37.71</v>
       </c>
-      <c r="M64" s="10" t="n">
+      <c r="M64" s="6" t="n">
         <v>35.95</v>
       </c>
-      <c r="N64" s="10" t="n">
+      <c r="N64" s="6" t="n">
         <v>35.99</v>
       </c>
-      <c r="O64" s="10" t="n">
+      <c r="O64" s="6" t="n">
         <v>38.22</v>
       </c>
-      <c r="P64" s="10" t="n">
+      <c r="P64" s="6" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q64" s="10" t="n">
+      <c r="Q64" s="6" t="n">
         <v>37.15</v>
       </c>
-      <c r="R64" s="10" t="n">
+      <c r="R64" s="6" t="n">
         <v>37.29</v>
       </c>
-      <c r="S64" s="10" t="n">
+      <c r="S64" s="6" t="n">
         <v>38.9</v>
       </c>
-      <c r="T64" s="10" t="n">
+      <c r="T64" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="U64" s="10" t="n">
+      <c r="U64" s="6" t="n">
         <v>37.5</v>
       </c>
-      <c r="V64" s="10" t="n">
+      <c r="V64" s="6" t="n">
         <v>36.25</v>
       </c>
-      <c r="W64" s="10" t="n">
+      <c r="W64" s="6" t="n">
         <v>36.9</v>
       </c>
-      <c r="X64" s="10" t="n">
+      <c r="X64" s="6" t="n">
         <v>36.92</v>
       </c>
-      <c r="Y64" s="10" t="n">
+      <c r="Y64" s="6" t="n">
         <v>35.42</v>
       </c>
-      <c r="Z64" s="10" t="n">
+      <c r="Z64" s="6" t="n">
         <v>38.12</v>
       </c>
-      <c r="AA64" s="10" t="n">
+      <c r="AA64" s="6" t="n">
         <v>37.35</v>
       </c>
-      <c r="AB64" s="10" t="n">
+      <c r="AB64" s="6" t="n">
         <v>38.41</v>
       </c>
-      <c r="AC64" s="10" t="n">
+      <c r="AC64" s="6" t="n">
         <v>37.71</v>
       </c>
-      <c r="AD64" s="10" t="n">
+      <c r="AD64" s="6" t="n">
         <v>37.56</v>
       </c>
-      <c r="AE64" s="10" t="n">
+      <c r="AE64" s="6" t="n">
         <v>38.91</v>
       </c>
-      <c r="AF64" s="10" t="n">
+      <c r="AF64" s="6" t="n">
         <v>36.38</v>
       </c>
-      <c r="AG64" s="10" t="n">
+      <c r="AG64" s="6" t="n">
         <v>37.45</v>
       </c>
       <c r="AH64" s="6" t="n">
@@ -5978,7 +5945,7 @@
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="16" t="n"/>
+      <c r="AK64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5989,97 +5956,97 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C65" s="6" t="n">
         <v>39.7</v>
       </c>
-      <c r="D65" s="10" t="n">
+      <c r="D65" s="6" t="n">
         <v>37.34</v>
       </c>
-      <c r="E65" s="10" t="n">
+      <c r="E65" s="6" t="n">
         <v>38.12</v>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F65" s="6" t="n">
         <v>37.12</v>
       </c>
-      <c r="G65" s="10" t="n">
+      <c r="G65" s="6" t="n">
         <v>38.33</v>
       </c>
-      <c r="H65" s="10" t="n">
+      <c r="H65" s="6" t="n">
         <v>39.69</v>
       </c>
-      <c r="I65" s="10" t="n">
+      <c r="I65" s="6" t="n">
         <v>42.09</v>
       </c>
-      <c r="J65" s="10" t="n">
+      <c r="J65" s="6" t="n">
         <v>42.04</v>
       </c>
-      <c r="K65" s="10" t="n">
+      <c r="K65" s="6" t="n">
         <v>38.28</v>
       </c>
-      <c r="L65" s="10" t="n">
+      <c r="L65" s="6" t="n">
         <v>41.34</v>
       </c>
-      <c r="M65" s="10" t="n">
+      <c r="M65" s="6" t="n">
         <v>41.94</v>
       </c>
-      <c r="N65" s="10" t="n">
+      <c r="N65" s="6" t="n">
         <v>40.49</v>
       </c>
-      <c r="O65" s="10" t="n">
+      <c r="O65" s="6" t="n">
         <v>38.61</v>
       </c>
-      <c r="P65" s="10" t="n">
+      <c r="P65" s="6" t="n">
         <v>37.79</v>
       </c>
-      <c r="Q65" s="10" t="n">
+      <c r="Q65" s="6" t="n">
         <v>37.79</v>
       </c>
-      <c r="R65" s="10" t="n">
+      <c r="R65" s="6" t="n">
         <v>36.92</v>
       </c>
-      <c r="S65" s="10" t="n">
+      <c r="S65" s="6" t="n">
         <v>38.35</v>
       </c>
-      <c r="T65" s="10" t="n">
+      <c r="T65" s="6" t="n">
         <v>36.67</v>
       </c>
-      <c r="U65" s="10" t="n">
+      <c r="U65" s="6" t="n">
         <v>36.88</v>
       </c>
-      <c r="V65" s="10" t="n">
+      <c r="V65" s="6" t="n">
         <v>37.59</v>
       </c>
-      <c r="W65" s="10" t="n">
+      <c r="W65" s="6" t="n">
         <v>37.49</v>
       </c>
-      <c r="X65" s="10" t="n">
+      <c r="X65" s="6" t="n">
         <v>40.59</v>
       </c>
-      <c r="Y65" s="10" t="n">
+      <c r="Y65" s="6" t="n">
         <v>42.94</v>
       </c>
-      <c r="Z65" s="10" t="n">
+      <c r="Z65" s="6" t="n">
         <v>38.3</v>
       </c>
-      <c r="AA65" s="10" t="n">
+      <c r="AA65" s="6" t="n">
         <v>36.58</v>
       </c>
-      <c r="AB65" s="9" t="n">
+      <c r="AB65" s="6" t="n">
         <v>43.08</v>
       </c>
-      <c r="AC65" s="10" t="n">
+      <c r="AC65" s="6" t="n">
         <v>39.4</v>
       </c>
-      <c r="AD65" s="10" t="n">
+      <c r="AD65" s="6" t="n">
         <v>37.41</v>
       </c>
-      <c r="AE65" s="10" t="n">
+      <c r="AE65" s="6" t="n">
         <v>37.99</v>
       </c>
-      <c r="AF65" s="10" t="n">
+      <c r="AF65" s="6" t="n">
         <v>41.21</v>
       </c>
-      <c r="AG65" s="10" t="n">
+      <c r="AG65" s="6" t="n">
         <v>37.2</v>
       </c>
       <c r="AH65" s="6" t="n">
@@ -6087,7 +6054,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="16" t="n"/>
+      <c r="AK65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6098,97 +6065,97 @@
       <c r="B66" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="6" t="n">
         <v>77.92</v>
       </c>
-      <c r="D66" s="7" t="n">
+      <c r="D66" s="6" t="n">
         <v>77.51000000000001</v>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E66" s="6" t="n">
         <v>77.88</v>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="6" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="6" t="n">
         <v>77.39</v>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H66" s="6" t="n">
         <v>77.95</v>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="I66" s="6" t="n">
         <v>77.47</v>
       </c>
-      <c r="J66" s="7" t="n">
+      <c r="J66" s="6" t="n">
         <v>77.65000000000001</v>
       </c>
-      <c r="K66" s="7" t="n">
+      <c r="K66" s="6" t="n">
         <v>77.83</v>
       </c>
-      <c r="L66" s="7" t="n">
+      <c r="L66" s="6" t="n">
         <v>77.78</v>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="6" t="n">
         <v>77.59</v>
       </c>
-      <c r="N66" s="7" t="n">
+      <c r="N66" s="6" t="n">
         <v>77.76000000000001</v>
       </c>
-      <c r="O66" s="7" t="n">
+      <c r="O66" s="6" t="n">
         <v>77.22</v>
       </c>
-      <c r="P66" s="7" t="n">
+      <c r="P66" s="6" t="n">
         <v>77.45</v>
       </c>
-      <c r="Q66" s="7" t="n">
+      <c r="Q66" s="6" t="n">
         <v>77.72</v>
       </c>
-      <c r="R66" s="7" t="n">
+      <c r="R66" s="6" t="n">
         <v>77.34</v>
       </c>
-      <c r="S66" s="7" t="n">
+      <c r="S66" s="6" t="n">
         <v>77.19</v>
       </c>
-      <c r="T66" s="7" t="n">
+      <c r="T66" s="6" t="n">
         <v>77.66</v>
       </c>
-      <c r="U66" s="7" t="n">
+      <c r="U66" s="6" t="n">
         <v>77.62</v>
       </c>
-      <c r="V66" s="7" t="n">
+      <c r="V66" s="6" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="W66" s="7" t="n">
+      <c r="W66" s="6" t="n">
         <v>77.11</v>
       </c>
-      <c r="X66" s="7" t="n">
+      <c r="X66" s="6" t="n">
         <v>76.81</v>
       </c>
-      <c r="Y66" s="7" t="n">
+      <c r="Y66" s="6" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="Z66" s="7" t="n">
+      <c r="Z66" s="6" t="n">
         <v>77.7</v>
       </c>
-      <c r="AA66" s="7" t="n">
+      <c r="AA66" s="6" t="n">
         <v>77.28</v>
       </c>
-      <c r="AB66" s="7" t="n">
+      <c r="AB66" s="6" t="n">
         <v>77.31</v>
       </c>
-      <c r="AC66" s="7" t="n">
+      <c r="AC66" s="6" t="n">
         <v>77.28</v>
       </c>
-      <c r="AD66" s="7" t="n">
+      <c r="AD66" s="6" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="AE66" s="7" t="n">
+      <c r="AE66" s="6" t="n">
         <v>77.23</v>
       </c>
-      <c r="AF66" s="7" t="n">
+      <c r="AF66" s="6" t="n">
         <v>77.73999999999999</v>
       </c>
-      <c r="AG66" s="7" t="n">
+      <c r="AG66" s="6" t="n">
         <v>77.44</v>
       </c>
       <c r="AH66" s="6" t="n">
@@ -6196,7 +6163,7 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="16" t="n"/>
+      <c r="AK66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6207,97 +6174,97 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C67" s="6" t="n">
         <v>40.3</v>
       </c>
-      <c r="D67" s="10" t="n">
+      <c r="D67" s="6" t="n">
         <v>41.59</v>
       </c>
-      <c r="E67" s="10" t="n">
+      <c r="E67" s="6" t="n">
         <v>38.95</v>
       </c>
-      <c r="F67" s="10" t="n">
+      <c r="F67" s="6" t="n">
         <v>40.75</v>
       </c>
-      <c r="G67" s="10" t="n">
+      <c r="G67" s="6" t="n">
         <v>41.29</v>
       </c>
-      <c r="H67" s="10" t="n">
+      <c r="H67" s="6" t="n">
         <v>40.61</v>
       </c>
-      <c r="I67" s="10" t="n">
+      <c r="I67" s="6" t="n">
         <v>40.69</v>
       </c>
-      <c r="J67" s="9" t="n">
+      <c r="J67" s="6" t="n">
         <v>43.48</v>
       </c>
-      <c r="K67" s="10" t="n">
+      <c r="K67" s="6" t="n">
         <v>41.87</v>
       </c>
-      <c r="L67" s="10" t="n">
+      <c r="L67" s="6" t="n">
         <v>41.22</v>
       </c>
-      <c r="M67" s="10" t="n">
+      <c r="M67" s="6" t="n">
         <v>40.41</v>
       </c>
-      <c r="N67" s="10" t="n">
+      <c r="N67" s="6" t="n">
         <v>41.46</v>
       </c>
-      <c r="O67" s="10" t="n">
+      <c r="O67" s="6" t="n">
         <v>40.07</v>
       </c>
-      <c r="P67" s="10" t="n">
+      <c r="P67" s="6" t="n">
         <v>40.54</v>
       </c>
-      <c r="Q67" s="10" t="n">
+      <c r="Q67" s="6" t="n">
         <v>40.48</v>
       </c>
-      <c r="R67" s="10" t="n">
+      <c r="R67" s="6" t="n">
         <v>41.38</v>
       </c>
-      <c r="S67" s="10" t="n">
+      <c r="S67" s="6" t="n">
         <v>41.15</v>
       </c>
-      <c r="T67" s="10" t="n">
+      <c r="T67" s="6" t="n">
         <v>39.41</v>
       </c>
-      <c r="U67" s="10" t="n">
+      <c r="U67" s="6" t="n">
         <v>39.12</v>
       </c>
-      <c r="V67" s="10" t="n">
+      <c r="V67" s="6" t="n">
         <v>40.48</v>
       </c>
-      <c r="W67" s="10" t="n">
+      <c r="W67" s="6" t="n">
         <v>40.44</v>
       </c>
-      <c r="X67" s="10" t="n">
+      <c r="X67" s="6" t="n">
         <v>40.11</v>
       </c>
-      <c r="Y67" s="10" t="n">
+      <c r="Y67" s="6" t="n">
         <v>38.81</v>
       </c>
-      <c r="Z67" s="10" t="n">
+      <c r="Z67" s="6" t="n">
         <v>40.83</v>
       </c>
-      <c r="AA67" s="10" t="n">
+      <c r="AA67" s="6" t="n">
         <v>39.05</v>
       </c>
-      <c r="AB67" s="10" t="n">
+      <c r="AB67" s="6" t="n">
         <v>39.54</v>
       </c>
-      <c r="AC67" s="10" t="n">
+      <c r="AC67" s="6" t="n">
         <v>38.81</v>
       </c>
-      <c r="AD67" s="10" t="n">
+      <c r="AD67" s="6" t="n">
         <v>39.5</v>
       </c>
-      <c r="AE67" s="10" t="n">
+      <c r="AE67" s="6" t="n">
         <v>40.44</v>
       </c>
-      <c r="AF67" s="10" t="n">
+      <c r="AF67" s="6" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG67" s="10" t="n">
+      <c r="AG67" s="6" t="n">
         <v>39.62</v>
       </c>
       <c r="AH67" s="6" t="n">
@@ -6305,7 +6272,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="16" t="n"/>
+      <c r="AK67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6316,97 +6283,97 @@
       <c r="B68" s="6" t="n">
         <v>199.25</v>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="6" t="n">
         <v>77.72</v>
       </c>
-      <c r="D68" s="7" t="n">
+      <c r="D68" s="6" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E68" s="6" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="6" t="n">
         <v>78.12</v>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="6" t="n">
         <v>78.11</v>
       </c>
-      <c r="H68" s="7" t="n">
+      <c r="H68" s="6" t="n">
         <v>78.5</v>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="I68" s="6" t="n">
         <v>78.06</v>
       </c>
-      <c r="J68" s="7" t="n">
+      <c r="J68" s="6" t="n">
         <v>78.15000000000001</v>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="K68" s="6" t="n">
         <v>78.7</v>
       </c>
-      <c r="L68" s="7" t="n">
+      <c r="L68" s="6" t="n">
         <v>78.45</v>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="6" t="n">
         <v>78.76000000000001</v>
       </c>
-      <c r="N68" s="7" t="n">
+      <c r="N68" s="6" t="n">
         <v>78.95</v>
       </c>
-      <c r="O68" s="7" t="n">
+      <c r="O68" s="6" t="n">
         <v>77.97</v>
       </c>
-      <c r="P68" s="7" t="n">
+      <c r="P68" s="6" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="Q68" s="7" t="n">
+      <c r="Q68" s="6" t="n">
         <v>78.45999999999999</v>
       </c>
-      <c r="R68" s="7" t="n">
+      <c r="R68" s="6" t="n">
         <v>78.12</v>
       </c>
-      <c r="S68" s="7" t="n">
+      <c r="S68" s="6" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="T68" s="7" t="n">
+      <c r="T68" s="6" t="n">
         <v>78.47</v>
       </c>
-      <c r="U68" s="7" t="n">
+      <c r="U68" s="6" t="n">
         <v>78.36</v>
       </c>
-      <c r="V68" s="7" t="n">
+      <c r="V68" s="6" t="n">
         <v>78.39</v>
       </c>
-      <c r="W68" s="7" t="n">
+      <c r="W68" s="6" t="n">
         <v>78.31</v>
       </c>
-      <c r="X68" s="7" t="n">
+      <c r="X68" s="6" t="n">
         <v>77.81999999999999</v>
       </c>
-      <c r="Y68" s="7" t="n">
+      <c r="Y68" s="6" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="Z68" s="7" t="n">
+      <c r="Z68" s="6" t="n">
         <v>78.55</v>
       </c>
-      <c r="AA68" s="7" t="n">
+      <c r="AA68" s="6" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="AB68" s="7" t="n">
+      <c r="AB68" s="6" t="n">
         <v>78.45</v>
       </c>
-      <c r="AC68" s="7" t="n">
+      <c r="AC68" s="6" t="n">
         <v>78.31</v>
       </c>
-      <c r="AD68" s="7" t="n">
+      <c r="AD68" s="6" t="n">
         <v>78.41</v>
       </c>
-      <c r="AE68" s="7" t="n">
+      <c r="AE68" s="6" t="n">
         <v>77.87</v>
       </c>
-      <c r="AF68" s="7" t="n">
+      <c r="AF68" s="6" t="n">
         <v>78.44</v>
       </c>
-      <c r="AG68" s="7" t="n">
+      <c r="AG68" s="6" t="n">
         <v>78.26000000000001</v>
       </c>
       <c r="AH68" s="6" t="n">
@@ -6414,7 +6381,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="16" t="n"/>
+      <c r="AK68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6425,97 +6392,97 @@
       <c r="B69" s="6" t="n">
         <v>211.25</v>
       </c>
-      <c r="C69" s="7" t="n">
+      <c r="C69" s="6" t="n">
         <v>72.53</v>
       </c>
-      <c r="D69" s="7" t="n">
+      <c r="D69" s="6" t="n">
         <v>72.84</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" s="6" t="n">
         <v>73.08</v>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F69" s="6" t="n">
         <v>72.03</v>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="6" t="n">
         <v>72.42</v>
       </c>
-      <c r="H69" s="7" t="n">
+      <c r="H69" s="6" t="n">
         <v>72.61</v>
       </c>
-      <c r="I69" s="7" t="n">
+      <c r="I69" s="6" t="n">
         <v>72.16</v>
       </c>
-      <c r="J69" s="7" t="n">
+      <c r="J69" s="6" t="n">
         <v>72.28</v>
       </c>
-      <c r="K69" s="7" t="n">
+      <c r="K69" s="6" t="n">
         <v>72.98</v>
       </c>
-      <c r="L69" s="7" t="n">
+      <c r="L69" s="6" t="n">
         <v>72.66</v>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="6" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="N69" s="7" t="n">
+      <c r="N69" s="6" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="O69" s="7" t="n">
+      <c r="O69" s="6" t="n">
         <v>71.54000000000001</v>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="P69" s="6" t="n">
         <v>72.36</v>
       </c>
-      <c r="Q69" s="7" t="n">
+      <c r="Q69" s="6" t="n">
         <v>72.65000000000001</v>
       </c>
-      <c r="R69" s="7" t="n">
+      <c r="R69" s="6" t="n">
         <v>72.38</v>
       </c>
-      <c r="S69" s="7" t="n">
+      <c r="S69" s="6" t="n">
         <v>72.12</v>
       </c>
-      <c r="T69" s="7" t="n">
+      <c r="T69" s="6" t="n">
         <v>72.94</v>
       </c>
-      <c r="U69" s="7" t="n">
+      <c r="U69" s="6" t="n">
         <v>72.81</v>
       </c>
-      <c r="V69" s="7" t="n">
+      <c r="V69" s="6" t="n">
         <v>72.56</v>
       </c>
-      <c r="W69" s="7" t="n">
+      <c r="W69" s="6" t="n">
         <v>72.27</v>
       </c>
-      <c r="X69" s="7" t="n">
+      <c r="X69" s="6" t="n">
         <v>72.03</v>
       </c>
-      <c r="Y69" s="7" t="n">
+      <c r="Y69" s="6" t="n">
         <v>72.51000000000001</v>
       </c>
-      <c r="Z69" s="7" t="n">
+      <c r="Z69" s="6" t="n">
         <v>72.88</v>
       </c>
-      <c r="AA69" s="7" t="n">
+      <c r="AA69" s="6" t="n">
         <v>72.31999999999999</v>
       </c>
-      <c r="AB69" s="7" t="n">
+      <c r="AB69" s="6" t="n">
         <v>72.3</v>
       </c>
-      <c r="AC69" s="7" t="n">
+      <c r="AC69" s="6" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="AD69" s="7" t="n">
+      <c r="AD69" s="6" t="n">
         <v>72.77</v>
       </c>
-      <c r="AE69" s="7" t="n">
+      <c r="AE69" s="6" t="n">
         <v>72.26000000000001</v>
       </c>
-      <c r="AF69" s="7" t="n">
+      <c r="AF69" s="6" t="n">
         <v>72.72</v>
       </c>
-      <c r="AG69" s="7" t="n">
+      <c r="AG69" s="6" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="AH69" s="6" t="n">
@@ -6523,7 +6490,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="16" t="n"/>
+      <c r="AK69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6534,97 +6501,97 @@
       <c r="B70" s="6" t="n">
         <v>549.25</v>
       </c>
-      <c r="C70" s="10" t="n">
+      <c r="C70" s="6" t="n">
         <v>31.82</v>
       </c>
-      <c r="D70" s="10" t="n">
+      <c r="D70" s="6" t="n">
         <v>34.01</v>
       </c>
-      <c r="E70" s="10" t="n">
+      <c r="E70" s="6" t="n">
         <v>31.3</v>
       </c>
-      <c r="F70" s="10" t="n">
+      <c r="F70" s="6" t="n">
         <v>31.78</v>
       </c>
-      <c r="G70" s="10" t="n">
+      <c r="G70" s="6" t="n">
         <v>31.44</v>
       </c>
-      <c r="H70" s="10" t="n">
+      <c r="H70" s="6" t="n">
         <v>31.81</v>
       </c>
-      <c r="I70" s="10" t="n">
+      <c r="I70" s="6" t="n">
         <v>31.13</v>
       </c>
-      <c r="J70" s="10" t="n">
+      <c r="J70" s="6" t="n">
         <v>32.33</v>
       </c>
-      <c r="K70" s="10" t="n">
+      <c r="K70" s="6" t="n">
         <v>31.17</v>
       </c>
-      <c r="L70" s="10" t="n">
+      <c r="L70" s="6" t="n">
         <v>30.91</v>
       </c>
-      <c r="M70" s="10" t="n">
+      <c r="M70" s="6" t="n">
         <v>31.56</v>
       </c>
-      <c r="N70" s="10" t="n">
+      <c r="N70" s="6" t="n">
         <v>31.3</v>
       </c>
-      <c r="O70" s="10" t="n">
+      <c r="O70" s="6" t="n">
         <v>31.59</v>
       </c>
-      <c r="P70" s="10" t="n">
+      <c r="P70" s="6" t="n">
         <v>31.9</v>
       </c>
-      <c r="Q70" s="10" t="n">
+      <c r="Q70" s="6" t="n">
         <v>31.52</v>
       </c>
-      <c r="R70" s="10" t="n">
+      <c r="R70" s="6" t="n">
         <v>31.22</v>
       </c>
-      <c r="S70" s="10" t="n">
+      <c r="S70" s="6" t="n">
         <v>31.62</v>
       </c>
-      <c r="T70" s="10" t="n">
+      <c r="T70" s="6" t="n">
         <v>31.62</v>
       </c>
-      <c r="U70" s="10" t="n">
+      <c r="U70" s="6" t="n">
         <v>31.75</v>
       </c>
-      <c r="V70" s="10" t="n">
+      <c r="V70" s="6" t="n">
         <v>32.01</v>
       </c>
-      <c r="W70" s="10" t="n">
+      <c r="W70" s="6" t="n">
         <v>32.09</v>
       </c>
-      <c r="X70" s="10" t="n">
+      <c r="X70" s="6" t="n">
         <v>32.17</v>
       </c>
-      <c r="Y70" s="10" t="n">
+      <c r="Y70" s="6" t="n">
         <v>31.41</v>
       </c>
-      <c r="Z70" s="10" t="n">
+      <c r="Z70" s="6" t="n">
         <v>31.92</v>
       </c>
-      <c r="AA70" s="10" t="n">
+      <c r="AA70" s="6" t="n">
         <v>34.1</v>
       </c>
-      <c r="AB70" s="10" t="n">
+      <c r="AB70" s="6" t="n">
         <v>31.28</v>
       </c>
-      <c r="AC70" s="10" t="n">
+      <c r="AC70" s="6" t="n">
         <v>31.6</v>
       </c>
-      <c r="AD70" s="10" t="n">
+      <c r="AD70" s="6" t="n">
         <v>32.31</v>
       </c>
-      <c r="AE70" s="10" t="n">
+      <c r="AE70" s="6" t="n">
         <v>32.11</v>
       </c>
-      <c r="AF70" s="10" t="n">
+      <c r="AF70" s="6" t="n">
         <v>31.26</v>
       </c>
-      <c r="AG70" s="10" t="n">
+      <c r="AG70" s="6" t="n">
         <v>32.11</v>
       </c>
       <c r="AH70" s="6" t="n">
@@ -6632,7 +6599,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="16" t="n"/>
+      <c r="AK70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6643,97 +6610,97 @@
       <c r="B71" s="6" t="n">
         <v>573.25</v>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C71" s="6" t="n">
         <v>30.1</v>
       </c>
-      <c r="D71" s="10" t="n">
+      <c r="D71" s="6" t="n">
         <v>31.2</v>
       </c>
-      <c r="E71" s="10" t="n">
+      <c r="E71" s="6" t="n">
         <v>29.72</v>
       </c>
-      <c r="F71" s="10" t="n">
+      <c r="F71" s="6" t="n">
         <v>30.8</v>
       </c>
-      <c r="G71" s="10" t="n">
+      <c r="G71" s="6" t="n">
         <v>31.7</v>
       </c>
-      <c r="H71" s="10" t="n">
+      <c r="H71" s="6" t="n">
         <v>29.91</v>
       </c>
-      <c r="I71" s="10" t="n">
+      <c r="I71" s="6" t="n">
         <v>30.73</v>
       </c>
-      <c r="J71" s="10" t="n">
+      <c r="J71" s="6" t="n">
         <v>34.14</v>
       </c>
-      <c r="K71" s="10" t="n">
+      <c r="K71" s="6" t="n">
         <v>30.47</v>
       </c>
-      <c r="L71" s="10" t="n">
+      <c r="L71" s="6" t="n">
         <v>32.12</v>
       </c>
-      <c r="M71" s="10" t="n">
+      <c r="M71" s="6" t="n">
         <v>29.9</v>
       </c>
-      <c r="N71" s="10" t="n">
+      <c r="N71" s="6" t="n">
         <v>30.12</v>
       </c>
-      <c r="O71" s="10" t="n">
+      <c r="O71" s="6" t="n">
         <v>29.56</v>
       </c>
-      <c r="P71" s="10" t="n">
+      <c r="P71" s="6" t="n">
         <v>30.11</v>
       </c>
-      <c r="Q71" s="10" t="n">
+      <c r="Q71" s="6" t="n">
         <v>31.05</v>
       </c>
-      <c r="R71" s="10" t="n">
+      <c r="R71" s="6" t="n">
         <v>29.82</v>
       </c>
-      <c r="S71" s="10" t="n">
+      <c r="S71" s="6" t="n">
         <v>30.34</v>
       </c>
-      <c r="T71" s="10" t="n">
+      <c r="T71" s="6" t="n">
         <v>29.44</v>
       </c>
-      <c r="U71" s="10" t="n">
+      <c r="U71" s="6" t="n">
         <v>29.68</v>
       </c>
-      <c r="V71" s="10" t="n">
+      <c r="V71" s="6" t="n">
         <v>29.7</v>
       </c>
-      <c r="W71" s="10" t="n">
+      <c r="W71" s="6" t="n">
         <v>29.73</v>
       </c>
-      <c r="X71" s="10" t="n">
+      <c r="X71" s="6" t="n">
         <v>31.34</v>
       </c>
-      <c r="Y71" s="10" t="n">
+      <c r="Y71" s="6" t="n">
         <v>34.96</v>
       </c>
-      <c r="Z71" s="10" t="n">
+      <c r="Z71" s="6" t="n">
         <v>29.62</v>
       </c>
-      <c r="AA71" s="10" t="n">
+      <c r="AA71" s="6" t="n">
         <v>29.48</v>
       </c>
-      <c r="AB71" s="10" t="n">
+      <c r="AB71" s="6" t="n">
         <v>29.66</v>
       </c>
-      <c r="AC71" s="10" t="n">
+      <c r="AC71" s="6" t="n">
         <v>29.65</v>
       </c>
-      <c r="AD71" s="10" t="n">
+      <c r="AD71" s="6" t="n">
         <v>29.81</v>
       </c>
-      <c r="AE71" s="10" t="n">
+      <c r="AE71" s="6" t="n">
         <v>29.57</v>
       </c>
-      <c r="AF71" s="10" t="n">
+      <c r="AF71" s="6" t="n">
         <v>29.62</v>
       </c>
-      <c r="AG71" s="10" t="n">
+      <c r="AG71" s="6" t="n">
         <v>32.01</v>
       </c>
       <c r="AH71" s="6" t="n">
@@ -6741,7 +6708,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="16" t="n"/>
+      <c r="AK71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6752,97 +6719,97 @@
       <c r="B72" s="6" t="n">
         <v>585.25</v>
       </c>
-      <c r="C72" s="10" t="n">
+      <c r="C72" s="6" t="n">
         <v>33.38</v>
       </c>
-      <c r="D72" s="10" t="n">
+      <c r="D72" s="6" t="n">
         <v>32.61</v>
       </c>
-      <c r="E72" s="10" t="n">
+      <c r="E72" s="6" t="n">
         <v>32.72</v>
       </c>
-      <c r="F72" s="10" t="n">
+      <c r="F72" s="6" t="n">
         <v>32.6</v>
       </c>
-      <c r="G72" s="10" t="n">
+      <c r="G72" s="6" t="n">
         <v>32.51</v>
       </c>
-      <c r="H72" s="10" t="n">
+      <c r="H72" s="6" t="n">
         <v>32.48</v>
       </c>
-      <c r="I72" s="10" t="n">
+      <c r="I72" s="6" t="n">
         <v>31.93</v>
       </c>
-      <c r="J72" s="10" t="n">
+      <c r="J72" s="6" t="n">
         <v>35.1</v>
       </c>
-      <c r="K72" s="10" t="n">
+      <c r="K72" s="6" t="n">
         <v>32.72</v>
       </c>
-      <c r="L72" s="10" t="n">
+      <c r="L72" s="6" t="n">
         <v>34.05</v>
       </c>
-      <c r="M72" s="10" t="n">
+      <c r="M72" s="6" t="n">
         <v>34.14</v>
       </c>
-      <c r="N72" s="10" t="n">
+      <c r="N72" s="6" t="n">
         <v>32.36</v>
       </c>
-      <c r="O72" s="10" t="n">
+      <c r="O72" s="6" t="n">
         <v>32.78</v>
       </c>
-      <c r="P72" s="10" t="n">
+      <c r="P72" s="6" t="n">
         <v>34.24</v>
       </c>
-      <c r="Q72" s="10" t="n">
+      <c r="Q72" s="6" t="n">
         <v>32.56</v>
       </c>
-      <c r="R72" s="10" t="n">
+      <c r="R72" s="6" t="n">
         <v>32.69</v>
       </c>
-      <c r="S72" s="10" t="n">
+      <c r="S72" s="6" t="n">
         <v>32.33</v>
       </c>
-      <c r="T72" s="10" t="n">
+      <c r="T72" s="6" t="n">
         <v>32.36</v>
       </c>
-      <c r="U72" s="10" t="n">
+      <c r="U72" s="6" t="n">
         <v>32.29</v>
       </c>
-      <c r="V72" s="10" t="n">
+      <c r="V72" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="W72" s="10" t="n">
+      <c r="W72" s="6" t="n">
         <v>32.46</v>
       </c>
-      <c r="X72" s="10" t="n">
+      <c r="X72" s="6" t="n">
         <v>31.89</v>
       </c>
-      <c r="Y72" s="10" t="n">
+      <c r="Y72" s="6" t="n">
         <v>32.44</v>
       </c>
-      <c r="Z72" s="10" t="n">
+      <c r="Z72" s="6" t="n">
         <v>31.9</v>
       </c>
-      <c r="AA72" s="10" t="n">
+      <c r="AA72" s="6" t="n">
         <v>32.17</v>
       </c>
-      <c r="AB72" s="10" t="n">
+      <c r="AB72" s="6" t="n">
         <v>33.28</v>
       </c>
-      <c r="AC72" s="10" t="n">
+      <c r="AC72" s="6" t="n">
         <v>32.95</v>
       </c>
-      <c r="AD72" s="10" t="n">
+      <c r="AD72" s="6" t="n">
         <v>32.63</v>
       </c>
-      <c r="AE72" s="10" t="n">
+      <c r="AE72" s="6" t="n">
         <v>32.53</v>
       </c>
-      <c r="AF72" s="10" t="n">
+      <c r="AF72" s="6" t="n">
         <v>32.38</v>
       </c>
-      <c r="AG72" s="10" t="n">
+      <c r="AG72" s="6" t="n">
         <v>32.41</v>
       </c>
       <c r="AH72" s="6" t="n">
@@ -6850,7 +6817,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="16" t="n"/>
+      <c r="AK72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6861,97 +6828,97 @@
       <c r="B73" s="6" t="n">
         <v>597.25</v>
       </c>
-      <c r="C73" s="7" t="n">
+      <c r="C73" s="6" t="n">
         <v>79.81999999999999</v>
       </c>
-      <c r="D73" s="7" t="n">
+      <c r="D73" s="6" t="n">
         <v>79.70999999999999</v>
       </c>
-      <c r="E73" s="7" t="n">
+      <c r="E73" s="6" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="F73" s="7" t="n">
+      <c r="F73" s="6" t="n">
         <v>79.84999999999999</v>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="G73" s="6" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="H73" s="7" t="n">
+      <c r="H73" s="6" t="n">
         <v>79.95</v>
       </c>
-      <c r="I73" s="7" t="n">
+      <c r="I73" s="6" t="n">
         <v>80.20999999999999</v>
       </c>
-      <c r="J73" s="7" t="n">
+      <c r="J73" s="6" t="n">
         <v>79.58</v>
       </c>
-      <c r="K73" s="7" t="n">
+      <c r="K73" s="6" t="n">
         <v>79.67</v>
       </c>
-      <c r="L73" s="7" t="n">
+      <c r="L73" s="6" t="n">
         <v>79.06</v>
       </c>
-      <c r="M73" s="7" t="n">
+      <c r="M73" s="6" t="n">
         <v>79.97</v>
       </c>
-      <c r="N73" s="7" t="n">
+      <c r="N73" s="6" t="n">
         <v>55.45</v>
       </c>
-      <c r="O73" s="7" t="n">
+      <c r="O73" s="6" t="n">
         <v>79.84999999999999</v>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="P73" s="6" t="n">
         <v>79.78</v>
       </c>
-      <c r="Q73" s="7" t="n">
+      <c r="Q73" s="6" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="R73" s="7" t="n">
+      <c r="R73" s="6" t="n">
         <v>79.95999999999999</v>
       </c>
-      <c r="S73" s="7" t="n">
+      <c r="S73" s="6" t="n">
         <v>79.34</v>
       </c>
-      <c r="T73" s="7" t="n">
+      <c r="T73" s="6" t="n">
         <v>78.88</v>
       </c>
-      <c r="U73" s="7" t="n">
+      <c r="U73" s="6" t="n">
         <v>79.08</v>
       </c>
-      <c r="V73" s="7" t="n">
+      <c r="V73" s="6" t="n">
         <v>79.84</v>
       </c>
-      <c r="W73" s="7" t="n">
+      <c r="W73" s="6" t="n">
         <v>79.31</v>
       </c>
-      <c r="X73" s="7" t="n">
+      <c r="X73" s="6" t="n">
         <v>80.03</v>
       </c>
-      <c r="Y73" s="7" t="n">
+      <c r="Y73" s="6" t="n">
         <v>79.94</v>
       </c>
-      <c r="Z73" s="7" t="n">
+      <c r="Z73" s="6" t="n">
         <v>80.08</v>
       </c>
-      <c r="AA73" s="7" t="n">
+      <c r="AA73" s="6" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="AB73" s="7" t="n">
+      <c r="AB73" s="6" t="n">
         <v>79.20999999999999</v>
       </c>
-      <c r="AC73" s="7" t="n">
+      <c r="AC73" s="6" t="n">
         <v>79.62</v>
       </c>
-      <c r="AD73" s="7" t="n">
+      <c r="AD73" s="6" t="n">
         <v>80.29000000000001</v>
       </c>
-      <c r="AE73" s="7" t="n">
+      <c r="AE73" s="6" t="n">
         <v>80.06</v>
       </c>
-      <c r="AF73" s="7" t="n">
+      <c r="AF73" s="6" t="n">
         <v>79.29000000000001</v>
       </c>
-      <c r="AG73" s="7" t="n">
+      <c r="AG73" s="6" t="n">
         <v>79.79000000000001</v>
       </c>
       <c r="AH73" s="6" t="n">
@@ -6959,7 +6926,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="16" t="n"/>
+      <c r="AK73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6970,97 +6937,97 @@
       <c r="B74" s="6" t="n">
         <v>621.25</v>
       </c>
-      <c r="C74" s="10" t="n">
+      <c r="C74" s="6" t="n">
         <v>30.32</v>
       </c>
-      <c r="D74" s="10" t="n">
+      <c r="D74" s="6" t="n">
         <v>30.3</v>
       </c>
-      <c r="E74" s="10" t="n">
+      <c r="E74" s="6" t="n">
         <v>30.2</v>
       </c>
-      <c r="F74" s="10" t="n">
+      <c r="F74" s="6" t="n">
         <v>29.75</v>
       </c>
-      <c r="G74" s="10" t="n">
+      <c r="G74" s="6" t="n">
         <v>29.9</v>
       </c>
-      <c r="H74" s="10" t="n">
+      <c r="H74" s="6" t="n">
         <v>29.98</v>
       </c>
-      <c r="I74" s="10" t="n">
+      <c r="I74" s="6" t="n">
         <v>29.66</v>
       </c>
-      <c r="J74" s="10" t="n">
+      <c r="J74" s="6" t="n">
         <v>29.84</v>
       </c>
-      <c r="K74" s="10" t="n">
+      <c r="K74" s="6" t="n">
         <v>30.35</v>
       </c>
-      <c r="L74" s="10" t="n">
+      <c r="L74" s="6" t="n">
         <v>33.02</v>
       </c>
-      <c r="M74" s="10" t="n">
+      <c r="M74" s="6" t="n">
         <v>30.01</v>
       </c>
-      <c r="N74" s="10" t="n">
+      <c r="N74" s="6" t="n">
         <v>29.79</v>
       </c>
-      <c r="O74" s="10" t="n">
+      <c r="O74" s="6" t="n">
         <v>32.08</v>
       </c>
-      <c r="P74" s="10" t="n">
+      <c r="P74" s="6" t="n">
         <v>30.26</v>
       </c>
-      <c r="Q74" s="10" t="n">
+      <c r="Q74" s="6" t="n">
         <v>30.26</v>
       </c>
-      <c r="R74" s="10" t="n">
+      <c r="R74" s="6" t="n">
         <v>29.52</v>
       </c>
-      <c r="S74" s="10" t="n">
+      <c r="S74" s="6" t="n">
         <v>30.26</v>
       </c>
-      <c r="T74" s="10" t="n">
+      <c r="T74" s="6" t="n">
         <v>29.72</v>
       </c>
-      <c r="U74" s="10" t="n">
+      <c r="U74" s="6" t="n">
         <v>31.64</v>
       </c>
-      <c r="V74" s="10" t="n">
+      <c r="V74" s="6" t="n">
         <v>29.29</v>
       </c>
-      <c r="W74" s="10" t="n">
+      <c r="W74" s="6" t="n">
         <v>29.83</v>
       </c>
-      <c r="X74" s="10" t="n">
+      <c r="X74" s="6" t="n">
         <v>30.21</v>
       </c>
-      <c r="Y74" s="10" t="n">
+      <c r="Y74" s="6" t="n">
         <v>31.16</v>
       </c>
-      <c r="Z74" s="10" t="n">
+      <c r="Z74" s="6" t="n">
         <v>29.88</v>
       </c>
-      <c r="AA74" s="10" t="n">
+      <c r="AA74" s="6" t="n">
         <v>33.85</v>
       </c>
-      <c r="AB74" s="10" t="n">
+      <c r="AB74" s="6" t="n">
         <v>29.26</v>
       </c>
-      <c r="AC74" s="10" t="n">
+      <c r="AC74" s="6" t="n">
         <v>31.25</v>
       </c>
-      <c r="AD74" s="10" t="n">
+      <c r="AD74" s="6" t="n">
         <v>30.8</v>
       </c>
-      <c r="AE74" s="10" t="n">
+      <c r="AE74" s="6" t="n">
         <v>29.49</v>
       </c>
-      <c r="AF74" s="10" t="n">
+      <c r="AF74" s="6" t="n">
         <v>30.38</v>
       </c>
-      <c r="AG74" s="10" t="n">
+      <c r="AG74" s="6" t="n">
         <v>30.25</v>
       </c>
       <c r="AH74" s="6" t="n">
@@ -7068,116 +7035,116 @@
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="16" t="n"/>
+      <c r="AK74" s="12" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="9" t="n">
         <v>633.25</v>
       </c>
-      <c r="C75" s="17" t="n">
+      <c r="C75" s="9" t="n">
         <v>29.02</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="9" t="n">
         <v>30.64</v>
       </c>
-      <c r="E75" s="17" t="n">
+      <c r="E75" s="9" t="n">
         <v>28.75</v>
       </c>
-      <c r="F75" s="17" t="n">
+      <c r="F75" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="G75" s="17" t="n">
+      <c r="G75" s="9" t="n">
         <v>29.96</v>
       </c>
-      <c r="H75" s="17" t="n">
+      <c r="H75" s="9" t="n">
         <v>29.38</v>
       </c>
-      <c r="I75" s="17" t="n">
+      <c r="I75" s="9" t="n">
         <v>28.91</v>
       </c>
-      <c r="J75" s="17" t="n">
+      <c r="J75" s="9" t="n">
         <v>29.28</v>
       </c>
-      <c r="K75" s="17" t="n">
+      <c r="K75" s="9" t="n">
         <v>30.2</v>
       </c>
-      <c r="L75" s="17" t="n">
+      <c r="L75" s="9" t="n">
         <v>30.12</v>
       </c>
-      <c r="M75" s="17" t="n">
+      <c r="M75" s="9" t="n">
         <v>31.44</v>
       </c>
-      <c r="N75" s="17" t="n">
+      <c r="N75" s="9" t="n">
         <v>29.04</v>
       </c>
-      <c r="O75" s="17" t="n">
+      <c r="O75" s="9" t="n">
         <v>29.02</v>
       </c>
-      <c r="P75" s="17" t="n">
+      <c r="P75" s="9" t="n">
         <v>29.38</v>
       </c>
-      <c r="Q75" s="17" t="n">
+      <c r="Q75" s="9" t="n">
         <v>29.29</v>
       </c>
-      <c r="R75" s="17" t="n">
+      <c r="R75" s="9" t="n">
         <v>29.71</v>
       </c>
-      <c r="S75" s="17" t="n">
+      <c r="S75" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="T75" s="17" t="n">
+      <c r="T75" s="9" t="n">
         <v>29.38</v>
       </c>
-      <c r="U75" s="17" t="n">
+      <c r="U75" s="9" t="n">
         <v>29.78</v>
       </c>
-      <c r="V75" s="17" t="n">
+      <c r="V75" s="9" t="n">
         <v>29.85</v>
       </c>
-      <c r="W75" s="17" t="n">
+      <c r="W75" s="9" t="n">
         <v>29.16</v>
       </c>
-      <c r="X75" s="17" t="n">
+      <c r="X75" s="9" t="n">
         <v>29.29</v>
       </c>
-      <c r="Y75" s="17" t="n">
+      <c r="Y75" s="9" t="n">
         <v>29.48</v>
       </c>
-      <c r="Z75" s="17" t="n">
+      <c r="Z75" s="9" t="n">
         <v>37.17</v>
       </c>
-      <c r="AA75" s="17" t="n">
+      <c r="AA75" s="9" t="n">
         <v>28.92</v>
       </c>
-      <c r="AB75" s="17" t="n">
+      <c r="AB75" s="9" t="n">
         <v>31.6</v>
       </c>
-      <c r="AC75" s="17" t="n">
+      <c r="AC75" s="9" t="n">
         <v>30.51</v>
       </c>
-      <c r="AD75" s="17" t="n">
+      <c r="AD75" s="9" t="n">
         <v>29.07</v>
       </c>
-      <c r="AE75" s="17" t="n">
+      <c r="AE75" s="9" t="n">
         <v>28.94</v>
       </c>
-      <c r="AF75" s="17" t="n">
+      <c r="AF75" s="9" t="n">
         <v>29.25</v>
       </c>
-      <c r="AG75" s="17" t="n">
+      <c r="AG75" s="9" t="n">
         <v>29.59</v>
       </c>
-      <c r="AH75" s="12" t="n">
+      <c r="AH75" s="9" t="n">
         <v>29.84</v>
       </c>
-      <c r="AI75" s="12" t="inlineStr"/>
-      <c r="AJ75" s="12" t="inlineStr"/>
-      <c r="AK75" s="18" t="n"/>
+      <c r="AI75" s="9" t="inlineStr"/>
+      <c r="AJ75" s="9" t="inlineStr"/>
+      <c r="AK75" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFD9BCB"/>
         <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6666"/>
+        <bgColor rgb="FFFF6666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,6 +206,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -210,6 +228,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1027,14 +1048,14 @@
       <c r="AG11" s="7" t="n">
         <v>71.29000000000001</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="8" t="n">
         <v>70.81</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="9" t="n">
         <v>244.66</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1138,14 +1159,14 @@
       <c r="AG12" s="7" t="n">
         <v>72.84</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="8" t="n">
         <v>72.27</v>
       </c>
       <c r="AI12" s="6" t="n">
         <v>160.6</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1249,14 +1270,14 @@
       <c r="AG13" s="7" t="n">
         <v>70.06999999999999</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="8" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="9" t="n">
         <v>200.59</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1306,7 +1327,7 @@
       <c r="O14" s="7" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="11" t="n">
         <v>51.91</v>
       </c>
       <c r="Q14" s="7" t="n">
@@ -1360,14 +1381,14 @@
       <c r="AG14" s="7" t="n">
         <v>68.75</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="8" t="n">
         <v>66.97</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="9" t="n">
         <v>265.65</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1471,14 +1492,14 @@
       <c r="AG15" s="7" t="n">
         <v>75.70999999999999</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="8" t="n">
         <v>75.67</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="9" t="n">
         <v>229.65</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1582,14 +1603,14 @@
       <c r="AG16" s="7" t="n">
         <v>68.09</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="8" t="n">
         <v>67.72</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="9" t="n">
         <v>428.49</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1693,14 +1714,14 @@
       <c r="AG17" s="7" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="8" t="n">
         <v>70.15000000000001</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="9" t="n">
         <v>388.85</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1711,107 +1732,107 @@
       <c r="B18" s="6" t="n">
         <v>91.5</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="11" t="n">
         <v>52.72</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="11" t="n">
         <v>50.06</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>58.76</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="11" t="n">
         <v>50.41</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="11" t="n">
         <v>46.62</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="11" t="n">
         <v>49.69</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="11" t="n">
         <v>50.71</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="11" t="n">
         <v>48.24</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="11" t="n">
         <v>50.75</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="11" t="n">
         <v>50.51</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="11" t="n">
         <v>52.76</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="11" t="n">
         <v>51.64</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="11" t="n">
         <v>48.68</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" s="11" t="n">
         <v>49.17</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="11" t="n">
         <v>53.33</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="11" t="n">
         <v>50.15</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="11" t="n">
         <v>48.7</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="11" t="n">
         <v>49.26</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="11" t="n">
         <v>47.96</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="11" t="n">
         <v>47.53</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="11" t="n">
         <v>49.54</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" s="11" t="n">
         <v>49.93</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="11" t="n">
         <v>52.67</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="Z18" s="11" t="n">
         <v>48.81</v>
       </c>
-      <c r="AA18" s="9" t="n">
+      <c r="AA18" s="11" t="n">
         <v>48.32</v>
       </c>
-      <c r="AB18" s="9" t="n">
+      <c r="AB18" s="11" t="n">
         <v>49.61</v>
       </c>
-      <c r="AC18" s="9" t="n">
+      <c r="AC18" s="11" t="n">
         <v>49.47</v>
       </c>
-      <c r="AD18" s="9" t="n">
+      <c r="AD18" s="11" t="n">
         <v>47.34</v>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AE18" s="11" t="n">
         <v>49.9</v>
       </c>
-      <c r="AF18" s="9" t="n">
+      <c r="AF18" s="11" t="n">
         <v>52.66</v>
       </c>
-      <c r="AG18" s="9" t="n">
+      <c r="AG18" s="11" t="n">
         <v>51.71</v>
       </c>
       <c r="AH18" s="6" t="n">
         <v>50.25</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="9" t="n">
         <v>499.47</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1915,14 +1936,14 @@
       <c r="AG19" s="7" t="n">
         <v>67.03</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH19" s="8" t="n">
         <v>67.31</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="9" t="n">
         <v>315.82</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2026,14 +2047,14 @@
       <c r="AG20" s="7" t="n">
         <v>58.85</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="8" t="n">
         <v>60.42</v>
       </c>
-      <c r="AI20" s="6" t="n">
+      <c r="AI20" s="9" t="n">
         <v>478.59</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2119,10 +2140,10 @@
       <c r="AA21" s="7" t="n">
         <v>62.14</v>
       </c>
-      <c r="AB21" s="9" t="n">
+      <c r="AB21" s="11" t="n">
         <v>48.92</v>
       </c>
-      <c r="AC21" s="10" t="n">
+      <c r="AC21" s="12" t="n">
         <v>42.56</v>
       </c>
       <c r="AD21" s="7" t="n">
@@ -2137,14 +2158,14 @@
       <c r="AG21" s="7" t="n">
         <v>66.41</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="8" t="n">
         <v>63.62</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="9" t="n">
         <v>349.62</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2215,7 +2236,7 @@
       <c r="V22" s="7" t="n">
         <v>56.63</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="11" t="n">
         <v>53.21</v>
       </c>
       <c r="X22" s="7" t="n">
@@ -2233,29 +2254,29 @@
       <c r="AB22" s="7" t="n">
         <v>56.89</v>
       </c>
-      <c r="AC22" s="9" t="n">
+      <c r="AC22" s="11" t="n">
         <v>51.04</v>
       </c>
-      <c r="AD22" s="9" t="n">
+      <c r="AD22" s="11" t="n">
         <v>45.58</v>
       </c>
-      <c r="AE22" s="9" t="n">
+      <c r="AE22" s="11" t="n">
         <v>45.66</v>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AF22" s="11" t="n">
         <v>48.05</v>
       </c>
-      <c r="AG22" s="9" t="n">
+      <c r="AG22" s="11" t="n">
         <v>47.09</v>
       </c>
       <c r="AH22" s="6" t="n">
         <v>56.95</v>
       </c>
-      <c r="AI22" s="6" t="n">
+      <c r="AI22" s="9" t="n">
         <v>386.51</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2359,14 +2380,14 @@
       <c r="AG23" s="7" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="8" t="n">
         <v>66.53</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="9" t="n">
         <v>219.15</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2470,14 +2491,14 @@
       <c r="AG24" s="7" t="n">
         <v>64.79000000000001</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="8" t="n">
         <v>64.73999999999999</v>
       </c>
-      <c r="AI24" s="6" t="n">
+      <c r="AI24" s="9" t="n">
         <v>226.77</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2581,14 +2602,14 @@
       <c r="AG25" s="7" t="n">
         <v>69.81</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH25" s="8" t="n">
         <v>68.48</v>
       </c>
       <c r="AI25" s="6" t="n">
         <v>123.83</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2692,14 +2713,14 @@
       <c r="AG26" s="7" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="8" t="n">
         <v>73.31</v>
       </c>
-      <c r="AI26" s="6" t="n">
+      <c r="AI26" s="9" t="n">
         <v>223.97</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2716,7 +2737,7 @@
       <c r="D27" s="7" t="n">
         <v>60.51</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="11" t="n">
         <v>52.24</v>
       </c>
       <c r="F27" s="7" t="n">
@@ -2806,11 +2827,11 @@
       <c r="AH27" s="6" t="n">
         <v>59.85</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="9" t="n">
         <v>431.6</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2914,14 +2935,14 @@
       <c r="AG28" s="7" t="n">
         <v>63.46</v>
       </c>
-      <c r="AH28" s="6" t="n">
+      <c r="AH28" s="8" t="n">
         <v>62.51</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="9" t="n">
         <v>478.51</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3025,14 +3046,14 @@
       <c r="AG29" s="7" t="n">
         <v>70.56</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH29" s="8" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="9" t="n">
         <v>258.64</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3136,14 +3157,14 @@
       <c r="AG30" s="7" t="n">
         <v>69.2</v>
       </c>
-      <c r="AH30" s="6" t="n">
+      <c r="AH30" s="8" t="n">
         <v>68.58</v>
       </c>
-      <c r="AI30" s="6" t="n">
+      <c r="AI30" s="9" t="n">
         <v>254.74</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3154,107 +3175,107 @@
       <c r="B31" s="6" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="11" t="n">
         <v>49.18</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="12" t="n">
         <v>38.17</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="12" t="n">
         <v>39.78</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="11" t="n">
         <v>48.22</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="11" t="n">
         <v>45.28</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="11" t="n">
         <v>47.22</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="11" t="n">
         <v>47.81</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="11" t="n">
         <v>46.02</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="11" t="n">
         <v>47.37</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="11" t="n">
         <v>45.26</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="11" t="n">
         <v>49.09</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="11" t="n">
         <v>47.71</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="P31" s="11" t="n">
         <v>53.23</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="11" t="n">
         <v>43.31</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="12" t="n">
         <v>42.73</v>
       </c>
-      <c r="S31" s="10" t="n">
+      <c r="S31" s="12" t="n">
         <v>36.38</v>
       </c>
-      <c r="T31" s="10" t="n">
+      <c r="T31" s="12" t="n">
         <v>42.77</v>
       </c>
-      <c r="U31" s="10" t="n">
+      <c r="U31" s="12" t="n">
         <v>40.38</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="11" t="n">
         <v>44.49</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="11" t="n">
         <v>45.69</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X31" s="11" t="n">
         <v>45.4</v>
       </c>
-      <c r="Y31" s="10" t="n">
+      <c r="Y31" s="12" t="n">
         <v>40.74</v>
       </c>
-      <c r="Z31" s="10" t="n">
+      <c r="Z31" s="12" t="n">
         <v>41.24</v>
       </c>
-      <c r="AA31" s="10" t="n">
+      <c r="AA31" s="12" t="n">
         <v>41.48</v>
       </c>
-      <c r="AB31" s="10" t="n">
+      <c r="AB31" s="12" t="n">
         <v>42.87</v>
       </c>
-      <c r="AC31" s="9" t="n">
+      <c r="AC31" s="11" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="10" t="n">
+      <c r="AD31" s="12" t="n">
         <v>40.41</v>
       </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AE31" s="11" t="n">
         <v>47.34</v>
       </c>
-      <c r="AF31" s="9" t="n">
+      <c r="AF31" s="11" t="n">
         <v>51.7</v>
       </c>
-      <c r="AG31" s="9" t="n">
+      <c r="AG31" s="11" t="n">
         <v>45.77</v>
       </c>
       <c r="AH31" s="6" t="n">
         <v>44.94</v>
       </c>
-      <c r="AI31" s="6" t="n">
+      <c r="AI31" s="9" t="n">
         <v>485.2</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3271,7 +3292,7 @@
       <c r="D32" s="7" t="n">
         <v>55.07</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="11" t="n">
         <v>52.52</v>
       </c>
       <c r="F32" s="7" t="n">
@@ -3361,11 +3382,11 @@
       <c r="AH32" s="6" t="n">
         <v>55.72</v>
       </c>
-      <c r="AI32" s="6" t="n">
+      <c r="AI32" s="9" t="n">
         <v>474.57</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3469,14 +3490,14 @@
       <c r="AG33" s="7" t="n">
         <v>76.45999999999999</v>
       </c>
-      <c r="AH33" s="6" t="n">
+      <c r="AH33" s="8" t="n">
         <v>76.88</v>
       </c>
-      <c r="AI33" s="6" t="n">
+      <c r="AI33" s="9" t="n">
         <v>326</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="8" t="inlineStr"/>
+      <c r="AK33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3580,14 +3601,14 @@
       <c r="AG34" s="7" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="AH34" s="6" t="n">
+      <c r="AH34" s="8" t="n">
         <v>65.95999999999999</v>
       </c>
-      <c r="AI34" s="6" t="n">
+      <c r="AI34" s="9" t="n">
         <v>478.65</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="8" t="inlineStr"/>
+      <c r="AK34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3691,14 +3712,14 @@
       <c r="AG35" s="7" t="n">
         <v>61.26</v>
       </c>
-      <c r="AH35" s="6" t="n">
+      <c r="AH35" s="8" t="n">
         <v>60.41</v>
       </c>
-      <c r="AI35" s="6" t="n">
+      <c r="AI35" s="9" t="n">
         <v>497.28</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="8" t="inlineStr"/>
+      <c r="AK35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3802,14 +3823,14 @@
       <c r="AG36" s="7" t="n">
         <v>65.62</v>
       </c>
-      <c r="AH36" s="6" t="n">
+      <c r="AH36" s="8" t="n">
         <v>65.18000000000001</v>
       </c>
-      <c r="AI36" s="6" t="n">
+      <c r="AI36" s="9" t="n">
         <v>431.37</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="8" t="inlineStr"/>
+      <c r="AK36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3820,107 +3841,107 @@
       <c r="B37" s="6" t="n">
         <v>101.1</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="12" t="n">
         <v>41.52</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="12" t="n">
         <v>37.06</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="12" t="n">
         <v>39.89</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="12" t="n">
         <v>41.01</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="12" t="n">
         <v>40.08</v>
       </c>
-      <c r="H37" s="10" t="n">
+      <c r="H37" s="12" t="n">
         <v>41.32</v>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="I37" s="12" t="n">
         <v>40.03</v>
       </c>
-      <c r="J37" s="10" t="n">
+      <c r="J37" s="12" t="n">
         <v>40.92</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="K37" s="12" t="n">
         <v>39.57</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="12" t="n">
         <v>40.51</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="11" t="n">
         <v>44.43</v>
       </c>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="12" t="n">
         <v>40.55</v>
       </c>
-      <c r="O37" s="9" t="n">
+      <c r="O37" s="11" t="n">
         <v>43.01</v>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P37" s="11" t="n">
         <v>43.79</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="12" t="n">
         <v>40.86</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="12" t="n">
         <v>36.73</v>
       </c>
-      <c r="S37" s="10" t="n">
+      <c r="S37" s="12" t="n">
         <v>36.76</v>
       </c>
-      <c r="T37" s="10" t="n">
+      <c r="T37" s="12" t="n">
         <v>38.71</v>
       </c>
-      <c r="U37" s="10" t="n">
+      <c r="U37" s="12" t="n">
         <v>36.86</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="12" t="n">
         <v>40.22</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="12" t="n">
         <v>40.92</v>
       </c>
-      <c r="X37" s="10" t="n">
+      <c r="X37" s="12" t="n">
         <v>39.83</v>
       </c>
-      <c r="Y37" s="10" t="n">
+      <c r="Y37" s="12" t="n">
         <v>37.26</v>
       </c>
-      <c r="Z37" s="10" t="n">
+      <c r="Z37" s="12" t="n">
         <v>38.74</v>
       </c>
-      <c r="AA37" s="10" t="n">
+      <c r="AA37" s="12" t="n">
         <v>37.96</v>
       </c>
-      <c r="AB37" s="10" t="n">
+      <c r="AB37" s="12" t="n">
         <v>41.61</v>
       </c>
-      <c r="AC37" s="10" t="n">
+      <c r="AC37" s="12" t="n">
         <v>41.84</v>
       </c>
-      <c r="AD37" s="10" t="n">
+      <c r="AD37" s="12" t="n">
         <v>38.69</v>
       </c>
-      <c r="AE37" s="10" t="n">
+      <c r="AE37" s="12" t="n">
         <v>41.51</v>
       </c>
-      <c r="AF37" s="10" t="n">
+      <c r="AF37" s="12" t="n">
         <v>41.72</v>
       </c>
-      <c r="AG37" s="10" t="n">
+      <c r="AG37" s="12" t="n">
         <v>41.58</v>
       </c>
       <c r="AH37" s="6" t="n">
         <v>40.18</v>
       </c>
-      <c r="AI37" s="6" t="n">
+      <c r="AI37" s="9" t="n">
         <v>499.53</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="8" t="inlineStr"/>
+      <c r="AK37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4024,14 +4045,14 @@
       <c r="AG38" s="7" t="n">
         <v>77.81</v>
       </c>
-      <c r="AH38" s="6" t="n">
+      <c r="AH38" s="8" t="n">
         <v>77.34999999999999</v>
       </c>
       <c r="AI38" s="6" t="n">
         <v>159.74</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="8" t="inlineStr"/>
+      <c r="AK38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4135,14 +4156,14 @@
       <c r="AG39" s="7" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="AH39" s="6" t="n">
+      <c r="AH39" s="8" t="n">
         <v>71.44</v>
       </c>
-      <c r="AI39" s="6" t="n">
+      <c r="AI39" s="9" t="n">
         <v>422.29</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="8" t="inlineStr"/>
+      <c r="AK39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4249,11 +4270,11 @@
       <c r="AH40" s="6" t="n">
         <v>58.38</v>
       </c>
-      <c r="AI40" s="6" t="n">
+      <c r="AI40" s="9" t="n">
         <v>471.03</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="8" t="inlineStr"/>
+      <c r="AK40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4264,97 +4285,97 @@
       <c r="B41" s="6" t="n">
         <v>103.1</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="11" t="n">
         <v>46.72</v>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="12" t="n">
         <v>35.76</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="12" t="n">
         <v>36.4</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="11" t="n">
         <v>45.76</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="11" t="n">
         <v>43.98</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="11" t="n">
         <v>45.91</v>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I41" s="12" t="n">
         <v>42.62</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" s="11" t="n">
         <v>44.54</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="11" t="n">
         <v>43.32</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="11" t="n">
         <v>43.78</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="11" t="n">
         <v>46.12</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="11" t="n">
         <v>45.71</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="11" t="n">
         <v>45.21</v>
       </c>
-      <c r="P41" s="10" t="n">
+      <c r="P41" s="12" t="n">
         <v>42.01</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="11" t="n">
         <v>47.36</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="11" t="n">
         <v>43.31</v>
       </c>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="12" t="n">
         <v>37.48</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="11" t="n">
         <v>43.12</v>
       </c>
-      <c r="U41" s="10" t="n">
+      <c r="U41" s="12" t="n">
         <v>41.52</v>
       </c>
-      <c r="V41" s="10" t="n">
+      <c r="V41" s="12" t="n">
         <v>42.48</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="12" t="n">
         <v>42.72</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="11" t="n">
         <v>46.34</v>
       </c>
-      <c r="Y41" s="10" t="n">
+      <c r="Y41" s="12" t="n">
         <v>42.01</v>
       </c>
-      <c r="Z41" s="10" t="n">
+      <c r="Z41" s="12" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA41" s="10" t="n">
+      <c r="AA41" s="12" t="n">
         <v>41.55</v>
       </c>
-      <c r="AB41" s="10" t="n">
+      <c r="AB41" s="12" t="n">
         <v>41.22</v>
       </c>
-      <c r="AC41" s="9" t="n">
+      <c r="AC41" s="11" t="n">
         <v>44.88</v>
       </c>
-      <c r="AD41" s="10" t="n">
+      <c r="AD41" s="12" t="n">
         <v>38.64</v>
       </c>
-      <c r="AE41" s="10" t="n">
+      <c r="AE41" s="12" t="n">
         <v>41.14</v>
       </c>
-      <c r="AF41" s="9" t="n">
+      <c r="AF41" s="11" t="n">
         <v>47.4</v>
       </c>
-      <c r="AG41" s="9" t="n">
+      <c r="AG41" s="11" t="n">
         <v>48.04</v>
       </c>
       <c r="AH41" s="6" t="n">
@@ -4364,7 +4385,7 @@
         <v>161.11</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="8" t="inlineStr"/>
+      <c r="AK41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4375,97 +4396,97 @@
       <c r="B42" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="11" t="n">
         <v>46.89</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="12" t="n">
         <v>36.46</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="12" t="n">
         <v>37.76</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="11" t="n">
         <v>45.51</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="11" t="n">
         <v>44.04</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="11" t="n">
         <v>45.22</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="11" t="n">
         <v>43.04</v>
       </c>
-      <c r="J42" s="10" t="n">
+      <c r="J42" s="12" t="n">
         <v>42.79</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="11" t="n">
         <v>47.75</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="11" t="n">
         <v>45.64</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="11" t="n">
         <v>46.23</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="11" t="n">
         <v>44.39</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="11" t="n">
         <v>45.54</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="11" t="n">
         <v>46.71</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="12" t="n">
         <v>42.49</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="12" t="n">
         <v>39.33</v>
       </c>
-      <c r="S42" s="10" t="n">
+      <c r="S42" s="12" t="n">
         <v>40.14</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="T42" s="12" t="n">
         <v>38.01</v>
       </c>
-      <c r="U42" s="10" t="n">
+      <c r="U42" s="12" t="n">
         <v>38.08</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="V42" s="12" t="n">
         <v>38.74</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="11" t="n">
         <v>43.46</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="11" t="n">
         <v>46.21</v>
       </c>
-      <c r="Y42" s="10" t="n">
+      <c r="Y42" s="12" t="n">
         <v>40.55</v>
       </c>
-      <c r="Z42" s="10" t="n">
+      <c r="Z42" s="12" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA42" s="10" t="n">
+      <c r="AA42" s="12" t="n">
         <v>36.65</v>
       </c>
-      <c r="AB42" s="10" t="n">
+      <c r="AB42" s="12" t="n">
         <v>42.29</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="11" t="n">
         <v>45.95</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AD42" s="11" t="n">
         <v>43.71</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="11" t="n">
         <v>45.76</v>
       </c>
-      <c r="AF42" s="9" t="n">
+      <c r="AF42" s="11" t="n">
         <v>47.26</v>
       </c>
-      <c r="AG42" s="9" t="n">
+      <c r="AG42" s="11" t="n">
         <v>44.16</v>
       </c>
       <c r="AH42" s="6" t="n">
@@ -4475,7 +4496,7 @@
         <v>141.85</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="8" t="inlineStr"/>
+      <c r="AK42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4486,97 +4507,97 @@
       <c r="B43" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="11" t="n">
         <v>47.79</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="12" t="n">
         <v>36.54</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="12" t="n">
         <v>35.36</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="12" t="n">
         <v>39.5</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="12" t="n">
         <v>39.05</v>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="H43" s="11" t="n">
         <v>44.41</v>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="12" t="n">
         <v>42.89</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="11" t="n">
         <v>45.39</v>
       </c>
-      <c r="K43" s="9" t="n">
+      <c r="K43" s="11" t="n">
         <v>46.43</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="11" t="n">
         <v>44.24</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="11" t="n">
         <v>46.82</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" s="11" t="n">
         <v>43.69</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="11" t="n">
         <v>48.21</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="P43" s="11" t="n">
         <v>47.44</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="11" t="n">
         <v>43.59</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="12" t="n">
         <v>39.13</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="S43" s="12" t="n">
         <v>38.44</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="T43" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="U43" s="10" t="n">
+      <c r="U43" s="12" t="n">
         <v>42.06</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="12" t="n">
         <v>39.01</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="12" t="n">
         <v>42.07</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" s="11" t="n">
         <v>46.61</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="12" t="n">
         <v>36.92</v>
       </c>
-      <c r="Z43" s="10" t="n">
+      <c r="Z43" s="12" t="n">
         <v>37.61</v>
       </c>
-      <c r="AA43" s="10" t="n">
+      <c r="AA43" s="12" t="n">
         <v>36.41</v>
       </c>
-      <c r="AB43" s="10" t="n">
+      <c r="AB43" s="12" t="n">
         <v>40.19</v>
       </c>
-      <c r="AC43" s="10" t="n">
+      <c r="AC43" s="12" t="n">
         <v>39.22</v>
       </c>
-      <c r="AD43" s="10" t="n">
+      <c r="AD43" s="12" t="n">
         <v>40.28</v>
       </c>
-      <c r="AE43" s="9" t="n">
+      <c r="AE43" s="11" t="n">
         <v>47.26</v>
       </c>
-      <c r="AF43" s="9" t="n">
+      <c r="AF43" s="11" t="n">
         <v>46.28</v>
       </c>
-      <c r="AG43" s="9" t="n">
+      <c r="AG43" s="11" t="n">
         <v>45.59</v>
       </c>
       <c r="AH43" s="6" t="n">
@@ -4586,7 +4607,7 @@
         <v>140.45</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="8" t="inlineStr"/>
+      <c r="AK43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4690,14 +4711,14 @@
       <c r="AG44" s="7" t="n">
         <v>78.26000000000001</v>
       </c>
-      <c r="AH44" s="6" t="n">
+      <c r="AH44" s="8" t="n">
         <v>77.54000000000001</v>
       </c>
       <c r="AI44" s="6" t="n">
         <v>181.85</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="8" t="inlineStr"/>
+      <c r="AK44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4801,14 +4822,14 @@
       <c r="AG45" s="7" t="n">
         <v>66.86</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="8" t="n">
         <v>66.86</v>
       </c>
-      <c r="AI45" s="6" t="n">
+      <c r="AI45" s="9" t="n">
         <v>243.9</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="8" t="inlineStr"/>
+      <c r="AK45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4912,14 +4933,14 @@
       <c r="AG46" s="7" t="n">
         <v>71.01000000000001</v>
       </c>
-      <c r="AH46" s="6" t="n">
+      <c r="AH46" s="8" t="n">
         <v>70.11</v>
       </c>
-      <c r="AI46" s="6" t="n">
+      <c r="AI46" s="9" t="n">
         <v>252.32</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="8" t="inlineStr"/>
+      <c r="AK46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -5023,14 +5044,14 @@
       <c r="AG47" s="7" t="n">
         <v>80.06</v>
       </c>
-      <c r="AH47" s="6" t="n">
+      <c r="AH47" s="8" t="n">
         <v>79.56999999999999</v>
       </c>
-      <c r="AI47" s="6" t="n">
+      <c r="AI47" s="9" t="n">
         <v>254.37</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="8" t="inlineStr"/>
+      <c r="AK47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5047,7 +5068,7 @@
       <c r="D48" s="7" t="n">
         <v>56.33</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="11" t="n">
         <v>52.45</v>
       </c>
       <c r="F48" s="7" t="n">
@@ -5137,11 +5158,11 @@
       <c r="AH48" s="6" t="n">
         <v>55.88</v>
       </c>
-      <c r="AI48" s="6" t="n">
+      <c r="AI48" s="9" t="n">
         <v>487.79</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="8" t="inlineStr"/>
+      <c r="AK48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5245,14 +5266,14 @@
       <c r="AG49" s="7" t="n">
         <v>66.27</v>
       </c>
-      <c r="AH49" s="6" t="n">
+      <c r="AH49" s="8" t="n">
         <v>66.84</v>
       </c>
-      <c r="AI49" s="6" t="n">
+      <c r="AI49" s="9" t="n">
         <v>385.5</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="8" t="inlineStr"/>
+      <c r="AK49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5356,14 +5377,14 @@
       <c r="AG50" s="7" t="n">
         <v>73.59</v>
       </c>
-      <c r="AH50" s="6" t="n">
+      <c r="AH50" s="8" t="n">
         <v>73.84</v>
       </c>
-      <c r="AI50" s="6" t="n">
+      <c r="AI50" s="9" t="n">
         <v>236.24</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="8" t="inlineStr"/>
+      <c r="AK50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -5374,218 +5395,218 @@
       <c r="B51" s="6" t="n">
         <v>106.7</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="11" t="n">
         <v>45.59</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D51" s="11" t="n">
         <v>44.29</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="11" t="n">
         <v>45.42</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="11" t="n">
         <v>45.54</v>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G51" s="11" t="n">
         <v>45.36</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H51" s="11" t="n">
         <v>44.1</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="I51" s="11" t="n">
         <v>45.04</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J51" s="11" t="n">
         <v>45.04</v>
       </c>
-      <c r="K51" s="9" t="n">
+      <c r="K51" s="11" t="n">
         <v>45.84</v>
       </c>
-      <c r="L51" s="9" t="n">
+      <c r="L51" s="11" t="n">
         <v>43.74</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" s="11" t="n">
         <v>44.87</v>
       </c>
-      <c r="N51" s="9" t="n">
+      <c r="N51" s="11" t="n">
         <v>45.91</v>
       </c>
-      <c r="O51" s="9" t="n">
+      <c r="O51" s="11" t="n">
         <v>45.61</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P51" s="11" t="n">
         <v>45.42</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="Q51" s="11" t="n">
         <v>45.88</v>
       </c>
-      <c r="R51" s="9" t="n">
+      <c r="R51" s="11" t="n">
         <v>45.66</v>
       </c>
-      <c r="S51" s="9" t="n">
+      <c r="S51" s="11" t="n">
         <v>45.7</v>
       </c>
-      <c r="T51" s="9" t="n">
+      <c r="T51" s="11" t="n">
         <v>46.39</v>
       </c>
-      <c r="U51" s="9" t="n">
+      <c r="U51" s="11" t="n">
         <v>45.44</v>
       </c>
-      <c r="V51" s="9" t="n">
+      <c r="V51" s="11" t="n">
         <v>43.86</v>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W51" s="11" t="n">
         <v>44.56</v>
       </c>
-      <c r="X51" s="9" t="n">
+      <c r="X51" s="11" t="n">
         <v>44.54</v>
       </c>
-      <c r="Y51" s="9" t="n">
+      <c r="Y51" s="11" t="n">
         <v>44.78</v>
       </c>
-      <c r="Z51" s="9" t="n">
+      <c r="Z51" s="11" t="n">
         <v>43.79</v>
       </c>
-      <c r="AA51" s="9" t="n">
+      <c r="AA51" s="11" t="n">
         <v>45.58</v>
       </c>
-      <c r="AB51" s="9" t="n">
+      <c r="AB51" s="11" t="n">
         <v>43.16</v>
       </c>
-      <c r="AC51" s="9" t="n">
+      <c r="AC51" s="11" t="n">
         <v>43.36</v>
       </c>
-      <c r="AD51" s="9" t="n">
+      <c r="AD51" s="11" t="n">
         <v>44.17</v>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AE51" s="11" t="n">
         <v>46.02</v>
       </c>
-      <c r="AF51" s="9" t="n">
+      <c r="AF51" s="11" t="n">
         <v>45.81</v>
       </c>
-      <c r="AG51" s="9" t="n">
+      <c r="AG51" s="11" t="n">
         <v>44.48</v>
       </c>
       <c r="AH51" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="AI51" s="6" t="n">
+      <c r="AI51" s="9" t="n">
         <v>468.87</v>
       </c>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="8" t="inlineStr"/>
+      <c r="AK51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>GENESIS FM STEREO</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="14" t="n">
         <v>107.5</v>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C52" s="15" t="n">
         <v>45.55</v>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="15" t="n">
         <v>45.58</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="15" t="n">
         <v>46.18</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F52" s="15" t="n">
         <v>45.65</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="15" t="n">
         <v>47.34</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="15" t="n">
         <v>47.62</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="I52" s="15" t="n">
         <v>46.46</v>
       </c>
-      <c r="J52" s="13" t="n">
+      <c r="J52" s="15" t="n">
         <v>45.94</v>
       </c>
-      <c r="K52" s="13" t="n">
+      <c r="K52" s="15" t="n">
         <v>45.49</v>
       </c>
-      <c r="L52" s="13" t="n">
+      <c r="L52" s="15" t="n">
         <v>45.62</v>
       </c>
-      <c r="M52" s="13" t="n">
+      <c r="M52" s="15" t="n">
         <v>46.22</v>
       </c>
-      <c r="N52" s="13" t="n">
+      <c r="N52" s="15" t="n">
         <v>47.42</v>
       </c>
-      <c r="O52" s="13" t="n">
+      <c r="O52" s="15" t="n">
         <v>46.59</v>
       </c>
-      <c r="P52" s="13" t="n">
+      <c r="P52" s="15" t="n">
         <v>46.35</v>
       </c>
-      <c r="Q52" s="13" t="n">
+      <c r="Q52" s="15" t="n">
         <v>46.21</v>
       </c>
-      <c r="R52" s="13" t="n">
+      <c r="R52" s="15" t="n">
         <v>46.19</v>
       </c>
-      <c r="S52" s="13" t="n">
+      <c r="S52" s="15" t="n">
         <v>47.04</v>
       </c>
-      <c r="T52" s="13" t="n">
+      <c r="T52" s="15" t="n">
         <v>45.74</v>
       </c>
-      <c r="U52" s="13" t="n">
+      <c r="U52" s="15" t="n">
         <v>45.27</v>
       </c>
-      <c r="V52" s="13" t="n">
+      <c r="V52" s="15" t="n">
         <v>45.62</v>
       </c>
-      <c r="W52" s="13" t="n">
+      <c r="W52" s="15" t="n">
         <v>44.74</v>
       </c>
-      <c r="X52" s="13" t="n">
+      <c r="X52" s="15" t="n">
         <v>49.16</v>
       </c>
-      <c r="Y52" s="13" t="n">
+      <c r="Y52" s="15" t="n">
         <v>46.34</v>
       </c>
-      <c r="Z52" s="13" t="n">
+      <c r="Z52" s="15" t="n">
         <v>45.4</v>
       </c>
-      <c r="AA52" s="13" t="n">
+      <c r="AA52" s="15" t="n">
         <v>45.42</v>
       </c>
-      <c r="AB52" s="13" t="n">
+      <c r="AB52" s="15" t="n">
         <v>47.13</v>
       </c>
-      <c r="AC52" s="13" t="n">
+      <c r="AC52" s="15" t="n">
         <v>45.49</v>
       </c>
-      <c r="AD52" s="13" t="n">
+      <c r="AD52" s="15" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE52" s="13" t="n">
+      <c r="AE52" s="15" t="n">
         <v>46.79</v>
       </c>
-      <c r="AF52" s="13" t="n">
+      <c r="AF52" s="15" t="n">
         <v>47.06</v>
       </c>
-      <c r="AG52" s="13" t="n">
+      <c r="AG52" s="15" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH52" s="12" t="n">
+      <c r="AH52" s="14" t="n">
         <v>46.28</v>
       </c>
-      <c r="AI52" s="12" t="n">
+      <c r="AI52" s="16" t="n">
         <v>497.9</v>
       </c>
-      <c r="AJ52" s="12" t="inlineStr"/>
-      <c r="AK52" s="14" t="inlineStr"/>
+      <c r="AJ52" s="14" t="inlineStr"/>
+      <c r="AK52" s="17" t="inlineStr"/>
     </row>
     <row r="53"/>
     <row r="54"/>
@@ -5760,7 +5781,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK62" s="15" t="n"/>
+      <c r="AK62" s="18" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5864,12 +5885,12 @@
       <c r="AG63" s="7" t="n">
         <v>63.04</v>
       </c>
-      <c r="AH63" s="6" t="n">
+      <c r="AH63" s="8" t="n">
         <v>63.58</v>
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="16" t="n"/>
+      <c r="AK63" s="19" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5880,97 +5901,97 @@
       <c r="B64" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C64" s="10" t="n">
+      <c r="C64" s="12" t="n">
         <v>37.2</v>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D64" s="12" t="n">
         <v>37.1</v>
       </c>
-      <c r="E64" s="10" t="n">
+      <c r="E64" s="12" t="n">
         <v>36.25</v>
       </c>
-      <c r="F64" s="10" t="n">
+      <c r="F64" s="12" t="n">
         <v>35.95</v>
       </c>
-      <c r="G64" s="10" t="n">
+      <c r="G64" s="12" t="n">
         <v>38.22</v>
       </c>
-      <c r="H64" s="10" t="n">
+      <c r="H64" s="12" t="n">
         <v>35.83</v>
       </c>
-      <c r="I64" s="10" t="n">
+      <c r="I64" s="12" t="n">
         <v>38.13</v>
       </c>
-      <c r="J64" s="10" t="n">
+      <c r="J64" s="12" t="n">
         <v>36.34</v>
       </c>
-      <c r="K64" s="10" t="n">
+      <c r="K64" s="12" t="n">
         <v>37.93</v>
       </c>
-      <c r="L64" s="10" t="n">
+      <c r="L64" s="12" t="n">
         <v>37.71</v>
       </c>
-      <c r="M64" s="10" t="n">
+      <c r="M64" s="12" t="n">
         <v>35.95</v>
       </c>
-      <c r="N64" s="10" t="n">
+      <c r="N64" s="12" t="n">
         <v>35.99</v>
       </c>
-      <c r="O64" s="10" t="n">
+      <c r="O64" s="12" t="n">
         <v>38.22</v>
       </c>
-      <c r="P64" s="10" t="n">
+      <c r="P64" s="12" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q64" s="10" t="n">
+      <c r="Q64" s="12" t="n">
         <v>37.15</v>
       </c>
-      <c r="R64" s="10" t="n">
+      <c r="R64" s="12" t="n">
         <v>37.29</v>
       </c>
-      <c r="S64" s="10" t="n">
+      <c r="S64" s="12" t="n">
         <v>38.9</v>
       </c>
-      <c r="T64" s="10" t="n">
+      <c r="T64" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="U64" s="10" t="n">
+      <c r="U64" s="12" t="n">
         <v>37.5</v>
       </c>
-      <c r="V64" s="10" t="n">
+      <c r="V64" s="12" t="n">
         <v>36.25</v>
       </c>
-      <c r="W64" s="10" t="n">
+      <c r="W64" s="12" t="n">
         <v>36.9</v>
       </c>
-      <c r="X64" s="10" t="n">
+      <c r="X64" s="12" t="n">
         <v>36.92</v>
       </c>
-      <c r="Y64" s="10" t="n">
+      <c r="Y64" s="12" t="n">
         <v>35.42</v>
       </c>
-      <c r="Z64" s="10" t="n">
+      <c r="Z64" s="12" t="n">
         <v>38.12</v>
       </c>
-      <c r="AA64" s="10" t="n">
+      <c r="AA64" s="12" t="n">
         <v>37.35</v>
       </c>
-      <c r="AB64" s="10" t="n">
+      <c r="AB64" s="12" t="n">
         <v>38.41</v>
       </c>
-      <c r="AC64" s="10" t="n">
+      <c r="AC64" s="12" t="n">
         <v>37.71</v>
       </c>
-      <c r="AD64" s="10" t="n">
+      <c r="AD64" s="12" t="n">
         <v>37.56</v>
       </c>
-      <c r="AE64" s="10" t="n">
+      <c r="AE64" s="12" t="n">
         <v>38.91</v>
       </c>
-      <c r="AF64" s="10" t="n">
+      <c r="AF64" s="12" t="n">
         <v>36.38</v>
       </c>
-      <c r="AG64" s="10" t="n">
+      <c r="AG64" s="12" t="n">
         <v>37.45</v>
       </c>
       <c r="AH64" s="6" t="n">
@@ -5978,7 +5999,7 @@
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="16" t="n"/>
+      <c r="AK64" s="19" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5989,97 +6010,97 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C65" s="12" t="n">
         <v>39.7</v>
       </c>
-      <c r="D65" s="10" t="n">
+      <c r="D65" s="12" t="n">
         <v>37.34</v>
       </c>
-      <c r="E65" s="10" t="n">
+      <c r="E65" s="12" t="n">
         <v>38.12</v>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F65" s="12" t="n">
         <v>37.12</v>
       </c>
-      <c r="G65" s="10" t="n">
+      <c r="G65" s="12" t="n">
         <v>38.33</v>
       </c>
-      <c r="H65" s="10" t="n">
+      <c r="H65" s="12" t="n">
         <v>39.69</v>
       </c>
-      <c r="I65" s="10" t="n">
+      <c r="I65" s="12" t="n">
         <v>42.09</v>
       </c>
-      <c r="J65" s="10" t="n">
+      <c r="J65" s="12" t="n">
         <v>42.04</v>
       </c>
-      <c r="K65" s="10" t="n">
+      <c r="K65" s="12" t="n">
         <v>38.28</v>
       </c>
-      <c r="L65" s="10" t="n">
+      <c r="L65" s="12" t="n">
         <v>41.34</v>
       </c>
-      <c r="M65" s="10" t="n">
+      <c r="M65" s="12" t="n">
         <v>41.94</v>
       </c>
-      <c r="N65" s="10" t="n">
+      <c r="N65" s="12" t="n">
         <v>40.49</v>
       </c>
-      <c r="O65" s="10" t="n">
+      <c r="O65" s="12" t="n">
         <v>38.61</v>
       </c>
-      <c r="P65" s="10" t="n">
+      <c r="P65" s="12" t="n">
         <v>37.79</v>
       </c>
-      <c r="Q65" s="10" t="n">
+      <c r="Q65" s="12" t="n">
         <v>37.79</v>
       </c>
-      <c r="R65" s="10" t="n">
+      <c r="R65" s="12" t="n">
         <v>36.92</v>
       </c>
-      <c r="S65" s="10" t="n">
+      <c r="S65" s="12" t="n">
         <v>38.35</v>
       </c>
-      <c r="T65" s="10" t="n">
+      <c r="T65" s="12" t="n">
         <v>36.67</v>
       </c>
-      <c r="U65" s="10" t="n">
+      <c r="U65" s="12" t="n">
         <v>36.88</v>
       </c>
-      <c r="V65" s="10" t="n">
+      <c r="V65" s="12" t="n">
         <v>37.59</v>
       </c>
-      <c r="W65" s="10" t="n">
+      <c r="W65" s="12" t="n">
         <v>37.49</v>
       </c>
-      <c r="X65" s="10" t="n">
+      <c r="X65" s="12" t="n">
         <v>40.59</v>
       </c>
-      <c r="Y65" s="10" t="n">
+      <c r="Y65" s="12" t="n">
         <v>42.94</v>
       </c>
-      <c r="Z65" s="10" t="n">
+      <c r="Z65" s="12" t="n">
         <v>38.3</v>
       </c>
-      <c r="AA65" s="10" t="n">
+      <c r="AA65" s="12" t="n">
         <v>36.58</v>
       </c>
-      <c r="AB65" s="9" t="n">
+      <c r="AB65" s="11" t="n">
         <v>43.08</v>
       </c>
-      <c r="AC65" s="10" t="n">
+      <c r="AC65" s="12" t="n">
         <v>39.4</v>
       </c>
-      <c r="AD65" s="10" t="n">
+      <c r="AD65" s="12" t="n">
         <v>37.41</v>
       </c>
-      <c r="AE65" s="10" t="n">
+      <c r="AE65" s="12" t="n">
         <v>37.99</v>
       </c>
-      <c r="AF65" s="10" t="n">
+      <c r="AF65" s="12" t="n">
         <v>41.21</v>
       </c>
-      <c r="AG65" s="10" t="n">
+      <c r="AG65" s="12" t="n">
         <v>37.2</v>
       </c>
       <c r="AH65" s="6" t="n">
@@ -6087,7 +6108,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="16" t="n"/>
+      <c r="AK65" s="19" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6191,12 +6212,12 @@
       <c r="AG66" s="7" t="n">
         <v>77.44</v>
       </c>
-      <c r="AH66" s="6" t="n">
+      <c r="AH66" s="8" t="n">
         <v>77.48</v>
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="16" t="n"/>
+      <c r="AK66" s="19" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6207,97 +6228,97 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C67" s="12" t="n">
         <v>40.3</v>
       </c>
-      <c r="D67" s="10" t="n">
+      <c r="D67" s="12" t="n">
         <v>41.59</v>
       </c>
-      <c r="E67" s="10" t="n">
+      <c r="E67" s="12" t="n">
         <v>38.95</v>
       </c>
-      <c r="F67" s="10" t="n">
+      <c r="F67" s="12" t="n">
         <v>40.75</v>
       </c>
-      <c r="G67" s="10" t="n">
+      <c r="G67" s="12" t="n">
         <v>41.29</v>
       </c>
-      <c r="H67" s="10" t="n">
+      <c r="H67" s="12" t="n">
         <v>40.61</v>
       </c>
-      <c r="I67" s="10" t="n">
+      <c r="I67" s="12" t="n">
         <v>40.69</v>
       </c>
-      <c r="J67" s="9" t="n">
+      <c r="J67" s="11" t="n">
         <v>43.48</v>
       </c>
-      <c r="K67" s="10" t="n">
+      <c r="K67" s="12" t="n">
         <v>41.87</v>
       </c>
-      <c r="L67" s="10" t="n">
+      <c r="L67" s="12" t="n">
         <v>41.22</v>
       </c>
-      <c r="M67" s="10" t="n">
+      <c r="M67" s="12" t="n">
         <v>40.41</v>
       </c>
-      <c r="N67" s="10" t="n">
+      <c r="N67" s="12" t="n">
         <v>41.46</v>
       </c>
-      <c r="O67" s="10" t="n">
+      <c r="O67" s="12" t="n">
         <v>40.07</v>
       </c>
-      <c r="P67" s="10" t="n">
+      <c r="P67" s="12" t="n">
         <v>40.54</v>
       </c>
-      <c r="Q67" s="10" t="n">
+      <c r="Q67" s="12" t="n">
         <v>40.48</v>
       </c>
-      <c r="R67" s="10" t="n">
+      <c r="R67" s="12" t="n">
         <v>41.38</v>
       </c>
-      <c r="S67" s="10" t="n">
+      <c r="S67" s="12" t="n">
         <v>41.15</v>
       </c>
-      <c r="T67" s="10" t="n">
+      <c r="T67" s="12" t="n">
         <v>39.41</v>
       </c>
-      <c r="U67" s="10" t="n">
+      <c r="U67" s="12" t="n">
         <v>39.12</v>
       </c>
-      <c r="V67" s="10" t="n">
+      <c r="V67" s="12" t="n">
         <v>40.48</v>
       </c>
-      <c r="W67" s="10" t="n">
+      <c r="W67" s="12" t="n">
         <v>40.44</v>
       </c>
-      <c r="X67" s="10" t="n">
+      <c r="X67" s="12" t="n">
         <v>40.11</v>
       </c>
-      <c r="Y67" s="10" t="n">
+      <c r="Y67" s="12" t="n">
         <v>38.81</v>
       </c>
-      <c r="Z67" s="10" t="n">
+      <c r="Z67" s="12" t="n">
         <v>40.83</v>
       </c>
-      <c r="AA67" s="10" t="n">
+      <c r="AA67" s="12" t="n">
         <v>39.05</v>
       </c>
-      <c r="AB67" s="10" t="n">
+      <c r="AB67" s="12" t="n">
         <v>39.54</v>
       </c>
-      <c r="AC67" s="10" t="n">
+      <c r="AC67" s="12" t="n">
         <v>38.81</v>
       </c>
-      <c r="AD67" s="10" t="n">
+      <c r="AD67" s="12" t="n">
         <v>39.5</v>
       </c>
-      <c r="AE67" s="10" t="n">
+      <c r="AE67" s="12" t="n">
         <v>40.44</v>
       </c>
-      <c r="AF67" s="10" t="n">
+      <c r="AF67" s="12" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG67" s="10" t="n">
+      <c r="AG67" s="12" t="n">
         <v>39.62</v>
       </c>
       <c r="AH67" s="6" t="n">
@@ -6305,7 +6326,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="16" t="n"/>
+      <c r="AK67" s="19" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6409,12 +6430,12 @@
       <c r="AG68" s="7" t="n">
         <v>78.26000000000001</v>
       </c>
-      <c r="AH68" s="6" t="n">
+      <c r="AH68" s="8" t="n">
         <v>78.28</v>
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="16" t="n"/>
+      <c r="AK68" s="19" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6518,12 +6539,12 @@
       <c r="AG69" s="7" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="AH69" s="6" t="n">
+      <c r="AH69" s="8" t="n">
         <v>72.51000000000001</v>
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="16" t="n"/>
+      <c r="AK69" s="19" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6534,97 +6555,97 @@
       <c r="B70" s="6" t="n">
         <v>549.25</v>
       </c>
-      <c r="C70" s="10" t="n">
+      <c r="C70" s="12" t="n">
         <v>31.82</v>
       </c>
-      <c r="D70" s="10" t="n">
+      <c r="D70" s="12" t="n">
         <v>34.01</v>
       </c>
-      <c r="E70" s="10" t="n">
+      <c r="E70" s="12" t="n">
         <v>31.3</v>
       </c>
-      <c r="F70" s="10" t="n">
+      <c r="F70" s="12" t="n">
         <v>31.78</v>
       </c>
-      <c r="G70" s="10" t="n">
+      <c r="G70" s="12" t="n">
         <v>31.44</v>
       </c>
-      <c r="H70" s="10" t="n">
+      <c r="H70" s="12" t="n">
         <v>31.81</v>
       </c>
-      <c r="I70" s="10" t="n">
+      <c r="I70" s="12" t="n">
         <v>31.13</v>
       </c>
-      <c r="J70" s="10" t="n">
+      <c r="J70" s="12" t="n">
         <v>32.33</v>
       </c>
-      <c r="K70" s="10" t="n">
+      <c r="K70" s="12" t="n">
         <v>31.17</v>
       </c>
-      <c r="L70" s="10" t="n">
+      <c r="L70" s="12" t="n">
         <v>30.91</v>
       </c>
-      <c r="M70" s="10" t="n">
+      <c r="M70" s="12" t="n">
         <v>31.56</v>
       </c>
-      <c r="N70" s="10" t="n">
+      <c r="N70" s="12" t="n">
         <v>31.3</v>
       </c>
-      <c r="O70" s="10" t="n">
+      <c r="O70" s="12" t="n">
         <v>31.59</v>
       </c>
-      <c r="P70" s="10" t="n">
+      <c r="P70" s="12" t="n">
         <v>31.9</v>
       </c>
-      <c r="Q70" s="10" t="n">
+      <c r="Q70" s="12" t="n">
         <v>31.52</v>
       </c>
-      <c r="R70" s="10" t="n">
+      <c r="R70" s="12" t="n">
         <v>31.22</v>
       </c>
-      <c r="S70" s="10" t="n">
+      <c r="S70" s="12" t="n">
         <v>31.62</v>
       </c>
-      <c r="T70" s="10" t="n">
+      <c r="T70" s="12" t="n">
         <v>31.62</v>
       </c>
-      <c r="U70" s="10" t="n">
+      <c r="U70" s="12" t="n">
         <v>31.75</v>
       </c>
-      <c r="V70" s="10" t="n">
+      <c r="V70" s="12" t="n">
         <v>32.01</v>
       </c>
-      <c r="W70" s="10" t="n">
+      <c r="W70" s="12" t="n">
         <v>32.09</v>
       </c>
-      <c r="X70" s="10" t="n">
+      <c r="X70" s="12" t="n">
         <v>32.17</v>
       </c>
-      <c r="Y70" s="10" t="n">
+      <c r="Y70" s="12" t="n">
         <v>31.41</v>
       </c>
-      <c r="Z70" s="10" t="n">
+      <c r="Z70" s="12" t="n">
         <v>31.92</v>
       </c>
-      <c r="AA70" s="10" t="n">
+      <c r="AA70" s="12" t="n">
         <v>34.1</v>
       </c>
-      <c r="AB70" s="10" t="n">
+      <c r="AB70" s="12" t="n">
         <v>31.28</v>
       </c>
-      <c r="AC70" s="10" t="n">
+      <c r="AC70" s="12" t="n">
         <v>31.6</v>
       </c>
-      <c r="AD70" s="10" t="n">
+      <c r="AD70" s="12" t="n">
         <v>32.31</v>
       </c>
-      <c r="AE70" s="10" t="n">
+      <c r="AE70" s="12" t="n">
         <v>32.11</v>
       </c>
-      <c r="AF70" s="10" t="n">
+      <c r="AF70" s="12" t="n">
         <v>31.26</v>
       </c>
-      <c r="AG70" s="10" t="n">
+      <c r="AG70" s="12" t="n">
         <v>32.11</v>
       </c>
       <c r="AH70" s="6" t="n">
@@ -6632,7 +6653,7 @@
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="16" t="n"/>
+      <c r="AK70" s="19" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6643,97 +6664,97 @@
       <c r="B71" s="6" t="n">
         <v>573.25</v>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C71" s="12" t="n">
         <v>30.1</v>
       </c>
-      <c r="D71" s="10" t="n">
+      <c r="D71" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="E71" s="10" t="n">
+      <c r="E71" s="12" t="n">
         <v>29.72</v>
       </c>
-      <c r="F71" s="10" t="n">
+      <c r="F71" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="G71" s="10" t="n">
+      <c r="G71" s="12" t="n">
         <v>31.7</v>
       </c>
-      <c r="H71" s="10" t="n">
+      <c r="H71" s="12" t="n">
         <v>29.91</v>
       </c>
-      <c r="I71" s="10" t="n">
+      <c r="I71" s="12" t="n">
         <v>30.73</v>
       </c>
-      <c r="J71" s="10" t="n">
+      <c r="J71" s="12" t="n">
         <v>34.14</v>
       </c>
-      <c r="K71" s="10" t="n">
+      <c r="K71" s="12" t="n">
         <v>30.47</v>
       </c>
-      <c r="L71" s="10" t="n">
+      <c r="L71" s="12" t="n">
         <v>32.12</v>
       </c>
-      <c r="M71" s="10" t="n">
+      <c r="M71" s="12" t="n">
         <v>29.9</v>
       </c>
-      <c r="N71" s="10" t="n">
+      <c r="N71" s="12" t="n">
         <v>30.12</v>
       </c>
-      <c r="O71" s="10" t="n">
+      <c r="O71" s="12" t="n">
         <v>29.56</v>
       </c>
-      <c r="P71" s="10" t="n">
+      <c r="P71" s="12" t="n">
         <v>30.11</v>
       </c>
-      <c r="Q71" s="10" t="n">
+      <c r="Q71" s="12" t="n">
         <v>31.05</v>
       </c>
-      <c r="R71" s="10" t="n">
+      <c r="R71" s="12" t="n">
         <v>29.82</v>
       </c>
-      <c r="S71" s="10" t="n">
+      <c r="S71" s="12" t="n">
         <v>30.34</v>
       </c>
-      <c r="T71" s="10" t="n">
+      <c r="T71" s="12" t="n">
         <v>29.44</v>
       </c>
-      <c r="U71" s="10" t="n">
+      <c r="U71" s="12" t="n">
         <v>29.68</v>
       </c>
-      <c r="V71" s="10" t="n">
+      <c r="V71" s="12" t="n">
         <v>29.7</v>
       </c>
-      <c r="W71" s="10" t="n">
+      <c r="W71" s="12" t="n">
         <v>29.73</v>
       </c>
-      <c r="X71" s="10" t="n">
+      <c r="X71" s="12" t="n">
         <v>31.34</v>
       </c>
-      <c r="Y71" s="10" t="n">
+      <c r="Y71" s="12" t="n">
         <v>34.96</v>
       </c>
-      <c r="Z71" s="10" t="n">
+      <c r="Z71" s="12" t="n">
         <v>29.62</v>
       </c>
-      <c r="AA71" s="10" t="n">
+      <c r="AA71" s="12" t="n">
         <v>29.48</v>
       </c>
-      <c r="AB71" s="10" t="n">
+      <c r="AB71" s="12" t="n">
         <v>29.66</v>
       </c>
-      <c r="AC71" s="10" t="n">
+      <c r="AC71" s="12" t="n">
         <v>29.65</v>
       </c>
-      <c r="AD71" s="10" t="n">
+      <c r="AD71" s="12" t="n">
         <v>29.81</v>
       </c>
-      <c r="AE71" s="10" t="n">
+      <c r="AE71" s="12" t="n">
         <v>29.57</v>
       </c>
-      <c r="AF71" s="10" t="n">
+      <c r="AF71" s="12" t="n">
         <v>29.62</v>
       </c>
-      <c r="AG71" s="10" t="n">
+      <c r="AG71" s="12" t="n">
         <v>32.01</v>
       </c>
       <c r="AH71" s="6" t="n">
@@ -6741,7 +6762,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="16" t="n"/>
+      <c r="AK71" s="19" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6752,97 +6773,97 @@
       <c r="B72" s="6" t="n">
         <v>585.25</v>
       </c>
-      <c r="C72" s="10" t="n">
+      <c r="C72" s="12" t="n">
         <v>33.38</v>
       </c>
-      <c r="D72" s="10" t="n">
+      <c r="D72" s="12" t="n">
         <v>32.61</v>
       </c>
-      <c r="E72" s="10" t="n">
+      <c r="E72" s="12" t="n">
         <v>32.72</v>
       </c>
-      <c r="F72" s="10" t="n">
+      <c r="F72" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="G72" s="10" t="n">
+      <c r="G72" s="12" t="n">
         <v>32.51</v>
       </c>
-      <c r="H72" s="10" t="n">
+      <c r="H72" s="12" t="n">
         <v>32.48</v>
       </c>
-      <c r="I72" s="10" t="n">
+      <c r="I72" s="12" t="n">
         <v>31.93</v>
       </c>
-      <c r="J72" s="10" t="n">
+      <c r="J72" s="12" t="n">
         <v>35.1</v>
       </c>
-      <c r="K72" s="10" t="n">
+      <c r="K72" s="12" t="n">
         <v>32.72</v>
       </c>
-      <c r="L72" s="10" t="n">
+      <c r="L72" s="12" t="n">
         <v>34.05</v>
       </c>
-      <c r="M72" s="10" t="n">
+      <c r="M72" s="12" t="n">
         <v>34.14</v>
       </c>
-      <c r="N72" s="10" t="n">
+      <c r="N72" s="12" t="n">
         <v>32.36</v>
       </c>
-      <c r="O72" s="10" t="n">
+      <c r="O72" s="12" t="n">
         <v>32.78</v>
       </c>
-      <c r="P72" s="10" t="n">
+      <c r="P72" s="12" t="n">
         <v>34.24</v>
       </c>
-      <c r="Q72" s="10" t="n">
+      <c r="Q72" s="12" t="n">
         <v>32.56</v>
       </c>
-      <c r="R72" s="10" t="n">
+      <c r="R72" s="12" t="n">
         <v>32.69</v>
       </c>
-      <c r="S72" s="10" t="n">
+      <c r="S72" s="12" t="n">
         <v>32.33</v>
       </c>
-      <c r="T72" s="10" t="n">
+      <c r="T72" s="12" t="n">
         <v>32.36</v>
       </c>
-      <c r="U72" s="10" t="n">
+      <c r="U72" s="12" t="n">
         <v>32.29</v>
       </c>
-      <c r="V72" s="10" t="n">
+      <c r="V72" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="W72" s="10" t="n">
+      <c r="W72" s="12" t="n">
         <v>32.46</v>
       </c>
-      <c r="X72" s="10" t="n">
+      <c r="X72" s="12" t="n">
         <v>31.89</v>
       </c>
-      <c r="Y72" s="10" t="n">
+      <c r="Y72" s="12" t="n">
         <v>32.44</v>
       </c>
-      <c r="Z72" s="10" t="n">
+      <c r="Z72" s="12" t="n">
         <v>31.9</v>
       </c>
-      <c r="AA72" s="10" t="n">
+      <c r="AA72" s="12" t="n">
         <v>32.17</v>
       </c>
-      <c r="AB72" s="10" t="n">
+      <c r="AB72" s="12" t="n">
         <v>33.28</v>
       </c>
-      <c r="AC72" s="10" t="n">
+      <c r="AC72" s="12" t="n">
         <v>32.95</v>
       </c>
-      <c r="AD72" s="10" t="n">
+      <c r="AD72" s="12" t="n">
         <v>32.63</v>
       </c>
-      <c r="AE72" s="10" t="n">
+      <c r="AE72" s="12" t="n">
         <v>32.53</v>
       </c>
-      <c r="AF72" s="10" t="n">
+      <c r="AF72" s="12" t="n">
         <v>32.38</v>
       </c>
-      <c r="AG72" s="10" t="n">
+      <c r="AG72" s="12" t="n">
         <v>32.41</v>
       </c>
       <c r="AH72" s="6" t="n">
@@ -6850,7 +6871,7 @@
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="16" t="n"/>
+      <c r="AK72" s="19" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6954,12 +6975,12 @@
       <c r="AG73" s="7" t="n">
         <v>79.79000000000001</v>
       </c>
-      <c r="AH73" s="6" t="n">
+      <c r="AH73" s="8" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="16" t="n"/>
+      <c r="AK73" s="19" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6970,97 +6991,97 @@
       <c r="B74" s="6" t="n">
         <v>621.25</v>
       </c>
-      <c r="C74" s="10" t="n">
+      <c r="C74" s="12" t="n">
         <v>30.32</v>
       </c>
-      <c r="D74" s="10" t="n">
+      <c r="D74" s="12" t="n">
         <v>30.3</v>
       </c>
-      <c r="E74" s="10" t="n">
+      <c r="E74" s="12" t="n">
         <v>30.2</v>
       </c>
-      <c r="F74" s="10" t="n">
+      <c r="F74" s="12" t="n">
         <v>29.75</v>
       </c>
-      <c r="G74" s="10" t="n">
+      <c r="G74" s="12" t="n">
         <v>29.9</v>
       </c>
-      <c r="H74" s="10" t="n">
+      <c r="H74" s="12" t="n">
         <v>29.98</v>
       </c>
-      <c r="I74" s="10" t="n">
+      <c r="I74" s="12" t="n">
         <v>29.66</v>
       </c>
-      <c r="J74" s="10" t="n">
+      <c r="J74" s="12" t="n">
         <v>29.84</v>
       </c>
-      <c r="K74" s="10" t="n">
+      <c r="K74" s="12" t="n">
         <v>30.35</v>
       </c>
-      <c r="L74" s="10" t="n">
+      <c r="L74" s="12" t="n">
         <v>33.02</v>
       </c>
-      <c r="M74" s="10" t="n">
+      <c r="M74" s="12" t="n">
         <v>30.01</v>
       </c>
-      <c r="N74" s="10" t="n">
+      <c r="N74" s="12" t="n">
         <v>29.79</v>
       </c>
-      <c r="O74" s="10" t="n">
+      <c r="O74" s="12" t="n">
         <v>32.08</v>
       </c>
-      <c r="P74" s="10" t="n">
+      <c r="P74" s="12" t="n">
         <v>30.26</v>
       </c>
-      <c r="Q74" s="10" t="n">
+      <c r="Q74" s="12" t="n">
         <v>30.26</v>
       </c>
-      <c r="R74" s="10" t="n">
+      <c r="R74" s="12" t="n">
         <v>29.52</v>
       </c>
-      <c r="S74" s="10" t="n">
+      <c r="S74" s="12" t="n">
         <v>30.26</v>
       </c>
-      <c r="T74" s="10" t="n">
+      <c r="T74" s="12" t="n">
         <v>29.72</v>
       </c>
-      <c r="U74" s="10" t="n">
+      <c r="U74" s="12" t="n">
         <v>31.64</v>
       </c>
-      <c r="V74" s="10" t="n">
+      <c r="V74" s="12" t="n">
         <v>29.29</v>
       </c>
-      <c r="W74" s="10" t="n">
+      <c r="W74" s="12" t="n">
         <v>29.83</v>
       </c>
-      <c r="X74" s="10" t="n">
+      <c r="X74" s="12" t="n">
         <v>30.21</v>
       </c>
-      <c r="Y74" s="10" t="n">
+      <c r="Y74" s="12" t="n">
         <v>31.16</v>
       </c>
-      <c r="Z74" s="10" t="n">
+      <c r="Z74" s="12" t="n">
         <v>29.88</v>
       </c>
-      <c r="AA74" s="10" t="n">
+      <c r="AA74" s="12" t="n">
         <v>33.85</v>
       </c>
-      <c r="AB74" s="10" t="n">
+      <c r="AB74" s="12" t="n">
         <v>29.26</v>
       </c>
-      <c r="AC74" s="10" t="n">
+      <c r="AC74" s="12" t="n">
         <v>31.25</v>
       </c>
-      <c r="AD74" s="10" t="n">
+      <c r="AD74" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="AE74" s="10" t="n">
+      <c r="AE74" s="12" t="n">
         <v>29.49</v>
       </c>
-      <c r="AF74" s="10" t="n">
+      <c r="AF74" s="12" t="n">
         <v>30.38</v>
       </c>
-      <c r="AG74" s="10" t="n">
+      <c r="AG74" s="12" t="n">
         <v>30.25</v>
       </c>
       <c r="AH74" s="6" t="n">
@@ -7068,116 +7089,116 @@
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="16" t="n"/>
+      <c r="AK74" s="19" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="14" t="n">
         <v>633.25</v>
       </c>
-      <c r="C75" s="17" t="n">
+      <c r="C75" s="20" t="n">
         <v>29.02</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="20" t="n">
         <v>30.64</v>
       </c>
-      <c r="E75" s="17" t="n">
+      <c r="E75" s="20" t="n">
         <v>28.75</v>
       </c>
-      <c r="F75" s="17" t="n">
+      <c r="F75" s="20" t="n">
         <v>29.3</v>
       </c>
-      <c r="G75" s="17" t="n">
+      <c r="G75" s="20" t="n">
         <v>29.96</v>
       </c>
-      <c r="H75" s="17" t="n">
+      <c r="H75" s="20" t="n">
         <v>29.38</v>
       </c>
-      <c r="I75" s="17" t="n">
+      <c r="I75" s="20" t="n">
         <v>28.91</v>
       </c>
-      <c r="J75" s="17" t="n">
+      <c r="J75" s="20" t="n">
         <v>29.28</v>
       </c>
-      <c r="K75" s="17" t="n">
+      <c r="K75" s="20" t="n">
         <v>30.2</v>
       </c>
-      <c r="L75" s="17" t="n">
+      <c r="L75" s="20" t="n">
         <v>30.12</v>
       </c>
-      <c r="M75" s="17" t="n">
+      <c r="M75" s="20" t="n">
         <v>31.44</v>
       </c>
-      <c r="N75" s="17" t="n">
+      <c r="N75" s="20" t="n">
         <v>29.04</v>
       </c>
-      <c r="O75" s="17" t="n">
+      <c r="O75" s="20" t="n">
         <v>29.02</v>
       </c>
-      <c r="P75" s="17" t="n">
+      <c r="P75" s="20" t="n">
         <v>29.38</v>
       </c>
-      <c r="Q75" s="17" t="n">
+      <c r="Q75" s="20" t="n">
         <v>29.29</v>
       </c>
-      <c r="R75" s="17" t="n">
+      <c r="R75" s="20" t="n">
         <v>29.71</v>
       </c>
-      <c r="S75" s="17" t="n">
+      <c r="S75" s="20" t="n">
         <v>29.5</v>
       </c>
-      <c r="T75" s="17" t="n">
+      <c r="T75" s="20" t="n">
         <v>29.38</v>
       </c>
-      <c r="U75" s="17" t="n">
+      <c r="U75" s="20" t="n">
         <v>29.78</v>
       </c>
-      <c r="V75" s="17" t="n">
+      <c r="V75" s="20" t="n">
         <v>29.85</v>
       </c>
-      <c r="W75" s="17" t="n">
+      <c r="W75" s="20" t="n">
         <v>29.16</v>
       </c>
-      <c r="X75" s="17" t="n">
+      <c r="X75" s="20" t="n">
         <v>29.29</v>
       </c>
-      <c r="Y75" s="17" t="n">
+      <c r="Y75" s="20" t="n">
         <v>29.48</v>
       </c>
-      <c r="Z75" s="17" t="n">
+      <c r="Z75" s="20" t="n">
         <v>37.17</v>
       </c>
-      <c r="AA75" s="17" t="n">
+      <c r="AA75" s="20" t="n">
         <v>28.92</v>
       </c>
-      <c r="AB75" s="17" t="n">
+      <c r="AB75" s="20" t="n">
         <v>31.6</v>
       </c>
-      <c r="AC75" s="17" t="n">
+      <c r="AC75" s="20" t="n">
         <v>30.51</v>
       </c>
-      <c r="AD75" s="17" t="n">
+      <c r="AD75" s="20" t="n">
         <v>29.07</v>
       </c>
-      <c r="AE75" s="17" t="n">
+      <c r="AE75" s="20" t="n">
         <v>28.94</v>
       </c>
-      <c r="AF75" s="17" t="n">
+      <c r="AF75" s="20" t="n">
         <v>29.25</v>
       </c>
-      <c r="AG75" s="17" t="n">
+      <c r="AG75" s="20" t="n">
         <v>29.59</v>
       </c>
-      <c r="AH75" s="12" t="n">
+      <c r="AH75" s="14" t="n">
         <v>29.84</v>
       </c>
-      <c r="AI75" s="12" t="inlineStr"/>
-      <c r="AJ75" s="12" t="inlineStr"/>
-      <c r="AK75" s="18" t="n"/>
+      <c r="AI75" s="14" t="inlineStr"/>
+      <c r="AJ75" s="14" t="inlineStr"/>
+      <c r="AK75" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -303,7 +303,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -326,9 +326,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2476500" cy="1143000"/>
@@ -376,7 +376,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
       <row>56</row>
       <rowOff>0</rowOff>

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -30,12 +30,18 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -171,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,16 +197,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,7 +218,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,7 +229,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -792,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -1030,11 +1042,11 @@
       <c r="AH11" s="6" t="n">
         <v>70.81</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="8" t="n">
         <v>244.66</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1145,7 +1157,7 @@
         <v>160.6</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1256,7 +1268,7 @@
         <v>200.59</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1306,7 +1318,7 @@
       <c r="O14" s="7" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="10" t="n">
         <v>51.91</v>
       </c>
       <c r="Q14" s="7" t="n">
@@ -1363,11 +1375,11 @@
       <c r="AH14" s="6" t="n">
         <v>66.97</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="8" t="n">
         <v>265.65</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1474,11 +1486,11 @@
       <c r="AH15" s="6" t="n">
         <v>75.67</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="8" t="n">
         <v>229.65</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1585,11 +1597,11 @@
       <c r="AH16" s="6" t="n">
         <v>67.72</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="8" t="n">
         <v>428.49</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1696,11 +1708,11 @@
       <c r="AH17" s="6" t="n">
         <v>70.15000000000001</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="8" t="n">
         <v>388.85</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1711,107 +1723,107 @@
       <c r="B18" s="6" t="n">
         <v>91.5</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="10" t="n">
         <v>52.72</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="10" t="n">
         <v>50.06</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>58.76</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <v>50.41</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="10" t="n">
         <v>46.62</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="10" t="n">
         <v>49.69</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="10" t="n">
         <v>50.71</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="10" t="n">
         <v>48.24</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="10" t="n">
         <v>50.75</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="10" t="n">
         <v>50.51</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="10" t="n">
         <v>52.76</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="10" t="n">
         <v>51.64</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="10" t="n">
         <v>48.68</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" s="10" t="n">
         <v>49.17</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="10" t="n">
         <v>53.33</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="10" t="n">
         <v>50.15</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="10" t="n">
         <v>48.7</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="10" t="n">
         <v>49.26</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="10" t="n">
         <v>47.96</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="10" t="n">
         <v>47.53</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="10" t="n">
         <v>49.54</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" s="10" t="n">
         <v>49.93</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="10" t="n">
         <v>52.67</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="Z18" s="10" t="n">
         <v>48.81</v>
       </c>
-      <c r="AA18" s="9" t="n">
+      <c r="AA18" s="10" t="n">
         <v>48.32</v>
       </c>
-      <c r="AB18" s="9" t="n">
+      <c r="AB18" s="10" t="n">
         <v>49.61</v>
       </c>
-      <c r="AC18" s="9" t="n">
+      <c r="AC18" s="10" t="n">
         <v>49.47</v>
       </c>
-      <c r="AD18" s="9" t="n">
+      <c r="AD18" s="10" t="n">
         <v>47.34</v>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AE18" s="10" t="n">
         <v>49.9</v>
       </c>
-      <c r="AF18" s="9" t="n">
+      <c r="AF18" s="10" t="n">
         <v>52.66</v>
       </c>
-      <c r="AG18" s="9" t="n">
+      <c r="AG18" s="10" t="n">
         <v>51.71</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="8" t="n">
         <v>50.25</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="8" t="n">
         <v>499.47</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1918,11 +1930,11 @@
       <c r="AH19" s="6" t="n">
         <v>67.31</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="8" t="n">
         <v>315.82</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2029,11 +2041,11 @@
       <c r="AH20" s="6" t="n">
         <v>60.42</v>
       </c>
-      <c r="AI20" s="6" t="n">
+      <c r="AI20" s="8" t="n">
         <v>478.59</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2119,10 +2131,10 @@
       <c r="AA21" s="7" t="n">
         <v>62.14</v>
       </c>
-      <c r="AB21" s="9" t="n">
+      <c r="AB21" s="10" t="n">
         <v>48.92</v>
       </c>
-      <c r="AC21" s="10" t="n">
+      <c r="AC21" s="11" t="n">
         <v>42.56</v>
       </c>
       <c r="AD21" s="7" t="n">
@@ -2140,11 +2152,11 @@
       <c r="AH21" s="6" t="n">
         <v>63.62</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="8" t="n">
         <v>349.62</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2215,7 +2227,7 @@
       <c r="V22" s="7" t="n">
         <v>56.63</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="10" t="n">
         <v>53.21</v>
       </c>
       <c r="X22" s="7" t="n">
@@ -2233,29 +2245,29 @@
       <c r="AB22" s="7" t="n">
         <v>56.89</v>
       </c>
-      <c r="AC22" s="9" t="n">
+      <c r="AC22" s="10" t="n">
         <v>51.04</v>
       </c>
-      <c r="AD22" s="9" t="n">
+      <c r="AD22" s="10" t="n">
         <v>45.58</v>
       </c>
-      <c r="AE22" s="9" t="n">
+      <c r="AE22" s="10" t="n">
         <v>45.66</v>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AF22" s="10" t="n">
         <v>48.05</v>
       </c>
-      <c r="AG22" s="9" t="n">
+      <c r="AG22" s="10" t="n">
         <v>47.09</v>
       </c>
       <c r="AH22" s="6" t="n">
         <v>56.95</v>
       </c>
-      <c r="AI22" s="6" t="n">
+      <c r="AI22" s="8" t="n">
         <v>386.51</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2366,7 +2378,7 @@
         <v>219.15</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2473,11 +2485,11 @@
       <c r="AH24" s="6" t="n">
         <v>64.73999999999999</v>
       </c>
-      <c r="AI24" s="6" t="n">
+      <c r="AI24" s="8" t="n">
         <v>226.77</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2588,7 +2600,7 @@
         <v>123.83</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2695,11 +2707,11 @@
       <c r="AH26" s="6" t="n">
         <v>73.31</v>
       </c>
-      <c r="AI26" s="6" t="n">
+      <c r="AI26" s="8" t="n">
         <v>223.97</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2716,7 +2728,7 @@
       <c r="D27" s="7" t="n">
         <v>60.51</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="10" t="n">
         <v>52.24</v>
       </c>
       <c r="F27" s="7" t="n">
@@ -2806,11 +2818,11 @@
       <c r="AH27" s="6" t="n">
         <v>59.85</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="8" t="n">
         <v>431.6</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2917,11 +2929,11 @@
       <c r="AH28" s="6" t="n">
         <v>62.51</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="8" t="n">
         <v>478.51</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3028,11 +3040,11 @@
       <c r="AH29" s="6" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="8" t="n">
         <v>258.64</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3139,11 +3151,11 @@
       <c r="AH30" s="6" t="n">
         <v>68.58</v>
       </c>
-      <c r="AI30" s="6" t="n">
+      <c r="AI30" s="8" t="n">
         <v>254.74</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3154,107 +3166,107 @@
       <c r="B31" s="6" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="10" t="n">
         <v>49.18</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="11" t="n">
         <v>38.17</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="11" t="n">
         <v>39.78</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>48.22</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="10" t="n">
         <v>45.28</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="10" t="n">
         <v>47.22</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="10" t="n">
         <v>47.81</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="10" t="n">
         <v>46.02</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="10" t="n">
         <v>47.37</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="10" t="n">
         <v>45.26</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="10" t="n">
         <v>49.09</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="10" t="n">
         <v>47.71</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="P31" s="10" t="n">
         <v>53.23</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="10" t="n">
         <v>43.31</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="11" t="n">
         <v>42.73</v>
       </c>
-      <c r="S31" s="10" t="n">
+      <c r="S31" s="11" t="n">
         <v>36.38</v>
       </c>
-      <c r="T31" s="10" t="n">
+      <c r="T31" s="11" t="n">
         <v>42.77</v>
       </c>
-      <c r="U31" s="10" t="n">
+      <c r="U31" s="11" t="n">
         <v>40.38</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="10" t="n">
         <v>44.49</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="10" t="n">
         <v>45.69</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X31" s="10" t="n">
         <v>45.4</v>
       </c>
-      <c r="Y31" s="10" t="n">
+      <c r="Y31" s="11" t="n">
         <v>40.74</v>
       </c>
-      <c r="Z31" s="10" t="n">
+      <c r="Z31" s="11" t="n">
         <v>41.24</v>
       </c>
-      <c r="AA31" s="10" t="n">
+      <c r="AA31" s="11" t="n">
         <v>41.48</v>
       </c>
-      <c r="AB31" s="10" t="n">
+      <c r="AB31" s="11" t="n">
         <v>42.87</v>
       </c>
-      <c r="AC31" s="9" t="n">
+      <c r="AC31" s="10" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="10" t="n">
+      <c r="AD31" s="11" t="n">
         <v>40.41</v>
       </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AE31" s="10" t="n">
         <v>47.34</v>
       </c>
-      <c r="AF31" s="9" t="n">
+      <c r="AF31" s="10" t="n">
         <v>51.7</v>
       </c>
-      <c r="AG31" s="9" t="n">
+      <c r="AG31" s="10" t="n">
         <v>45.77</v>
       </c>
-      <c r="AH31" s="6" t="n">
+      <c r="AH31" s="8" t="n">
         <v>44.94</v>
       </c>
-      <c r="AI31" s="6" t="n">
+      <c r="AI31" s="8" t="n">
         <v>485.2</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3271,7 +3283,7 @@
       <c r="D32" s="7" t="n">
         <v>55.07</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="10" t="n">
         <v>52.52</v>
       </c>
       <c r="F32" s="7" t="n">
@@ -3361,11 +3373,11 @@
       <c r="AH32" s="6" t="n">
         <v>55.72</v>
       </c>
-      <c r="AI32" s="6" t="n">
+      <c r="AI32" s="8" t="n">
         <v>474.57</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3472,11 +3484,11 @@
       <c r="AH33" s="6" t="n">
         <v>76.88</v>
       </c>
-      <c r="AI33" s="6" t="n">
+      <c r="AI33" s="8" t="n">
         <v>326</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="8" t="inlineStr"/>
+      <c r="AK33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3583,11 +3595,11 @@
       <c r="AH34" s="6" t="n">
         <v>65.95999999999999</v>
       </c>
-      <c r="AI34" s="6" t="n">
+      <c r="AI34" s="8" t="n">
         <v>478.65</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="8" t="inlineStr"/>
+      <c r="AK34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3694,11 +3706,11 @@
       <c r="AH35" s="6" t="n">
         <v>60.41</v>
       </c>
-      <c r="AI35" s="6" t="n">
+      <c r="AI35" s="8" t="n">
         <v>497.28</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="8" t="inlineStr"/>
+      <c r="AK35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3805,11 +3817,11 @@
       <c r="AH36" s="6" t="n">
         <v>65.18000000000001</v>
       </c>
-      <c r="AI36" s="6" t="n">
+      <c r="AI36" s="8" t="n">
         <v>431.37</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="8" t="inlineStr"/>
+      <c r="AK36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3820,107 +3832,107 @@
       <c r="B37" s="6" t="n">
         <v>101.1</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="11" t="n">
         <v>41.52</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="11" t="n">
         <v>37.06</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="11" t="n">
         <v>39.89</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="11" t="n">
         <v>41.01</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="11" t="n">
         <v>40.08</v>
       </c>
-      <c r="H37" s="10" t="n">
+      <c r="H37" s="11" t="n">
         <v>41.32</v>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="I37" s="11" t="n">
         <v>40.03</v>
       </c>
-      <c r="J37" s="10" t="n">
+      <c r="J37" s="11" t="n">
         <v>40.92</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="K37" s="11" t="n">
         <v>39.57</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="11" t="n">
         <v>40.51</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="10" t="n">
         <v>44.43</v>
       </c>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="11" t="n">
         <v>40.55</v>
       </c>
-      <c r="O37" s="9" t="n">
+      <c r="O37" s="10" t="n">
         <v>43.01</v>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P37" s="10" t="n">
         <v>43.79</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="11" t="n">
         <v>40.86</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="11" t="n">
         <v>36.73</v>
       </c>
-      <c r="S37" s="10" t="n">
+      <c r="S37" s="11" t="n">
         <v>36.76</v>
       </c>
-      <c r="T37" s="10" t="n">
+      <c r="T37" s="11" t="n">
         <v>38.71</v>
       </c>
-      <c r="U37" s="10" t="n">
+      <c r="U37" s="11" t="n">
         <v>36.86</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="11" t="n">
         <v>40.22</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="11" t="n">
         <v>40.92</v>
       </c>
-      <c r="X37" s="10" t="n">
+      <c r="X37" s="11" t="n">
         <v>39.83</v>
       </c>
-      <c r="Y37" s="10" t="n">
+      <c r="Y37" s="11" t="n">
         <v>37.26</v>
       </c>
-      <c r="Z37" s="10" t="n">
+      <c r="Z37" s="11" t="n">
         <v>38.74</v>
       </c>
-      <c r="AA37" s="10" t="n">
+      <c r="AA37" s="11" t="n">
         <v>37.96</v>
       </c>
-      <c r="AB37" s="10" t="n">
+      <c r="AB37" s="11" t="n">
         <v>41.61</v>
       </c>
-      <c r="AC37" s="10" t="n">
+      <c r="AC37" s="11" t="n">
         <v>41.84</v>
       </c>
-      <c r="AD37" s="10" t="n">
+      <c r="AD37" s="11" t="n">
         <v>38.69</v>
       </c>
-      <c r="AE37" s="10" t="n">
+      <c r="AE37" s="11" t="n">
         <v>41.51</v>
       </c>
-      <c r="AF37" s="10" t="n">
+      <c r="AF37" s="11" t="n">
         <v>41.72</v>
       </c>
-      <c r="AG37" s="10" t="n">
+      <c r="AG37" s="11" t="n">
         <v>41.58</v>
       </c>
-      <c r="AH37" s="6" t="n">
+      <c r="AH37" s="8" t="n">
         <v>40.18</v>
       </c>
-      <c r="AI37" s="6" t="n">
+      <c r="AI37" s="8" t="n">
         <v>499.53</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="8" t="inlineStr"/>
+      <c r="AK37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4031,7 +4043,7 @@
         <v>159.74</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="8" t="inlineStr"/>
+      <c r="AK38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4138,11 +4150,11 @@
       <c r="AH39" s="6" t="n">
         <v>71.44</v>
       </c>
-      <c r="AI39" s="6" t="n">
+      <c r="AI39" s="8" t="n">
         <v>422.29</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="8" t="inlineStr"/>
+      <c r="AK39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4249,11 +4261,11 @@
       <c r="AH40" s="6" t="n">
         <v>58.38</v>
       </c>
-      <c r="AI40" s="6" t="n">
+      <c r="AI40" s="8" t="n">
         <v>471.03</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="8" t="inlineStr"/>
+      <c r="AK40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4264,107 +4276,107 @@
       <c r="B41" s="6" t="n">
         <v>103.1</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="10" t="n">
         <v>46.72</v>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="11" t="n">
         <v>35.76</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="11" t="n">
         <v>36.4</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>45.76</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="10" t="n">
         <v>43.98</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="10" t="n">
         <v>45.91</v>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I41" s="11" t="n">
         <v>42.62</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" s="10" t="n">
         <v>44.54</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="10" t="n">
         <v>43.32</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="10" t="n">
         <v>43.78</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="10" t="n">
         <v>46.12</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="10" t="n">
         <v>45.71</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="10" t="n">
         <v>45.21</v>
       </c>
-      <c r="P41" s="10" t="n">
+      <c r="P41" s="11" t="n">
         <v>42.01</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="10" t="n">
         <v>47.36</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="10" t="n">
         <v>43.31</v>
       </c>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="11" t="n">
         <v>37.48</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="10" t="n">
         <v>43.12</v>
       </c>
-      <c r="U41" s="10" t="n">
+      <c r="U41" s="11" t="n">
         <v>41.52</v>
       </c>
-      <c r="V41" s="10" t="n">
+      <c r="V41" s="11" t="n">
         <v>42.48</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="11" t="n">
         <v>42.72</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="10" t="n">
         <v>46.34</v>
       </c>
-      <c r="Y41" s="10" t="n">
+      <c r="Y41" s="11" t="n">
         <v>42.01</v>
       </c>
-      <c r="Z41" s="10" t="n">
+      <c r="Z41" s="11" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA41" s="10" t="n">
+      <c r="AA41" s="11" t="n">
         <v>41.55</v>
       </c>
-      <c r="AB41" s="10" t="n">
+      <c r="AB41" s="11" t="n">
         <v>41.22</v>
       </c>
-      <c r="AC41" s="9" t="n">
+      <c r="AC41" s="10" t="n">
         <v>44.88</v>
       </c>
-      <c r="AD41" s="10" t="n">
+      <c r="AD41" s="11" t="n">
         <v>38.64</v>
       </c>
-      <c r="AE41" s="10" t="n">
+      <c r="AE41" s="11" t="n">
         <v>41.14</v>
       </c>
-      <c r="AF41" s="9" t="n">
+      <c r="AF41" s="10" t="n">
         <v>47.4</v>
       </c>
-      <c r="AG41" s="9" t="n">
+      <c r="AG41" s="10" t="n">
         <v>48.04</v>
       </c>
-      <c r="AH41" s="6" t="n">
+      <c r="AH41" s="8" t="n">
         <v>43.14</v>
       </c>
       <c r="AI41" s="6" t="n">
         <v>161.11</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="8" t="inlineStr"/>
+      <c r="AK41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4375,107 +4387,107 @@
       <c r="B42" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="10" t="n">
         <v>46.89</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="11" t="n">
         <v>36.46</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="11" t="n">
         <v>37.76</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>45.51</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="10" t="n">
         <v>44.04</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="10" t="n">
         <v>45.22</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="10" t="n">
         <v>43.04</v>
       </c>
-      <c r="J42" s="10" t="n">
+      <c r="J42" s="11" t="n">
         <v>42.79</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="10" t="n">
         <v>47.75</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="10" t="n">
         <v>45.64</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="10" t="n">
         <v>46.23</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="10" t="n">
         <v>44.39</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="10" t="n">
         <v>45.54</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="10" t="n">
         <v>46.71</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="11" t="n">
         <v>42.49</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="11" t="n">
         <v>39.33</v>
       </c>
-      <c r="S42" s="10" t="n">
+      <c r="S42" s="11" t="n">
         <v>40.14</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="T42" s="11" t="n">
         <v>38.01</v>
       </c>
-      <c r="U42" s="10" t="n">
+      <c r="U42" s="11" t="n">
         <v>38.08</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="V42" s="11" t="n">
         <v>38.74</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="10" t="n">
         <v>43.46</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="10" t="n">
         <v>46.21</v>
       </c>
-      <c r="Y42" s="10" t="n">
+      <c r="Y42" s="11" t="n">
         <v>40.55</v>
       </c>
-      <c r="Z42" s="10" t="n">
+      <c r="Z42" s="11" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA42" s="10" t="n">
+      <c r="AA42" s="11" t="n">
         <v>36.65</v>
       </c>
-      <c r="AB42" s="10" t="n">
+      <c r="AB42" s="11" t="n">
         <v>42.29</v>
       </c>
-      <c r="AC42" s="9" t="n">
+      <c r="AC42" s="10" t="n">
         <v>45.95</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AD42" s="10" t="n">
         <v>43.71</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="10" t="n">
         <v>45.76</v>
       </c>
-      <c r="AF42" s="9" t="n">
+      <c r="AF42" s="10" t="n">
         <v>47.26</v>
       </c>
-      <c r="AG42" s="9" t="n">
+      <c r="AG42" s="10" t="n">
         <v>44.16</v>
       </c>
-      <c r="AH42" s="6" t="n">
+      <c r="AH42" s="8" t="n">
         <v>42.94</v>
       </c>
       <c r="AI42" s="6" t="n">
         <v>141.85</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="8" t="inlineStr"/>
+      <c r="AK42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4486,107 +4498,107 @@
       <c r="B43" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="10" t="n">
         <v>47.79</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="11" t="n">
         <v>36.54</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="11" t="n">
         <v>35.36</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="11" t="n">
         <v>39.5</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="11" t="n">
         <v>39.05</v>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="H43" s="10" t="n">
         <v>44.41</v>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="11" t="n">
         <v>42.89</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="10" t="n">
         <v>45.39</v>
       </c>
-      <c r="K43" s="9" t="n">
+      <c r="K43" s="10" t="n">
         <v>46.43</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="10" t="n">
         <v>44.24</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="10" t="n">
         <v>46.82</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" s="10" t="n">
         <v>43.69</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="10" t="n">
         <v>48.21</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="P43" s="10" t="n">
         <v>47.44</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="10" t="n">
         <v>43.59</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="11" t="n">
         <v>39.13</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="S43" s="11" t="n">
         <v>38.44</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="T43" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="U43" s="10" t="n">
+      <c r="U43" s="11" t="n">
         <v>42.06</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="11" t="n">
         <v>39.01</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="11" t="n">
         <v>42.07</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" s="10" t="n">
         <v>46.61</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="11" t="n">
         <v>36.92</v>
       </c>
-      <c r="Z43" s="10" t="n">
+      <c r="Z43" s="11" t="n">
         <v>37.61</v>
       </c>
-      <c r="AA43" s="10" t="n">
+      <c r="AA43" s="11" t="n">
         <v>36.41</v>
       </c>
-      <c r="AB43" s="10" t="n">
+      <c r="AB43" s="11" t="n">
         <v>40.19</v>
       </c>
-      <c r="AC43" s="10" t="n">
+      <c r="AC43" s="11" t="n">
         <v>39.22</v>
       </c>
-      <c r="AD43" s="10" t="n">
+      <c r="AD43" s="11" t="n">
         <v>40.28</v>
       </c>
-      <c r="AE43" s="9" t="n">
+      <c r="AE43" s="10" t="n">
         <v>47.26</v>
       </c>
-      <c r="AF43" s="9" t="n">
+      <c r="AF43" s="10" t="n">
         <v>46.28</v>
       </c>
-      <c r="AG43" s="9" t="n">
+      <c r="AG43" s="10" t="n">
         <v>45.59</v>
       </c>
-      <c r="AH43" s="6" t="n">
+      <c r="AH43" s="8" t="n">
         <v>42.27</v>
       </c>
       <c r="AI43" s="6" t="n">
         <v>140.45</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="8" t="inlineStr"/>
+      <c r="AK43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4697,7 +4709,7 @@
         <v>181.85</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="8" t="inlineStr"/>
+      <c r="AK44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4804,11 +4816,11 @@
       <c r="AH45" s="6" t="n">
         <v>66.86</v>
       </c>
-      <c r="AI45" s="6" t="n">
+      <c r="AI45" s="8" t="n">
         <v>243.9</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="8" t="inlineStr"/>
+      <c r="AK45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4915,11 +4927,11 @@
       <c r="AH46" s="6" t="n">
         <v>70.11</v>
       </c>
-      <c r="AI46" s="6" t="n">
+      <c r="AI46" s="8" t="n">
         <v>252.32</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="8" t="inlineStr"/>
+      <c r="AK46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -5026,11 +5038,11 @@
       <c r="AH47" s="6" t="n">
         <v>79.56999999999999</v>
       </c>
-      <c r="AI47" s="6" t="n">
+      <c r="AI47" s="8" t="n">
         <v>254.37</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="8" t="inlineStr"/>
+      <c r="AK47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5047,7 +5059,7 @@
       <c r="D48" s="7" t="n">
         <v>56.33</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="10" t="n">
         <v>52.45</v>
       </c>
       <c r="F48" s="7" t="n">
@@ -5137,11 +5149,11 @@
       <c r="AH48" s="6" t="n">
         <v>55.88</v>
       </c>
-      <c r="AI48" s="6" t="n">
+      <c r="AI48" s="8" t="n">
         <v>487.79</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="8" t="inlineStr"/>
+      <c r="AK48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5248,11 +5260,11 @@
       <c r="AH49" s="6" t="n">
         <v>66.84</v>
       </c>
-      <c r="AI49" s="6" t="n">
+      <c r="AI49" s="8" t="n">
         <v>385.5</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="8" t="inlineStr"/>
+      <c r="AK49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5359,11 +5371,11 @@
       <c r="AH50" s="6" t="n">
         <v>73.84</v>
       </c>
-      <c r="AI50" s="6" t="n">
+      <c r="AI50" s="8" t="n">
         <v>236.24</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="8" t="inlineStr"/>
+      <c r="AK50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -5374,218 +5386,218 @@
       <c r="B51" s="6" t="n">
         <v>106.7</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="10" t="n">
         <v>45.59</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D51" s="10" t="n">
         <v>44.29</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="10" t="n">
         <v>45.42</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="10" t="n">
         <v>45.54</v>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G51" s="10" t="n">
         <v>45.36</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H51" s="10" t="n">
         <v>44.1</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="I51" s="10" t="n">
         <v>45.04</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J51" s="10" t="n">
         <v>45.04</v>
       </c>
-      <c r="K51" s="9" t="n">
+      <c r="K51" s="10" t="n">
         <v>45.84</v>
       </c>
-      <c r="L51" s="9" t="n">
+      <c r="L51" s="10" t="n">
         <v>43.74</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" s="10" t="n">
         <v>44.87</v>
       </c>
-      <c r="N51" s="9" t="n">
+      <c r="N51" s="10" t="n">
         <v>45.91</v>
       </c>
-      <c r="O51" s="9" t="n">
+      <c r="O51" s="10" t="n">
         <v>45.61</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P51" s="10" t="n">
         <v>45.42</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="Q51" s="10" t="n">
         <v>45.88</v>
       </c>
-      <c r="R51" s="9" t="n">
+      <c r="R51" s="10" t="n">
         <v>45.66</v>
       </c>
-      <c r="S51" s="9" t="n">
+      <c r="S51" s="10" t="n">
         <v>45.7</v>
       </c>
-      <c r="T51" s="9" t="n">
+      <c r="T51" s="10" t="n">
         <v>46.39</v>
       </c>
-      <c r="U51" s="9" t="n">
+      <c r="U51" s="10" t="n">
         <v>45.44</v>
       </c>
-      <c r="V51" s="9" t="n">
+      <c r="V51" s="10" t="n">
         <v>43.86</v>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W51" s="10" t="n">
         <v>44.56</v>
       </c>
-      <c r="X51" s="9" t="n">
+      <c r="X51" s="10" t="n">
         <v>44.54</v>
       </c>
-      <c r="Y51" s="9" t="n">
+      <c r="Y51" s="10" t="n">
         <v>44.78</v>
       </c>
-      <c r="Z51" s="9" t="n">
+      <c r="Z51" s="10" t="n">
         <v>43.79</v>
       </c>
-      <c r="AA51" s="9" t="n">
+      <c r="AA51" s="10" t="n">
         <v>45.58</v>
       </c>
-      <c r="AB51" s="9" t="n">
+      <c r="AB51" s="10" t="n">
         <v>43.16</v>
       </c>
-      <c r="AC51" s="9" t="n">
+      <c r="AC51" s="10" t="n">
         <v>43.36</v>
       </c>
-      <c r="AD51" s="9" t="n">
+      <c r="AD51" s="10" t="n">
         <v>44.17</v>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AE51" s="10" t="n">
         <v>46.02</v>
       </c>
-      <c r="AF51" s="9" t="n">
+      <c r="AF51" s="10" t="n">
         <v>45.81</v>
       </c>
-      <c r="AG51" s="9" t="n">
+      <c r="AG51" s="10" t="n">
         <v>44.48</v>
       </c>
-      <c r="AH51" s="6" t="n">
+      <c r="AH51" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="AI51" s="6" t="n">
+      <c r="AI51" s="8" t="n">
         <v>468.87</v>
       </c>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="8" t="inlineStr"/>
+      <c r="AK51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>GENESIS FM STEREO</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="13" t="n">
         <v>107.5</v>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C52" s="14" t="n">
         <v>45.55</v>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="14" t="n">
         <v>45.58</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="14" t="n">
         <v>46.18</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F52" s="14" t="n">
         <v>45.65</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="14" t="n">
         <v>47.34</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="14" t="n">
         <v>47.62</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="I52" s="14" t="n">
         <v>46.46</v>
       </c>
-      <c r="J52" s="13" t="n">
+      <c r="J52" s="14" t="n">
         <v>45.94</v>
       </c>
-      <c r="K52" s="13" t="n">
+      <c r="K52" s="14" t="n">
         <v>45.49</v>
       </c>
-      <c r="L52" s="13" t="n">
+      <c r="L52" s="14" t="n">
         <v>45.62</v>
       </c>
-      <c r="M52" s="13" t="n">
+      <c r="M52" s="14" t="n">
         <v>46.22</v>
       </c>
-      <c r="N52" s="13" t="n">
+      <c r="N52" s="14" t="n">
         <v>47.42</v>
       </c>
-      <c r="O52" s="13" t="n">
+      <c r="O52" s="14" t="n">
         <v>46.59</v>
       </c>
-      <c r="P52" s="13" t="n">
+      <c r="P52" s="14" t="n">
         <v>46.35</v>
       </c>
-      <c r="Q52" s="13" t="n">
+      <c r="Q52" s="14" t="n">
         <v>46.21</v>
       </c>
-      <c r="R52" s="13" t="n">
+      <c r="R52" s="14" t="n">
         <v>46.19</v>
       </c>
-      <c r="S52" s="13" t="n">
+      <c r="S52" s="14" t="n">
         <v>47.04</v>
       </c>
-      <c r="T52" s="13" t="n">
+      <c r="T52" s="14" t="n">
         <v>45.74</v>
       </c>
-      <c r="U52" s="13" t="n">
+      <c r="U52" s="14" t="n">
         <v>45.27</v>
       </c>
-      <c r="V52" s="13" t="n">
+      <c r="V52" s="14" t="n">
         <v>45.62</v>
       </c>
-      <c r="W52" s="13" t="n">
+      <c r="W52" s="14" t="n">
         <v>44.74</v>
       </c>
-      <c r="X52" s="13" t="n">
+      <c r="X52" s="14" t="n">
         <v>49.16</v>
       </c>
-      <c r="Y52" s="13" t="n">
+      <c r="Y52" s="14" t="n">
         <v>46.34</v>
       </c>
-      <c r="Z52" s="13" t="n">
+      <c r="Z52" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="AA52" s="13" t="n">
+      <c r="AA52" s="14" t="n">
         <v>45.42</v>
       </c>
-      <c r="AB52" s="13" t="n">
+      <c r="AB52" s="14" t="n">
         <v>47.13</v>
       </c>
-      <c r="AC52" s="13" t="n">
+      <c r="AC52" s="14" t="n">
         <v>45.49</v>
       </c>
-      <c r="AD52" s="13" t="n">
+      <c r="AD52" s="14" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE52" s="13" t="n">
+      <c r="AE52" s="14" t="n">
         <v>46.79</v>
       </c>
-      <c r="AF52" s="13" t="n">
+      <c r="AF52" s="14" t="n">
         <v>47.06</v>
       </c>
-      <c r="AG52" s="13" t="n">
+      <c r="AG52" s="14" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH52" s="12" t="n">
+      <c r="AH52" s="15" t="n">
         <v>46.28</v>
       </c>
-      <c r="AI52" s="12" t="n">
+      <c r="AI52" s="15" t="n">
         <v>497.9</v>
       </c>
-      <c r="AJ52" s="12" t="inlineStr"/>
-      <c r="AK52" s="14" t="inlineStr"/>
+      <c r="AJ52" s="13" t="inlineStr"/>
+      <c r="AK52" s="16" t="inlineStr"/>
     </row>
     <row r="53"/>
     <row r="54"/>
@@ -5634,7 +5646,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5772,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK62" s="15" t="n"/>
+      <c r="AK62" s="17" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5771,105 +5783,105 @@
       <c r="B63" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="10" t="n">
         <v>64.05</v>
       </c>
-      <c r="D63" s="7" t="n">
+      <c r="D63" s="10" t="n">
         <v>63.56</v>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" s="10" t="n">
         <v>64.08</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="10" t="n">
         <v>63.48</v>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="10" t="n">
         <v>64.12</v>
       </c>
-      <c r="H63" s="7" t="n">
+      <c r="H63" s="10" t="n">
         <v>64.53</v>
       </c>
-      <c r="I63" s="7" t="n">
+      <c r="I63" s="10" t="n">
         <v>64.03</v>
       </c>
-      <c r="J63" s="7" t="n">
+      <c r="J63" s="10" t="n">
         <v>63.8</v>
       </c>
-      <c r="K63" s="7" t="n">
+      <c r="K63" s="10" t="n">
         <v>63.63</v>
       </c>
-      <c r="L63" s="7" t="n">
+      <c r="L63" s="10" t="n">
         <v>63.38</v>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="10" t="n">
         <v>63.85</v>
       </c>
-      <c r="N63" s="7" t="n">
+      <c r="N63" s="10" t="n">
         <v>63.69</v>
       </c>
-      <c r="O63" s="7" t="n">
+      <c r="O63" s="10" t="n">
         <v>63.81</v>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P63" s="10" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="Q63" s="7" t="n">
+      <c r="Q63" s="10" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="R63" s="7" t="n">
+      <c r="R63" s="10" t="n">
         <v>63.94</v>
       </c>
-      <c r="S63" s="7" t="n">
+      <c r="S63" s="10" t="n">
         <v>62.96</v>
       </c>
-      <c r="T63" s="7" t="n">
+      <c r="T63" s="10" t="n">
         <v>62.88</v>
       </c>
-      <c r="U63" s="7" t="n">
+      <c r="U63" s="10" t="n">
         <v>62.7</v>
       </c>
-      <c r="V63" s="7" t="n">
+      <c r="V63" s="10" t="n">
         <v>62.84</v>
       </c>
-      <c r="W63" s="7" t="n">
+      <c r="W63" s="10" t="n">
         <v>62.69</v>
       </c>
-      <c r="X63" s="7" t="n">
+      <c r="X63" s="10" t="n">
         <v>62.51</v>
       </c>
-      <c r="Y63" s="7" t="n">
+      <c r="Y63" s="10" t="n">
         <v>62.42</v>
       </c>
-      <c r="Z63" s="7" t="n">
+      <c r="Z63" s="10" t="n">
         <v>63.88</v>
       </c>
-      <c r="AA63" s="7" t="n">
+      <c r="AA63" s="10" t="n">
         <v>63.6</v>
       </c>
-      <c r="AB63" s="7" t="n">
+      <c r="AB63" s="10" t="n">
         <v>64.08</v>
       </c>
-      <c r="AC63" s="7" t="n">
+      <c r="AC63" s="10" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="AD63" s="7" t="n">
+      <c r="AD63" s="10" t="n">
         <v>64.01000000000001</v>
       </c>
-      <c r="AE63" s="7" t="n">
+      <c r="AE63" s="10" t="n">
         <v>63.49</v>
       </c>
-      <c r="AF63" s="7" t="n">
+      <c r="AF63" s="10" t="n">
         <v>63.14</v>
       </c>
-      <c r="AG63" s="7" t="n">
+      <c r="AG63" s="10" t="n">
         <v>63.04</v>
       </c>
-      <c r="AH63" s="6" t="n">
+      <c r="AH63" s="10" t="n">
         <v>63.58</v>
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="16" t="n"/>
+      <c r="AK63" s="18" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5880,105 +5892,105 @@
       <c r="B64" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C64" s="10" t="n">
+      <c r="C64" s="11" t="n">
         <v>37.2</v>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D64" s="11" t="n">
         <v>37.1</v>
       </c>
-      <c r="E64" s="10" t="n">
+      <c r="E64" s="11" t="n">
         <v>36.25</v>
       </c>
-      <c r="F64" s="10" t="n">
+      <c r="F64" s="11" t="n">
         <v>35.95</v>
       </c>
-      <c r="G64" s="10" t="n">
+      <c r="G64" s="11" t="n">
         <v>38.22</v>
       </c>
-      <c r="H64" s="10" t="n">
+      <c r="H64" s="11" t="n">
         <v>35.83</v>
       </c>
-      <c r="I64" s="10" t="n">
+      <c r="I64" s="11" t="n">
         <v>38.13</v>
       </c>
-      <c r="J64" s="10" t="n">
+      <c r="J64" s="11" t="n">
         <v>36.34</v>
       </c>
-      <c r="K64" s="10" t="n">
+      <c r="K64" s="11" t="n">
         <v>37.93</v>
       </c>
-      <c r="L64" s="10" t="n">
+      <c r="L64" s="11" t="n">
         <v>37.71</v>
       </c>
-      <c r="M64" s="10" t="n">
+      <c r="M64" s="11" t="n">
         <v>35.95</v>
       </c>
-      <c r="N64" s="10" t="n">
+      <c r="N64" s="11" t="n">
         <v>35.99</v>
       </c>
-      <c r="O64" s="10" t="n">
+      <c r="O64" s="11" t="n">
         <v>38.22</v>
       </c>
-      <c r="P64" s="10" t="n">
+      <c r="P64" s="11" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q64" s="10" t="n">
+      <c r="Q64" s="11" t="n">
         <v>37.15</v>
       </c>
-      <c r="R64" s="10" t="n">
+      <c r="R64" s="11" t="n">
         <v>37.29</v>
       </c>
-      <c r="S64" s="10" t="n">
+      <c r="S64" s="11" t="n">
         <v>38.9</v>
       </c>
-      <c r="T64" s="10" t="n">
+      <c r="T64" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="U64" s="10" t="n">
+      <c r="U64" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="V64" s="10" t="n">
+      <c r="V64" s="11" t="n">
         <v>36.25</v>
       </c>
-      <c r="W64" s="10" t="n">
+      <c r="W64" s="11" t="n">
         <v>36.9</v>
       </c>
-      <c r="X64" s="10" t="n">
+      <c r="X64" s="11" t="n">
         <v>36.92</v>
       </c>
-      <c r="Y64" s="10" t="n">
+      <c r="Y64" s="11" t="n">
         <v>35.42</v>
       </c>
-      <c r="Z64" s="10" t="n">
+      <c r="Z64" s="11" t="n">
         <v>38.12</v>
       </c>
-      <c r="AA64" s="10" t="n">
+      <c r="AA64" s="11" t="n">
         <v>37.35</v>
       </c>
-      <c r="AB64" s="10" t="n">
+      <c r="AB64" s="11" t="n">
         <v>38.41</v>
       </c>
-      <c r="AC64" s="10" t="n">
+      <c r="AC64" s="11" t="n">
         <v>37.71</v>
       </c>
-      <c r="AD64" s="10" t="n">
+      <c r="AD64" s="11" t="n">
         <v>37.56</v>
       </c>
-      <c r="AE64" s="10" t="n">
+      <c r="AE64" s="11" t="n">
         <v>38.91</v>
       </c>
-      <c r="AF64" s="10" t="n">
+      <c r="AF64" s="11" t="n">
         <v>36.38</v>
       </c>
-      <c r="AG64" s="10" t="n">
+      <c r="AG64" s="11" t="n">
         <v>37.45</v>
       </c>
-      <c r="AH64" s="6" t="n">
+      <c r="AH64" s="8" t="n">
         <v>37.24</v>
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="16" t="n"/>
+      <c r="AK64" s="18" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5989,105 +6001,105 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C65" s="11" t="n">
         <v>39.7</v>
       </c>
-      <c r="D65" s="10" t="n">
+      <c r="D65" s="11" t="n">
         <v>37.34</v>
       </c>
-      <c r="E65" s="10" t="n">
+      <c r="E65" s="11" t="n">
         <v>38.12</v>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F65" s="11" t="n">
         <v>37.12</v>
       </c>
-      <c r="G65" s="10" t="n">
+      <c r="G65" s="11" t="n">
         <v>38.33</v>
       </c>
-      <c r="H65" s="10" t="n">
+      <c r="H65" s="11" t="n">
         <v>39.69</v>
       </c>
-      <c r="I65" s="10" t="n">
+      <c r="I65" s="11" t="n">
         <v>42.09</v>
       </c>
-      <c r="J65" s="10" t="n">
+      <c r="J65" s="11" t="n">
         <v>42.04</v>
       </c>
-      <c r="K65" s="10" t="n">
+      <c r="K65" s="11" t="n">
         <v>38.28</v>
       </c>
-      <c r="L65" s="10" t="n">
+      <c r="L65" s="11" t="n">
         <v>41.34</v>
       </c>
-      <c r="M65" s="10" t="n">
+      <c r="M65" s="11" t="n">
         <v>41.94</v>
       </c>
-      <c r="N65" s="10" t="n">
+      <c r="N65" s="11" t="n">
         <v>40.49</v>
       </c>
-      <c r="O65" s="10" t="n">
+      <c r="O65" s="11" t="n">
         <v>38.61</v>
       </c>
-      <c r="P65" s="10" t="n">
+      <c r="P65" s="11" t="n">
         <v>37.79</v>
       </c>
-      <c r="Q65" s="10" t="n">
+      <c r="Q65" s="11" t="n">
         <v>37.79</v>
       </c>
-      <c r="R65" s="10" t="n">
+      <c r="R65" s="11" t="n">
         <v>36.92</v>
       </c>
-      <c r="S65" s="10" t="n">
+      <c r="S65" s="11" t="n">
         <v>38.35</v>
       </c>
-      <c r="T65" s="10" t="n">
+      <c r="T65" s="11" t="n">
         <v>36.67</v>
       </c>
-      <c r="U65" s="10" t="n">
+      <c r="U65" s="11" t="n">
         <v>36.88</v>
       </c>
-      <c r="V65" s="10" t="n">
+      <c r="V65" s="11" t="n">
         <v>37.59</v>
       </c>
-      <c r="W65" s="10" t="n">
+      <c r="W65" s="11" t="n">
         <v>37.49</v>
       </c>
-      <c r="X65" s="10" t="n">
+      <c r="X65" s="11" t="n">
         <v>40.59</v>
       </c>
-      <c r="Y65" s="10" t="n">
+      <c r="Y65" s="11" t="n">
         <v>42.94</v>
       </c>
-      <c r="Z65" s="10" t="n">
+      <c r="Z65" s="11" t="n">
         <v>38.3</v>
       </c>
-      <c r="AA65" s="10" t="n">
+      <c r="AA65" s="11" t="n">
         <v>36.58</v>
       </c>
-      <c r="AB65" s="9" t="n">
+      <c r="AB65" s="11" t="n">
         <v>43.08</v>
       </c>
-      <c r="AC65" s="10" t="n">
+      <c r="AC65" s="11" t="n">
         <v>39.4</v>
       </c>
-      <c r="AD65" s="10" t="n">
+      <c r="AD65" s="11" t="n">
         <v>37.41</v>
       </c>
-      <c r="AE65" s="10" t="n">
+      <c r="AE65" s="11" t="n">
         <v>37.99</v>
       </c>
-      <c r="AF65" s="10" t="n">
+      <c r="AF65" s="11" t="n">
         <v>41.21</v>
       </c>
-      <c r="AG65" s="10" t="n">
+      <c r="AG65" s="11" t="n">
         <v>37.2</v>
       </c>
-      <c r="AH65" s="6" t="n">
+      <c r="AH65" s="8" t="n">
         <v>39.01</v>
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="16" t="n"/>
+      <c r="AK65" s="18" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6191,12 +6203,12 @@
       <c r="AG66" s="7" t="n">
         <v>77.44</v>
       </c>
-      <c r="AH66" s="6" t="n">
+      <c r="AH66" s="7" t="n">
         <v>77.48</v>
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="16" t="n"/>
+      <c r="AK66" s="18" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6207,105 +6219,105 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C67" s="11" t="n">
         <v>40.3</v>
       </c>
-      <c r="D67" s="10" t="n">
+      <c r="D67" s="11" t="n">
         <v>41.59</v>
       </c>
-      <c r="E67" s="10" t="n">
+      <c r="E67" s="11" t="n">
         <v>38.95</v>
       </c>
-      <c r="F67" s="10" t="n">
+      <c r="F67" s="11" t="n">
         <v>40.75</v>
       </c>
-      <c r="G67" s="10" t="n">
+      <c r="G67" s="11" t="n">
         <v>41.29</v>
       </c>
-      <c r="H67" s="10" t="n">
+      <c r="H67" s="11" t="n">
         <v>40.61</v>
       </c>
-      <c r="I67" s="10" t="n">
+      <c r="I67" s="11" t="n">
         <v>40.69</v>
       </c>
-      <c r="J67" s="9" t="n">
+      <c r="J67" s="11" t="n">
         <v>43.48</v>
       </c>
-      <c r="K67" s="10" t="n">
+      <c r="K67" s="11" t="n">
         <v>41.87</v>
       </c>
-      <c r="L67" s="10" t="n">
+      <c r="L67" s="11" t="n">
         <v>41.22</v>
       </c>
-      <c r="M67" s="10" t="n">
+      <c r="M67" s="11" t="n">
         <v>40.41</v>
       </c>
-      <c r="N67" s="10" t="n">
+      <c r="N67" s="11" t="n">
         <v>41.46</v>
       </c>
-      <c r="O67" s="10" t="n">
+      <c r="O67" s="11" t="n">
         <v>40.07</v>
       </c>
-      <c r="P67" s="10" t="n">
+      <c r="P67" s="11" t="n">
         <v>40.54</v>
       </c>
-      <c r="Q67" s="10" t="n">
+      <c r="Q67" s="11" t="n">
         <v>40.48</v>
       </c>
-      <c r="R67" s="10" t="n">
+      <c r="R67" s="11" t="n">
         <v>41.38</v>
       </c>
-      <c r="S67" s="10" t="n">
+      <c r="S67" s="11" t="n">
         <v>41.15</v>
       </c>
-      <c r="T67" s="10" t="n">
+      <c r="T67" s="11" t="n">
         <v>39.41</v>
       </c>
-      <c r="U67" s="10" t="n">
+      <c r="U67" s="11" t="n">
         <v>39.12</v>
       </c>
-      <c r="V67" s="10" t="n">
+      <c r="V67" s="11" t="n">
         <v>40.48</v>
       </c>
-      <c r="W67" s="10" t="n">
+      <c r="W67" s="11" t="n">
         <v>40.44</v>
       </c>
-      <c r="X67" s="10" t="n">
+      <c r="X67" s="11" t="n">
         <v>40.11</v>
       </c>
-      <c r="Y67" s="10" t="n">
+      <c r="Y67" s="11" t="n">
         <v>38.81</v>
       </c>
-      <c r="Z67" s="10" t="n">
+      <c r="Z67" s="11" t="n">
         <v>40.83</v>
       </c>
-      <c r="AA67" s="10" t="n">
+      <c r="AA67" s="11" t="n">
         <v>39.05</v>
       </c>
-      <c r="AB67" s="10" t="n">
+      <c r="AB67" s="11" t="n">
         <v>39.54</v>
       </c>
-      <c r="AC67" s="10" t="n">
+      <c r="AC67" s="11" t="n">
         <v>38.81</v>
       </c>
-      <c r="AD67" s="10" t="n">
+      <c r="AD67" s="11" t="n">
         <v>39.5</v>
       </c>
-      <c r="AE67" s="10" t="n">
+      <c r="AE67" s="11" t="n">
         <v>40.44</v>
       </c>
-      <c r="AF67" s="10" t="n">
+      <c r="AF67" s="11" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG67" s="10" t="n">
+      <c r="AG67" s="11" t="n">
         <v>39.62</v>
       </c>
-      <c r="AH67" s="6" t="n">
+      <c r="AH67" s="8" t="n">
         <v>40.4</v>
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="16" t="n"/>
+      <c r="AK67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6409,12 +6421,12 @@
       <c r="AG68" s="7" t="n">
         <v>78.26000000000001</v>
       </c>
-      <c r="AH68" s="6" t="n">
+      <c r="AH68" s="7" t="n">
         <v>78.28</v>
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="16" t="n"/>
+      <c r="AK68" s="18" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6518,12 +6530,12 @@
       <c r="AG69" s="7" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="AH69" s="6" t="n">
+      <c r="AH69" s="7" t="n">
         <v>72.51000000000001</v>
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="16" t="n"/>
+      <c r="AK69" s="18" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6534,105 +6546,105 @@
       <c r="B70" s="6" t="n">
         <v>549.25</v>
       </c>
-      <c r="C70" s="10" t="n">
+      <c r="C70" s="11" t="n">
         <v>31.82</v>
       </c>
-      <c r="D70" s="10" t="n">
+      <c r="D70" s="11" t="n">
         <v>34.01</v>
       </c>
-      <c r="E70" s="10" t="n">
+      <c r="E70" s="11" t="n">
         <v>31.3</v>
       </c>
-      <c r="F70" s="10" t="n">
+      <c r="F70" s="11" t="n">
         <v>31.78</v>
       </c>
-      <c r="G70" s="10" t="n">
+      <c r="G70" s="11" t="n">
         <v>31.44</v>
       </c>
-      <c r="H70" s="10" t="n">
+      <c r="H70" s="11" t="n">
         <v>31.81</v>
       </c>
-      <c r="I70" s="10" t="n">
+      <c r="I70" s="11" t="n">
         <v>31.13</v>
       </c>
-      <c r="J70" s="10" t="n">
+      <c r="J70" s="11" t="n">
         <v>32.33</v>
       </c>
-      <c r="K70" s="10" t="n">
+      <c r="K70" s="11" t="n">
         <v>31.17</v>
       </c>
-      <c r="L70" s="10" t="n">
+      <c r="L70" s="11" t="n">
         <v>30.91</v>
       </c>
-      <c r="M70" s="10" t="n">
+      <c r="M70" s="11" t="n">
         <v>31.56</v>
       </c>
-      <c r="N70" s="10" t="n">
+      <c r="N70" s="11" t="n">
         <v>31.3</v>
       </c>
-      <c r="O70" s="10" t="n">
+      <c r="O70" s="11" t="n">
         <v>31.59</v>
       </c>
-      <c r="P70" s="10" t="n">
+      <c r="P70" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="Q70" s="10" t="n">
+      <c r="Q70" s="11" t="n">
         <v>31.52</v>
       </c>
-      <c r="R70" s="10" t="n">
+      <c r="R70" s="11" t="n">
         <v>31.22</v>
       </c>
-      <c r="S70" s="10" t="n">
+      <c r="S70" s="11" t="n">
         <v>31.62</v>
       </c>
-      <c r="T70" s="10" t="n">
+      <c r="T70" s="11" t="n">
         <v>31.62</v>
       </c>
-      <c r="U70" s="10" t="n">
+      <c r="U70" s="11" t="n">
         <v>31.75</v>
       </c>
-      <c r="V70" s="10" t="n">
+      <c r="V70" s="11" t="n">
         <v>32.01</v>
       </c>
-      <c r="W70" s="10" t="n">
+      <c r="W70" s="11" t="n">
         <v>32.09</v>
       </c>
-      <c r="X70" s="10" t="n">
+      <c r="X70" s="11" t="n">
         <v>32.17</v>
       </c>
-      <c r="Y70" s="10" t="n">
+      <c r="Y70" s="11" t="n">
         <v>31.41</v>
       </c>
-      <c r="Z70" s="10" t="n">
+      <c r="Z70" s="11" t="n">
         <v>31.92</v>
       </c>
-      <c r="AA70" s="10" t="n">
+      <c r="AA70" s="11" t="n">
         <v>34.1</v>
       </c>
-      <c r="AB70" s="10" t="n">
+      <c r="AB70" s="11" t="n">
         <v>31.28</v>
       </c>
-      <c r="AC70" s="10" t="n">
+      <c r="AC70" s="11" t="n">
         <v>31.6</v>
       </c>
-      <c r="AD70" s="10" t="n">
+      <c r="AD70" s="11" t="n">
         <v>32.31</v>
       </c>
-      <c r="AE70" s="10" t="n">
+      <c r="AE70" s="11" t="n">
         <v>32.11</v>
       </c>
-      <c r="AF70" s="10" t="n">
+      <c r="AF70" s="11" t="n">
         <v>31.26</v>
       </c>
-      <c r="AG70" s="10" t="n">
+      <c r="AG70" s="11" t="n">
         <v>32.11</v>
       </c>
-      <c r="AH70" s="6" t="n">
+      <c r="AH70" s="8" t="n">
         <v>31.81</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="16" t="n"/>
+      <c r="AK70" s="18" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6643,105 +6655,105 @@
       <c r="B71" s="6" t="n">
         <v>573.25</v>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C71" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="D71" s="10" t="n">
+      <c r="D71" s="11" t="n">
         <v>31.2</v>
       </c>
-      <c r="E71" s="10" t="n">
+      <c r="E71" s="11" t="n">
         <v>29.72</v>
       </c>
-      <c r="F71" s="10" t="n">
+      <c r="F71" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="G71" s="10" t="n">
+      <c r="G71" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="H71" s="10" t="n">
+      <c r="H71" s="11" t="n">
         <v>29.91</v>
       </c>
-      <c r="I71" s="10" t="n">
+      <c r="I71" s="11" t="n">
         <v>30.73</v>
       </c>
-      <c r="J71" s="10" t="n">
+      <c r="J71" s="11" t="n">
         <v>34.14</v>
       </c>
-      <c r="K71" s="10" t="n">
+      <c r="K71" s="11" t="n">
         <v>30.47</v>
       </c>
-      <c r="L71" s="10" t="n">
+      <c r="L71" s="11" t="n">
         <v>32.12</v>
       </c>
-      <c r="M71" s="10" t="n">
+      <c r="M71" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="N71" s="10" t="n">
+      <c r="N71" s="11" t="n">
         <v>30.12</v>
       </c>
-      <c r="O71" s="10" t="n">
+      <c r="O71" s="11" t="n">
         <v>29.56</v>
       </c>
-      <c r="P71" s="10" t="n">
+      <c r="P71" s="11" t="n">
         <v>30.11</v>
       </c>
-      <c r="Q71" s="10" t="n">
+      <c r="Q71" s="11" t="n">
         <v>31.05</v>
       </c>
-      <c r="R71" s="10" t="n">
+      <c r="R71" s="11" t="n">
         <v>29.82</v>
       </c>
-      <c r="S71" s="10" t="n">
+      <c r="S71" s="11" t="n">
         <v>30.34</v>
       </c>
-      <c r="T71" s="10" t="n">
+      <c r="T71" s="11" t="n">
         <v>29.44</v>
       </c>
-      <c r="U71" s="10" t="n">
+      <c r="U71" s="11" t="n">
         <v>29.68</v>
       </c>
-      <c r="V71" s="10" t="n">
+      <c r="V71" s="11" t="n">
         <v>29.7</v>
       </c>
-      <c r="W71" s="10" t="n">
+      <c r="W71" s="11" t="n">
         <v>29.73</v>
       </c>
-      <c r="X71" s="10" t="n">
+      <c r="X71" s="11" t="n">
         <v>31.34</v>
       </c>
-      <c r="Y71" s="10" t="n">
+      <c r="Y71" s="11" t="n">
         <v>34.96</v>
       </c>
-      <c r="Z71" s="10" t="n">
+      <c r="Z71" s="11" t="n">
         <v>29.62</v>
       </c>
-      <c r="AA71" s="10" t="n">
+      <c r="AA71" s="11" t="n">
         <v>29.48</v>
       </c>
-      <c r="AB71" s="10" t="n">
+      <c r="AB71" s="11" t="n">
         <v>29.66</v>
       </c>
-      <c r="AC71" s="10" t="n">
+      <c r="AC71" s="11" t="n">
         <v>29.65</v>
       </c>
-      <c r="AD71" s="10" t="n">
+      <c r="AD71" s="11" t="n">
         <v>29.81</v>
       </c>
-      <c r="AE71" s="10" t="n">
+      <c r="AE71" s="11" t="n">
         <v>29.57</v>
       </c>
-      <c r="AF71" s="10" t="n">
+      <c r="AF71" s="11" t="n">
         <v>29.62</v>
       </c>
-      <c r="AG71" s="10" t="n">
+      <c r="AG71" s="11" t="n">
         <v>32.01</v>
       </c>
-      <c r="AH71" s="6" t="n">
+      <c r="AH71" s="8" t="n">
         <v>30.52</v>
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="16" t="n"/>
+      <c r="AK71" s="18" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6752,105 +6764,105 @@
       <c r="B72" s="6" t="n">
         <v>585.25</v>
       </c>
-      <c r="C72" s="10" t="n">
+      <c r="C72" s="11" t="n">
         <v>33.38</v>
       </c>
-      <c r="D72" s="10" t="n">
+      <c r="D72" s="11" t="n">
         <v>32.61</v>
       </c>
-      <c r="E72" s="10" t="n">
+      <c r="E72" s="11" t="n">
         <v>32.72</v>
       </c>
-      <c r="F72" s="10" t="n">
+      <c r="F72" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="G72" s="10" t="n">
+      <c r="G72" s="11" t="n">
         <v>32.51</v>
       </c>
-      <c r="H72" s="10" t="n">
+      <c r="H72" s="11" t="n">
         <v>32.48</v>
       </c>
-      <c r="I72" s="10" t="n">
+      <c r="I72" s="11" t="n">
         <v>31.93</v>
       </c>
-      <c r="J72" s="10" t="n">
+      <c r="J72" s="11" t="n">
         <v>35.1</v>
       </c>
-      <c r="K72" s="10" t="n">
+      <c r="K72" s="11" t="n">
         <v>32.72</v>
       </c>
-      <c r="L72" s="10" t="n">
+      <c r="L72" s="11" t="n">
         <v>34.05</v>
       </c>
-      <c r="M72" s="10" t="n">
+      <c r="M72" s="11" t="n">
         <v>34.14</v>
       </c>
-      <c r="N72" s="10" t="n">
+      <c r="N72" s="11" t="n">
         <v>32.36</v>
       </c>
-      <c r="O72" s="10" t="n">
+      <c r="O72" s="11" t="n">
         <v>32.78</v>
       </c>
-      <c r="P72" s="10" t="n">
+      <c r="P72" s="11" t="n">
         <v>34.24</v>
       </c>
-      <c r="Q72" s="10" t="n">
+      <c r="Q72" s="11" t="n">
         <v>32.56</v>
       </c>
-      <c r="R72" s="10" t="n">
+      <c r="R72" s="11" t="n">
         <v>32.69</v>
       </c>
-      <c r="S72" s="10" t="n">
+      <c r="S72" s="11" t="n">
         <v>32.33</v>
       </c>
-      <c r="T72" s="10" t="n">
+      <c r="T72" s="11" t="n">
         <v>32.36</v>
       </c>
-      <c r="U72" s="10" t="n">
+      <c r="U72" s="11" t="n">
         <v>32.29</v>
       </c>
-      <c r="V72" s="10" t="n">
+      <c r="V72" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="W72" s="10" t="n">
+      <c r="W72" s="11" t="n">
         <v>32.46</v>
       </c>
-      <c r="X72" s="10" t="n">
+      <c r="X72" s="11" t="n">
         <v>31.89</v>
       </c>
-      <c r="Y72" s="10" t="n">
+      <c r="Y72" s="11" t="n">
         <v>32.44</v>
       </c>
-      <c r="Z72" s="10" t="n">
+      <c r="Z72" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="AA72" s="10" t="n">
+      <c r="AA72" s="11" t="n">
         <v>32.17</v>
       </c>
-      <c r="AB72" s="10" t="n">
+      <c r="AB72" s="11" t="n">
         <v>33.28</v>
       </c>
-      <c r="AC72" s="10" t="n">
+      <c r="AC72" s="11" t="n">
         <v>32.95</v>
       </c>
-      <c r="AD72" s="10" t="n">
+      <c r="AD72" s="11" t="n">
         <v>32.63</v>
       </c>
-      <c r="AE72" s="10" t="n">
+      <c r="AE72" s="11" t="n">
         <v>32.53</v>
       </c>
-      <c r="AF72" s="10" t="n">
+      <c r="AF72" s="11" t="n">
         <v>32.38</v>
       </c>
-      <c r="AG72" s="10" t="n">
+      <c r="AG72" s="11" t="n">
         <v>32.41</v>
       </c>
-      <c r="AH72" s="6" t="n">
+      <c r="AH72" s="8" t="n">
         <v>32.74</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="16" t="n"/>
+      <c r="AK72" s="18" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6894,7 +6906,7 @@
       <c r="M73" s="7" t="n">
         <v>79.97</v>
       </c>
-      <c r="N73" s="7" t="n">
+      <c r="N73" s="11" t="n">
         <v>55.45</v>
       </c>
       <c r="O73" s="7" t="n">
@@ -6954,12 +6966,12 @@
       <c r="AG73" s="7" t="n">
         <v>79.79000000000001</v>
       </c>
-      <c r="AH73" s="6" t="n">
+      <c r="AH73" s="7" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="16" t="n"/>
+      <c r="AK73" s="18" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6970,214 +6982,214 @@
       <c r="B74" s="6" t="n">
         <v>621.25</v>
       </c>
-      <c r="C74" s="10" t="n">
+      <c r="C74" s="11" t="n">
         <v>30.32</v>
       </c>
-      <c r="D74" s="10" t="n">
+      <c r="D74" s="11" t="n">
         <v>30.3</v>
       </c>
-      <c r="E74" s="10" t="n">
+      <c r="E74" s="11" t="n">
         <v>30.2</v>
       </c>
-      <c r="F74" s="10" t="n">
+      <c r="F74" s="11" t="n">
         <v>29.75</v>
       </c>
-      <c r="G74" s="10" t="n">
+      <c r="G74" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="H74" s="10" t="n">
+      <c r="H74" s="11" t="n">
         <v>29.98</v>
       </c>
-      <c r="I74" s="10" t="n">
+      <c r="I74" s="11" t="n">
         <v>29.66</v>
       </c>
-      <c r="J74" s="10" t="n">
+      <c r="J74" s="11" t="n">
         <v>29.84</v>
       </c>
-      <c r="K74" s="10" t="n">
+      <c r="K74" s="11" t="n">
         <v>30.35</v>
       </c>
-      <c r="L74" s="10" t="n">
+      <c r="L74" s="11" t="n">
         <v>33.02</v>
       </c>
-      <c r="M74" s="10" t="n">
+      <c r="M74" s="11" t="n">
         <v>30.01</v>
       </c>
-      <c r="N74" s="10" t="n">
+      <c r="N74" s="11" t="n">
         <v>29.79</v>
       </c>
-      <c r="O74" s="10" t="n">
+      <c r="O74" s="11" t="n">
         <v>32.08</v>
       </c>
-      <c r="P74" s="10" t="n">
+      <c r="P74" s="11" t="n">
         <v>30.26</v>
       </c>
-      <c r="Q74" s="10" t="n">
+      <c r="Q74" s="11" t="n">
         <v>30.26</v>
       </c>
-      <c r="R74" s="10" t="n">
+      <c r="R74" s="11" t="n">
         <v>29.52</v>
       </c>
-      <c r="S74" s="10" t="n">
+      <c r="S74" s="11" t="n">
         <v>30.26</v>
       </c>
-      <c r="T74" s="10" t="n">
+      <c r="T74" s="11" t="n">
         <v>29.72</v>
       </c>
-      <c r="U74" s="10" t="n">
+      <c r="U74" s="11" t="n">
         <v>31.64</v>
       </c>
-      <c r="V74" s="10" t="n">
+      <c r="V74" s="11" t="n">
         <v>29.29</v>
       </c>
-      <c r="W74" s="10" t="n">
+      <c r="W74" s="11" t="n">
         <v>29.83</v>
       </c>
-      <c r="X74" s="10" t="n">
+      <c r="X74" s="11" t="n">
         <v>30.21</v>
       </c>
-      <c r="Y74" s="10" t="n">
+      <c r="Y74" s="11" t="n">
         <v>31.16</v>
       </c>
-      <c r="Z74" s="10" t="n">
+      <c r="Z74" s="11" t="n">
         <v>29.88</v>
       </c>
-      <c r="AA74" s="10" t="n">
+      <c r="AA74" s="11" t="n">
         <v>33.85</v>
       </c>
-      <c r="AB74" s="10" t="n">
+      <c r="AB74" s="11" t="n">
         <v>29.26</v>
       </c>
-      <c r="AC74" s="10" t="n">
+      <c r="AC74" s="11" t="n">
         <v>31.25</v>
       </c>
-      <c r="AD74" s="10" t="n">
+      <c r="AD74" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="AE74" s="10" t="n">
+      <c r="AE74" s="11" t="n">
         <v>29.49</v>
       </c>
-      <c r="AF74" s="10" t="n">
+      <c r="AF74" s="11" t="n">
         <v>30.38</v>
       </c>
-      <c r="AG74" s="10" t="n">
+      <c r="AG74" s="11" t="n">
         <v>30.25</v>
       </c>
-      <c r="AH74" s="6" t="n">
+      <c r="AH74" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="16" t="n"/>
+      <c r="AK74" s="18" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="13" t="n">
         <v>633.25</v>
       </c>
-      <c r="C75" s="17" t="n">
+      <c r="C75" s="19" t="n">
         <v>29.02</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="19" t="n">
         <v>30.64</v>
       </c>
-      <c r="E75" s="17" t="n">
+      <c r="E75" s="19" t="n">
         <v>28.75</v>
       </c>
-      <c r="F75" s="17" t="n">
+      <c r="F75" s="19" t="n">
         <v>29.3</v>
       </c>
-      <c r="G75" s="17" t="n">
+      <c r="G75" s="19" t="n">
         <v>29.96</v>
       </c>
-      <c r="H75" s="17" t="n">
+      <c r="H75" s="19" t="n">
         <v>29.38</v>
       </c>
-      <c r="I75" s="17" t="n">
+      <c r="I75" s="19" t="n">
         <v>28.91</v>
       </c>
-      <c r="J75" s="17" t="n">
+      <c r="J75" s="19" t="n">
         <v>29.28</v>
       </c>
-      <c r="K75" s="17" t="n">
+      <c r="K75" s="19" t="n">
         <v>30.2</v>
       </c>
-      <c r="L75" s="17" t="n">
+      <c r="L75" s="19" t="n">
         <v>30.12</v>
       </c>
-      <c r="M75" s="17" t="n">
+      <c r="M75" s="19" t="n">
         <v>31.44</v>
       </c>
-      <c r="N75" s="17" t="n">
+      <c r="N75" s="19" t="n">
         <v>29.04</v>
       </c>
-      <c r="O75" s="17" t="n">
+      <c r="O75" s="19" t="n">
         <v>29.02</v>
       </c>
-      <c r="P75" s="17" t="n">
+      <c r="P75" s="19" t="n">
         <v>29.38</v>
       </c>
-      <c r="Q75" s="17" t="n">
+      <c r="Q75" s="19" t="n">
         <v>29.29</v>
       </c>
-      <c r="R75" s="17" t="n">
+      <c r="R75" s="19" t="n">
         <v>29.71</v>
       </c>
-      <c r="S75" s="17" t="n">
+      <c r="S75" s="19" t="n">
         <v>29.5</v>
       </c>
-      <c r="T75" s="17" t="n">
+      <c r="T75" s="19" t="n">
         <v>29.38</v>
       </c>
-      <c r="U75" s="17" t="n">
+      <c r="U75" s="19" t="n">
         <v>29.78</v>
       </c>
-      <c r="V75" s="17" t="n">
+      <c r="V75" s="19" t="n">
         <v>29.85</v>
       </c>
-      <c r="W75" s="17" t="n">
+      <c r="W75" s="19" t="n">
         <v>29.16</v>
       </c>
-      <c r="X75" s="17" t="n">
+      <c r="X75" s="19" t="n">
         <v>29.29</v>
       </c>
-      <c r="Y75" s="17" t="n">
+      <c r="Y75" s="19" t="n">
         <v>29.48</v>
       </c>
-      <c r="Z75" s="17" t="n">
+      <c r="Z75" s="19" t="n">
         <v>37.17</v>
       </c>
-      <c r="AA75" s="17" t="n">
+      <c r="AA75" s="19" t="n">
         <v>28.92</v>
       </c>
-      <c r="AB75" s="17" t="n">
+      <c r="AB75" s="19" t="n">
         <v>31.6</v>
       </c>
-      <c r="AC75" s="17" t="n">
+      <c r="AC75" s="19" t="n">
         <v>30.51</v>
       </c>
-      <c r="AD75" s="17" t="n">
+      <c r="AD75" s="19" t="n">
         <v>29.07</v>
       </c>
-      <c r="AE75" s="17" t="n">
+      <c r="AE75" s="19" t="n">
         <v>28.94</v>
       </c>
-      <c r="AF75" s="17" t="n">
+      <c r="AF75" s="19" t="n">
         <v>29.25</v>
       </c>
-      <c r="AG75" s="17" t="n">
+      <c r="AG75" s="19" t="n">
         <v>29.59</v>
       </c>
-      <c r="AH75" s="12" t="n">
+      <c r="AH75" s="15" t="n">
         <v>29.84</v>
       </c>
-      <c r="AI75" s="12" t="inlineStr"/>
-      <c r="AJ75" s="12" t="inlineStr"/>
-      <c r="AK75" s="18" t="n"/>
+      <c r="AI75" s="13" t="inlineStr"/>
+      <c r="AJ75" s="13" t="inlineStr"/>
+      <c r="AK75" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFC4A2C"/>
-        <bgColor rgb="FFFC4A2C"/>
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
       </patternFill>
     </fill>
     <fill>
@@ -197,10 +197,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,7 +221,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -804,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       <c r="AG11" s="7" t="n">
         <v>71.29000000000001</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="7" t="n">
         <v>70.81</v>
       </c>
       <c r="AI11" s="8" t="n">
@@ -1150,10 +1150,10 @@
       <c r="AG12" s="7" t="n">
         <v>72.84</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="7" t="n">
         <v>72.27</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="7" t="n">
         <v>160.6</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
       <c r="AG13" s="7" t="n">
         <v>70.06999999999999</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="7" t="n">
         <v>71.45999999999999</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="7" t="n">
         <v>200.59</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
       <c r="AG14" s="7" t="n">
         <v>68.75</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="7" t="n">
         <v>66.97</v>
       </c>
       <c r="AI14" s="8" t="n">
@@ -1483,7 +1483,7 @@
       <c r="AG15" s="7" t="n">
         <v>75.70999999999999</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="7" t="n">
         <v>75.67</v>
       </c>
       <c r="AI15" s="8" t="n">
@@ -1594,7 +1594,7 @@
       <c r="AG16" s="7" t="n">
         <v>68.09</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="7" t="n">
         <v>67.72</v>
       </c>
       <c r="AI16" s="8" t="n">
@@ -1705,7 +1705,7 @@
       <c r="AG17" s="7" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="7" t="n">
         <v>70.15000000000001</v>
       </c>
       <c r="AI17" s="8" t="n">
@@ -1816,7 +1816,7 @@
       <c r="AG18" s="10" t="n">
         <v>51.71</v>
       </c>
-      <c r="AH18" s="8" t="n">
+      <c r="AH18" s="10" t="n">
         <v>50.25</v>
       </c>
       <c r="AI18" s="8" t="n">
@@ -1927,7 +1927,7 @@
       <c r="AG19" s="7" t="n">
         <v>67.03</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH19" s="7" t="n">
         <v>67.31</v>
       </c>
       <c r="AI19" s="8" t="n">
@@ -2038,7 +2038,7 @@
       <c r="AG20" s="7" t="n">
         <v>58.85</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="7" t="n">
         <v>60.42</v>
       </c>
       <c r="AI20" s="8" t="n">
@@ -2149,7 +2149,7 @@
       <c r="AG21" s="7" t="n">
         <v>66.41</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="7" t="n">
         <v>63.62</v>
       </c>
       <c r="AI21" s="8" t="n">
@@ -2260,7 +2260,7 @@
       <c r="AG22" s="10" t="n">
         <v>47.09</v>
       </c>
-      <c r="AH22" s="6" t="n">
+      <c r="AH22" s="7" t="n">
         <v>56.95</v>
       </c>
       <c r="AI22" s="8" t="n">
@@ -2371,10 +2371,10 @@
       <c r="AG23" s="7" t="n">
         <v>66.70999999999999</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="7" t="n">
         <v>66.53</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="7" t="n">
         <v>219.15</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
       <c r="AG24" s="7" t="n">
         <v>64.79000000000001</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="7" t="n">
         <v>64.73999999999999</v>
       </c>
       <c r="AI24" s="8" t="n">
@@ -2593,10 +2593,10 @@
       <c r="AG25" s="7" t="n">
         <v>69.81</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH25" s="7" t="n">
         <v>68.48</v>
       </c>
-      <c r="AI25" s="6" t="n">
+      <c r="AI25" s="7" t="n">
         <v>123.83</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
       <c r="AG26" s="7" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="7" t="n">
         <v>73.31</v>
       </c>
       <c r="AI26" s="8" t="n">
@@ -2815,7 +2815,7 @@
       <c r="AG27" s="7" t="n">
         <v>60.81</v>
       </c>
-      <c r="AH27" s="6" t="n">
+      <c r="AH27" s="7" t="n">
         <v>59.85</v>
       </c>
       <c r="AI27" s="8" t="n">
@@ -2926,7 +2926,7 @@
       <c r="AG28" s="7" t="n">
         <v>63.46</v>
       </c>
-      <c r="AH28" s="6" t="n">
+      <c r="AH28" s="7" t="n">
         <v>62.51</v>
       </c>
       <c r="AI28" s="8" t="n">
@@ -3037,7 +3037,7 @@
       <c r="AG29" s="7" t="n">
         <v>70.56</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH29" s="7" t="n">
         <v>70.29000000000001</v>
       </c>
       <c r="AI29" s="8" t="n">
@@ -3148,7 +3148,7 @@
       <c r="AG30" s="7" t="n">
         <v>69.2</v>
       </c>
-      <c r="AH30" s="6" t="n">
+      <c r="AH30" s="7" t="n">
         <v>68.58</v>
       </c>
       <c r="AI30" s="8" t="n">
@@ -3259,7 +3259,7 @@
       <c r="AG31" s="10" t="n">
         <v>45.77</v>
       </c>
-      <c r="AH31" s="8" t="n">
+      <c r="AH31" s="10" t="n">
         <v>44.94</v>
       </c>
       <c r="AI31" s="8" t="n">
@@ -3370,7 +3370,7 @@
       <c r="AG32" s="7" t="n">
         <v>55.64</v>
       </c>
-      <c r="AH32" s="6" t="n">
+      <c r="AH32" s="7" t="n">
         <v>55.72</v>
       </c>
       <c r="AI32" s="8" t="n">
@@ -3481,7 +3481,7 @@
       <c r="AG33" s="7" t="n">
         <v>76.45999999999999</v>
       </c>
-      <c r="AH33" s="6" t="n">
+      <c r="AH33" s="7" t="n">
         <v>76.88</v>
       </c>
       <c r="AI33" s="8" t="n">
@@ -3592,7 +3592,7 @@
       <c r="AG34" s="7" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="AH34" s="6" t="n">
+      <c r="AH34" s="7" t="n">
         <v>65.95999999999999</v>
       </c>
       <c r="AI34" s="8" t="n">
@@ -3703,7 +3703,7 @@
       <c r="AG35" s="7" t="n">
         <v>61.26</v>
       </c>
-      <c r="AH35" s="6" t="n">
+      <c r="AH35" s="7" t="n">
         <v>60.41</v>
       </c>
       <c r="AI35" s="8" t="n">
@@ -3814,7 +3814,7 @@
       <c r="AG36" s="7" t="n">
         <v>65.62</v>
       </c>
-      <c r="AH36" s="6" t="n">
+      <c r="AH36" s="7" t="n">
         <v>65.18000000000001</v>
       </c>
       <c r="AI36" s="8" t="n">
@@ -4036,10 +4036,10 @@
       <c r="AG38" s="7" t="n">
         <v>77.81</v>
       </c>
-      <c r="AH38" s="6" t="n">
+      <c r="AH38" s="7" t="n">
         <v>77.34999999999999</v>
       </c>
-      <c r="AI38" s="6" t="n">
+      <c r="AI38" s="7" t="n">
         <v>159.74</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
@@ -4147,7 +4147,7 @@
       <c r="AG39" s="7" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="AH39" s="6" t="n">
+      <c r="AH39" s="7" t="n">
         <v>71.44</v>
       </c>
       <c r="AI39" s="8" t="n">
@@ -4258,7 +4258,7 @@
       <c r="AG40" s="7" t="n">
         <v>58.96</v>
       </c>
-      <c r="AH40" s="6" t="n">
+      <c r="AH40" s="7" t="n">
         <v>58.38</v>
       </c>
       <c r="AI40" s="8" t="n">
@@ -4369,10 +4369,10 @@
       <c r="AG41" s="10" t="n">
         <v>48.04</v>
       </c>
-      <c r="AH41" s="8" t="n">
+      <c r="AH41" s="10" t="n">
         <v>43.14</v>
       </c>
-      <c r="AI41" s="6" t="n">
+      <c r="AI41" s="7" t="n">
         <v>161.11</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
@@ -4483,7 +4483,7 @@
       <c r="AH42" s="8" t="n">
         <v>42.94</v>
       </c>
-      <c r="AI42" s="6" t="n">
+      <c r="AI42" s="7" t="n">
         <v>141.85</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
@@ -4594,7 +4594,7 @@
       <c r="AH43" s="8" t="n">
         <v>42.27</v>
       </c>
-      <c r="AI43" s="6" t="n">
+      <c r="AI43" s="7" t="n">
         <v>140.45</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
       <c r="AG44" s="7" t="n">
         <v>78.26000000000001</v>
       </c>
-      <c r="AH44" s="6" t="n">
+      <c r="AH44" s="7" t="n">
         <v>77.54000000000001</v>
       </c>
-      <c r="AI44" s="6" t="n">
+      <c r="AI44" s="7" t="n">
         <v>181.85</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
       <c r="AG45" s="7" t="n">
         <v>66.86</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="7" t="n">
         <v>66.86</v>
       </c>
       <c r="AI45" s="8" t="n">
@@ -4924,7 +4924,7 @@
       <c r="AG46" s="7" t="n">
         <v>71.01000000000001</v>
       </c>
-      <c r="AH46" s="6" t="n">
+      <c r="AH46" s="7" t="n">
         <v>70.11</v>
       </c>
       <c r="AI46" s="8" t="n">
@@ -5035,7 +5035,7 @@
       <c r="AG47" s="7" t="n">
         <v>80.06</v>
       </c>
-      <c r="AH47" s="6" t="n">
+      <c r="AH47" s="7" t="n">
         <v>79.56999999999999</v>
       </c>
       <c r="AI47" s="8" t="n">
@@ -5146,7 +5146,7 @@
       <c r="AG48" s="7" t="n">
         <v>55.31</v>
       </c>
-      <c r="AH48" s="6" t="n">
+      <c r="AH48" s="7" t="n">
         <v>55.88</v>
       </c>
       <c r="AI48" s="8" t="n">
@@ -5257,7 +5257,7 @@
       <c r="AG49" s="7" t="n">
         <v>66.27</v>
       </c>
-      <c r="AH49" s="6" t="n">
+      <c r="AH49" s="7" t="n">
         <v>66.84</v>
       </c>
       <c r="AI49" s="8" t="n">
@@ -5368,7 +5368,7 @@
       <c r="AG50" s="7" t="n">
         <v>73.59</v>
       </c>
-      <c r="AH50" s="6" t="n">
+      <c r="AH50" s="7" t="n">
         <v>73.84</v>
       </c>
       <c r="AI50" s="8" t="n">
@@ -5479,7 +5479,7 @@
       <c r="AG51" s="10" t="n">
         <v>44.48</v>
       </c>
-      <c r="AH51" s="8" t="n">
+      <c r="AH51" s="10" t="n">
         <v>45</v>
       </c>
       <c r="AI51" s="8" t="n">
@@ -5590,7 +5590,7 @@
       <c r="AG52" s="14" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH52" s="15" t="n">
+      <c r="AH52" s="14" t="n">
         <v>46.28</v>
       </c>
       <c r="AI52" s="15" t="n">
@@ -5646,7 +5646,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -209,9 +209,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -229,6 +226,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2134,7 +2134,7 @@
       <c r="AB21" s="10" t="n">
         <v>48.92</v>
       </c>
-      <c r="AC21" s="11" t="n">
+      <c r="AC21" s="10" t="n">
         <v>42.56</v>
       </c>
       <c r="AD21" s="7" t="n">
@@ -3169,10 +3169,10 @@
       <c r="C31" s="10" t="n">
         <v>49.18</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="10" t="n">
         <v>38.17</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="10" t="n">
         <v>39.78</v>
       </c>
       <c r="F31" s="10" t="n">
@@ -3211,16 +3211,16 @@
       <c r="Q31" s="10" t="n">
         <v>43.31</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" s="10" t="n">
         <v>42.73</v>
       </c>
-      <c r="S31" s="11" t="n">
+      <c r="S31" s="10" t="n">
         <v>36.38</v>
       </c>
-      <c r="T31" s="11" t="n">
+      <c r="T31" s="10" t="n">
         <v>42.77</v>
       </c>
-      <c r="U31" s="11" t="n">
+      <c r="U31" s="10" t="n">
         <v>40.38</v>
       </c>
       <c r="V31" s="10" t="n">
@@ -3232,22 +3232,22 @@
       <c r="X31" s="10" t="n">
         <v>45.4</v>
       </c>
-      <c r="Y31" s="11" t="n">
+      <c r="Y31" s="10" t="n">
         <v>40.74</v>
       </c>
-      <c r="Z31" s="11" t="n">
+      <c r="Z31" s="10" t="n">
         <v>41.24</v>
       </c>
-      <c r="AA31" s="11" t="n">
+      <c r="AA31" s="10" t="n">
         <v>41.48</v>
       </c>
-      <c r="AB31" s="11" t="n">
+      <c r="AB31" s="10" t="n">
         <v>42.87</v>
       </c>
       <c r="AC31" s="10" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="11" t="n">
+      <c r="AD31" s="10" t="n">
         <v>40.41</v>
       </c>
       <c r="AE31" s="10" t="n">
@@ -3832,40 +3832,40 @@
       <c r="B37" s="6" t="n">
         <v>101.1</v>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="10" t="n">
         <v>41.52</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="10" t="n">
         <v>37.06</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="10" t="n">
         <v>39.89</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="10" t="n">
         <v>41.01</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="10" t="n">
         <v>40.08</v>
       </c>
-      <c r="H37" s="11" t="n">
+      <c r="H37" s="10" t="n">
         <v>41.32</v>
       </c>
-      <c r="I37" s="11" t="n">
+      <c r="I37" s="10" t="n">
         <v>40.03</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J37" s="10" t="n">
         <v>40.92</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="10" t="n">
         <v>39.57</v>
       </c>
-      <c r="L37" s="11" t="n">
+      <c r="L37" s="10" t="n">
         <v>40.51</v>
       </c>
       <c r="M37" s="10" t="n">
         <v>44.43</v>
       </c>
-      <c r="N37" s="11" t="n">
+      <c r="N37" s="10" t="n">
         <v>40.55</v>
       </c>
       <c r="O37" s="10" t="n">
@@ -3874,58 +3874,58 @@
       <c r="P37" s="10" t="n">
         <v>43.79</v>
       </c>
-      <c r="Q37" s="11" t="n">
+      <c r="Q37" s="10" t="n">
         <v>40.86</v>
       </c>
-      <c r="R37" s="11" t="n">
+      <c r="R37" s="10" t="n">
         <v>36.73</v>
       </c>
-      <c r="S37" s="11" t="n">
+      <c r="S37" s="10" t="n">
         <v>36.76</v>
       </c>
-      <c r="T37" s="11" t="n">
+      <c r="T37" s="10" t="n">
         <v>38.71</v>
       </c>
-      <c r="U37" s="11" t="n">
+      <c r="U37" s="10" t="n">
         <v>36.86</v>
       </c>
-      <c r="V37" s="11" t="n">
+      <c r="V37" s="10" t="n">
         <v>40.22</v>
       </c>
-      <c r="W37" s="11" t="n">
+      <c r="W37" s="10" t="n">
         <v>40.92</v>
       </c>
-      <c r="X37" s="11" t="n">
+      <c r="X37" s="10" t="n">
         <v>39.83</v>
       </c>
-      <c r="Y37" s="11" t="n">
+      <c r="Y37" s="10" t="n">
         <v>37.26</v>
       </c>
-      <c r="Z37" s="11" t="n">
+      <c r="Z37" s="10" t="n">
         <v>38.74</v>
       </c>
-      <c r="AA37" s="11" t="n">
+      <c r="AA37" s="10" t="n">
         <v>37.96</v>
       </c>
-      <c r="AB37" s="11" t="n">
+      <c r="AB37" s="10" t="n">
         <v>41.61</v>
       </c>
-      <c r="AC37" s="11" t="n">
+      <c r="AC37" s="10" t="n">
         <v>41.84</v>
       </c>
-      <c r="AD37" s="11" t="n">
+      <c r="AD37" s="10" t="n">
         <v>38.69</v>
       </c>
-      <c r="AE37" s="11" t="n">
+      <c r="AE37" s="10" t="n">
         <v>41.51</v>
       </c>
-      <c r="AF37" s="11" t="n">
+      <c r="AF37" s="10" t="n">
         <v>41.72</v>
       </c>
-      <c r="AG37" s="11" t="n">
+      <c r="AG37" s="10" t="n">
         <v>41.58</v>
       </c>
-      <c r="AH37" s="8" t="n">
+      <c r="AH37" s="10" t="n">
         <v>40.18</v>
       </c>
       <c r="AI37" s="8" t="n">
@@ -4279,10 +4279,10 @@
       <c r="C41" s="10" t="n">
         <v>46.72</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="10" t="n">
         <v>35.76</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="10" t="n">
         <v>36.4</v>
       </c>
       <c r="F41" s="10" t="n">
@@ -4294,7 +4294,7 @@
       <c r="H41" s="10" t="n">
         <v>45.91</v>
       </c>
-      <c r="I41" s="11" t="n">
+      <c r="I41" s="10" t="n">
         <v>42.62</v>
       </c>
       <c r="J41" s="10" t="n">
@@ -4315,7 +4315,7 @@
       <c r="O41" s="10" t="n">
         <v>45.21</v>
       </c>
-      <c r="P41" s="11" t="n">
+      <c r="P41" s="10" t="n">
         <v>42.01</v>
       </c>
       <c r="Q41" s="10" t="n">
@@ -4324,43 +4324,43 @@
       <c r="R41" s="10" t="n">
         <v>43.31</v>
       </c>
-      <c r="S41" s="11" t="n">
+      <c r="S41" s="10" t="n">
         <v>37.48</v>
       </c>
       <c r="T41" s="10" t="n">
         <v>43.12</v>
       </c>
-      <c r="U41" s="11" t="n">
+      <c r="U41" s="10" t="n">
         <v>41.52</v>
       </c>
-      <c r="V41" s="11" t="n">
+      <c r="V41" s="10" t="n">
         <v>42.48</v>
       </c>
-      <c r="W41" s="11" t="n">
+      <c r="W41" s="10" t="n">
         <v>42.72</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>46.34</v>
       </c>
-      <c r="Y41" s="11" t="n">
+      <c r="Y41" s="10" t="n">
         <v>42.01</v>
       </c>
-      <c r="Z41" s="11" t="n">
+      <c r="Z41" s="10" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA41" s="11" t="n">
+      <c r="AA41" s="10" t="n">
         <v>41.55</v>
       </c>
-      <c r="AB41" s="11" t="n">
+      <c r="AB41" s="10" t="n">
         <v>41.22</v>
       </c>
       <c r="AC41" s="10" t="n">
         <v>44.88</v>
       </c>
-      <c r="AD41" s="11" t="n">
+      <c r="AD41" s="10" t="n">
         <v>38.64</v>
       </c>
-      <c r="AE41" s="11" t="n">
+      <c r="AE41" s="10" t="n">
         <v>41.14</v>
       </c>
       <c r="AF41" s="10" t="n">
@@ -4390,10 +4390,10 @@
       <c r="C42" s="10" t="n">
         <v>46.89</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="10" t="n">
         <v>36.46</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="10" t="n">
         <v>37.76</v>
       </c>
       <c r="F42" s="10" t="n">
@@ -4408,7 +4408,7 @@
       <c r="I42" s="10" t="n">
         <v>43.04</v>
       </c>
-      <c r="J42" s="11" t="n">
+      <c r="J42" s="10" t="n">
         <v>42.79</v>
       </c>
       <c r="K42" s="10" t="n">
@@ -4429,22 +4429,22 @@
       <c r="P42" s="10" t="n">
         <v>46.71</v>
       </c>
-      <c r="Q42" s="11" t="n">
+      <c r="Q42" s="10" t="n">
         <v>42.49</v>
       </c>
-      <c r="R42" s="11" t="n">
+      <c r="R42" s="10" t="n">
         <v>39.33</v>
       </c>
-      <c r="S42" s="11" t="n">
+      <c r="S42" s="10" t="n">
         <v>40.14</v>
       </c>
-      <c r="T42" s="11" t="n">
+      <c r="T42" s="10" t="n">
         <v>38.01</v>
       </c>
-      <c r="U42" s="11" t="n">
+      <c r="U42" s="10" t="n">
         <v>38.08</v>
       </c>
-      <c r="V42" s="11" t="n">
+      <c r="V42" s="10" t="n">
         <v>38.74</v>
       </c>
       <c r="W42" s="10" t="n">
@@ -4453,16 +4453,16 @@
       <c r="X42" s="10" t="n">
         <v>46.21</v>
       </c>
-      <c r="Y42" s="11" t="n">
+      <c r="Y42" s="10" t="n">
         <v>40.55</v>
       </c>
-      <c r="Z42" s="11" t="n">
+      <c r="Z42" s="10" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA42" s="11" t="n">
+      <c r="AA42" s="10" t="n">
         <v>36.65</v>
       </c>
-      <c r="AB42" s="11" t="n">
+      <c r="AB42" s="10" t="n">
         <v>42.29</v>
       </c>
       <c r="AC42" s="10" t="n">
@@ -4480,7 +4480,7 @@
       <c r="AG42" s="10" t="n">
         <v>44.16</v>
       </c>
-      <c r="AH42" s="8" t="n">
+      <c r="AH42" s="10" t="n">
         <v>42.94</v>
       </c>
       <c r="AI42" s="7" t="n">
@@ -4501,22 +4501,22 @@
       <c r="C43" s="10" t="n">
         <v>47.79</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="10" t="n">
         <v>36.54</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="10" t="n">
         <v>35.36</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="10" t="n">
         <v>39.5</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="10" t="n">
         <v>39.05</v>
       </c>
       <c r="H43" s="10" t="n">
         <v>44.41</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="10" t="n">
         <v>42.89</v>
       </c>
       <c r="J43" s="10" t="n">
@@ -4543,43 +4543,43 @@
       <c r="Q43" s="10" t="n">
         <v>43.59</v>
       </c>
-      <c r="R43" s="11" t="n">
+      <c r="R43" s="10" t="n">
         <v>39.13</v>
       </c>
-      <c r="S43" s="11" t="n">
+      <c r="S43" s="10" t="n">
         <v>38.44</v>
       </c>
-      <c r="T43" s="11" t="n">
+      <c r="T43" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="U43" s="11" t="n">
+      <c r="U43" s="10" t="n">
         <v>42.06</v>
       </c>
-      <c r="V43" s="11" t="n">
+      <c r="V43" s="10" t="n">
         <v>39.01</v>
       </c>
-      <c r="W43" s="11" t="n">
+      <c r="W43" s="10" t="n">
         <v>42.07</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>46.61</v>
       </c>
-      <c r="Y43" s="11" t="n">
+      <c r="Y43" s="10" t="n">
         <v>36.92</v>
       </c>
-      <c r="Z43" s="11" t="n">
+      <c r="Z43" s="10" t="n">
         <v>37.61</v>
       </c>
-      <c r="AA43" s="11" t="n">
+      <c r="AA43" s="10" t="n">
         <v>36.41</v>
       </c>
-      <c r="AB43" s="11" t="n">
+      <c r="AB43" s="10" t="n">
         <v>40.19</v>
       </c>
-      <c r="AC43" s="11" t="n">
+      <c r="AC43" s="10" t="n">
         <v>39.22</v>
       </c>
-      <c r="AD43" s="11" t="n">
+      <c r="AD43" s="10" t="n">
         <v>40.28</v>
       </c>
       <c r="AE43" s="10" t="n">
@@ -4591,7 +4591,7 @@
       <c r="AG43" s="10" t="n">
         <v>45.59</v>
       </c>
-      <c r="AH43" s="8" t="n">
+      <c r="AH43" s="10" t="n">
         <v>42.27</v>
       </c>
       <c r="AI43" s="7" t="n">
@@ -5489,115 +5489,115 @@
       <c r="AK51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>GENESIS FM STEREO</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
+      <c r="B52" s="12" t="n">
         <v>107.5</v>
       </c>
-      <c r="C52" s="14" t="n">
+      <c r="C52" s="13" t="n">
         <v>45.55</v>
       </c>
-      <c r="D52" s="14" t="n">
+      <c r="D52" s="13" t="n">
         <v>45.58</v>
       </c>
-      <c r="E52" s="14" t="n">
+      <c r="E52" s="13" t="n">
         <v>46.18</v>
       </c>
-      <c r="F52" s="14" t="n">
+      <c r="F52" s="13" t="n">
         <v>45.65</v>
       </c>
-      <c r="G52" s="14" t="n">
+      <c r="G52" s="13" t="n">
         <v>47.34</v>
       </c>
-      <c r="H52" s="14" t="n">
+      <c r="H52" s="13" t="n">
         <v>47.62</v>
       </c>
-      <c r="I52" s="14" t="n">
+      <c r="I52" s="13" t="n">
         <v>46.46</v>
       </c>
-      <c r="J52" s="14" t="n">
+      <c r="J52" s="13" t="n">
         <v>45.94</v>
       </c>
-      <c r="K52" s="14" t="n">
+      <c r="K52" s="13" t="n">
         <v>45.49</v>
       </c>
-      <c r="L52" s="14" t="n">
+      <c r="L52" s="13" t="n">
         <v>45.62</v>
       </c>
-      <c r="M52" s="14" t="n">
+      <c r="M52" s="13" t="n">
         <v>46.22</v>
       </c>
-      <c r="N52" s="14" t="n">
+      <c r="N52" s="13" t="n">
         <v>47.42</v>
       </c>
-      <c r="O52" s="14" t="n">
+      <c r="O52" s="13" t="n">
         <v>46.59</v>
       </c>
-      <c r="P52" s="14" t="n">
+      <c r="P52" s="13" t="n">
         <v>46.35</v>
       </c>
-      <c r="Q52" s="14" t="n">
+      <c r="Q52" s="13" t="n">
         <v>46.21</v>
       </c>
-      <c r="R52" s="14" t="n">
+      <c r="R52" s="13" t="n">
         <v>46.19</v>
       </c>
-      <c r="S52" s="14" t="n">
+      <c r="S52" s="13" t="n">
         <v>47.04</v>
       </c>
-      <c r="T52" s="14" t="n">
+      <c r="T52" s="13" t="n">
         <v>45.74</v>
       </c>
-      <c r="U52" s="14" t="n">
+      <c r="U52" s="13" t="n">
         <v>45.27</v>
       </c>
-      <c r="V52" s="14" t="n">
+      <c r="V52" s="13" t="n">
         <v>45.62</v>
       </c>
-      <c r="W52" s="14" t="n">
+      <c r="W52" s="13" t="n">
         <v>44.74</v>
       </c>
-      <c r="X52" s="14" t="n">
+      <c r="X52" s="13" t="n">
         <v>49.16</v>
       </c>
-      <c r="Y52" s="14" t="n">
+      <c r="Y52" s="13" t="n">
         <v>46.34</v>
       </c>
-      <c r="Z52" s="14" t="n">
+      <c r="Z52" s="13" t="n">
         <v>45.4</v>
       </c>
-      <c r="AA52" s="14" t="n">
+      <c r="AA52" s="13" t="n">
         <v>45.42</v>
       </c>
-      <c r="AB52" s="14" t="n">
+      <c r="AB52" s="13" t="n">
         <v>47.13</v>
       </c>
-      <c r="AC52" s="14" t="n">
+      <c r="AC52" s="13" t="n">
         <v>45.49</v>
       </c>
-      <c r="AD52" s="14" t="n">
+      <c r="AD52" s="13" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE52" s="14" t="n">
+      <c r="AE52" s="13" t="n">
         <v>46.79</v>
       </c>
-      <c r="AF52" s="14" t="n">
+      <c r="AF52" s="13" t="n">
         <v>47.06</v>
       </c>
-      <c r="AG52" s="14" t="n">
+      <c r="AG52" s="13" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH52" s="14" t="n">
+      <c r="AH52" s="13" t="n">
         <v>46.28</v>
       </c>
-      <c r="AI52" s="15" t="n">
+      <c r="AI52" s="14" t="n">
         <v>497.9</v>
       </c>
-      <c r="AJ52" s="13" t="inlineStr"/>
-      <c r="AK52" s="16" t="inlineStr"/>
+      <c r="AJ52" s="12" t="inlineStr"/>
+      <c r="AK52" s="15" t="inlineStr"/>
     </row>
     <row r="53"/>
     <row r="54"/>
@@ -5772,7 +5772,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK62" s="17" t="n"/>
+      <c r="AK62" s="16" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="18" t="n"/>
+      <c r="AK63" s="17" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5892,105 +5892,105 @@
       <c r="B64" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C64" s="11" t="n">
+      <c r="C64" s="18" t="n">
         <v>37.2</v>
       </c>
-      <c r="D64" s="11" t="n">
+      <c r="D64" s="18" t="n">
         <v>37.1</v>
       </c>
-      <c r="E64" s="11" t="n">
+      <c r="E64" s="18" t="n">
         <v>36.25</v>
       </c>
-      <c r="F64" s="11" t="n">
+      <c r="F64" s="18" t="n">
         <v>35.95</v>
       </c>
-      <c r="G64" s="11" t="n">
+      <c r="G64" s="18" t="n">
         <v>38.22</v>
       </c>
-      <c r="H64" s="11" t="n">
+      <c r="H64" s="18" t="n">
         <v>35.83</v>
       </c>
-      <c r="I64" s="11" t="n">
+      <c r="I64" s="18" t="n">
         <v>38.13</v>
       </c>
-      <c r="J64" s="11" t="n">
+      <c r="J64" s="18" t="n">
         <v>36.34</v>
       </c>
-      <c r="K64" s="11" t="n">
+      <c r="K64" s="18" t="n">
         <v>37.93</v>
       </c>
-      <c r="L64" s="11" t="n">
+      <c r="L64" s="18" t="n">
         <v>37.71</v>
       </c>
-      <c r="M64" s="11" t="n">
+      <c r="M64" s="18" t="n">
         <v>35.95</v>
       </c>
-      <c r="N64" s="11" t="n">
+      <c r="N64" s="18" t="n">
         <v>35.99</v>
       </c>
-      <c r="O64" s="11" t="n">
+      <c r="O64" s="18" t="n">
         <v>38.22</v>
       </c>
-      <c r="P64" s="11" t="n">
+      <c r="P64" s="18" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q64" s="11" t="n">
+      <c r="Q64" s="18" t="n">
         <v>37.15</v>
       </c>
-      <c r="R64" s="11" t="n">
+      <c r="R64" s="18" t="n">
         <v>37.29</v>
       </c>
-      <c r="S64" s="11" t="n">
+      <c r="S64" s="18" t="n">
         <v>38.9</v>
       </c>
-      <c r="T64" s="11" t="n">
+      <c r="T64" s="18" t="n">
         <v>38</v>
       </c>
-      <c r="U64" s="11" t="n">
+      <c r="U64" s="18" t="n">
         <v>37.5</v>
       </c>
-      <c r="V64" s="11" t="n">
+      <c r="V64" s="18" t="n">
         <v>36.25</v>
       </c>
-      <c r="W64" s="11" t="n">
+      <c r="W64" s="18" t="n">
         <v>36.9</v>
       </c>
-      <c r="X64" s="11" t="n">
+      <c r="X64" s="18" t="n">
         <v>36.92</v>
       </c>
-      <c r="Y64" s="11" t="n">
+      <c r="Y64" s="18" t="n">
         <v>35.42</v>
       </c>
-      <c r="Z64" s="11" t="n">
+      <c r="Z64" s="18" t="n">
         <v>38.12</v>
       </c>
-      <c r="AA64" s="11" t="n">
+      <c r="AA64" s="18" t="n">
         <v>37.35</v>
       </c>
-      <c r="AB64" s="11" t="n">
+      <c r="AB64" s="18" t="n">
         <v>38.41</v>
       </c>
-      <c r="AC64" s="11" t="n">
+      <c r="AC64" s="18" t="n">
         <v>37.71</v>
       </c>
-      <c r="AD64" s="11" t="n">
+      <c r="AD64" s="18" t="n">
         <v>37.56</v>
       </c>
-      <c r="AE64" s="11" t="n">
+      <c r="AE64" s="18" t="n">
         <v>38.91</v>
       </c>
-      <c r="AF64" s="11" t="n">
+      <c r="AF64" s="18" t="n">
         <v>36.38</v>
       </c>
-      <c r="AG64" s="11" t="n">
+      <c r="AG64" s="18" t="n">
         <v>37.45</v>
       </c>
-      <c r="AH64" s="8" t="n">
+      <c r="AH64" s="18" t="n">
         <v>37.24</v>
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
       <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="18" t="n"/>
+      <c r="AK64" s="17" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -6001,105 +6001,105 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="11" t="n">
+      <c r="C65" s="18" t="n">
         <v>39.7</v>
       </c>
-      <c r="D65" s="11" t="n">
+      <c r="D65" s="18" t="n">
         <v>37.34</v>
       </c>
-      <c r="E65" s="11" t="n">
+      <c r="E65" s="18" t="n">
         <v>38.12</v>
       </c>
-      <c r="F65" s="11" t="n">
+      <c r="F65" s="18" t="n">
         <v>37.12</v>
       </c>
-      <c r="G65" s="11" t="n">
+      <c r="G65" s="18" t="n">
         <v>38.33</v>
       </c>
-      <c r="H65" s="11" t="n">
+      <c r="H65" s="18" t="n">
         <v>39.69</v>
       </c>
-      <c r="I65" s="11" t="n">
+      <c r="I65" s="18" t="n">
         <v>42.09</v>
       </c>
-      <c r="J65" s="11" t="n">
+      <c r="J65" s="18" t="n">
         <v>42.04</v>
       </c>
-      <c r="K65" s="11" t="n">
+      <c r="K65" s="18" t="n">
         <v>38.28</v>
       </c>
-      <c r="L65" s="11" t="n">
+      <c r="L65" s="18" t="n">
         <v>41.34</v>
       </c>
-      <c r="M65" s="11" t="n">
+      <c r="M65" s="18" t="n">
         <v>41.94</v>
       </c>
-      <c r="N65" s="11" t="n">
+      <c r="N65" s="18" t="n">
         <v>40.49</v>
       </c>
-      <c r="O65" s="11" t="n">
+      <c r="O65" s="18" t="n">
         <v>38.61</v>
       </c>
-      <c r="P65" s="11" t="n">
+      <c r="P65" s="18" t="n">
         <v>37.79</v>
       </c>
-      <c r="Q65" s="11" t="n">
+      <c r="Q65" s="18" t="n">
         <v>37.79</v>
       </c>
-      <c r="R65" s="11" t="n">
+      <c r="R65" s="18" t="n">
         <v>36.92</v>
       </c>
-      <c r="S65" s="11" t="n">
+      <c r="S65" s="18" t="n">
         <v>38.35</v>
       </c>
-      <c r="T65" s="11" t="n">
+      <c r="T65" s="18" t="n">
         <v>36.67</v>
       </c>
-      <c r="U65" s="11" t="n">
+      <c r="U65" s="18" t="n">
         <v>36.88</v>
       </c>
-      <c r="V65" s="11" t="n">
+      <c r="V65" s="18" t="n">
         <v>37.59</v>
       </c>
-      <c r="W65" s="11" t="n">
+      <c r="W65" s="18" t="n">
         <v>37.49</v>
       </c>
-      <c r="X65" s="11" t="n">
+      <c r="X65" s="18" t="n">
         <v>40.59</v>
       </c>
-      <c r="Y65" s="11" t="n">
+      <c r="Y65" s="18" t="n">
         <v>42.94</v>
       </c>
-      <c r="Z65" s="11" t="n">
+      <c r="Z65" s="18" t="n">
         <v>38.3</v>
       </c>
-      <c r="AA65" s="11" t="n">
+      <c r="AA65" s="18" t="n">
         <v>36.58</v>
       </c>
-      <c r="AB65" s="11" t="n">
+      <c r="AB65" s="18" t="n">
         <v>43.08</v>
       </c>
-      <c r="AC65" s="11" t="n">
+      <c r="AC65" s="18" t="n">
         <v>39.4</v>
       </c>
-      <c r="AD65" s="11" t="n">
+      <c r="AD65" s="18" t="n">
         <v>37.41</v>
       </c>
-      <c r="AE65" s="11" t="n">
+      <c r="AE65" s="18" t="n">
         <v>37.99</v>
       </c>
-      <c r="AF65" s="11" t="n">
+      <c r="AF65" s="18" t="n">
         <v>41.21</v>
       </c>
-      <c r="AG65" s="11" t="n">
+      <c r="AG65" s="18" t="n">
         <v>37.2</v>
       </c>
-      <c r="AH65" s="8" t="n">
+      <c r="AH65" s="18" t="n">
         <v>39.01</v>
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
       <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="18" t="n"/>
+      <c r="AK65" s="17" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="18" t="n"/>
+      <c r="AK66" s="17" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6219,105 +6219,105 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="11" t="n">
+      <c r="C67" s="18" t="n">
         <v>40.3</v>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D67" s="18" t="n">
         <v>41.59</v>
       </c>
-      <c r="E67" s="11" t="n">
+      <c r="E67" s="18" t="n">
         <v>38.95</v>
       </c>
-      <c r="F67" s="11" t="n">
+      <c r="F67" s="18" t="n">
         <v>40.75</v>
       </c>
-      <c r="G67" s="11" t="n">
+      <c r="G67" s="18" t="n">
         <v>41.29</v>
       </c>
-      <c r="H67" s="11" t="n">
+      <c r="H67" s="18" t="n">
         <v>40.61</v>
       </c>
-      <c r="I67" s="11" t="n">
+      <c r="I67" s="18" t="n">
         <v>40.69</v>
       </c>
-      <c r="J67" s="11" t="n">
+      <c r="J67" s="18" t="n">
         <v>43.48</v>
       </c>
-      <c r="K67" s="11" t="n">
+      <c r="K67" s="18" t="n">
         <v>41.87</v>
       </c>
-      <c r="L67" s="11" t="n">
+      <c r="L67" s="18" t="n">
         <v>41.22</v>
       </c>
-      <c r="M67" s="11" t="n">
+      <c r="M67" s="18" t="n">
         <v>40.41</v>
       </c>
-      <c r="N67" s="11" t="n">
+      <c r="N67" s="18" t="n">
         <v>41.46</v>
       </c>
-      <c r="O67" s="11" t="n">
+      <c r="O67" s="18" t="n">
         <v>40.07</v>
       </c>
-      <c r="P67" s="11" t="n">
+      <c r="P67" s="18" t="n">
         <v>40.54</v>
       </c>
-      <c r="Q67" s="11" t="n">
+      <c r="Q67" s="18" t="n">
         <v>40.48</v>
       </c>
-      <c r="R67" s="11" t="n">
+      <c r="R67" s="18" t="n">
         <v>41.38</v>
       </c>
-      <c r="S67" s="11" t="n">
+      <c r="S67" s="18" t="n">
         <v>41.15</v>
       </c>
-      <c r="T67" s="11" t="n">
+      <c r="T67" s="18" t="n">
         <v>39.41</v>
       </c>
-      <c r="U67" s="11" t="n">
+      <c r="U67" s="18" t="n">
         <v>39.12</v>
       </c>
-      <c r="V67" s="11" t="n">
+      <c r="V67" s="18" t="n">
         <v>40.48</v>
       </c>
-      <c r="W67" s="11" t="n">
+      <c r="W67" s="18" t="n">
         <v>40.44</v>
       </c>
-      <c r="X67" s="11" t="n">
+      <c r="X67" s="18" t="n">
         <v>40.11</v>
       </c>
-      <c r="Y67" s="11" t="n">
+      <c r="Y67" s="18" t="n">
         <v>38.81</v>
       </c>
-      <c r="Z67" s="11" t="n">
+      <c r="Z67" s="18" t="n">
         <v>40.83</v>
       </c>
-      <c r="AA67" s="11" t="n">
+      <c r="AA67" s="18" t="n">
         <v>39.05</v>
       </c>
-      <c r="AB67" s="11" t="n">
+      <c r="AB67" s="18" t="n">
         <v>39.54</v>
       </c>
-      <c r="AC67" s="11" t="n">
+      <c r="AC67" s="18" t="n">
         <v>38.81</v>
       </c>
-      <c r="AD67" s="11" t="n">
+      <c r="AD67" s="18" t="n">
         <v>39.5</v>
       </c>
-      <c r="AE67" s="11" t="n">
+      <c r="AE67" s="18" t="n">
         <v>40.44</v>
       </c>
-      <c r="AF67" s="11" t="n">
+      <c r="AF67" s="18" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG67" s="11" t="n">
+      <c r="AG67" s="18" t="n">
         <v>39.62</v>
       </c>
-      <c r="AH67" s="8" t="n">
+      <c r="AH67" s="18" t="n">
         <v>40.4</v>
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
       <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="18" t="n"/>
+      <c r="AK67" s="17" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="18" t="n"/>
+      <c r="AK68" s="17" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="18" t="n"/>
+      <c r="AK69" s="17" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6546,105 +6546,105 @@
       <c r="B70" s="6" t="n">
         <v>549.25</v>
       </c>
-      <c r="C70" s="11" t="n">
+      <c r="C70" s="18" t="n">
         <v>31.82</v>
       </c>
-      <c r="D70" s="11" t="n">
+      <c r="D70" s="18" t="n">
         <v>34.01</v>
       </c>
-      <c r="E70" s="11" t="n">
+      <c r="E70" s="18" t="n">
         <v>31.3</v>
       </c>
-      <c r="F70" s="11" t="n">
+      <c r="F70" s="18" t="n">
         <v>31.78</v>
       </c>
-      <c r="G70" s="11" t="n">
+      <c r="G70" s="18" t="n">
         <v>31.44</v>
       </c>
-      <c r="H70" s="11" t="n">
+      <c r="H70" s="18" t="n">
         <v>31.81</v>
       </c>
-      <c r="I70" s="11" t="n">
+      <c r="I70" s="18" t="n">
         <v>31.13</v>
       </c>
-      <c r="J70" s="11" t="n">
+      <c r="J70" s="18" t="n">
         <v>32.33</v>
       </c>
-      <c r="K70" s="11" t="n">
+      <c r="K70" s="18" t="n">
         <v>31.17</v>
       </c>
-      <c r="L70" s="11" t="n">
+      <c r="L70" s="18" t="n">
         <v>30.91</v>
       </c>
-      <c r="M70" s="11" t="n">
+      <c r="M70" s="18" t="n">
         <v>31.56</v>
       </c>
-      <c r="N70" s="11" t="n">
+      <c r="N70" s="18" t="n">
         <v>31.3</v>
       </c>
-      <c r="O70" s="11" t="n">
+      <c r="O70" s="18" t="n">
         <v>31.59</v>
       </c>
-      <c r="P70" s="11" t="n">
+      <c r="P70" s="18" t="n">
         <v>31.9</v>
       </c>
-      <c r="Q70" s="11" t="n">
+      <c r="Q70" s="18" t="n">
         <v>31.52</v>
       </c>
-      <c r="R70" s="11" t="n">
+      <c r="R70" s="18" t="n">
         <v>31.22</v>
       </c>
-      <c r="S70" s="11" t="n">
+      <c r="S70" s="18" t="n">
         <v>31.62</v>
       </c>
-      <c r="T70" s="11" t="n">
+      <c r="T70" s="18" t="n">
         <v>31.62</v>
       </c>
-      <c r="U70" s="11" t="n">
+      <c r="U70" s="18" t="n">
         <v>31.75</v>
       </c>
-      <c r="V70" s="11" t="n">
+      <c r="V70" s="18" t="n">
         <v>32.01</v>
       </c>
-      <c r="W70" s="11" t="n">
+      <c r="W70" s="18" t="n">
         <v>32.09</v>
       </c>
-      <c r="X70" s="11" t="n">
+      <c r="X70" s="18" t="n">
         <v>32.17</v>
       </c>
-      <c r="Y70" s="11" t="n">
+      <c r="Y70" s="18" t="n">
         <v>31.41</v>
       </c>
-      <c r="Z70" s="11" t="n">
+      <c r="Z70" s="18" t="n">
         <v>31.92</v>
       </c>
-      <c r="AA70" s="11" t="n">
+      <c r="AA70" s="18" t="n">
         <v>34.1</v>
       </c>
-      <c r="AB70" s="11" t="n">
+      <c r="AB70" s="18" t="n">
         <v>31.28</v>
       </c>
-      <c r="AC70" s="11" t="n">
+      <c r="AC70" s="18" t="n">
         <v>31.6</v>
       </c>
-      <c r="AD70" s="11" t="n">
+      <c r="AD70" s="18" t="n">
         <v>32.31</v>
       </c>
-      <c r="AE70" s="11" t="n">
+      <c r="AE70" s="18" t="n">
         <v>32.11</v>
       </c>
-      <c r="AF70" s="11" t="n">
+      <c r="AF70" s="18" t="n">
         <v>31.26</v>
       </c>
-      <c r="AG70" s="11" t="n">
+      <c r="AG70" s="18" t="n">
         <v>32.11</v>
       </c>
-      <c r="AH70" s="8" t="n">
+      <c r="AH70" s="18" t="n">
         <v>31.81</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
       <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="18" t="n"/>
+      <c r="AK70" s="17" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6655,105 +6655,105 @@
       <c r="B71" s="6" t="n">
         <v>573.25</v>
       </c>
-      <c r="C71" s="11" t="n">
+      <c r="C71" s="18" t="n">
         <v>30.1</v>
       </c>
-      <c r="D71" s="11" t="n">
+      <c r="D71" s="18" t="n">
         <v>31.2</v>
       </c>
-      <c r="E71" s="11" t="n">
+      <c r="E71" s="18" t="n">
         <v>29.72</v>
       </c>
-      <c r="F71" s="11" t="n">
+      <c r="F71" s="18" t="n">
         <v>30.8</v>
       </c>
-      <c r="G71" s="11" t="n">
+      <c r="G71" s="18" t="n">
         <v>31.7</v>
       </c>
-      <c r="H71" s="11" t="n">
+      <c r="H71" s="18" t="n">
         <v>29.91</v>
       </c>
-      <c r="I71" s="11" t="n">
+      <c r="I71" s="18" t="n">
         <v>30.73</v>
       </c>
-      <c r="J71" s="11" t="n">
+      <c r="J71" s="18" t="n">
         <v>34.14</v>
       </c>
-      <c r="K71" s="11" t="n">
+      <c r="K71" s="18" t="n">
         <v>30.47</v>
       </c>
-      <c r="L71" s="11" t="n">
+      <c r="L71" s="18" t="n">
         <v>32.12</v>
       </c>
-      <c r="M71" s="11" t="n">
+      <c r="M71" s="18" t="n">
         <v>29.9</v>
       </c>
-      <c r="N71" s="11" t="n">
+      <c r="N71" s="18" t="n">
         <v>30.12</v>
       </c>
-      <c r="O71" s="11" t="n">
+      <c r="O71" s="18" t="n">
         <v>29.56</v>
       </c>
-      <c r="P71" s="11" t="n">
+      <c r="P71" s="18" t="n">
         <v>30.11</v>
       </c>
-      <c r="Q71" s="11" t="n">
+      <c r="Q71" s="18" t="n">
         <v>31.05</v>
       </c>
-      <c r="R71" s="11" t="n">
+      <c r="R71" s="18" t="n">
         <v>29.82</v>
       </c>
-      <c r="S71" s="11" t="n">
+      <c r="S71" s="18" t="n">
         <v>30.34</v>
       </c>
-      <c r="T71" s="11" t="n">
+      <c r="T71" s="18" t="n">
         <v>29.44</v>
       </c>
-      <c r="U71" s="11" t="n">
+      <c r="U71" s="18" t="n">
         <v>29.68</v>
       </c>
-      <c r="V71" s="11" t="n">
+      <c r="V71" s="18" t="n">
         <v>29.7</v>
       </c>
-      <c r="W71" s="11" t="n">
+      <c r="W71" s="18" t="n">
         <v>29.73</v>
       </c>
-      <c r="X71" s="11" t="n">
+      <c r="X71" s="18" t="n">
         <v>31.34</v>
       </c>
-      <c r="Y71" s="11" t="n">
+      <c r="Y71" s="18" t="n">
         <v>34.96</v>
       </c>
-      <c r="Z71" s="11" t="n">
+      <c r="Z71" s="18" t="n">
         <v>29.62</v>
       </c>
-      <c r="AA71" s="11" t="n">
+      <c r="AA71" s="18" t="n">
         <v>29.48</v>
       </c>
-      <c r="AB71" s="11" t="n">
+      <c r="AB71" s="18" t="n">
         <v>29.66</v>
       </c>
-      <c r="AC71" s="11" t="n">
+      <c r="AC71" s="18" t="n">
         <v>29.65</v>
       </c>
-      <c r="AD71" s="11" t="n">
+      <c r="AD71" s="18" t="n">
         <v>29.81</v>
       </c>
-      <c r="AE71" s="11" t="n">
+      <c r="AE71" s="18" t="n">
         <v>29.57</v>
       </c>
-      <c r="AF71" s="11" t="n">
+      <c r="AF71" s="18" t="n">
         <v>29.62</v>
       </c>
-      <c r="AG71" s="11" t="n">
+      <c r="AG71" s="18" t="n">
         <v>32.01</v>
       </c>
-      <c r="AH71" s="8" t="n">
+      <c r="AH71" s="18" t="n">
         <v>30.52</v>
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
       <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="18" t="n"/>
+      <c r="AK71" s="17" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6764,105 +6764,105 @@
       <c r="B72" s="6" t="n">
         <v>585.25</v>
       </c>
-      <c r="C72" s="11" t="n">
+      <c r="C72" s="18" t="n">
         <v>33.38</v>
       </c>
-      <c r="D72" s="11" t="n">
+      <c r="D72" s="18" t="n">
         <v>32.61</v>
       </c>
-      <c r="E72" s="11" t="n">
+      <c r="E72" s="18" t="n">
         <v>32.72</v>
       </c>
-      <c r="F72" s="11" t="n">
+      <c r="F72" s="18" t="n">
         <v>32.6</v>
       </c>
-      <c r="G72" s="11" t="n">
+      <c r="G72" s="18" t="n">
         <v>32.51</v>
       </c>
-      <c r="H72" s="11" t="n">
+      <c r="H72" s="18" t="n">
         <v>32.48</v>
       </c>
-      <c r="I72" s="11" t="n">
+      <c r="I72" s="18" t="n">
         <v>31.93</v>
       </c>
-      <c r="J72" s="11" t="n">
+      <c r="J72" s="18" t="n">
         <v>35.1</v>
       </c>
-      <c r="K72" s="11" t="n">
+      <c r="K72" s="18" t="n">
         <v>32.72</v>
       </c>
-      <c r="L72" s="11" t="n">
+      <c r="L72" s="18" t="n">
         <v>34.05</v>
       </c>
-      <c r="M72" s="11" t="n">
+      <c r="M72" s="18" t="n">
         <v>34.14</v>
       </c>
-      <c r="N72" s="11" t="n">
+      <c r="N72" s="18" t="n">
         <v>32.36</v>
       </c>
-      <c r="O72" s="11" t="n">
+      <c r="O72" s="18" t="n">
         <v>32.78</v>
       </c>
-      <c r="P72" s="11" t="n">
+      <c r="P72" s="18" t="n">
         <v>34.24</v>
       </c>
-      <c r="Q72" s="11" t="n">
+      <c r="Q72" s="18" t="n">
         <v>32.56</v>
       </c>
-      <c r="R72" s="11" t="n">
+      <c r="R72" s="18" t="n">
         <v>32.69</v>
       </c>
-      <c r="S72" s="11" t="n">
+      <c r="S72" s="18" t="n">
         <v>32.33</v>
       </c>
-      <c r="T72" s="11" t="n">
+      <c r="T72" s="18" t="n">
         <v>32.36</v>
       </c>
-      <c r="U72" s="11" t="n">
+      <c r="U72" s="18" t="n">
         <v>32.29</v>
       </c>
-      <c r="V72" s="11" t="n">
+      <c r="V72" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="W72" s="11" t="n">
+      <c r="W72" s="18" t="n">
         <v>32.46</v>
       </c>
-      <c r="X72" s="11" t="n">
+      <c r="X72" s="18" t="n">
         <v>31.89</v>
       </c>
-      <c r="Y72" s="11" t="n">
+      <c r="Y72" s="18" t="n">
         <v>32.44</v>
       </c>
-      <c r="Z72" s="11" t="n">
+      <c r="Z72" s="18" t="n">
         <v>31.9</v>
       </c>
-      <c r="AA72" s="11" t="n">
+      <c r="AA72" s="18" t="n">
         <v>32.17</v>
       </c>
-      <c r="AB72" s="11" t="n">
+      <c r="AB72" s="18" t="n">
         <v>33.28</v>
       </c>
-      <c r="AC72" s="11" t="n">
+      <c r="AC72" s="18" t="n">
         <v>32.95</v>
       </c>
-      <c r="AD72" s="11" t="n">
+      <c r="AD72" s="18" t="n">
         <v>32.63</v>
       </c>
-      <c r="AE72" s="11" t="n">
+      <c r="AE72" s="18" t="n">
         <v>32.53</v>
       </c>
-      <c r="AF72" s="11" t="n">
+      <c r="AF72" s="18" t="n">
         <v>32.38</v>
       </c>
-      <c r="AG72" s="11" t="n">
+      <c r="AG72" s="18" t="n">
         <v>32.41</v>
       </c>
-      <c r="AH72" s="8" t="n">
+      <c r="AH72" s="18" t="n">
         <v>32.74</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
       <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="18" t="n"/>
+      <c r="AK72" s="17" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6906,7 +6906,7 @@
       <c r="M73" s="7" t="n">
         <v>79.97</v>
       </c>
-      <c r="N73" s="11" t="n">
+      <c r="N73" s="18" t="n">
         <v>55.45</v>
       </c>
       <c r="O73" s="7" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
       <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="18" t="n"/>
+      <c r="AK73" s="17" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6982,113 +6982,113 @@
       <c r="B74" s="6" t="n">
         <v>621.25</v>
       </c>
-      <c r="C74" s="11" t="n">
+      <c r="C74" s="18" t="n">
         <v>30.32</v>
       </c>
-      <c r="D74" s="11" t="n">
+      <c r="D74" s="18" t="n">
         <v>30.3</v>
       </c>
-      <c r="E74" s="11" t="n">
+      <c r="E74" s="18" t="n">
         <v>30.2</v>
       </c>
-      <c r="F74" s="11" t="n">
+      <c r="F74" s="18" t="n">
         <v>29.75</v>
       </c>
-      <c r="G74" s="11" t="n">
+      <c r="G74" s="18" t="n">
         <v>29.9</v>
       </c>
-      <c r="H74" s="11" t="n">
+      <c r="H74" s="18" t="n">
         <v>29.98</v>
       </c>
-      <c r="I74" s="11" t="n">
+      <c r="I74" s="18" t="n">
         <v>29.66</v>
       </c>
-      <c r="J74" s="11" t="n">
+      <c r="J74" s="18" t="n">
         <v>29.84</v>
       </c>
-      <c r="K74" s="11" t="n">
+      <c r="K74" s="18" t="n">
         <v>30.35</v>
       </c>
-      <c r="L74" s="11" t="n">
+      <c r="L74" s="18" t="n">
         <v>33.02</v>
       </c>
-      <c r="M74" s="11" t="n">
+      <c r="M74" s="18" t="n">
         <v>30.01</v>
       </c>
-      <c r="N74" s="11" t="n">
+      <c r="N74" s="18" t="n">
         <v>29.79</v>
       </c>
-      <c r="O74" s="11" t="n">
+      <c r="O74" s="18" t="n">
         <v>32.08</v>
       </c>
-      <c r="P74" s="11" t="n">
+      <c r="P74" s="18" t="n">
         <v>30.26</v>
       </c>
-      <c r="Q74" s="11" t="n">
+      <c r="Q74" s="18" t="n">
         <v>30.26</v>
       </c>
-      <c r="R74" s="11" t="n">
+      <c r="R74" s="18" t="n">
         <v>29.52</v>
       </c>
-      <c r="S74" s="11" t="n">
+      <c r="S74" s="18" t="n">
         <v>30.26</v>
       </c>
-      <c r="T74" s="11" t="n">
+      <c r="T74" s="18" t="n">
         <v>29.72</v>
       </c>
-      <c r="U74" s="11" t="n">
+      <c r="U74" s="18" t="n">
         <v>31.64</v>
       </c>
-      <c r="V74" s="11" t="n">
+      <c r="V74" s="18" t="n">
         <v>29.29</v>
       </c>
-      <c r="W74" s="11" t="n">
+      <c r="W74" s="18" t="n">
         <v>29.83</v>
       </c>
-      <c r="X74" s="11" t="n">
+      <c r="X74" s="18" t="n">
         <v>30.21</v>
       </c>
-      <c r="Y74" s="11" t="n">
+      <c r="Y74" s="18" t="n">
         <v>31.16</v>
       </c>
-      <c r="Z74" s="11" t="n">
+      <c r="Z74" s="18" t="n">
         <v>29.88</v>
       </c>
-      <c r="AA74" s="11" t="n">
+      <c r="AA74" s="18" t="n">
         <v>33.85</v>
       </c>
-      <c r="AB74" s="11" t="n">
+      <c r="AB74" s="18" t="n">
         <v>29.26</v>
       </c>
-      <c r="AC74" s="11" t="n">
+      <c r="AC74" s="18" t="n">
         <v>31.25</v>
       </c>
-      <c r="AD74" s="11" t="n">
+      <c r="AD74" s="18" t="n">
         <v>30.8</v>
       </c>
-      <c r="AE74" s="11" t="n">
+      <c r="AE74" s="18" t="n">
         <v>29.49</v>
       </c>
-      <c r="AF74" s="11" t="n">
+      <c r="AF74" s="18" t="n">
         <v>30.38</v>
       </c>
-      <c r="AG74" s="11" t="n">
+      <c r="AG74" s="18" t="n">
         <v>30.25</v>
       </c>
-      <c r="AH74" s="8" t="n">
+      <c r="AH74" s="18" t="n">
         <v>30.4</v>
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
       <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="18" t="n"/>
+      <c r="AK74" s="17" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B75" s="13" t="n">
+      <c r="B75" s="12" t="n">
         <v>633.25</v>
       </c>
       <c r="C75" s="19" t="n">
@@ -7184,11 +7184,11 @@
       <c r="AG75" s="19" t="n">
         <v>29.59</v>
       </c>
-      <c r="AH75" s="15" t="n">
+      <c r="AH75" s="19" t="n">
         <v>29.84</v>
       </c>
-      <c r="AI75" s="13" t="inlineStr"/>
-      <c r="AJ75" s="13" t="inlineStr"/>
+      <c r="AI75" s="12" t="inlineStr"/>
+      <c r="AJ75" s="12" t="inlineStr"/>
       <c r="AK75" s="20" t="n"/>
     </row>
   </sheetData>

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,6 +204,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,15 +225,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1046,7 +1055,12 @@
         <v>244.66</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="9" t="inlineStr"/>
+      <c r="AK11" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1157,7 +1171,7 @@
         <v>160.6</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="9" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1268,7 +1282,7 @@
         <v>200.59</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="9" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1318,7 +1332,7 @@
       <c r="O14" s="7" t="n">
         <v>68.06999999999999</v>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="P14" s="11" t="n">
         <v>51.91</v>
       </c>
       <c r="Q14" s="7" t="n">
@@ -1379,7 +1393,12 @@
         <v>265.65</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="9" t="inlineStr"/>
+      <c r="AK14" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1490,7 +1509,12 @@
         <v>229.65</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="9" t="inlineStr"/>
+      <c r="AK15" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1601,7 +1625,12 @@
         <v>428.49</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="9" t="inlineStr"/>
+      <c r="AK16" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1712,7 +1741,12 @@
         <v>388.85</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="9" t="inlineStr"/>
+      <c r="AK17" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1723,107 +1757,112 @@
       <c r="B18" s="6" t="n">
         <v>91.5</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="11" t="n">
         <v>52.72</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>50.06</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>58.76</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="11" t="n">
         <v>50.41</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="11" t="n">
         <v>46.62</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" s="11" t="n">
         <v>49.69</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I18" s="11" t="n">
         <v>50.71</v>
       </c>
-      <c r="J18" s="10" t="n">
+      <c r="J18" s="11" t="n">
         <v>48.24</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="K18" s="11" t="n">
         <v>50.75</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L18" s="11" t="n">
         <v>50.51</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="M18" s="11" t="n">
         <v>52.76</v>
       </c>
-      <c r="N18" s="10" t="n">
+      <c r="N18" s="11" t="n">
         <v>51.64</v>
       </c>
-      <c r="O18" s="10" t="n">
+      <c r="O18" s="11" t="n">
         <v>48.68</v>
       </c>
-      <c r="P18" s="10" t="n">
+      <c r="P18" s="11" t="n">
         <v>49.17</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="11" t="n">
         <v>53.33</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="R18" s="11" t="n">
         <v>50.15</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="S18" s="11" t="n">
         <v>48.7</v>
       </c>
-      <c r="T18" s="10" t="n">
+      <c r="T18" s="11" t="n">
         <v>49.26</v>
       </c>
-      <c r="U18" s="10" t="n">
+      <c r="U18" s="11" t="n">
         <v>47.96</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="11" t="n">
         <v>47.53</v>
       </c>
-      <c r="W18" s="10" t="n">
+      <c r="W18" s="11" t="n">
         <v>49.54</v>
       </c>
-      <c r="X18" s="10" t="n">
+      <c r="X18" s="11" t="n">
         <v>49.93</v>
       </c>
-      <c r="Y18" s="10" t="n">
+      <c r="Y18" s="11" t="n">
         <v>52.67</v>
       </c>
-      <c r="Z18" s="10" t="n">
+      <c r="Z18" s="11" t="n">
         <v>48.81</v>
       </c>
-      <c r="AA18" s="10" t="n">
+      <c r="AA18" s="11" t="n">
         <v>48.32</v>
       </c>
-      <c r="AB18" s="10" t="n">
+      <c r="AB18" s="11" t="n">
         <v>49.61</v>
       </c>
-      <c r="AC18" s="10" t="n">
+      <c r="AC18" s="11" t="n">
         <v>49.47</v>
       </c>
-      <c r="AD18" s="10" t="n">
+      <c r="AD18" s="11" t="n">
         <v>47.34</v>
       </c>
-      <c r="AE18" s="10" t="n">
+      <c r="AE18" s="11" t="n">
         <v>49.9</v>
       </c>
-      <c r="AF18" s="10" t="n">
+      <c r="AF18" s="11" t="n">
         <v>52.66</v>
       </c>
-      <c r="AG18" s="10" t="n">
+      <c r="AG18" s="11" t="n">
         <v>51.71</v>
       </c>
-      <c r="AH18" s="10" t="n">
+      <c r="AH18" s="11" t="n">
         <v>50.25</v>
       </c>
       <c r="AI18" s="8" t="n">
         <v>499.47</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="9" t="inlineStr"/>
+      <c r="AK18" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1934,7 +1973,12 @@
         <v>315.82</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="9" t="inlineStr"/>
+      <c r="AK19" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2045,7 +2089,12 @@
         <v>478.59</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="9" t="inlineStr"/>
+      <c r="AK20" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2131,10 +2180,10 @@
       <c r="AA21" s="7" t="n">
         <v>62.14</v>
       </c>
-      <c r="AB21" s="10" t="n">
+      <c r="AB21" s="11" t="n">
         <v>48.92</v>
       </c>
-      <c r="AC21" s="10" t="n">
+      <c r="AC21" s="11" t="n">
         <v>42.56</v>
       </c>
       <c r="AD21" s="7" t="n">
@@ -2156,7 +2205,12 @@
         <v>349.62</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="9" t="inlineStr"/>
+      <c r="AK21" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2227,7 +2281,7 @@
       <c r="V22" s="7" t="n">
         <v>56.63</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="11" t="n">
         <v>53.21</v>
       </c>
       <c r="X22" s="7" t="n">
@@ -2245,19 +2299,19 @@
       <c r="AB22" s="7" t="n">
         <v>56.89</v>
       </c>
-      <c r="AC22" s="10" t="n">
+      <c r="AC22" s="11" t="n">
         <v>51.04</v>
       </c>
-      <c r="AD22" s="10" t="n">
+      <c r="AD22" s="11" t="n">
         <v>45.58</v>
       </c>
-      <c r="AE22" s="10" t="n">
+      <c r="AE22" s="11" t="n">
         <v>45.66</v>
       </c>
-      <c r="AF22" s="10" t="n">
+      <c r="AF22" s="11" t="n">
         <v>48.05</v>
       </c>
-      <c r="AG22" s="10" t="n">
+      <c r="AG22" s="11" t="n">
         <v>47.09</v>
       </c>
       <c r="AH22" s="7" t="n">
@@ -2267,7 +2321,12 @@
         <v>386.51</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="9" t="inlineStr"/>
+      <c r="AK22" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2378,7 +2437,7 @@
         <v>219.15</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="9" t="inlineStr"/>
+      <c r="AK23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2489,7 +2548,12 @@
         <v>226.77</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="9" t="inlineStr"/>
+      <c r="AK24" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2600,7 +2664,7 @@
         <v>123.83</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="9" t="inlineStr"/>
+      <c r="AK25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2711,7 +2775,12 @@
         <v>223.97</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="9" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2728,7 +2797,7 @@
       <c r="D27" s="7" t="n">
         <v>60.51</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="11" t="n">
         <v>52.24</v>
       </c>
       <c r="F27" s="7" t="n">
@@ -2822,7 +2891,12 @@
         <v>431.6</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="9" t="inlineStr"/>
+      <c r="AK27" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2933,7 +3007,12 @@
         <v>478.51</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="9" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3044,7 +3123,12 @@
         <v>258.64</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="9" t="inlineStr"/>
+      <c r="AK29" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3155,7 +3239,12 @@
         <v>254.74</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="9" t="inlineStr"/>
+      <c r="AK30" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3166,107 +3255,112 @@
       <c r="B31" s="6" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="11" t="n">
         <v>49.18</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="11" t="n">
         <v>38.17</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="11" t="n">
         <v>39.78</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="11" t="n">
         <v>48.22</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G31" s="11" t="n">
         <v>45.28</v>
       </c>
-      <c r="H31" s="10" t="n">
+      <c r="H31" s="11" t="n">
         <v>47.22</v>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="11" t="n">
         <v>47.81</v>
       </c>
-      <c r="J31" s="10" t="n">
+      <c r="J31" s="11" t="n">
         <v>46.02</v>
       </c>
-      <c r="K31" s="10" t="n">
+      <c r="K31" s="11" t="n">
         <v>47.37</v>
       </c>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="11" t="n">
         <v>45.26</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="11" t="n">
         <v>49.09</v>
       </c>
-      <c r="N31" s="10" t="n">
+      <c r="N31" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="O31" s="10" t="n">
+      <c r="O31" s="11" t="n">
         <v>47.71</v>
       </c>
-      <c r="P31" s="10" t="n">
+      <c r="P31" s="11" t="n">
         <v>53.23</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="11" t="n">
         <v>43.31</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="11" t="n">
         <v>42.73</v>
       </c>
-      <c r="S31" s="10" t="n">
+      <c r="S31" s="11" t="n">
         <v>36.38</v>
       </c>
-      <c r="T31" s="10" t="n">
+      <c r="T31" s="11" t="n">
         <v>42.77</v>
       </c>
-      <c r="U31" s="10" t="n">
+      <c r="U31" s="11" t="n">
         <v>40.38</v>
       </c>
-      <c r="V31" s="10" t="n">
+      <c r="V31" s="11" t="n">
         <v>44.49</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="11" t="n">
         <v>45.69</v>
       </c>
-      <c r="X31" s="10" t="n">
+      <c r="X31" s="11" t="n">
         <v>45.4</v>
       </c>
-      <c r="Y31" s="10" t="n">
+      <c r="Y31" s="11" t="n">
         <v>40.74</v>
       </c>
-      <c r="Z31" s="10" t="n">
+      <c r="Z31" s="11" t="n">
         <v>41.24</v>
       </c>
-      <c r="AA31" s="10" t="n">
+      <c r="AA31" s="11" t="n">
         <v>41.48</v>
       </c>
-      <c r="AB31" s="10" t="n">
+      <c r="AB31" s="11" t="n">
         <v>42.87</v>
       </c>
-      <c r="AC31" s="10" t="n">
+      <c r="AC31" s="11" t="n">
         <v>49.16</v>
       </c>
-      <c r="AD31" s="10" t="n">
+      <c r="AD31" s="11" t="n">
         <v>40.41</v>
       </c>
-      <c r="AE31" s="10" t="n">
+      <c r="AE31" s="11" t="n">
         <v>47.34</v>
       </c>
-      <c r="AF31" s="10" t="n">
+      <c r="AF31" s="11" t="n">
         <v>51.7</v>
       </c>
-      <c r="AG31" s="10" t="n">
+      <c r="AG31" s="11" t="n">
         <v>45.77</v>
       </c>
-      <c r="AH31" s="10" t="n">
+      <c r="AH31" s="11" t="n">
         <v>44.94</v>
       </c>
       <c r="AI31" s="8" t="n">
         <v>485.2</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="9" t="inlineStr"/>
+      <c r="AK31" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3283,7 +3377,7 @@
       <c r="D32" s="7" t="n">
         <v>55.07</v>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E32" s="11" t="n">
         <v>52.52</v>
       </c>
       <c r="F32" s="7" t="n">
@@ -3377,7 +3471,12 @@
         <v>474.57</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="9" t="inlineStr"/>
+      <c r="AK32" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3488,7 +3587,12 @@
         <v>326</v>
       </c>
       <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="9" t="inlineStr"/>
+      <c r="AK33" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3599,7 +3703,12 @@
         <v>478.65</v>
       </c>
       <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="9" t="inlineStr"/>
+      <c r="AK34" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3710,7 +3819,12 @@
         <v>497.28</v>
       </c>
       <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="9" t="inlineStr"/>
+      <c r="AK35" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3821,7 +3935,12 @@
         <v>431.37</v>
       </c>
       <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="9" t="inlineStr"/>
+      <c r="AK36" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3832,107 +3951,112 @@
       <c r="B37" s="6" t="n">
         <v>101.1</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="11" t="n">
         <v>41.52</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="11" t="n">
         <v>37.06</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="11" t="n">
         <v>39.89</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="11" t="n">
         <v>41.01</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="11" t="n">
         <v>40.08</v>
       </c>
-      <c r="H37" s="10" t="n">
+      <c r="H37" s="11" t="n">
         <v>41.32</v>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="I37" s="11" t="n">
         <v>40.03</v>
       </c>
-      <c r="J37" s="10" t="n">
+      <c r="J37" s="11" t="n">
         <v>40.92</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="K37" s="11" t="n">
         <v>39.57</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="11" t="n">
         <v>40.51</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="11" t="n">
         <v>44.43</v>
       </c>
-      <c r="N37" s="10" t="n">
+      <c r="N37" s="11" t="n">
         <v>40.55</v>
       </c>
-      <c r="O37" s="10" t="n">
+      <c r="O37" s="11" t="n">
         <v>43.01</v>
       </c>
-      <c r="P37" s="10" t="n">
+      <c r="P37" s="11" t="n">
         <v>43.79</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="11" t="n">
         <v>40.86</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="11" t="n">
         <v>36.73</v>
       </c>
-      <c r="S37" s="10" t="n">
+      <c r="S37" s="11" t="n">
         <v>36.76</v>
       </c>
-      <c r="T37" s="10" t="n">
+      <c r="T37" s="11" t="n">
         <v>38.71</v>
       </c>
-      <c r="U37" s="10" t="n">
+      <c r="U37" s="11" t="n">
         <v>36.86</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="11" t="n">
         <v>40.22</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="11" t="n">
         <v>40.92</v>
       </c>
-      <c r="X37" s="10" t="n">
+      <c r="X37" s="11" t="n">
         <v>39.83</v>
       </c>
-      <c r="Y37" s="10" t="n">
+      <c r="Y37" s="11" t="n">
         <v>37.26</v>
       </c>
-      <c r="Z37" s="10" t="n">
+      <c r="Z37" s="11" t="n">
         <v>38.74</v>
       </c>
-      <c r="AA37" s="10" t="n">
+      <c r="AA37" s="11" t="n">
         <v>37.96</v>
       </c>
-      <c r="AB37" s="10" t="n">
+      <c r="AB37" s="11" t="n">
         <v>41.61</v>
       </c>
-      <c r="AC37" s="10" t="n">
+      <c r="AC37" s="11" t="n">
         <v>41.84</v>
       </c>
-      <c r="AD37" s="10" t="n">
+      <c r="AD37" s="11" t="n">
         <v>38.69</v>
       </c>
-      <c r="AE37" s="10" t="n">
+      <c r="AE37" s="11" t="n">
         <v>41.51</v>
       </c>
-      <c r="AF37" s="10" t="n">
+      <c r="AF37" s="11" t="n">
         <v>41.72</v>
       </c>
-      <c r="AG37" s="10" t="n">
+      <c r="AG37" s="11" t="n">
         <v>41.58</v>
       </c>
-      <c r="AH37" s="10" t="n">
+      <c r="AH37" s="11" t="n">
         <v>40.18</v>
       </c>
       <c r="AI37" s="8" t="n">
         <v>499.53</v>
       </c>
       <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="9" t="inlineStr"/>
+      <c r="AK37" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4043,7 +4167,7 @@
         <v>159.74</v>
       </c>
       <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="9" t="inlineStr"/>
+      <c r="AK38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4154,7 +4278,12 @@
         <v>422.29</v>
       </c>
       <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="9" t="inlineStr"/>
+      <c r="AK39" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4265,7 +4394,12 @@
         <v>471.03</v>
       </c>
       <c r="AJ40" s="6" t="inlineStr"/>
-      <c r="AK40" s="9" t="inlineStr"/>
+      <c r="AK40" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4276,107 +4410,107 @@
       <c r="B41" s="6" t="n">
         <v>103.1</v>
       </c>
-      <c r="C41" s="10" t="n">
+      <c r="C41" s="11" t="n">
         <v>46.72</v>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="11" t="n">
         <v>35.76</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="11" t="n">
         <v>36.4</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="11" t="n">
         <v>45.76</v>
       </c>
-      <c r="G41" s="10" t="n">
+      <c r="G41" s="11" t="n">
         <v>43.98</v>
       </c>
-      <c r="H41" s="10" t="n">
+      <c r="H41" s="11" t="n">
         <v>45.91</v>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I41" s="11" t="n">
         <v>42.62</v>
       </c>
-      <c r="J41" s="10" t="n">
+      <c r="J41" s="11" t="n">
         <v>44.54</v>
       </c>
-      <c r="K41" s="10" t="n">
+      <c r="K41" s="11" t="n">
         <v>43.32</v>
       </c>
-      <c r="L41" s="10" t="n">
+      <c r="L41" s="11" t="n">
         <v>43.78</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="11" t="n">
         <v>46.12</v>
       </c>
-      <c r="N41" s="10" t="n">
+      <c r="N41" s="11" t="n">
         <v>45.71</v>
       </c>
-      <c r="O41" s="10" t="n">
+      <c r="O41" s="11" t="n">
         <v>45.21</v>
       </c>
-      <c r="P41" s="10" t="n">
+      <c r="P41" s="11" t="n">
         <v>42.01</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="11" t="n">
         <v>47.36</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="11" t="n">
         <v>43.31</v>
       </c>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="11" t="n">
         <v>37.48</v>
       </c>
-      <c r="T41" s="10" t="n">
+      <c r="T41" s="11" t="n">
         <v>43.12</v>
       </c>
-      <c r="U41" s="10" t="n">
+      <c r="U41" s="11" t="n">
         <v>41.52</v>
       </c>
-      <c r="V41" s="10" t="n">
+      <c r="V41" s="11" t="n">
         <v>42.48</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="11" t="n">
         <v>42.72</v>
       </c>
-      <c r="X41" s="10" t="n">
+      <c r="X41" s="11" t="n">
         <v>46.34</v>
       </c>
-      <c r="Y41" s="10" t="n">
+      <c r="Y41" s="11" t="n">
         <v>42.01</v>
       </c>
-      <c r="Z41" s="10" t="n">
+      <c r="Z41" s="11" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA41" s="10" t="n">
+      <c r="AA41" s="11" t="n">
         <v>41.55</v>
       </c>
-      <c r="AB41" s="10" t="n">
+      <c r="AB41" s="11" t="n">
         <v>41.22</v>
       </c>
-      <c r="AC41" s="10" t="n">
+      <c r="AC41" s="11" t="n">
         <v>44.88</v>
       </c>
-      <c r="AD41" s="10" t="n">
+      <c r="AD41" s="11" t="n">
         <v>38.64</v>
       </c>
-      <c r="AE41" s="10" t="n">
+      <c r="AE41" s="11" t="n">
         <v>41.14</v>
       </c>
-      <c r="AF41" s="10" t="n">
+      <c r="AF41" s="11" t="n">
         <v>47.4</v>
       </c>
-      <c r="AG41" s="10" t="n">
+      <c r="AG41" s="11" t="n">
         <v>48.04</v>
       </c>
-      <c r="AH41" s="10" t="n">
+      <c r="AH41" s="11" t="n">
         <v>43.14</v>
       </c>
       <c r="AI41" s="7" t="n">
         <v>161.11</v>
       </c>
       <c r="AJ41" s="6" t="inlineStr"/>
-      <c r="AK41" s="9" t="inlineStr"/>
+      <c r="AK41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4387,107 +4521,107 @@
       <c r="B42" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="11" t="n">
         <v>46.89</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="11" t="n">
         <v>36.46</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="11" t="n">
         <v>37.76</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="11" t="n">
         <v>45.51</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="G42" s="11" t="n">
         <v>44.04</v>
       </c>
-      <c r="H42" s="10" t="n">
+      <c r="H42" s="11" t="n">
         <v>45.22</v>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="I42" s="11" t="n">
         <v>43.04</v>
       </c>
-      <c r="J42" s="10" t="n">
+      <c r="J42" s="11" t="n">
         <v>42.79</v>
       </c>
-      <c r="K42" s="10" t="n">
+      <c r="K42" s="11" t="n">
         <v>47.75</v>
       </c>
-      <c r="L42" s="10" t="n">
+      <c r="L42" s="11" t="n">
         <v>45.64</v>
       </c>
-      <c r="M42" s="10" t="n">
+      <c r="M42" s="11" t="n">
         <v>46.23</v>
       </c>
-      <c r="N42" s="10" t="n">
+      <c r="N42" s="11" t="n">
         <v>44.39</v>
       </c>
-      <c r="O42" s="10" t="n">
+      <c r="O42" s="11" t="n">
         <v>45.54</v>
       </c>
-      <c r="P42" s="10" t="n">
+      <c r="P42" s="11" t="n">
         <v>46.71</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="11" t="n">
         <v>42.49</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="11" t="n">
         <v>39.33</v>
       </c>
-      <c r="S42" s="10" t="n">
+      <c r="S42" s="11" t="n">
         <v>40.14</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="T42" s="11" t="n">
         <v>38.01</v>
       </c>
-      <c r="U42" s="10" t="n">
+      <c r="U42" s="11" t="n">
         <v>38.08</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="V42" s="11" t="n">
         <v>38.74</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="11" t="n">
         <v>43.46</v>
       </c>
-      <c r="X42" s="10" t="n">
+      <c r="X42" s="11" t="n">
         <v>46.21</v>
       </c>
-      <c r="Y42" s="10" t="n">
+      <c r="Y42" s="11" t="n">
         <v>40.55</v>
       </c>
-      <c r="Z42" s="10" t="n">
+      <c r="Z42" s="11" t="n">
         <v>40.41</v>
       </c>
-      <c r="AA42" s="10" t="n">
+      <c r="AA42" s="11" t="n">
         <v>36.65</v>
       </c>
-      <c r="AB42" s="10" t="n">
+      <c r="AB42" s="11" t="n">
         <v>42.29</v>
       </c>
-      <c r="AC42" s="10" t="n">
+      <c r="AC42" s="11" t="n">
         <v>45.95</v>
       </c>
-      <c r="AD42" s="10" t="n">
+      <c r="AD42" s="11" t="n">
         <v>43.71</v>
       </c>
-      <c r="AE42" s="10" t="n">
+      <c r="AE42" s="11" t="n">
         <v>45.76</v>
       </c>
-      <c r="AF42" s="10" t="n">
+      <c r="AF42" s="11" t="n">
         <v>47.26</v>
       </c>
-      <c r="AG42" s="10" t="n">
+      <c r="AG42" s="11" t="n">
         <v>44.16</v>
       </c>
-      <c r="AH42" s="10" t="n">
+      <c r="AH42" s="11" t="n">
         <v>42.94</v>
       </c>
       <c r="AI42" s="7" t="n">
         <v>141.85</v>
       </c>
       <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="9" t="inlineStr"/>
+      <c r="AK42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4498,107 +4632,107 @@
       <c r="B43" s="6" t="n">
         <v>103.7</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="11" t="n">
         <v>47.79</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="11" t="n">
         <v>36.54</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="11" t="n">
         <v>35.36</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="11" t="n">
         <v>39.5</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="11" t="n">
         <v>39.05</v>
       </c>
-      <c r="H43" s="10" t="n">
+      <c r="H43" s="11" t="n">
         <v>44.41</v>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="11" t="n">
         <v>42.89</v>
       </c>
-      <c r="J43" s="10" t="n">
+      <c r="J43" s="11" t="n">
         <v>45.39</v>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="K43" s="11" t="n">
         <v>46.43</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="11" t="n">
         <v>44.24</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="M43" s="11" t="n">
         <v>46.82</v>
       </c>
-      <c r="N43" s="10" t="n">
+      <c r="N43" s="11" t="n">
         <v>43.69</v>
       </c>
-      <c r="O43" s="10" t="n">
+      <c r="O43" s="11" t="n">
         <v>48.21</v>
       </c>
-      <c r="P43" s="10" t="n">
+      <c r="P43" s="11" t="n">
         <v>47.44</v>
       </c>
-      <c r="Q43" s="10" t="n">
+      <c r="Q43" s="11" t="n">
         <v>43.59</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="11" t="n">
         <v>39.13</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="S43" s="11" t="n">
         <v>38.44</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="T43" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="U43" s="10" t="n">
+      <c r="U43" s="11" t="n">
         <v>42.06</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="11" t="n">
         <v>39.01</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="11" t="n">
         <v>42.07</v>
       </c>
-      <c r="X43" s="10" t="n">
+      <c r="X43" s="11" t="n">
         <v>46.61</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="11" t="n">
         <v>36.92</v>
       </c>
-      <c r="Z43" s="10" t="n">
+      <c r="Z43" s="11" t="n">
         <v>37.61</v>
       </c>
-      <c r="AA43" s="10" t="n">
+      <c r="AA43" s="11" t="n">
         <v>36.41</v>
       </c>
-      <c r="AB43" s="10" t="n">
+      <c r="AB43" s="11" t="n">
         <v>40.19</v>
       </c>
-      <c r="AC43" s="10" t="n">
+      <c r="AC43" s="11" t="n">
         <v>39.22</v>
       </c>
-      <c r="AD43" s="10" t="n">
+      <c r="AD43" s="11" t="n">
         <v>40.28</v>
       </c>
-      <c r="AE43" s="10" t="n">
+      <c r="AE43" s="11" t="n">
         <v>47.26</v>
       </c>
-      <c r="AF43" s="10" t="n">
+      <c r="AF43" s="11" t="n">
         <v>46.28</v>
       </c>
-      <c r="AG43" s="10" t="n">
+      <c r="AG43" s="11" t="n">
         <v>45.59</v>
       </c>
-      <c r="AH43" s="10" t="n">
+      <c r="AH43" s="11" t="n">
         <v>42.27</v>
       </c>
       <c r="AI43" s="7" t="n">
         <v>140.45</v>
       </c>
       <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="9" t="inlineStr"/>
+      <c r="AK43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4709,7 +4843,7 @@
         <v>181.85</v>
       </c>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="9" t="inlineStr"/>
+      <c r="AK44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4820,7 +4954,12 @@
         <v>243.9</v>
       </c>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="9" t="inlineStr"/>
+      <c r="AK45" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4931,7 +5070,12 @@
         <v>252.32</v>
       </c>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="9" t="inlineStr"/>
+      <c r="AK46" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -5042,7 +5186,12 @@
         <v>254.37</v>
       </c>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="9" t="inlineStr"/>
+      <c r="AK47" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5059,7 +5208,7 @@
       <c r="D48" s="7" t="n">
         <v>56.33</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="11" t="n">
         <v>52.45</v>
       </c>
       <c r="F48" s="7" t="n">
@@ -5153,7 +5302,12 @@
         <v>487.79</v>
       </c>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="9" t="inlineStr"/>
+      <c r="AK48" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5264,7 +5418,12 @@
         <v>385.5</v>
       </c>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="9" t="inlineStr"/>
+      <c r="AK49" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5375,7 +5534,12 @@
         <v>236.24</v>
       </c>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="9" t="inlineStr"/>
+      <c r="AK50" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -5386,218 +5550,228 @@
       <c r="B51" s="6" t="n">
         <v>106.7</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="11" t="n">
         <v>45.59</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="11" t="n">
         <v>44.29</v>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E51" s="11" t="n">
         <v>45.42</v>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="11" t="n">
         <v>45.54</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G51" s="11" t="n">
         <v>45.36</v>
       </c>
-      <c r="H51" s="10" t="n">
+      <c r="H51" s="11" t="n">
         <v>44.1</v>
       </c>
-      <c r="I51" s="10" t="n">
+      <c r="I51" s="11" t="n">
         <v>45.04</v>
       </c>
-      <c r="J51" s="10" t="n">
+      <c r="J51" s="11" t="n">
         <v>45.04</v>
       </c>
-      <c r="K51" s="10" t="n">
+      <c r="K51" s="11" t="n">
         <v>45.84</v>
       </c>
-      <c r="L51" s="10" t="n">
+      <c r="L51" s="11" t="n">
         <v>43.74</v>
       </c>
-      <c r="M51" s="10" t="n">
+      <c r="M51" s="11" t="n">
         <v>44.87</v>
       </c>
-      <c r="N51" s="10" t="n">
+      <c r="N51" s="11" t="n">
         <v>45.91</v>
       </c>
-      <c r="O51" s="10" t="n">
+      <c r="O51" s="11" t="n">
         <v>45.61</v>
       </c>
-      <c r="P51" s="10" t="n">
+      <c r="P51" s="11" t="n">
         <v>45.42</v>
       </c>
-      <c r="Q51" s="10" t="n">
+      <c r="Q51" s="11" t="n">
         <v>45.88</v>
       </c>
-      <c r="R51" s="10" t="n">
+      <c r="R51" s="11" t="n">
         <v>45.66</v>
       </c>
-      <c r="S51" s="10" t="n">
+      <c r="S51" s="11" t="n">
         <v>45.7</v>
       </c>
-      <c r="T51" s="10" t="n">
+      <c r="T51" s="11" t="n">
         <v>46.39</v>
       </c>
-      <c r="U51" s="10" t="n">
+      <c r="U51" s="11" t="n">
         <v>45.44</v>
       </c>
-      <c r="V51" s="10" t="n">
+      <c r="V51" s="11" t="n">
         <v>43.86</v>
       </c>
-      <c r="W51" s="10" t="n">
+      <c r="W51" s="11" t="n">
         <v>44.56</v>
       </c>
-      <c r="X51" s="10" t="n">
+      <c r="X51" s="11" t="n">
         <v>44.54</v>
       </c>
-      <c r="Y51" s="10" t="n">
+      <c r="Y51" s="11" t="n">
         <v>44.78</v>
       </c>
-      <c r="Z51" s="10" t="n">
+      <c r="Z51" s="11" t="n">
         <v>43.79</v>
       </c>
-      <c r="AA51" s="10" t="n">
+      <c r="AA51" s="11" t="n">
         <v>45.58</v>
       </c>
-      <c r="AB51" s="10" t="n">
+      <c r="AB51" s="11" t="n">
         <v>43.16</v>
       </c>
-      <c r="AC51" s="10" t="n">
+      <c r="AC51" s="11" t="n">
         <v>43.36</v>
       </c>
-      <c r="AD51" s="10" t="n">
+      <c r="AD51" s="11" t="n">
         <v>44.17</v>
       </c>
-      <c r="AE51" s="10" t="n">
+      <c r="AE51" s="11" t="n">
         <v>46.02</v>
       </c>
-      <c r="AF51" s="10" t="n">
+      <c r="AF51" s="11" t="n">
         <v>45.81</v>
       </c>
-      <c r="AG51" s="10" t="n">
+      <c r="AG51" s="11" t="n">
         <v>44.48</v>
       </c>
-      <c r="AH51" s="10" t="n">
+      <c r="AH51" s="11" t="n">
         <v>45</v>
       </c>
       <c r="AI51" s="8" t="n">
         <v>468.87</v>
       </c>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="9" t="inlineStr"/>
+      <c r="AK51" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>GENESIS FM STEREO</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="13" t="n">
         <v>107.5</v>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C52" s="14" t="n">
         <v>45.55</v>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="14" t="n">
         <v>45.58</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="14" t="n">
         <v>46.18</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F52" s="14" t="n">
         <v>45.65</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="14" t="n">
         <v>47.34</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="14" t="n">
         <v>47.62</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="I52" s="14" t="n">
         <v>46.46</v>
       </c>
-      <c r="J52" s="13" t="n">
+      <c r="J52" s="14" t="n">
         <v>45.94</v>
       </c>
-      <c r="K52" s="13" t="n">
+      <c r="K52" s="14" t="n">
         <v>45.49</v>
       </c>
-      <c r="L52" s="13" t="n">
+      <c r="L52" s="14" t="n">
         <v>45.62</v>
       </c>
-      <c r="M52" s="13" t="n">
+      <c r="M52" s="14" t="n">
         <v>46.22</v>
       </c>
-      <c r="N52" s="13" t="n">
+      <c r="N52" s="14" t="n">
         <v>47.42</v>
       </c>
-      <c r="O52" s="13" t="n">
+      <c r="O52" s="14" t="n">
         <v>46.59</v>
       </c>
-      <c r="P52" s="13" t="n">
+      <c r="P52" s="14" t="n">
         <v>46.35</v>
       </c>
-      <c r="Q52" s="13" t="n">
+      <c r="Q52" s="14" t="n">
         <v>46.21</v>
       </c>
-      <c r="R52" s="13" t="n">
+      <c r="R52" s="14" t="n">
         <v>46.19</v>
       </c>
-      <c r="S52" s="13" t="n">
+      <c r="S52" s="14" t="n">
         <v>47.04</v>
       </c>
-      <c r="T52" s="13" t="n">
+      <c r="T52" s="14" t="n">
         <v>45.74</v>
       </c>
-      <c r="U52" s="13" t="n">
+      <c r="U52" s="14" t="n">
         <v>45.27</v>
       </c>
-      <c r="V52" s="13" t="n">
+      <c r="V52" s="14" t="n">
         <v>45.62</v>
       </c>
-      <c r="W52" s="13" t="n">
+      <c r="W52" s="14" t="n">
         <v>44.74</v>
       </c>
-      <c r="X52" s="13" t="n">
+      <c r="X52" s="14" t="n">
         <v>49.16</v>
       </c>
-      <c r="Y52" s="13" t="n">
+      <c r="Y52" s="14" t="n">
         <v>46.34</v>
       </c>
-      <c r="Z52" s="13" t="n">
+      <c r="Z52" s="14" t="n">
         <v>45.4</v>
       </c>
-      <c r="AA52" s="13" t="n">
+      <c r="AA52" s="14" t="n">
         <v>45.42</v>
       </c>
-      <c r="AB52" s="13" t="n">
+      <c r="AB52" s="14" t="n">
         <v>47.13</v>
       </c>
-      <c r="AC52" s="13" t="n">
+      <c r="AC52" s="14" t="n">
         <v>45.49</v>
       </c>
-      <c r="AD52" s="13" t="n">
+      <c r="AD52" s="14" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE52" s="13" t="n">
+      <c r="AE52" s="14" t="n">
         <v>46.79</v>
       </c>
-      <c r="AF52" s="13" t="n">
+      <c r="AF52" s="14" t="n">
         <v>47.06</v>
       </c>
-      <c r="AG52" s="13" t="n">
+      <c r="AG52" s="14" t="n">
         <v>47.36</v>
       </c>
-      <c r="AH52" s="13" t="n">
+      <c r="AH52" s="14" t="n">
         <v>46.28</v>
       </c>
-      <c r="AI52" s="14" t="n">
+      <c r="AI52" s="15" t="n">
         <v>497.9</v>
       </c>
-      <c r="AJ52" s="12" t="inlineStr"/>
-      <c r="AK52" s="15" t="inlineStr"/>
+      <c r="AJ52" s="13" t="inlineStr"/>
+      <c r="AK52" s="16" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="53"/>
     <row r="54"/>
@@ -5772,7 +5946,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK62" s="16" t="n"/>
+      <c r="AK62" s="17" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5783,107 +5957,107 @@
       <c r="B63" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C63" s="11" t="n">
         <v>64.05</v>
       </c>
-      <c r="D63" s="10" t="n">
+      <c r="D63" s="11" t="n">
         <v>63.56</v>
       </c>
-      <c r="E63" s="10" t="n">
+      <c r="E63" s="11" t="n">
         <v>64.08</v>
       </c>
-      <c r="F63" s="10" t="n">
+      <c r="F63" s="11" t="n">
         <v>63.48</v>
       </c>
-      <c r="G63" s="10" t="n">
+      <c r="G63" s="11" t="n">
         <v>64.12</v>
       </c>
-      <c r="H63" s="10" t="n">
+      <c r="H63" s="11" t="n">
         <v>64.53</v>
       </c>
-      <c r="I63" s="10" t="n">
+      <c r="I63" s="11" t="n">
         <v>64.03</v>
       </c>
-      <c r="J63" s="10" t="n">
+      <c r="J63" s="11" t="n">
         <v>63.8</v>
       </c>
-      <c r="K63" s="10" t="n">
+      <c r="K63" s="11" t="n">
         <v>63.63</v>
       </c>
-      <c r="L63" s="10" t="n">
+      <c r="L63" s="11" t="n">
         <v>63.38</v>
       </c>
-      <c r="M63" s="10" t="n">
+      <c r="M63" s="11" t="n">
         <v>63.85</v>
       </c>
-      <c r="N63" s="10" t="n">
+      <c r="N63" s="11" t="n">
         <v>63.69</v>
       </c>
-      <c r="O63" s="10" t="n">
+      <c r="O63" s="11" t="n">
         <v>63.81</v>
       </c>
-      <c r="P63" s="10" t="n">
+      <c r="P63" s="11" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="Q63" s="10" t="n">
+      <c r="Q63" s="11" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="R63" s="10" t="n">
+      <c r="R63" s="11" t="n">
         <v>63.94</v>
       </c>
-      <c r="S63" s="10" t="n">
+      <c r="S63" s="11" t="n">
         <v>62.96</v>
       </c>
-      <c r="T63" s="10" t="n">
+      <c r="T63" s="11" t="n">
         <v>62.88</v>
       </c>
-      <c r="U63" s="10" t="n">
+      <c r="U63" s="11" t="n">
         <v>62.7</v>
       </c>
-      <c r="V63" s="10" t="n">
+      <c r="V63" s="11" t="n">
         <v>62.84</v>
       </c>
-      <c r="W63" s="10" t="n">
+      <c r="W63" s="11" t="n">
         <v>62.69</v>
       </c>
-      <c r="X63" s="10" t="n">
+      <c r="X63" s="11" t="n">
         <v>62.51</v>
       </c>
-      <c r="Y63" s="10" t="n">
+      <c r="Y63" s="11" t="n">
         <v>62.42</v>
       </c>
-      <c r="Z63" s="10" t="n">
+      <c r="Z63" s="11" t="n">
         <v>63.88</v>
       </c>
-      <c r="AA63" s="10" t="n">
+      <c r="AA63" s="11" t="n">
         <v>63.6</v>
       </c>
-      <c r="AB63" s="10" t="n">
+      <c r="AB63" s="11" t="n">
         <v>64.08</v>
       </c>
-      <c r="AC63" s="10" t="n">
+      <c r="AC63" s="11" t="n">
         <v>64.26000000000001</v>
       </c>
-      <c r="AD63" s="10" t="n">
+      <c r="AD63" s="11" t="n">
         <v>64.01000000000001</v>
       </c>
-      <c r="AE63" s="10" t="n">
+      <c r="AE63" s="11" t="n">
         <v>63.49</v>
       </c>
-      <c r="AF63" s="10" t="n">
+      <c r="AF63" s="11" t="n">
         <v>63.14</v>
       </c>
-      <c r="AG63" s="10" t="n">
+      <c r="AG63" s="11" t="n">
         <v>63.04</v>
       </c>
-      <c r="AH63" s="10" t="n">
+      <c r="AH63" s="11" t="n">
         <v>63.58</v>
       </c>
       <c r="AI63" s="6" t="inlineStr"/>
       <c r="AJ63" s="6" t="inlineStr"/>
-      <c r="AK63" s="17" t="n"/>
+      <c r="AK63" s="18" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
           <t>TELERAMA</t>
@@ -5892,107 +6066,111 @@
       <c r="B64" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C64" s="18" t="n">
+      <c r="C64" s="19" t="n">
         <v>37.2</v>
       </c>
-      <c r="D64" s="18" t="n">
+      <c r="D64" s="19" t="n">
         <v>37.1</v>
       </c>
-      <c r="E64" s="18" t="n">
+      <c r="E64" s="19" t="n">
         <v>36.25</v>
       </c>
-      <c r="F64" s="18" t="n">
+      <c r="F64" s="19" t="n">
         <v>35.95</v>
       </c>
-      <c r="G64" s="18" t="n">
+      <c r="G64" s="19" t="n">
         <v>38.22</v>
       </c>
-      <c r="H64" s="18" t="n">
+      <c r="H64" s="19" t="n">
         <v>35.83</v>
       </c>
-      <c r="I64" s="18" t="n">
+      <c r="I64" s="19" t="n">
         <v>38.13</v>
       </c>
-      <c r="J64" s="18" t="n">
+      <c r="J64" s="19" t="n">
         <v>36.34</v>
       </c>
-      <c r="K64" s="18" t="n">
+      <c r="K64" s="19" t="n">
         <v>37.93</v>
       </c>
-      <c r="L64" s="18" t="n">
+      <c r="L64" s="19" t="n">
         <v>37.71</v>
       </c>
-      <c r="M64" s="18" t="n">
+      <c r="M64" s="19" t="n">
         <v>35.95</v>
       </c>
-      <c r="N64" s="18" t="n">
+      <c r="N64" s="19" t="n">
         <v>35.99</v>
       </c>
-      <c r="O64" s="18" t="n">
+      <c r="O64" s="19" t="n">
         <v>38.22</v>
       </c>
-      <c r="P64" s="18" t="n">
+      <c r="P64" s="19" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q64" s="18" t="n">
+      <c r="Q64" s="19" t="n">
         <v>37.15</v>
       </c>
-      <c r="R64" s="18" t="n">
+      <c r="R64" s="19" t="n">
         <v>37.29</v>
       </c>
-      <c r="S64" s="18" t="n">
+      <c r="S64" s="19" t="n">
         <v>38.9</v>
       </c>
-      <c r="T64" s="18" t="n">
+      <c r="T64" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="U64" s="18" t="n">
+      <c r="U64" s="19" t="n">
         <v>37.5</v>
       </c>
-      <c r="V64" s="18" t="n">
+      <c r="V64" s="19" t="n">
         <v>36.25</v>
       </c>
-      <c r="W64" s="18" t="n">
+      <c r="W64" s="19" t="n">
         <v>36.9</v>
       </c>
-      <c r="X64" s="18" t="n">
+      <c r="X64" s="19" t="n">
         <v>36.92</v>
       </c>
-      <c r="Y64" s="18" t="n">
+      <c r="Y64" s="19" t="n">
         <v>35.42</v>
       </c>
-      <c r="Z64" s="18" t="n">
+      <c r="Z64" s="19" t="n">
         <v>38.12</v>
       </c>
-      <c r="AA64" s="18" t="n">
+      <c r="AA64" s="19" t="n">
         <v>37.35</v>
       </c>
-      <c r="AB64" s="18" t="n">
+      <c r="AB64" s="19" t="n">
         <v>38.41</v>
       </c>
-      <c r="AC64" s="18" t="n">
+      <c r="AC64" s="19" t="n">
         <v>37.71</v>
       </c>
-      <c r="AD64" s="18" t="n">
+      <c r="AD64" s="19" t="n">
         <v>37.56</v>
       </c>
-      <c r="AE64" s="18" t="n">
+      <c r="AE64" s="19" t="n">
         <v>38.91</v>
       </c>
-      <c r="AF64" s="18" t="n">
+      <c r="AF64" s="19" t="n">
         <v>36.38</v>
       </c>
-      <c r="AG64" s="18" t="n">
+      <c r="AG64" s="19" t="n">
         <v>37.45</v>
       </c>
-      <c r="AH64" s="18" t="n">
+      <c r="AH64" s="19" t="n">
         <v>37.24</v>
       </c>
       <c r="AI64" s="6" t="inlineStr"/>
-      <c r="AJ64" s="6" t="inlineStr"/>
-      <c r="AK64" s="17" t="n"/>
+      <c r="AJ64" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK64" s="18" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>ECUADOR TV</t>
@@ -6001,105 +6179,109 @@
       <c r="B65" s="6" t="n">
         <v>175.25</v>
       </c>
-      <c r="C65" s="18" t="n">
+      <c r="C65" s="19" t="n">
         <v>39.7</v>
       </c>
-      <c r="D65" s="18" t="n">
+      <c r="D65" s="19" t="n">
         <v>37.34</v>
       </c>
-      <c r="E65" s="18" t="n">
+      <c r="E65" s="19" t="n">
         <v>38.12</v>
       </c>
-      <c r="F65" s="18" t="n">
+      <c r="F65" s="19" t="n">
         <v>37.12</v>
       </c>
-      <c r="G65" s="18" t="n">
+      <c r="G65" s="19" t="n">
         <v>38.33</v>
       </c>
-      <c r="H65" s="18" t="n">
+      <c r="H65" s="19" t="n">
         <v>39.69</v>
       </c>
-      <c r="I65" s="18" t="n">
+      <c r="I65" s="19" t="n">
         <v>42.09</v>
       </c>
-      <c r="J65" s="18" t="n">
+      <c r="J65" s="19" t="n">
         <v>42.04</v>
       </c>
-      <c r="K65" s="18" t="n">
+      <c r="K65" s="19" t="n">
         <v>38.28</v>
       </c>
-      <c r="L65" s="18" t="n">
+      <c r="L65" s="19" t="n">
         <v>41.34</v>
       </c>
-      <c r="M65" s="18" t="n">
+      <c r="M65" s="19" t="n">
         <v>41.94</v>
       </c>
-      <c r="N65" s="18" t="n">
+      <c r="N65" s="19" t="n">
         <v>40.49</v>
       </c>
-      <c r="O65" s="18" t="n">
+      <c r="O65" s="19" t="n">
         <v>38.61</v>
       </c>
-      <c r="P65" s="18" t="n">
+      <c r="P65" s="19" t="n">
         <v>37.79</v>
       </c>
-      <c r="Q65" s="18" t="n">
+      <c r="Q65" s="19" t="n">
         <v>37.79</v>
       </c>
-      <c r="R65" s="18" t="n">
+      <c r="R65" s="19" t="n">
         <v>36.92</v>
       </c>
-      <c r="S65" s="18" t="n">
+      <c r="S65" s="19" t="n">
         <v>38.35</v>
       </c>
-      <c r="T65" s="18" t="n">
+      <c r="T65" s="19" t="n">
         <v>36.67</v>
       </c>
-      <c r="U65" s="18" t="n">
+      <c r="U65" s="19" t="n">
         <v>36.88</v>
       </c>
-      <c r="V65" s="18" t="n">
+      <c r="V65" s="19" t="n">
         <v>37.59</v>
       </c>
-      <c r="W65" s="18" t="n">
+      <c r="W65" s="19" t="n">
         <v>37.49</v>
       </c>
-      <c r="X65" s="18" t="n">
+      <c r="X65" s="19" t="n">
         <v>40.59</v>
       </c>
-      <c r="Y65" s="18" t="n">
+      <c r="Y65" s="19" t="n">
         <v>42.94</v>
       </c>
-      <c r="Z65" s="18" t="n">
+      <c r="Z65" s="19" t="n">
         <v>38.3</v>
       </c>
-      <c r="AA65" s="18" t="n">
+      <c r="AA65" s="19" t="n">
         <v>36.58</v>
       </c>
-      <c r="AB65" s="18" t="n">
+      <c r="AB65" s="19" t="n">
         <v>43.08</v>
       </c>
-      <c r="AC65" s="18" t="n">
+      <c r="AC65" s="19" t="n">
         <v>39.4</v>
       </c>
-      <c r="AD65" s="18" t="n">
+      <c r="AD65" s="19" t="n">
         <v>37.41</v>
       </c>
-      <c r="AE65" s="18" t="n">
+      <c r="AE65" s="19" t="n">
         <v>37.99</v>
       </c>
-      <c r="AF65" s="18" t="n">
+      <c r="AF65" s="19" t="n">
         <v>41.21</v>
       </c>
-      <c r="AG65" s="18" t="n">
+      <c r="AG65" s="19" t="n">
         <v>37.2</v>
       </c>
-      <c r="AH65" s="18" t="n">
+      <c r="AH65" s="19" t="n">
         <v>39.01</v>
       </c>
       <c r="AI65" s="6" t="inlineStr"/>
-      <c r="AJ65" s="6" t="inlineStr"/>
-      <c r="AK65" s="17" t="n"/>
+      <c r="AJ65" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK65" s="18" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6208,9 +6390,9 @@
       </c>
       <c r="AI66" s="6" t="inlineStr"/>
       <c r="AJ66" s="6" t="inlineStr"/>
-      <c r="AK66" s="17" t="n"/>
+      <c r="AK66" s="18" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>TELEVISION DEL PACIFICO</t>
@@ -6219,105 +6401,109 @@
       <c r="B67" s="6" t="n">
         <v>187.25</v>
       </c>
-      <c r="C67" s="18" t="n">
+      <c r="C67" s="19" t="n">
         <v>40.3</v>
       </c>
-      <c r="D67" s="18" t="n">
+      <c r="D67" s="19" t="n">
         <v>41.59</v>
       </c>
-      <c r="E67" s="18" t="n">
+      <c r="E67" s="19" t="n">
         <v>38.95</v>
       </c>
-      <c r="F67" s="18" t="n">
+      <c r="F67" s="19" t="n">
         <v>40.75</v>
       </c>
-      <c r="G67" s="18" t="n">
+      <c r="G67" s="19" t="n">
         <v>41.29</v>
       </c>
-      <c r="H67" s="18" t="n">
+      <c r="H67" s="19" t="n">
         <v>40.61</v>
       </c>
-      <c r="I67" s="18" t="n">
+      <c r="I67" s="19" t="n">
         <v>40.69</v>
       </c>
-      <c r="J67" s="18" t="n">
+      <c r="J67" s="19" t="n">
         <v>43.48</v>
       </c>
-      <c r="K67" s="18" t="n">
+      <c r="K67" s="19" t="n">
         <v>41.87</v>
       </c>
-      <c r="L67" s="18" t="n">
+      <c r="L67" s="19" t="n">
         <v>41.22</v>
       </c>
-      <c r="M67" s="18" t="n">
+      <c r="M67" s="19" t="n">
         <v>40.41</v>
       </c>
-      <c r="N67" s="18" t="n">
+      <c r="N67" s="19" t="n">
         <v>41.46</v>
       </c>
-      <c r="O67" s="18" t="n">
+      <c r="O67" s="19" t="n">
         <v>40.07</v>
       </c>
-      <c r="P67" s="18" t="n">
+      <c r="P67" s="19" t="n">
         <v>40.54</v>
       </c>
-      <c r="Q67" s="18" t="n">
+      <c r="Q67" s="19" t="n">
         <v>40.48</v>
       </c>
-      <c r="R67" s="18" t="n">
+      <c r="R67" s="19" t="n">
         <v>41.38</v>
       </c>
-      <c r="S67" s="18" t="n">
+      <c r="S67" s="19" t="n">
         <v>41.15</v>
       </c>
-      <c r="T67" s="18" t="n">
+      <c r="T67" s="19" t="n">
         <v>39.41</v>
       </c>
-      <c r="U67" s="18" t="n">
+      <c r="U67" s="19" t="n">
         <v>39.12</v>
       </c>
-      <c r="V67" s="18" t="n">
+      <c r="V67" s="19" t="n">
         <v>40.48</v>
       </c>
-      <c r="W67" s="18" t="n">
+      <c r="W67" s="19" t="n">
         <v>40.44</v>
       </c>
-      <c r="X67" s="18" t="n">
+      <c r="X67" s="19" t="n">
         <v>40.11</v>
       </c>
-      <c r="Y67" s="18" t="n">
+      <c r="Y67" s="19" t="n">
         <v>38.81</v>
       </c>
-      <c r="Z67" s="18" t="n">
+      <c r="Z67" s="19" t="n">
         <v>40.83</v>
       </c>
-      <c r="AA67" s="18" t="n">
+      <c r="AA67" s="19" t="n">
         <v>39.05</v>
       </c>
-      <c r="AB67" s="18" t="n">
+      <c r="AB67" s="19" t="n">
         <v>39.54</v>
       </c>
-      <c r="AC67" s="18" t="n">
+      <c r="AC67" s="19" t="n">
         <v>38.81</v>
       </c>
-      <c r="AD67" s="18" t="n">
+      <c r="AD67" s="19" t="n">
         <v>39.5</v>
       </c>
-      <c r="AE67" s="18" t="n">
+      <c r="AE67" s="19" t="n">
         <v>40.44</v>
       </c>
-      <c r="AF67" s="18" t="n">
+      <c r="AF67" s="19" t="n">
         <v>40.04</v>
       </c>
-      <c r="AG67" s="18" t="n">
+      <c r="AG67" s="19" t="n">
         <v>39.62</v>
       </c>
-      <c r="AH67" s="18" t="n">
+      <c r="AH67" s="19" t="n">
         <v>40.4</v>
       </c>
       <c r="AI67" s="6" t="inlineStr"/>
-      <c r="AJ67" s="6" t="inlineStr"/>
-      <c r="AK67" s="17" t="n"/>
+      <c r="AJ67" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6426,7 +6612,7 @@
       </c>
       <c r="AI68" s="6" t="inlineStr"/>
       <c r="AJ68" s="6" t="inlineStr"/>
-      <c r="AK68" s="17" t="n"/>
+      <c r="AK68" s="18" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6535,9 +6721,9 @@
       </c>
       <c r="AI69" s="6" t="inlineStr"/>
       <c r="AJ69" s="6" t="inlineStr"/>
-      <c r="AK69" s="17" t="n"/>
+      <c r="AK69" s="18" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>OK TV-TEVECORP</t>
@@ -6546,107 +6732,111 @@
       <c r="B70" s="6" t="n">
         <v>549.25</v>
       </c>
-      <c r="C70" s="18" t="n">
+      <c r="C70" s="19" t="n">
         <v>31.82</v>
       </c>
-      <c r="D70" s="18" t="n">
+      <c r="D70" s="19" t="n">
         <v>34.01</v>
       </c>
-      <c r="E70" s="18" t="n">
+      <c r="E70" s="19" t="n">
         <v>31.3</v>
       </c>
-      <c r="F70" s="18" t="n">
+      <c r="F70" s="19" t="n">
         <v>31.78</v>
       </c>
-      <c r="G70" s="18" t="n">
+      <c r="G70" s="19" t="n">
         <v>31.44</v>
       </c>
-      <c r="H70" s="18" t="n">
+      <c r="H70" s="19" t="n">
         <v>31.81</v>
       </c>
-      <c r="I70" s="18" t="n">
+      <c r="I70" s="19" t="n">
         <v>31.13</v>
       </c>
-      <c r="J70" s="18" t="n">
+      <c r="J70" s="19" t="n">
         <v>32.33</v>
       </c>
-      <c r="K70" s="18" t="n">
+      <c r="K70" s="19" t="n">
         <v>31.17</v>
       </c>
-      <c r="L70" s="18" t="n">
+      <c r="L70" s="19" t="n">
         <v>30.91</v>
       </c>
-      <c r="M70" s="18" t="n">
+      <c r="M70" s="19" t="n">
         <v>31.56</v>
       </c>
-      <c r="N70" s="18" t="n">
+      <c r="N70" s="19" t="n">
         <v>31.3</v>
       </c>
-      <c r="O70" s="18" t="n">
+      <c r="O70" s="19" t="n">
         <v>31.59</v>
       </c>
-      <c r="P70" s="18" t="n">
+      <c r="P70" s="19" t="n">
         <v>31.9</v>
       </c>
-      <c r="Q70" s="18" t="n">
+      <c r="Q70" s="19" t="n">
         <v>31.52</v>
       </c>
-      <c r="R70" s="18" t="n">
+      <c r="R70" s="19" t="n">
         <v>31.22</v>
       </c>
-      <c r="S70" s="18" t="n">
+      <c r="S70" s="19" t="n">
         <v>31.62</v>
       </c>
-      <c r="T70" s="18" t="n">
+      <c r="T70" s="19" t="n">
         <v>31.62</v>
       </c>
-      <c r="U70" s="18" t="n">
+      <c r="U70" s="19" t="n">
         <v>31.75</v>
       </c>
-      <c r="V70" s="18" t="n">
+      <c r="V70" s="19" t="n">
         <v>32.01</v>
       </c>
-      <c r="W70" s="18" t="n">
+      <c r="W70" s="19" t="n">
         <v>32.09</v>
       </c>
-      <c r="X70" s="18" t="n">
+      <c r="X70" s="19" t="n">
         <v>32.17</v>
       </c>
-      <c r="Y70" s="18" t="n">
+      <c r="Y70" s="19" t="n">
         <v>31.41</v>
       </c>
-      <c r="Z70" s="18" t="n">
+      <c r="Z70" s="19" t="n">
         <v>31.92</v>
       </c>
-      <c r="AA70" s="18" t="n">
+      <c r="AA70" s="19" t="n">
         <v>34.1</v>
       </c>
-      <c r="AB70" s="18" t="n">
+      <c r="AB70" s="19" t="n">
         <v>31.28</v>
       </c>
-      <c r="AC70" s="18" t="n">
+      <c r="AC70" s="19" t="n">
         <v>31.6</v>
       </c>
-      <c r="AD70" s="18" t="n">
+      <c r="AD70" s="19" t="n">
         <v>32.31</v>
       </c>
-      <c r="AE70" s="18" t="n">
+      <c r="AE70" s="19" t="n">
         <v>32.11</v>
       </c>
-      <c r="AF70" s="18" t="n">
+      <c r="AF70" s="19" t="n">
         <v>31.26</v>
       </c>
-      <c r="AG70" s="18" t="n">
+      <c r="AG70" s="19" t="n">
         <v>32.11</v>
       </c>
-      <c r="AH70" s="18" t="n">
+      <c r="AH70" s="19" t="n">
         <v>31.81</v>
       </c>
       <c r="AI70" s="6" t="inlineStr"/>
-      <c r="AJ70" s="6" t="inlineStr"/>
-      <c r="AK70" s="17" t="n"/>
+      <c r="AJ70" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK70" s="18" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>CANAL UNO no</t>
@@ -6655,107 +6845,111 @@
       <c r="B71" s="6" t="n">
         <v>573.25</v>
       </c>
-      <c r="C71" s="18" t="n">
+      <c r="C71" s="19" t="n">
         <v>30.1</v>
       </c>
-      <c r="D71" s="18" t="n">
+      <c r="D71" s="19" t="n">
         <v>31.2</v>
       </c>
-      <c r="E71" s="18" t="n">
+      <c r="E71" s="19" t="n">
         <v>29.72</v>
       </c>
-      <c r="F71" s="18" t="n">
+      <c r="F71" s="19" t="n">
         <v>30.8</v>
       </c>
-      <c r="G71" s="18" t="n">
+      <c r="G71" s="19" t="n">
         <v>31.7</v>
       </c>
-      <c r="H71" s="18" t="n">
+      <c r="H71" s="19" t="n">
         <v>29.91</v>
       </c>
-      <c r="I71" s="18" t="n">
+      <c r="I71" s="19" t="n">
         <v>30.73</v>
       </c>
-      <c r="J71" s="18" t="n">
+      <c r="J71" s="19" t="n">
         <v>34.14</v>
       </c>
-      <c r="K71" s="18" t="n">
+      <c r="K71" s="19" t="n">
         <v>30.47</v>
       </c>
-      <c r="L71" s="18" t="n">
+      <c r="L71" s="19" t="n">
         <v>32.12</v>
       </c>
-      <c r="M71" s="18" t="n">
+      <c r="M71" s="19" t="n">
         <v>29.9</v>
       </c>
-      <c r="N71" s="18" t="n">
+      <c r="N71" s="19" t="n">
         <v>30.12</v>
       </c>
-      <c r="O71" s="18" t="n">
+      <c r="O71" s="19" t="n">
         <v>29.56</v>
       </c>
-      <c r="P71" s="18" t="n">
+      <c r="P71" s="19" t="n">
         <v>30.11</v>
       </c>
-      <c r="Q71" s="18" t="n">
+      <c r="Q71" s="19" t="n">
         <v>31.05</v>
       </c>
-      <c r="R71" s="18" t="n">
+      <c r="R71" s="19" t="n">
         <v>29.82</v>
       </c>
-      <c r="S71" s="18" t="n">
+      <c r="S71" s="19" t="n">
         <v>30.34</v>
       </c>
-      <c r="T71" s="18" t="n">
+      <c r="T71" s="19" t="n">
         <v>29.44</v>
       </c>
-      <c r="U71" s="18" t="n">
+      <c r="U71" s="19" t="n">
         <v>29.68</v>
       </c>
-      <c r="V71" s="18" t="n">
+      <c r="V71" s="19" t="n">
         <v>29.7</v>
       </c>
-      <c r="W71" s="18" t="n">
+      <c r="W71" s="19" t="n">
         <v>29.73</v>
       </c>
-      <c r="X71" s="18" t="n">
+      <c r="X71" s="19" t="n">
         <v>31.34</v>
       </c>
-      <c r="Y71" s="18" t="n">
+      <c r="Y71" s="19" t="n">
         <v>34.96</v>
       </c>
-      <c r="Z71" s="18" t="n">
+      <c r="Z71" s="19" t="n">
         <v>29.62</v>
       </c>
-      <c r="AA71" s="18" t="n">
+      <c r="AA71" s="19" t="n">
         <v>29.48</v>
       </c>
-      <c r="AB71" s="18" t="n">
+      <c r="AB71" s="19" t="n">
         <v>29.66</v>
       </c>
-      <c r="AC71" s="18" t="n">
+      <c r="AC71" s="19" t="n">
         <v>29.65</v>
       </c>
-      <c r="AD71" s="18" t="n">
+      <c r="AD71" s="19" t="n">
         <v>29.81</v>
       </c>
-      <c r="AE71" s="18" t="n">
+      <c r="AE71" s="19" t="n">
         <v>29.57</v>
       </c>
-      <c r="AF71" s="18" t="n">
+      <c r="AF71" s="19" t="n">
         <v>29.62</v>
       </c>
-      <c r="AG71" s="18" t="n">
+      <c r="AG71" s="19" t="n">
         <v>32.01</v>
       </c>
-      <c r="AH71" s="18" t="n">
+      <c r="AH71" s="19" t="n">
         <v>30.52</v>
       </c>
       <c r="AI71" s="6" t="inlineStr"/>
-      <c r="AJ71" s="6" t="inlineStr"/>
-      <c r="AK71" s="17" t="n"/>
+      <c r="AJ71" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK71" s="18" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>TELEATAHUALPA (RTU)</t>
@@ -6764,107 +6958,111 @@
       <c r="B72" s="6" t="n">
         <v>585.25</v>
       </c>
-      <c r="C72" s="18" t="n">
+      <c r="C72" s="19" t="n">
         <v>33.38</v>
       </c>
-      <c r="D72" s="18" t="n">
+      <c r="D72" s="19" t="n">
         <v>32.61</v>
       </c>
-      <c r="E72" s="18" t="n">
+      <c r="E72" s="19" t="n">
         <v>32.72</v>
       </c>
-      <c r="F72" s="18" t="n">
+      <c r="F72" s="19" t="n">
         <v>32.6</v>
       </c>
-      <c r="G72" s="18" t="n">
+      <c r="G72" s="19" t="n">
         <v>32.51</v>
       </c>
-      <c r="H72" s="18" t="n">
+      <c r="H72" s="19" t="n">
         <v>32.48</v>
       </c>
-      <c r="I72" s="18" t="n">
+      <c r="I72" s="19" t="n">
         <v>31.93</v>
       </c>
-      <c r="J72" s="18" t="n">
+      <c r="J72" s="19" t="n">
         <v>35.1</v>
       </c>
-      <c r="K72" s="18" t="n">
+      <c r="K72" s="19" t="n">
         <v>32.72</v>
       </c>
-      <c r="L72" s="18" t="n">
+      <c r="L72" s="19" t="n">
         <v>34.05</v>
       </c>
-      <c r="M72" s="18" t="n">
+      <c r="M72" s="19" t="n">
         <v>34.14</v>
       </c>
-      <c r="N72" s="18" t="n">
+      <c r="N72" s="19" t="n">
         <v>32.36</v>
       </c>
-      <c r="O72" s="18" t="n">
+      <c r="O72" s="19" t="n">
         <v>32.78</v>
       </c>
-      <c r="P72" s="18" t="n">
+      <c r="P72" s="19" t="n">
         <v>34.24</v>
       </c>
-      <c r="Q72" s="18" t="n">
+      <c r="Q72" s="19" t="n">
         <v>32.56</v>
       </c>
-      <c r="R72" s="18" t="n">
+      <c r="R72" s="19" t="n">
         <v>32.69</v>
       </c>
-      <c r="S72" s="18" t="n">
+      <c r="S72" s="19" t="n">
         <v>32.33</v>
       </c>
-      <c r="T72" s="18" t="n">
+      <c r="T72" s="19" t="n">
         <v>32.36</v>
       </c>
-      <c r="U72" s="18" t="n">
+      <c r="U72" s="19" t="n">
         <v>32.29</v>
       </c>
-      <c r="V72" s="18" t="n">
+      <c r="V72" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="W72" s="18" t="n">
+      <c r="W72" s="19" t="n">
         <v>32.46</v>
       </c>
-      <c r="X72" s="18" t="n">
+      <c r="X72" s="19" t="n">
         <v>31.89</v>
       </c>
-      <c r="Y72" s="18" t="n">
+      <c r="Y72" s="19" t="n">
         <v>32.44</v>
       </c>
-      <c r="Z72" s="18" t="n">
+      <c r="Z72" s="19" t="n">
         <v>31.9</v>
       </c>
-      <c r="AA72" s="18" t="n">
+      <c r="AA72" s="19" t="n">
         <v>32.17</v>
       </c>
-      <c r="AB72" s="18" t="n">
+      <c r="AB72" s="19" t="n">
         <v>33.28</v>
       </c>
-      <c r="AC72" s="18" t="n">
+      <c r="AC72" s="19" t="n">
         <v>32.95</v>
       </c>
-      <c r="AD72" s="18" t="n">
+      <c r="AD72" s="19" t="n">
         <v>32.63</v>
       </c>
-      <c r="AE72" s="18" t="n">
+      <c r="AE72" s="19" t="n">
         <v>32.53</v>
       </c>
-      <c r="AF72" s="18" t="n">
+      <c r="AF72" s="19" t="n">
         <v>32.38</v>
       </c>
-      <c r="AG72" s="18" t="n">
+      <c r="AG72" s="19" t="n">
         <v>32.41</v>
       </c>
-      <c r="AH72" s="18" t="n">
+      <c r="AH72" s="19" t="n">
         <v>32.74</v>
       </c>
       <c r="AI72" s="6" t="inlineStr"/>
-      <c r="AJ72" s="6" t="inlineStr"/>
-      <c r="AK72" s="17" t="n"/>
+      <c r="AJ72" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK72" s="18" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>TELEVICENTRO TVC</t>
@@ -6906,7 +7104,7 @@
       <c r="M73" s="7" t="n">
         <v>79.97</v>
       </c>
-      <c r="N73" s="18" t="n">
+      <c r="N73" s="19" t="n">
         <v>55.45</v>
       </c>
       <c r="O73" s="7" t="n">
@@ -6970,10 +7168,14 @@
         <v>78.90000000000001</v>
       </c>
       <c r="AI73" s="6" t="inlineStr"/>
-      <c r="AJ73" s="6" t="inlineStr"/>
-      <c r="AK73" s="17" t="n"/>
+      <c r="AJ73" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK73" s="18" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
           <t>UCSG TELEVISION</t>
@@ -6982,214 +7184,222 @@
       <c r="B74" s="6" t="n">
         <v>621.25</v>
       </c>
-      <c r="C74" s="18" t="n">
+      <c r="C74" s="19" t="n">
         <v>30.32</v>
       </c>
-      <c r="D74" s="18" t="n">
+      <c r="D74" s="19" t="n">
         <v>30.3</v>
       </c>
-      <c r="E74" s="18" t="n">
+      <c r="E74" s="19" t="n">
         <v>30.2</v>
       </c>
-      <c r="F74" s="18" t="n">
+      <c r="F74" s="19" t="n">
         <v>29.75</v>
       </c>
-      <c r="G74" s="18" t="n">
+      <c r="G74" s="19" t="n">
         <v>29.9</v>
       </c>
-      <c r="H74" s="18" t="n">
+      <c r="H74" s="19" t="n">
         <v>29.98</v>
       </c>
-      <c r="I74" s="18" t="n">
+      <c r="I74" s="19" t="n">
         <v>29.66</v>
       </c>
-      <c r="J74" s="18" t="n">
+      <c r="J74" s="19" t="n">
         <v>29.84</v>
       </c>
-      <c r="K74" s="18" t="n">
+      <c r="K74" s="19" t="n">
         <v>30.35</v>
       </c>
-      <c r="L74" s="18" t="n">
+      <c r="L74" s="19" t="n">
         <v>33.02</v>
       </c>
-      <c r="M74" s="18" t="n">
+      <c r="M74" s="19" t="n">
         <v>30.01</v>
       </c>
-      <c r="N74" s="18" t="n">
+      <c r="N74" s="19" t="n">
         <v>29.79</v>
       </c>
-      <c r="O74" s="18" t="n">
+      <c r="O74" s="19" t="n">
         <v>32.08</v>
       </c>
-      <c r="P74" s="18" t="n">
+      <c r="P74" s="19" t="n">
         <v>30.26</v>
       </c>
-      <c r="Q74" s="18" t="n">
+      <c r="Q74" s="19" t="n">
         <v>30.26</v>
       </c>
-      <c r="R74" s="18" t="n">
+      <c r="R74" s="19" t="n">
         <v>29.52</v>
       </c>
-      <c r="S74" s="18" t="n">
+      <c r="S74" s="19" t="n">
         <v>30.26</v>
       </c>
-      <c r="T74" s="18" t="n">
+      <c r="T74" s="19" t="n">
         <v>29.72</v>
       </c>
-      <c r="U74" s="18" t="n">
+      <c r="U74" s="19" t="n">
         <v>31.64</v>
       </c>
-      <c r="V74" s="18" t="n">
+      <c r="V74" s="19" t="n">
         <v>29.29</v>
       </c>
-      <c r="W74" s="18" t="n">
+      <c r="W74" s="19" t="n">
         <v>29.83</v>
       </c>
-      <c r="X74" s="18" t="n">
+      <c r="X74" s="19" t="n">
         <v>30.21</v>
       </c>
-      <c r="Y74" s="18" t="n">
+      <c r="Y74" s="19" t="n">
         <v>31.16</v>
       </c>
-      <c r="Z74" s="18" t="n">
+      <c r="Z74" s="19" t="n">
         <v>29.88</v>
       </c>
-      <c r="AA74" s="18" t="n">
+      <c r="AA74" s="19" t="n">
         <v>33.85</v>
       </c>
-      <c r="AB74" s="18" t="n">
+      <c r="AB74" s="19" t="n">
         <v>29.26</v>
       </c>
-      <c r="AC74" s="18" t="n">
+      <c r="AC74" s="19" t="n">
         <v>31.25</v>
       </c>
-      <c r="AD74" s="18" t="n">
+      <c r="AD74" s="19" t="n">
         <v>30.8</v>
       </c>
-      <c r="AE74" s="18" t="n">
+      <c r="AE74" s="19" t="n">
         <v>29.49</v>
       </c>
-      <c r="AF74" s="18" t="n">
+      <c r="AF74" s="19" t="n">
         <v>30.38</v>
       </c>
-      <c r="AG74" s="18" t="n">
+      <c r="AG74" s="19" t="n">
         <v>30.25</v>
       </c>
-      <c r="AH74" s="18" t="n">
+      <c r="AH74" s="19" t="n">
         <v>30.4</v>
       </c>
       <c r="AI74" s="6" t="inlineStr"/>
-      <c r="AJ74" s="6" t="inlineStr"/>
-      <c r="AK74" s="17" t="n"/>
+      <c r="AJ74" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK74" s="18" t="n"/>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="13" t="n">
         <v>633.25</v>
       </c>
-      <c r="C75" s="19" t="n">
+      <c r="C75" s="21" t="n">
         <v>29.02</v>
       </c>
-      <c r="D75" s="19" t="n">
+      <c r="D75" s="21" t="n">
         <v>30.64</v>
       </c>
-      <c r="E75" s="19" t="n">
+      <c r="E75" s="21" t="n">
         <v>28.75</v>
       </c>
-      <c r="F75" s="19" t="n">
+      <c r="F75" s="21" t="n">
         <v>29.3</v>
       </c>
-      <c r="G75" s="19" t="n">
+      <c r="G75" s="21" t="n">
         <v>29.96</v>
       </c>
-      <c r="H75" s="19" t="n">
+      <c r="H75" s="21" t="n">
         <v>29.38</v>
       </c>
-      <c r="I75" s="19" t="n">
+      <c r="I75" s="21" t="n">
         <v>28.91</v>
       </c>
-      <c r="J75" s="19" t="n">
+      <c r="J75" s="21" t="n">
         <v>29.28</v>
       </c>
-      <c r="K75" s="19" t="n">
+      <c r="K75" s="21" t="n">
         <v>30.2</v>
       </c>
-      <c r="L75" s="19" t="n">
+      <c r="L75" s="21" t="n">
         <v>30.12</v>
       </c>
-      <c r="M75" s="19" t="n">
+      <c r="M75" s="21" t="n">
         <v>31.44</v>
       </c>
-      <c r="N75" s="19" t="n">
+      <c r="N75" s="21" t="n">
         <v>29.04</v>
       </c>
-      <c r="O75" s="19" t="n">
+      <c r="O75" s="21" t="n">
         <v>29.02</v>
       </c>
-      <c r="P75" s="19" t="n">
+      <c r="P75" s="21" t="n">
         <v>29.38</v>
       </c>
-      <c r="Q75" s="19" t="n">
+      <c r="Q75" s="21" t="n">
         <v>29.29</v>
       </c>
-      <c r="R75" s="19" t="n">
+      <c r="R75" s="21" t="n">
         <v>29.71</v>
       </c>
-      <c r="S75" s="19" t="n">
+      <c r="S75" s="21" t="n">
         <v>29.5</v>
       </c>
-      <c r="T75" s="19" t="n">
+      <c r="T75" s="21" t="n">
         <v>29.38</v>
       </c>
-      <c r="U75" s="19" t="n">
+      <c r="U75" s="21" t="n">
         <v>29.78</v>
       </c>
-      <c r="V75" s="19" t="n">
+      <c r="V75" s="21" t="n">
         <v>29.85</v>
       </c>
-      <c r="W75" s="19" t="n">
+      <c r="W75" s="21" t="n">
         <v>29.16</v>
       </c>
-      <c r="X75" s="19" t="n">
+      <c r="X75" s="21" t="n">
         <v>29.29</v>
       </c>
-      <c r="Y75" s="19" t="n">
+      <c r="Y75" s="21" t="n">
         <v>29.48</v>
       </c>
-      <c r="Z75" s="19" t="n">
+      <c r="Z75" s="21" t="n">
         <v>37.17</v>
       </c>
-      <c r="AA75" s="19" t="n">
+      <c r="AA75" s="21" t="n">
         <v>28.92</v>
       </c>
-      <c r="AB75" s="19" t="n">
+      <c r="AB75" s="21" t="n">
         <v>31.6</v>
       </c>
-      <c r="AC75" s="19" t="n">
+      <c r="AC75" s="21" t="n">
         <v>30.51</v>
       </c>
-      <c r="AD75" s="19" t="n">
+      <c r="AD75" s="21" t="n">
         <v>29.07</v>
       </c>
-      <c r="AE75" s="19" t="n">
+      <c r="AE75" s="21" t="n">
         <v>28.94</v>
       </c>
-      <c r="AF75" s="19" t="n">
+      <c r="AF75" s="21" t="n">
         <v>29.25</v>
       </c>
-      <c r="AG75" s="19" t="n">
+      <c r="AG75" s="21" t="n">
         <v>29.59</v>
       </c>
-      <c r="AH75" s="19" t="n">
+      <c r="AH75" s="21" t="n">
         <v>29.84</v>
       </c>
-      <c r="AI75" s="12" t="inlineStr"/>
-      <c r="AJ75" s="12" t="inlineStr"/>
-      <c r="AK75" s="20" t="n"/>
+      <c r="AI75" s="13" t="inlineStr"/>
+      <c r="AJ75" s="22" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK75" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/ReportesUnificados/machala_ReporteUnificado.xlsx
+++ b/ReportesUnificados/machala_ReporteUnificado.xlsx
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
